--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>21052</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>53.7999992370605</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>51.7999992370605</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>51.7999992370605</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>53</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>32515</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>53.7999992370605</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>52</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>53.7999992370605</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>74871</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>54.7000007629395</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>54</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>39598</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>54.7999992370605</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>53.5999984741211</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>46322</v>
+        <v>59298</v>
       </c>
       <c r="C2715" t="n">
-        <v>50.9000015258789</v>
+        <v>50.4000015258789</v>
       </c>
       <c r="D2715" t="n">
-        <v>48.0999984741211</v>
+        <v>47.8499984741211</v>
       </c>
       <c r="E2715" t="n">
-        <v>48.3499984741211</v>
+        <v>50.4000015258789</v>
       </c>
       <c r="F2715" t="n">
-        <v>50.9000015258789</v>
+        <v>48.4500007629395</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>46572</v>
+        <v>46322</v>
       </c>
       <c r="C2716" t="n">
-        <v>52.9000015258789</v>
+        <v>50.9000015258789</v>
       </c>
       <c r="D2716" t="n">
-        <v>50.2999992370605</v>
+        <v>48.0999984741211</v>
       </c>
       <c r="E2716" t="n">
-        <v>51</v>
+        <v>48.3499984741211</v>
       </c>
       <c r="F2716" t="n">
-        <v>51.9000015258789</v>
+        <v>50.9000015258789</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>38175</v>
+        <v>46572</v>
       </c>
       <c r="C2717" t="n">
-        <v>53.2999992370605</v>
+        <v>52.9000015258789</v>
       </c>
       <c r="D2717" t="n">
-        <v>51.2000007629395</v>
+        <v>50.2999992370605</v>
       </c>
       <c r="E2717" t="n">
-        <v>52.2000007629395</v>
+        <v>51</v>
       </c>
       <c r="F2717" t="n">
-        <v>52.0999984741211</v>
+        <v>51.9000015258789</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>25522</v>
+        <v>38175</v>
       </c>
       <c r="C2718" t="n">
-        <v>53.4000015258789</v>
+        <v>53.2999992370605</v>
       </c>
       <c r="D2718" t="n">
-        <v>51.9000015258789</v>
+        <v>51.2000007629395</v>
       </c>
       <c r="E2718" t="n">
         <v>52.2000007629395</v>
       </c>
       <c r="F2718" t="n">
-        <v>52.7999992370605</v>
+        <v>52.0999984741211</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>21052</v>
+        <v>25522</v>
       </c>
       <c r="C2719" t="n">
-        <v>53.7999992370605</v>
+        <v>53.4000015258789</v>
       </c>
       <c r="D2719" t="n">
-        <v>51.7999992370605</v>
+        <v>51.9000015258789</v>
       </c>
       <c r="E2719" t="n">
-        <v>51.7999992370605</v>
+        <v>52.2000007629395</v>
       </c>
       <c r="F2719" t="n">
-        <v>53</v>
+        <v>52.7999992370605</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>32515</v>
+        <v>21052</v>
       </c>
       <c r="C2720" t="n">
         <v>53.7999992370605</v>
       </c>
       <c r="D2720" t="n">
-        <v>52</v>
+        <v>51.7999992370605</v>
       </c>
       <c r="E2720" t="n">
-        <v>53.7999992370605</v>
+        <v>51.7999992370605</v>
       </c>
       <c r="F2720" t="n">
-        <v>52.7999992370605</v>
+        <v>53</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>74871</v>
+        <v>32515</v>
       </c>
       <c r="C2721" t="n">
-        <v>54.7000007629395</v>
+        <v>53.7999992370605</v>
       </c>
       <c r="D2721" t="n">
-        <v>52.5999984741211</v>
+        <v>52</v>
       </c>
       <c r="E2721" t="n">
-        <v>53</v>
+        <v>53.7999992370605</v>
       </c>
       <c r="F2721" t="n">
-        <v>54</v>
+        <v>52.7999992370605</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>39598</v>
+        <v>74871</v>
       </c>
       <c r="C2722" t="n">
-        <v>55.5</v>
+        <v>54.7000007629395</v>
       </c>
       <c r="D2722" t="n">
-        <v>53.5</v>
+        <v>52.5999984741211</v>
       </c>
       <c r="E2722" t="n">
-        <v>54.7999992370605</v>
+        <v>53</v>
       </c>
       <c r="F2722" t="n">
-        <v>53.5999984741211</v>
+        <v>54</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>74875</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>54.5999984741211</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>53.7999992370605</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>6.32979154586792</v>
+        <v>6.32979106903076</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G4" t="n">
-        <v>6.33772325515747</v>
+        <v>6.33772277832031</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G5" t="n">
-        <v>6.17114973068237</v>
+        <v>6.17115020751953</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>6.21081066131592</v>
+        <v>6.21081018447876</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03630447387695</v>
+        <v>6.03630495071411</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>6.06803274154663</v>
+        <v>6.06803321838379</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>6.06803274154663</v>
+        <v>6.06803321838379</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>6.03630447387695</v>
+        <v>6.03630495071411</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>5.86973190307617</v>
+        <v>5.86973142623901</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>5.71109008789062</v>
+        <v>5.71108913421631</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.88956165313721</v>
+        <v>5.88956117630005</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G16" t="n">
-        <v>5.71109008789062</v>
+        <v>5.71108913421631</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>5.66746282577515</v>
+        <v>5.6674633026123</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>5.86973190307617</v>
+        <v>5.86973142623901</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G22" t="n">
-        <v>5.94112062454224</v>
+        <v>5.94112014770508</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.83007144927979</v>
+        <v>5.83007097244263</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G25" t="n">
-        <v>5.86973190307617</v>
+        <v>5.86973142623901</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>5.88559532165527</v>
+        <v>5.88559579849243</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>7.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.94905233383179</v>
+        <v>5.94905185699463</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>5.88956165313721</v>
+        <v>5.88956117630005</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>5.86973190307617</v>
+        <v>5.86973142623901</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G30" t="n">
-        <v>5.79437637329102</v>
+        <v>5.79437685012817</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.5</v>
       </c>
       <c r="G32" t="n">
-        <v>5.94905233383179</v>
+        <v>5.94905185699463</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.5</v>
       </c>
       <c r="G33" t="n">
-        <v>5.94905233383179</v>
+        <v>5.94905185699463</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>6.09182929992676</v>
+        <v>6.09182977676392</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>7.75</v>
       </c>
       <c r="G36" t="n">
-        <v>6.1473536491394</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>6.23460578918457</v>
+        <v>6.23460674285889</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>5.88559532165527</v>
+        <v>5.88559579849243</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>6.42497634887695</v>
+        <v>6.42497682571411</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>6.44083976745605</v>
+        <v>6.44084024429321</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G48" t="n">
-        <v>6.4329080581665</v>
+        <v>6.43290758132935</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>6.17908143997192</v>
+        <v>6.17908191680908</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G50" t="n">
-        <v>6.02044153213501</v>
+        <v>6.02044010162354</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>6.19494533538818</v>
+        <v>6.19494581222534</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>6.21081066131592</v>
+        <v>6.21081018447876</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>6.06803274154663</v>
+        <v>6.06803321838379</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G56" t="n">
-        <v>6.03630447387695</v>
+        <v>6.03630495071411</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.75</v>
       </c>
       <c r="G57" t="n">
-        <v>6.1473536491394</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>6.05216884613037</v>
+        <v>6.05216836929321</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G63" t="n">
-        <v>6.0561351776123</v>
+        <v>6.05613470077515</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.75</v>
       </c>
       <c r="G64" t="n">
-        <v>6.1473536491394</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G65" t="n">
-        <v>6.06803274154663</v>
+        <v>6.06803321838379</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>5.93318843841553</v>
+        <v>5.93318796157837</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G67" t="n">
-        <v>5.96094989776611</v>
+        <v>5.96095037460327</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G68" t="n">
-        <v>5.89352750778198</v>
+        <v>5.89352703094482</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G69" t="n">
-        <v>5.94112062454224</v>
+        <v>5.94112014770508</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G70" t="n">
-        <v>6.07596492767334</v>
+        <v>6.0759654045105</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>5.99664449691772</v>
+        <v>5.99664402008057</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>6.09976100921631</v>
+        <v>6.09976148605347</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>6.04027032852173</v>
+        <v>6.04026985168457</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>6.04027032852173</v>
+        <v>6.04026985168457</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G76" t="n">
-        <v>6.12355756759644</v>
+        <v>6.12355709075928</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G77" t="n">
-        <v>6.06406688690186</v>
+        <v>6.06406736373901</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.75</v>
       </c>
       <c r="G79" t="n">
-        <v>6.1473536491394</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.75</v>
       </c>
       <c r="G80" t="n">
-        <v>6.1473536491394</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>6.05216884613037</v>
+        <v>6.05216836929321</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G86" t="n">
-        <v>6.0561351776123</v>
+        <v>6.05613470077515</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>5.90146017074585</v>
+        <v>5.90145969390869</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G89" t="n">
-        <v>6.06010150909424</v>
+        <v>6.06010007858276</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>6.01250886917114</v>
+        <v>6.01250839233398</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>6.13499736785889</v>
+        <v>6.13499689102173</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>6.0160698890686</v>
+        <v>6.01606893539429</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G98" t="n">
-        <v>6.1021900177002</v>
+        <v>6.10218954086304</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G99" t="n">
-        <v>6.1021900177002</v>
+        <v>6.10218954086304</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.5</v>
       </c>
       <c r="G100" t="n">
-        <v>6.15140056610107</v>
+        <v>6.15140008926392</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>6.03657531738281</v>
+        <v>6.03657388687134</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>6.14319896697998</v>
+        <v>6.14319849014282</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>6.13499736785889</v>
+        <v>6.13499689102173</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.14319896697998</v>
+        <v>6.14319849014282</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G108" t="n">
-        <v>6.2293176651001</v>
+        <v>6.22931814193726</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G109" t="n">
-        <v>6.13909816741943</v>
+        <v>6.13909769058228</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>5.98736333847046</v>
+        <v>5.9873628616333</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>5.7577109336853</v>
+        <v>5.75771045684814</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G118" t="n">
-        <v>5.93815183639526</v>
+        <v>5.93815231323242</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.0283727645874</v>
+        <v>6.02837228775024</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G121" t="n">
-        <v>5.88894081115723</v>
+        <v>5.88894128799438</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>5.73310518264771</v>
+        <v>5.73310470581055</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G127" t="n">
-        <v>5.85613298416138</v>
+        <v>5.85613393783569</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G128" t="n">
-        <v>5.8110237121582</v>
+        <v>5.81102275848389</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G129" t="n">
-        <v>6.0652813911438</v>
+        <v>6.06528091430664</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>6.13499736785889</v>
+        <v>6.13499689102173</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>6.13909816741943</v>
+        <v>6.13909769058228</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G137" t="n">
-        <v>6.1021900177002</v>
+        <v>6.10218954086304</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="n">
-        <v>6.09808826446533</v>
+        <v>6.09808921813965</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="n">
-        <v>5.97506046295166</v>
+        <v>5.9750599861145</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>6.04067516326904</v>
+        <v>6.04067468643188</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G141" t="n">
-        <v>6.03657531738281</v>
+        <v>6.03657388687134</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>6.11859321594238</v>
+        <v>6.11859369277954</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>6.0652813911438</v>
+        <v>6.06528091430664</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="n">
-        <v>6.07348346710205</v>
+        <v>6.07348299026489</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>6.09398794174194</v>
+        <v>6.09398746490479</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>6.09398794174194</v>
+        <v>6.09398746490479</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G152" t="n">
-        <v>6.08578586578369</v>
+        <v>6.08578634262085</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="n">
-        <v>6.02017116546631</v>
+        <v>6.02017068862915</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G156" t="n">
-        <v>6.1021900177002</v>
+        <v>6.10218954086304</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>6.08988666534424</v>
+        <v>6.0898871421814</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>6.01196956634521</v>
+        <v>6.0119686126709</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>5.99556541442871</v>
+        <v>5.99556446075439</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.01196956634521</v>
+        <v>6.0119686126709</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>6.0283727645874</v>
+        <v>6.02837228775024</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.98736333847046</v>
+        <v>5.9873628616333</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>5.91354656219482</v>
+        <v>5.91354703903198</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>5.99556541442871</v>
+        <v>5.99556446075439</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G167" t="n">
-        <v>6.03657531738281</v>
+        <v>6.03657388687134</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>6.02017116546631</v>
+        <v>6.02017068862915</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>5.98736333847046</v>
+        <v>5.9873628616333</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G170" t="n">
-        <v>5.92994976043701</v>
+        <v>5.92995023727417</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="n">
-        <v>5.86843633651733</v>
+        <v>5.86843681335449</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>5.97916173934937</v>
+        <v>5.97916126251221</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90124320983887</v>
+        <v>5.90124368667603</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.25</v>
       </c>
       <c r="G176" t="n">
-        <v>5.94635391235352</v>
+        <v>5.94635438919067</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G177" t="n">
-        <v>5.90124320983887</v>
+        <v>5.90124368667603</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G179" t="n">
-        <v>5.8315281867981</v>
+        <v>5.83152770996094</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>5.87663841247559</v>
+        <v>5.87663793563843</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>5.77001285552979</v>
+        <v>5.7700138092041</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>5.76181125640869</v>
+        <v>5.76181173324585</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>5.87663841247559</v>
+        <v>5.87663793563843</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>5.80282115936279</v>
+        <v>5.80282068252563</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>5.7043981552124</v>
+        <v>5.70439863204956</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G189" t="n">
-        <v>5.73310518264771</v>
+        <v>5.73310470581055</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.84793138504028</v>
+        <v>5.84793186187744</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G192" t="n">
-        <v>5.88894081115723</v>
+        <v>5.88894128799438</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>5.82332611083984</v>
+        <v>5.82332563400269</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G196" t="n">
-        <v>5.90124320983887</v>
+        <v>5.90124368667603</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G197" t="n">
-        <v>5.88894081115723</v>
+        <v>5.88894128799438</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>5.86433506011963</v>
+        <v>5.86433601379395</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G199" t="n">
-        <v>5.93815183639526</v>
+        <v>5.93815231323242</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.86843633651733</v>
+        <v>5.86843681335449</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>6.00376749038696</v>
+        <v>6.0037670135498</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>5.98736333847046</v>
+        <v>5.9873628616333</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.5</v>
       </c>
       <c r="G203" t="n">
-        <v>6.15140056610107</v>
+        <v>6.15140008926392</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>6.38925409317017</v>
+        <v>6.38925457000732</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>6.38925409317017</v>
+        <v>6.38925457000732</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>6.47127246856689</v>
+        <v>6.47127342224121</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>6.4876766204834</v>
+        <v>6.48767614364624</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>6.39335536956787</v>
+        <v>6.39335632324219</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.23341941833496</v>
+        <v>6.2334189414978</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.39745712280273</v>
+        <v>6.39745664596558</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G216" t="n">
-        <v>6.17600679397583</v>
+        <v>6.17600631713867</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>6.31953859329224</v>
+        <v>6.31953907012939</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="n">
-        <v>6.44666719436646</v>
+        <v>6.44666814804077</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>6.43026399612427</v>
+        <v>6.43026351928711</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>6.27442836761475</v>
+        <v>6.2744288444519</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>6.31133651733398</v>
+        <v>6.31133699417114</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="n">
-        <v>6.12679433822632</v>
+        <v>6.12679481506348</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>6.00376749038696</v>
+        <v>6.0037670135498</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>5.91354656219482</v>
+        <v>5.91354703903198</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>5.95455598831177</v>
+        <v>5.95455694198608</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="n">
-        <v>6.12679433822632</v>
+        <v>6.12679481506348</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G242" t="n">
-        <v>6.0160698890686</v>
+        <v>6.01606893539429</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.23341941833496</v>
+        <v>6.2334189414978</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G244" t="n">
-        <v>6.26622676849365</v>
+        <v>6.26622629165649</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>6.30723571777344</v>
+        <v>6.30723667144775</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G246" t="n">
-        <v>6.22521781921387</v>
+        <v>6.22521686553955</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G250" t="n">
-        <v>6.2293176651001</v>
+        <v>6.22931814193726</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>6.23341941833496</v>
+        <v>6.2334189414978</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>6.13499736785889</v>
+        <v>6.13499689102173</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>6.18420791625977</v>
+        <v>6.18420839309692</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>6.11449193954468</v>
+        <v>6.11449241638184</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G256" t="n">
-        <v>6.14319896697998</v>
+        <v>6.14319849014282</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>7.5</v>
       </c>
       <c r="G257" t="n">
-        <v>6.15140056610107</v>
+        <v>6.15140008926392</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G259" t="n">
-        <v>6.61890745162964</v>
+        <v>6.61890697479248</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G262" t="n">
-        <v>6.67632150650024</v>
+        <v>6.67632055282593</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.13562488555908</v>
+        <v>7.13562440872192</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>6.96748638153076</v>
+        <v>6.9674859046936</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G267" t="n">
-        <v>6.94698190689087</v>
+        <v>6.94698143005371</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>7.01259708404541</v>
+        <v>7.01259660720825</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="n">
-        <v>6.92237567901611</v>
+        <v>6.92237520217896</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>7.13972473144531</v>
+        <v>7.13972520828247</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G275" t="n">
-        <v>7.52931451797485</v>
+        <v>7.5293140411377</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="n">
-        <v>7.56212282180786</v>
+        <v>7.56212186813354</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>7.52521419525146</v>
+        <v>7.52521371841431</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>7.02079820632935</v>
+        <v>7.02079916000366</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G279" t="n">
-        <v>7.234046459198</v>
+        <v>7.23404693603516</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="n">
-        <v>7.37347888946533</v>
+        <v>7.37347841262817</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G281" t="n">
-        <v>7.40628719329834</v>
+        <v>7.40628671646118</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>7.41858959197998</v>
+        <v>7.41859006881714</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>7.2094407081604</v>
+        <v>7.20944166183472</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>7.03720235824585</v>
+        <v>7.03720140457153</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="n">
-        <v>6.87726640701294</v>
+        <v>6.87726593017578</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G288" t="n">
-        <v>7.00439453125</v>
+        <v>7.00439548492432</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="n">
-        <v>6.99209117889404</v>
+        <v>6.9920916557312</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>6.97568893432617</v>
+        <v>6.97568845748901</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G293" t="n">
-        <v>6.77064180374146</v>
+        <v>6.77064228057861</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>6.88956880569458</v>
+        <v>6.88956832885742</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>6.95108222961426</v>
+        <v>6.95108270645142</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G297" t="n">
-        <v>6.8239541053772</v>
+        <v>6.82395362854004</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.84855937957764</v>
+        <v>6.84855985641479</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G299" t="n">
-        <v>6.89366865158081</v>
+        <v>6.89366912841797</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="n">
-        <v>7.02079820632935</v>
+        <v>7.02079916000366</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>7.13972473144531</v>
+        <v>7.13972520828247</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="n">
-        <v>7.16022968292236</v>
+        <v>7.16022920608521</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G304" t="n">
-        <v>7.47190046310425</v>
+        <v>7.47190141677856</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G306" t="n">
-        <v>7.57032299041748</v>
+        <v>7.57032346725464</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>7.61953496932983</v>
+        <v>7.61953449249268</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="n">
-        <v>7.58672666549683</v>
+        <v>7.5867280960083</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="n">
-        <v>7.56212282180786</v>
+        <v>7.56212186813354</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>7.82868194580078</v>
+        <v>7.8286828994751</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="n">
-        <v>7.93120527267456</v>
+        <v>7.93120622634888</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.75</v>
       </c>
       <c r="G313" t="n">
-        <v>7.99681949615479</v>
+        <v>7.99682140350342</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G314" t="n">
-        <v>7.7794713973999</v>
+        <v>7.77947044372559</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.18136405944824</v>
+        <v>8.18136310577393</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G317" t="n">
-        <v>8.11574840545654</v>
+        <v>8.11574935913086</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="n">
-        <v>8.40691184997559</v>
+        <v>8.4069128036499</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31669425964355</v>
+        <v>8.31669330596924</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="n">
-        <v>8.35770130157471</v>
+        <v>8.35770225524902</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G325" t="n">
-        <v>8.54634571075439</v>
+        <v>8.54634666442871</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G328" t="n">
-        <v>8.44792366027832</v>
+        <v>8.44792175292969</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G329" t="n">
-        <v>8.25107955932617</v>
+        <v>8.25107860565186</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G330" t="n">
-        <v>8.18136405944824</v>
+        <v>8.18136310577393</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>7.69335126876831</v>
+        <v>7.69335174560547</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="n">
-        <v>7.88609600067139</v>
+        <v>7.88609504699707</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.75</v>
       </c>
       <c r="G334" t="n">
-        <v>7.99681949615479</v>
+        <v>7.99682140350342</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="n">
-        <v>8.09934520721436</v>
+        <v>8.09934425354004</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.35770130157471</v>
+        <v>8.35770225524902</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="n">
-        <v>8.43151950836182</v>
+        <v>8.43151760101318</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="n">
-        <v>8.5217399597168</v>
+        <v>8.52174186706543</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G340" t="n">
-        <v>8.77599906921387</v>
+        <v>8.77599716186523</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>9.28451347351074</v>
+        <v>9.28451442718506</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G342" t="n">
-        <v>9.35833072662354</v>
+        <v>9.35832977294922</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="n">
-        <v>10.5886106491089</v>
+        <v>10.5886096954346</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G350" t="n">
-        <v>10.4792289733887</v>
+        <v>10.479229927063</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G351" t="n">
-        <v>10.3615789413452</v>
+        <v>10.3615798950195</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G352" t="n">
-        <v>9.78173637390137</v>
+        <v>9.78173446655273</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="n">
-        <v>9.96661281585693</v>
+        <v>9.96661376953125</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G354" t="n">
-        <v>10.0254383087158</v>
+        <v>10.0254373550415</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>9.95820903778076</v>
+        <v>9.95820999145508</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G356" t="n">
-        <v>10.0758581161499</v>
+        <v>10.0758590698242</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G358" t="n">
-        <v>10.0758581161499</v>
+        <v>10.0758590698242</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G359" t="n">
-        <v>10.0758581161499</v>
+        <v>10.0758590698242</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G361" t="n">
-        <v>10.2859477996826</v>
+        <v>10.2859487533569</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G362" t="n">
-        <v>10.6052837371826</v>
+        <v>10.6052827835083</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G363" t="n">
-        <v>10.5632658004761</v>
+        <v>10.5632648468018</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5128440856934</v>
+        <v>10.512843132019</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>10.2523336410522</v>
+        <v>10.2523345947266</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G369" t="n">
-        <v>10.5296516418457</v>
+        <v>10.5296506881714</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G371" t="n">
-        <v>10.3195638656616</v>
+        <v>10.3195629119873</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G372" t="n">
-        <v>10.2607383728027</v>
+        <v>10.2607364654541</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G373" t="n">
-        <v>10.0254383087158</v>
+        <v>10.0254373550415</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G375" t="n">
-        <v>10.2103147506714</v>
+        <v>10.2103157043457</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G376" t="n">
-        <v>10.0254383087158</v>
+        <v>10.0254373550415</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G377" t="n">
-        <v>9.94980525970459</v>
+        <v>9.94980621337891</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G378" t="n">
-        <v>9.81534862518311</v>
+        <v>9.81534957885742</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G381" t="n">
-        <v>9.52122497558594</v>
+        <v>9.52122592926025</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G382" t="n">
-        <v>9.34475040435791</v>
+        <v>9.34474945068359</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>9.01700973510742</v>
+        <v>9.01701068878174</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>9.09264469146729</v>
+        <v>9.09264373779297</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G386" t="n">
-        <v>9.10945129394531</v>
+        <v>9.109450340271</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G387" t="n">
-        <v>9.15146732330322</v>
+        <v>9.15146923065186</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>11</v>
       </c>
       <c r="G391" t="n">
-        <v>9.2439079284668</v>
+        <v>9.24390888214111</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G392" t="n">
-        <v>9.12625885009766</v>
+        <v>9.12625694274902</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>9.28592491149902</v>
+        <v>9.28592586517334</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G394" t="n">
-        <v>9.59685707092285</v>
+        <v>9.59685611724854</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>10.0002269744873</v>
+        <v>10.000226020813</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G396" t="n">
-        <v>9.94140148162842</v>
+        <v>9.94140243530273</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>9.94980525970459</v>
+        <v>9.94980621337891</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G398" t="n">
-        <v>9.80694484710693</v>
+        <v>9.80694580078125</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G400" t="n">
-        <v>10.1262817382812</v>
+        <v>10.1262807846069</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G401" t="n">
-        <v>10.1346855163574</v>
+        <v>10.1346845626831</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G402" t="n">
-        <v>10.0758581161499</v>
+        <v>10.0758590698242</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G403" t="n">
-        <v>10.1851072311401</v>
+        <v>10.1851062774658</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>10.1262817382812</v>
+        <v>10.1262807846069</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>10.1851072311401</v>
+        <v>10.1851062774658</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>10.2523336410522</v>
+        <v>10.2523345947266</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G410" t="n">
-        <v>10.2691421508789</v>
+        <v>10.2691411972046</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G411" t="n">
-        <v>10.2607383728027</v>
+        <v>10.2607364654541</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G412" t="n">
-        <v>10.1094732284546</v>
+        <v>10.1094741821289</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G414" t="n">
-        <v>9.80694484710693</v>
+        <v>9.80694580078125</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>11.75</v>
       </c>
       <c r="G415" t="n">
-        <v>9.87417411804199</v>
+        <v>9.87417507171631</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>10.0002269744873</v>
+        <v>10.000226020813</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>10.1262817382812</v>
+        <v>10.1262807846069</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G419" t="n">
-        <v>9.79854297637939</v>
+        <v>9.79854106903076</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>9.76492786407471</v>
+        <v>9.76492691040039</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>9.65568161010742</v>
+        <v>9.65568256378174</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G422" t="n">
-        <v>9.42038154602051</v>
+        <v>9.42038249969482</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G423" t="n">
-        <v>9.61366367340088</v>
+        <v>9.6136646270752</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>9.36996078491211</v>
+        <v>9.36995983123779</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G425" t="n">
-        <v>9.26911735534668</v>
+        <v>9.269118309021</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G429" t="n">
-        <v>9.42038154602051</v>
+        <v>9.42038249969482</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G431" t="n">
-        <v>9.30273342132568</v>
+        <v>9.30273246765137</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G432" t="n">
-        <v>9.34475040435791</v>
+        <v>9.34474945068359</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G434" t="n">
-        <v>9.2943286895752</v>
+        <v>9.29432964324951</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G435" t="n">
-        <v>9.36155891418457</v>
+        <v>9.36155700683594</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G436" t="n">
-        <v>9.42878532409668</v>
+        <v>9.428786277771</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G437" t="n">
-        <v>9.36155891418457</v>
+        <v>9.36155700683594</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G438" t="n">
-        <v>9.28592491149902</v>
+        <v>9.28592586517334</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G439" t="n">
-        <v>9.2943286895752</v>
+        <v>9.29432964324951</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G441" t="n">
-        <v>9.15146732330322</v>
+        <v>9.15146923065186</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>9.11785411834717</v>
+        <v>9.11785316467285</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G444" t="n">
-        <v>9.15146732330322</v>
+        <v>9.15146923065186</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G446" t="n">
-        <v>9.80694484710693</v>
+        <v>9.80694580078125</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G447" t="n">
-        <v>9.61366367340088</v>
+        <v>9.6136646270752</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G448" t="n">
-        <v>9.40357398986816</v>
+        <v>9.40357494354248</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>9.74812126159668</v>
+        <v>9.74812030792236</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G451" t="n">
-        <v>9.588454246521</v>
+        <v>9.58845329284668</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G452" t="n">
-        <v>9.59685707092285</v>
+        <v>9.59685611724854</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G453" t="n">
-        <v>9.42878532409668</v>
+        <v>9.428786277771</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G456" t="n">
-        <v>9.55483818054199</v>
+        <v>9.55483913421631</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.5</v>
       </c>
       <c r="G458" t="n">
-        <v>9.66408634185791</v>
+        <v>9.66408538818359</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G460" t="n">
-        <v>9.68089199066162</v>
+        <v>9.68089294433594</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G461" t="n">
-        <v>9.70610332489014</v>
+        <v>9.70610237121582</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>9.53803157806396</v>
+        <v>9.53803253173828</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>11.5</v>
       </c>
       <c r="G465" t="n">
-        <v>9.66408634185791</v>
+        <v>9.66408538818359</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>9.65568161010742</v>
+        <v>9.65568256378174</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G467" t="n">
-        <v>9.74812126159668</v>
+        <v>9.74812030792236</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G469" t="n">
-        <v>9.63887500762939</v>
+        <v>9.63887596130371</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G470" t="n">
-        <v>9.68089199066162</v>
+        <v>9.68089294433594</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G471" t="n">
-        <v>9.63887500762939</v>
+        <v>9.63887596130371</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>9.74812126159668</v>
+        <v>9.74812030792236</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G475" t="n">
-        <v>9.59685707092285</v>
+        <v>9.59685611724854</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.38676834106445</v>
+        <v>9.38676929473877</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G477" t="n">
-        <v>9.05062675476074</v>
+        <v>9.05062580108643</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G478" t="n">
-        <v>8.91616916656494</v>
+        <v>8.91617012023926</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G479" t="n">
-        <v>8.6388521194458</v>
+        <v>8.63885116577148</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G480" t="n">
-        <v>8.51279830932617</v>
+        <v>8.51279926300049</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G483" t="n">
-        <v>8.02539253234863</v>
+        <v>8.02539348602295</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>8.26489543914795</v>
+        <v>8.26489448547363</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>9.75</v>
       </c>
       <c r="G489" t="n">
-        <v>8.19346332550049</v>
+        <v>8.19346523284912</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G490" t="n">
-        <v>8.29430484771729</v>
+        <v>8.29430675506592</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G491" t="n">
-        <v>8.23548126220703</v>
+        <v>8.23548221588135</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>9.77499961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.21447372436523</v>
+        <v>8.21447277069092</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>8.01698875427246</v>
+        <v>8.01698970794678</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G494" t="n">
-        <v>7.96236753463745</v>
+        <v>7.96236658096313</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>7.77748727798462</v>
+        <v>7.77748823165894</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G496" t="n">
-        <v>7.75227737426758</v>
+        <v>7.75227642059326</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G497" t="n">
-        <v>7.72706651687622</v>
+        <v>7.7270655632019</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>7.83631324768066</v>
+        <v>7.83631181716919</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G501" t="n">
-        <v>7.90354108810425</v>
+        <v>7.90354061126709</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>7.94555902481079</v>
+        <v>7.94555807113647</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G503" t="n">
-        <v>7.93715476989746</v>
+        <v>7.93715524673462</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G504" t="n">
-        <v>8.17665576934814</v>
+        <v>8.17665672302246</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G505" t="n">
-        <v>8.17665576934814</v>
+        <v>8.17665672302246</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G508" t="n">
-        <v>7.97497129440308</v>
+        <v>7.97497034072876</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G509" t="n">
-        <v>8.0043830871582</v>
+        <v>8.00438404083252</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G511" t="n">
-        <v>8.09682369232178</v>
+        <v>8.09682273864746</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G512" t="n">
-        <v>8.14724540710449</v>
+        <v>8.14724349975586</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G514" t="n">
-        <v>8.3447265625</v>
+        <v>8.34472751617432</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>8.65566062927246</v>
+        <v>8.65565872192383</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G518" t="n">
-        <v>8.47078037261963</v>
+        <v>8.47078132629395</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10</v>
       </c>
       <c r="G519" t="n">
-        <v>8.40355205535889</v>
+        <v>8.40355110168457</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>8.47078037261963</v>
+        <v>8.47078132629395</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G523" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439643859863</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G524" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439643859863</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G525" t="n">
-        <v>8.38674545288086</v>
+        <v>8.38674449920654</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>10</v>
       </c>
       <c r="G526" t="n">
-        <v>8.40355205535889</v>
+        <v>8.40355110168457</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G529" t="n">
-        <v>8.30271053314209</v>
+        <v>8.30270957946777</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439643859863</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>8.23548126220703</v>
+        <v>8.23548221588135</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>8.23548126220703</v>
+        <v>8.23548221588135</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>7.94135570526123</v>
+        <v>7.94135618209839</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>7.91614723205566</v>
+        <v>7.91614580154419</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>8.05060386657715</v>
+        <v>8.05060291290283</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G542" t="n">
-        <v>8.47078037261963</v>
+        <v>8.47078132629395</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G544" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439643859863</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G545" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439643859863</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G547" t="n">
-        <v>8.6388521194458</v>
+        <v>8.63885116577148</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>10.5</v>
       </c>
       <c r="G548" t="n">
-        <v>8.82373142242432</v>
+        <v>8.82373046875</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G549" t="n">
-        <v>8.67246532440186</v>
+        <v>8.67246627807617</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G551" t="n">
-        <v>8.68927478790283</v>
+        <v>8.68927383422852</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>8.53800868988037</v>
+        <v>8.53800964355469</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G555" t="n">
-        <v>8.52120399475098</v>
+        <v>8.52120304107666</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G556" t="n">
-        <v>8.75650119781494</v>
+        <v>8.75650215148926</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G558" t="n">
-        <v>9.27752113342285</v>
+        <v>9.27752304077148</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>11</v>
       </c>
       <c r="G562" t="n">
-        <v>9.2439079284668</v>
+        <v>9.24390888214111</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G563" t="n">
-        <v>9.10945129394531</v>
+        <v>9.109450340271</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G564" t="n">
-        <v>9.12625885009766</v>
+        <v>9.12625694274902</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>9.15987110137939</v>
+        <v>9.15987300872803</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G567" t="n">
-        <v>9.12625885009766</v>
+        <v>9.12625694274902</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.10945129394531</v>
+        <v>9.109450340271</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G571" t="n">
-        <v>9.10945129394531</v>
+        <v>9.109450340271</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G573" t="n">
-        <v>9.02541446685791</v>
+        <v>9.02541542053223</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G576" t="n">
-        <v>8.9581880569458</v>
+        <v>8.95818710327148</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>9.15987110137939</v>
+        <v>9.15987300872803</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G582" t="n">
-        <v>9.12625885009766</v>
+        <v>9.12625694274902</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G583" t="n">
-        <v>9.17668056488037</v>
+        <v>9.17667961120605</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>9.32794380187988</v>
+        <v>9.32794284820557</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>9.59685707092285</v>
+        <v>9.59685611724854</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G588" t="n">
-        <v>10.1178770065308</v>
+        <v>10.1178779602051</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G590" t="n">
-        <v>10.5716705322266</v>
+        <v>10.5716695785522</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G593" t="n">
-        <v>10.5716705322266</v>
+        <v>10.5716695785522</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G595" t="n">
-        <v>11.3279876708984</v>
+        <v>11.3279886245728</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>11.2607612609863</v>
+        <v>11.2607593536377</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G597" t="n">
-        <v>11.3616037368774</v>
+        <v>11.3616027832031</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>11.4342012405396</v>
+        <v>11.4342002868652</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G599" t="n">
-        <v>11.760892868042</v>
+        <v>11.7608919143677</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G600" t="n">
-        <v>11.760892868042</v>
+        <v>11.7608919143677</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G601" t="n">
-        <v>11.7245941162109</v>
+        <v>11.7245931625366</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G602" t="n">
-        <v>11.3071537017822</v>
+        <v>11.3071546554565</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G603" t="n">
-        <v>11.1982564926147</v>
+        <v>11.1982574462891</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G605" t="n">
-        <v>10.8534173965454</v>
+        <v>10.8534154891968</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G606" t="n">
-        <v>10.7808179855347</v>
+        <v>10.7808170318604</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G608" t="n">
-        <v>10.5993223190308</v>
+        <v>10.5993232727051</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G609" t="n">
-        <v>10.5085754394531</v>
+        <v>10.5085744857788</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>10.5085754394531</v>
+        <v>10.5085744857788</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>9.90964126586914</v>
+        <v>9.90964031219482</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G616" t="n">
-        <v>9.96408939361572</v>
+        <v>9.96408748626709</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>11</v>
       </c>
       <c r="G618" t="n">
-        <v>9.98223876953125</v>
+        <v>9.98223781585693</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G619" t="n">
-        <v>10.1274347305298</v>
+        <v>10.1274337768555</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G624" t="n">
-        <v>10.2181835174561</v>
+        <v>10.2181844711304</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>10.3452301025391</v>
+        <v>10.3452291488647</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G627" t="n">
-        <v>10.1092863082886</v>
+        <v>10.1092853546143</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G628" t="n">
-        <v>9.96408939361572</v>
+        <v>9.96408748626709</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G629" t="n">
-        <v>10.1274347305298</v>
+        <v>10.1274337768555</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G630" t="n">
-        <v>10.1092863082886</v>
+        <v>10.1092853546143</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G633" t="n">
-        <v>9.69184684753418</v>
+        <v>9.69184589385986</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>9.61924934387207</v>
+        <v>9.61924839019775</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G636" t="n">
-        <v>9.38330459594727</v>
+        <v>9.38330364227295</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G638" t="n">
-        <v>9.6373987197876</v>
+        <v>9.63739776611328</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G639" t="n">
-        <v>9.56480026245117</v>
+        <v>9.56479930877686</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G641" t="n">
-        <v>9.6373987197876</v>
+        <v>9.63739776611328</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G643" t="n">
-        <v>9.60109806060791</v>
+        <v>9.60109901428223</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G644" t="n">
-        <v>9.4740514755249</v>
+        <v>9.47405242919922</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G648" t="n">
-        <v>9.27440738677979</v>
+        <v>9.2744083404541</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G651" t="n">
-        <v>9.18365955352783</v>
+        <v>9.18365859985352</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>9.00216484069824</v>
+        <v>9.00216579437256</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G658" t="n">
-        <v>8.87511825561523</v>
+        <v>8.87511730194092</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G668" t="n">
-        <v>8.55750179290771</v>
+        <v>8.55750274658203</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>8.57565021514893</v>
+        <v>8.57565116882324</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G671" t="n">
-        <v>8.27618312835693</v>
+        <v>8.27618408203125</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G675" t="n">
-        <v>9.31070518493652</v>
+        <v>9.31070613861084</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G680" t="n">
-        <v>9.11106204986572</v>
+        <v>9.11106109619141</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G681" t="n">
-        <v>8.92049217224121</v>
+        <v>8.92049121856689</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>9.31070518493652</v>
+        <v>9.31070613861084</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G683" t="n">
-        <v>9.27440738677979</v>
+        <v>9.2744083404541</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.0384635925293</v>
+        <v>9.03846454620361</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G686" t="n">
-        <v>8.95678997039795</v>
+        <v>8.95679092407227</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>8.88419342041016</v>
+        <v>8.88419246673584</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>8.88419342041016</v>
+        <v>8.88419246673584</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>8.88419342041016</v>
+        <v>8.88419246673584</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G690" t="n">
-        <v>8.91141700744629</v>
+        <v>8.91141605377197</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.80251884460449</v>
+        <v>8.80251979827881</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>8.88419342041016</v>
+        <v>8.88419246673584</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>8.80251884460449</v>
+        <v>8.80251979827881</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G696" t="n">
-        <v>8.80251884460449</v>
+        <v>8.80251979827881</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G697" t="n">
-        <v>8.70269775390625</v>
+        <v>8.70269680023193</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G698" t="n">
-        <v>8.74807071685791</v>
+        <v>8.74807167053223</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G699" t="n">
-        <v>8.75714683532715</v>
+        <v>8.75714588165283</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G701" t="n">
-        <v>8.63010025024414</v>
+        <v>8.63009929656982</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.57565021514893</v>
+        <v>8.57565116882324</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G706" t="n">
-        <v>8.33063220977783</v>
+        <v>8.33063125610352</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>8.27618312835693</v>
+        <v>8.27618408203125</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G710" t="n">
-        <v>7.66817378997803</v>
+        <v>7.66817331314087</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G711" t="n">
-        <v>7.63187456130981</v>
+        <v>7.63187551498413</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G712" t="n">
-        <v>7.6137261390686</v>
+        <v>7.61372709274292</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>7.52297830581665</v>
+        <v>7.52297735214233</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G715" t="n">
-        <v>7.42315626144409</v>
+        <v>7.42315673828125</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>7.33240842819214</v>
+        <v>7.33240795135498</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>7.31425952911377</v>
+        <v>7.31425905227661</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G721" t="n">
-        <v>7.09646511077881</v>
+        <v>7.09646463394165</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G722" t="n">
-        <v>7.23258543014526</v>
+        <v>7.23258590698242</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>7.41408109664917</v>
+        <v>7.41408157348633</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G725" t="n">
-        <v>7.35055780410767</v>
+        <v>7.35055732727051</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G726" t="n">
-        <v>7.6137261390686</v>
+        <v>7.61372709274292</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G727" t="n">
-        <v>7.69539785385132</v>
+        <v>7.69539833068848</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G728" t="n">
-        <v>7.73169803619385</v>
+        <v>7.73169755935669</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G730" t="n">
-        <v>7.3868579864502</v>
+        <v>7.38685703277588</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>7.44130516052246</v>
+        <v>7.44130563735962</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>6.99664163589478</v>
+        <v>6.99664211273193</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>6.98756694793701</v>
+        <v>6.98756647109985</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>6.99664163589478</v>
+        <v>6.99664211273193</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G742" t="n">
-        <v>7.35055780410767</v>
+        <v>7.35055732727051</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G743" t="n">
-        <v>7.36870718002319</v>
+        <v>7.36870765686035</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G744" t="n">
-        <v>7.35055780410767</v>
+        <v>7.35055732727051</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G745" t="n">
-        <v>7.46852970123291</v>
+        <v>7.46852922439575</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G750" t="n">
-        <v>7.40500688552856</v>
+        <v>7.40500640869141</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>7.22351169586182</v>
+        <v>7.22351121902466</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>7.36870718002319</v>
+        <v>7.36870765686035</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>7.41408109664917</v>
+        <v>7.41408157348633</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>7.41408109664917</v>
+        <v>7.41408157348633</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>7.33240842819214</v>
+        <v>7.33240795135498</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G759" t="n">
-        <v>7.24166107177734</v>
+        <v>7.24166059494019</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G763" t="n">
-        <v>7.42315626144409</v>
+        <v>7.42315673828125</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G765" t="n">
-        <v>7.6500244140625</v>
+        <v>7.65002393722534</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G767" t="n">
-        <v>7.96764087677002</v>
+        <v>7.96764183044434</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G768" t="n">
-        <v>8.27618312835693</v>
+        <v>8.27618408203125</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G769" t="n">
-        <v>8.29433345794678</v>
+        <v>8.29433441162109</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G772" t="n">
-        <v>8.33063220977783</v>
+        <v>8.33063125610352</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>8.32155799865723</v>
+        <v>8.32155704498291</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G775" t="n">
-        <v>8.25803470611572</v>
+        <v>8.25803565979004</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G776" t="n">
-        <v>8.29433345794678</v>
+        <v>8.29433441162109</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>8.93864154815674</v>
+        <v>8.93864250183105</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G783" t="n">
-        <v>9.04753971099854</v>
+        <v>9.0475378036499</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>8.65732288360596</v>
+        <v>8.65732383728027</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G786" t="n">
-        <v>8.75714683532715</v>
+        <v>8.75714588165283</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>9.02031421661377</v>
+        <v>9.02031326293945</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>8.77529621124268</v>
+        <v>8.77529525756836</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G796" t="n">
-        <v>8.91141700744629</v>
+        <v>8.91141605377197</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>8.92956733703613</v>
+        <v>8.92956638336182</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G800" t="n">
-        <v>8.74807071685791</v>
+        <v>8.74807167053223</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G802" t="n">
-        <v>8.87511825561523</v>
+        <v>8.87511730194092</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G803" t="n">
-        <v>8.82066917419434</v>
+        <v>8.82066822052002</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G804" t="n">
-        <v>8.76622009277344</v>
+        <v>8.76622104644775</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G807" t="n">
-        <v>8.75714683532715</v>
+        <v>8.75714588165283</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G809" t="n">
-        <v>8.87511825561523</v>
+        <v>8.87511730194092</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G810" t="n">
-        <v>8.74807071685791</v>
+        <v>8.74807167053223</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G812" t="n">
-        <v>8.60287475585938</v>
+        <v>8.60287380218506</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G815" t="n">
-        <v>8.30340766906738</v>
+        <v>8.30340671539307</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G817" t="n">
-        <v>8.19451141357422</v>
+        <v>8.19450950622559</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G819" t="n">
-        <v>8.32155799865723</v>
+        <v>8.32155704498291</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G822" t="n">
-        <v>8.04931545257568</v>
+        <v>8.04931449890137</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G827" t="n">
-        <v>8.30340766906738</v>
+        <v>8.30340671539307</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G830" t="n">
-        <v>8.27618312835693</v>
+        <v>8.27618408203125</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>9.25</v>
       </c>
       <c r="G832" t="n">
-        <v>8.39415454864502</v>
+        <v>8.39415550231934</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G833" t="n">
-        <v>8.42137908935547</v>
+        <v>8.42138004302979</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>9.25</v>
       </c>
       <c r="G835" t="n">
-        <v>8.39415454864502</v>
+        <v>8.39415550231934</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G836" t="n">
-        <v>8.38508033752441</v>
+        <v>8.38508129119873</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G837" t="n">
-        <v>8.43045425415039</v>
+        <v>8.43045330047607</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>8.43045425415039</v>
+        <v>8.43045330047607</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>8.46675395965576</v>
+        <v>8.46675205230713</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G850" t="n">
-        <v>8.32292461395264</v>
+        <v>8.32292556762695</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>8.25</v>
       </c>
       <c r="G854" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G855" t="n">
-        <v>8.21744823455811</v>
+        <v>8.21744918823242</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G856" t="n">
-        <v>8.01608848571777</v>
+        <v>8.01608753204346</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G857" t="n">
-        <v>7.95855665206909</v>
+        <v>7.95855569839478</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>7.94896793365479</v>
+        <v>7.94896697998047</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>8.02567577362061</v>
+        <v>8.02567672729492</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G861" t="n">
-        <v>8.02567577362061</v>
+        <v>8.02567672729492</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G863" t="n">
-        <v>8.07361888885498</v>
+        <v>8.07362079620361</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G864" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>8.25</v>
       </c>
       <c r="G865" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>8.25</v>
       </c>
       <c r="G866" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>8.25</v>
       </c>
       <c r="G867" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>8.25</v>
       </c>
       <c r="G868" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>8.25</v>
       </c>
       <c r="G870" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G871" t="n">
-        <v>8.09279727935791</v>
+        <v>8.09279537200928</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>7.94896793365479</v>
+        <v>7.94896697998047</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>8.02567577362061</v>
+        <v>8.02567672729492</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G880" t="n">
-        <v>8.02567577362061</v>
+        <v>8.02567672729492</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G881" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G883" t="n">
-        <v>8.00650024414062</v>
+        <v>8.00650119781494</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G885" t="n">
-        <v>7.86266994476318</v>
+        <v>7.8626708984375</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G886" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G887" t="n">
-        <v>7.86266994476318</v>
+        <v>7.8626708984375</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G889" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G891" t="n">
-        <v>8.10238456726074</v>
+        <v>8.10238552093506</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>8.10238456726074</v>
+        <v>8.10238552093506</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G894" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G896" t="n">
-        <v>8.10238456726074</v>
+        <v>8.10238552093506</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96814584732056</v>
+        <v>7.96814680099487</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G900" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G902" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G903" t="n">
-        <v>7.96814584732056</v>
+        <v>7.96814680099487</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>7.87225914001465</v>
+        <v>7.87225866317749</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G906" t="n">
-        <v>8.00650024414062</v>
+        <v>8.00650119781494</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G907" t="n">
-        <v>8.00650024414062</v>
+        <v>8.00650119781494</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>8.07361888885498</v>
+        <v>8.07362079620361</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G911" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G912" t="n">
-        <v>8.13115215301514</v>
+        <v>8.13115119934082</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G914" t="n">
-        <v>8.01608848571777</v>
+        <v>8.01608753204346</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G915" t="n">
-        <v>8.08320999145508</v>
+        <v>8.08320808410645</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G916" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>8.25</v>
       </c>
       <c r="G918" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G920" t="n">
-        <v>8.00650024414062</v>
+        <v>8.00650119781494</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G921" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G922" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G924" t="n">
-        <v>7.92979145050049</v>
+        <v>7.92979192733765</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G926" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>8.25</v>
       </c>
       <c r="G927" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>7.87225914001465</v>
+        <v>7.87225866317749</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G931" t="n">
-        <v>7.79555034637451</v>
+        <v>7.79555082321167</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G933" t="n">
-        <v>7.79555034637451</v>
+        <v>7.79555082321167</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G934" t="n">
-        <v>7.80513954162598</v>
+        <v>7.80513858795166</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G935" t="n">
-        <v>7.84349346160889</v>
+        <v>7.84349393844604</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G936" t="n">
-        <v>7.87225914001465</v>
+        <v>7.87225866317749</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G937" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>8.25</v>
       </c>
       <c r="G938" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>8.25</v>
       </c>
       <c r="G939" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>7.88184833526611</v>
+        <v>7.88184785842896</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G941" t="n">
-        <v>7.84349346160889</v>
+        <v>7.84349393844604</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>7.86266994476318</v>
+        <v>7.8626708984375</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G943" t="n">
-        <v>7.79555034637451</v>
+        <v>7.79555082321167</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G944" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>7.94896793365479</v>
+        <v>7.94896697998047</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>7.94896793365479</v>
+        <v>7.94896697998047</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G948" t="n">
-        <v>7.86266994476318</v>
+        <v>7.8626708984375</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>7.94896793365479</v>
+        <v>7.94896697998047</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G950" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G952" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G953" t="n">
-        <v>7.84349346160889</v>
+        <v>7.84349393844604</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G955" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G957" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G958" t="n">
-        <v>7.88184833526611</v>
+        <v>7.88184785842896</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G959" t="n">
-        <v>7.88184833526611</v>
+        <v>7.88184785842896</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G961" t="n">
-        <v>7.87225914001465</v>
+        <v>7.87225866317749</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G964" t="n">
-        <v>7.84349346160889</v>
+        <v>7.84349393844604</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G965" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G966" t="n">
-        <v>7.80513954162598</v>
+        <v>7.80513858795166</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G968" t="n">
-        <v>7.84349346160889</v>
+        <v>7.84349393844604</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G969" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G973" t="n">
-        <v>8.20786285400391</v>
+        <v>8.20786190032959</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>8.5</v>
       </c>
       <c r="G974" t="n">
-        <v>8.15032863616943</v>
+        <v>8.15033054351807</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.10238456726074</v>
+        <v>8.10238552093506</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>8.5</v>
       </c>
       <c r="G977" t="n">
-        <v>8.15032863616943</v>
+        <v>8.15033054351807</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G978" t="n">
-        <v>8.32292461395264</v>
+        <v>8.32292556762695</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G979" t="n">
-        <v>8.37086772918701</v>
+        <v>8.3708667755127</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.44757747650146</v>
+        <v>8.44757556915283</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G983" t="n">
-        <v>9.05166053771973</v>
+        <v>9.05165958404541</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G985" t="n">
-        <v>9.30096340179443</v>
+        <v>9.30096435546875</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G987" t="n">
-        <v>9.36808490753174</v>
+        <v>9.36808586120605</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>9.46396923065186</v>
+        <v>9.46397018432617</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G992" t="n">
-        <v>9.93381214141846</v>
+        <v>9.93381309509277</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G993" t="n">
-        <v>10.2214708328247</v>
+        <v>10.221471786499</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G994" t="n">
-        <v>9.9529914855957</v>
+        <v>9.95298957824707</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>9.97216606140137</v>
+        <v>9.97216701507568</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G996" t="n">
-        <v>9.89545726776123</v>
+        <v>9.89545822143555</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G997" t="n">
-        <v>9.85710430145264</v>
+        <v>9.85710334777832</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>9.51191234588623</v>
+        <v>9.51191520690918</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10</v>
       </c>
       <c r="G999" t="n">
-        <v>9.58862113952637</v>
+        <v>9.58862209320068</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.52150344848633</v>
+        <v>9.52150249481201</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.6077995300293</v>
+        <v>9.60780048370361</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.62697696685791</v>
+        <v>9.62697601318359</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1003" t="n">
-        <v>9.41602611541748</v>
+        <v>9.4160270690918</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.36808490753174</v>
+        <v>9.36808586120605</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>10</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.58862113952637</v>
+        <v>9.58862209320068</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1011" t="n">
-        <v>9.41602611541748</v>
+        <v>9.4160270690918</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.36808490753174</v>
+        <v>9.36808586120605</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1020" t="n">
-        <v>9.24343395233154</v>
+        <v>9.24343299865723</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1021" t="n">
-        <v>9.41602611541748</v>
+        <v>9.4160270690918</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.68450832366943</v>
+        <v>9.68450927734375</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.56944561004639</v>
+        <v>9.56944465637207</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>9.5</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.10919094085693</v>
+        <v>9.10919189453125</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.77359008789062</v>
+        <v>8.77358913421631</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.68729209899902</v>
+        <v>8.68729305267334</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.90783023834229</v>
+        <v>8.90782928466797</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1045" t="n">
-        <v>9.05166053771973</v>
+        <v>9.05165958404541</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.90783023834229</v>
+        <v>8.90782928466797</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.77359008789062</v>
+        <v>8.77358913421631</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.76678419113159</v>
+        <v>7.76678466796875</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.53665781021118</v>
+        <v>7.53665733337402</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.46273136138916</v>
+        <v>6.462730884552</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.38602209091187</v>
+        <v>6.38602256774902</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1067" t="n">
-        <v>5.42715978622437</v>
+        <v>5.42716026306152</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.60253858566284</v>
+        <v>4.6025390625</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.47788715362549</v>
+        <v>4.47788667678833</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.79431056976318</v>
+        <v>4.79431104660034</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.08197021484375</v>
+        <v>5.08196973800659</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.46551418304443</v>
+        <v>5.46551465988159</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.98329973220825</v>
+        <v>5.98330020904541</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.92576885223389</v>
+        <v>5.92576837539673</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.98329973220825</v>
+        <v>5.98330020904541</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.82988214492798</v>
+        <v>5.82988262176514</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.09836339950562</v>
+        <v>6.09836435317993</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.38602209091187</v>
+        <v>6.38602256774902</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1086" t="n">
-        <v>6.40519952774048</v>
+        <v>6.40520000457764</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.16548442840576</v>
+        <v>6.1654839515686</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6.75</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.47232055664062</v>
+        <v>6.47232007980347</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.48190879821777</v>
+        <v>6.48190927505493</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.48190879821777</v>
+        <v>6.48190927505493</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.76678419113159</v>
+        <v>7.76678466796875</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.60377788543701</v>
+        <v>7.60377740859985</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.47912549972534</v>
+        <v>7.4791259765625</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1098" t="n">
-        <v>7.47912549972534</v>
+        <v>7.4791259765625</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.51748037338257</v>
+        <v>7.51748085021973</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.47912549972534</v>
+        <v>7.4791259765625</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.56542301177979</v>
+        <v>7.56542348861694</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.33529567718506</v>
+        <v>7.33529615402222</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.62295436859131</v>
+        <v>7.62295484542847</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.53665781021118</v>
+        <v>7.53665733337402</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.62295436859131</v>
+        <v>7.62295484542847</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>7.84349346160889</v>
+        <v>7.84349393844604</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>8.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1119" t="n">
-        <v>7.80513954162598</v>
+        <v>7.80513858795166</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1120" t="n">
-        <v>7.85308170318604</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.96814584732056</v>
+        <v>7.96814680099487</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.88184833526611</v>
+        <v>7.88184785842896</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.08320999145508</v>
+        <v>8.08320808410645</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1130" t="n">
-        <v>7.48871421813965</v>
+        <v>7.48871374130249</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1131" t="n">
-        <v>7.52706813812256</v>
+        <v>7.52706861495972</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1133" t="n">
-        <v>7.48871421813965</v>
+        <v>7.48871374130249</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1134" t="n">
-        <v>7.47912549972534</v>
+        <v>7.4791259765625</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1135" t="n">
-        <v>7.47912549972534</v>
+        <v>7.4791259765625</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>7.75</v>
       </c>
       <c r="G1136" t="n">
-        <v>7.43118190765381</v>
+        <v>7.43118238449097</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>7.24899864196777</v>
+        <v>7.24899911880493</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.23941040039062</v>
+        <v>7.23940992355347</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1139" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1141" t="n">
-        <v>7.24899864196777</v>
+        <v>7.24899911880493</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1144" t="n">
-        <v>7.44077205657959</v>
+        <v>7.44077157974243</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1154" t="n">
-        <v>7.60377788543701</v>
+        <v>7.60377740859985</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1155" t="n">
-        <v>7.51748037338257</v>
+        <v>7.51748085021973</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.52706813812256</v>
+        <v>7.52706861495972</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.47912549972534</v>
+        <v>7.4791259765625</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1159" t="n">
-        <v>7.56542301177979</v>
+        <v>7.56542348861694</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.34488534927368</v>
+        <v>7.34488439559937</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>7.22982120513916</v>
+        <v>7.22982168197632</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.40241670608521</v>
+        <v>7.40241622924805</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.51748037338257</v>
+        <v>7.51748085021973</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>7.22982120513916</v>
+        <v>7.22982168197632</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1170" t="n">
-        <v>7.81472635269165</v>
+        <v>7.81472730636597</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>8.25</v>
       </c>
       <c r="G1172" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1173" t="n">
-        <v>7.79555034637451</v>
+        <v>7.79555082321167</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1178" t="n">
-        <v>7.62295436859131</v>
+        <v>7.62295484542847</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1179" t="n">
-        <v>7.66130924224854</v>
+        <v>7.66130971908569</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1182" t="n">
-        <v>7.66130924224854</v>
+        <v>7.66130971908569</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1185" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1186" t="n">
-        <v>7.40241670608521</v>
+        <v>7.40241622924805</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1194" t="n">
-        <v>7.34488534927368</v>
+        <v>7.34488439559937</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>7.24899864196777</v>
+        <v>7.24899911880493</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1198" t="n">
-        <v>7.20105600357056</v>
+        <v>7.2010555267334</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1202" t="n">
-        <v>7.22982120513916</v>
+        <v>7.22982168197632</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.05722618103027</v>
+        <v>7.05722570419312</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.15311288833618</v>
+        <v>7.15311241149902</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.15311288833618</v>
+        <v>7.15311241149902</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.52706813812256</v>
+        <v>7.52706861495972</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1215" t="n">
-        <v>7.62295436859131</v>
+        <v>7.62295484542847</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1216" t="n">
-        <v>7.65172100067139</v>
+        <v>7.65172052383423</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.56542301177979</v>
+        <v>7.56542348861694</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.59418964385986</v>
+        <v>7.59418916702271</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1224" t="n">
-        <v>7.52706813812256</v>
+        <v>7.52706861495972</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.98051738739014</v>
+        <v>6.98051786422729</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1229" t="n">
-        <v>7.03804969787598</v>
+        <v>7.03804922103882</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.98051738739014</v>
+        <v>6.98051786422729</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>7.03804969787598</v>
+        <v>7.03804922103882</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.04763746261597</v>
+        <v>7.04763793945312</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>7.04763746261597</v>
+        <v>7.04763793945312</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.10516929626465</v>
+        <v>7.10516881942749</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.40241670608521</v>
+        <v>7.40241622924805</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>7.75</v>
       </c>
       <c r="G1242" t="n">
-        <v>7.43118190765381</v>
+        <v>7.43118238449097</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1246" t="n">
-        <v>7.33529567718506</v>
+        <v>7.33529615402222</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>7.22982120513916</v>
+        <v>7.22982168197632</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>7.15311288833618</v>
+        <v>7.15311241149902</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>7.65172100067139</v>
+        <v>7.65172052383423</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.55583477020264</v>
+        <v>7.55583429336548</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.34488534927368</v>
+        <v>7.34488439559937</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1273" t="n">
-        <v>7.33529567718506</v>
+        <v>7.33529615402222</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1277" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>7.33529567718506</v>
+        <v>7.33529615402222</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1279" t="n">
-        <v>7.23941040039062</v>
+        <v>7.23940992355347</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.10516929626465</v>
+        <v>7.10516881942749</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1287" t="n">
-        <v>7.00928258895874</v>
+        <v>7.0092830657959</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.90380764007568</v>
+        <v>6.90380811691284</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.91339731216431</v>
+        <v>6.91339683532715</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.99969482421875</v>
+        <v>6.99969434738159</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.03804969787598</v>
+        <v>7.03804922103882</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1297" t="n">
-        <v>7.05722618103027</v>
+        <v>7.05722570419312</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1301" t="n">
-        <v>6.99969482421875</v>
+        <v>6.99969434738159</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>6.99010610580444</v>
+        <v>6.99010562896729</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.90380764007568</v>
+        <v>6.90380811691284</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.80792188644409</v>
+        <v>6.80792140960693</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1305" t="n">
-        <v>6.87504291534424</v>
+        <v>6.87504243850708</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1307" t="n">
-        <v>6.75997877120972</v>
+        <v>6.75997924804688</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1308" t="n">
-        <v>6.74080228805542</v>
+        <v>6.74080181121826</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>7</v>
       </c>
       <c r="G1310" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.80792188644409</v>
+        <v>6.80792140960693</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1312" t="n">
-        <v>6.80792188644409</v>
+        <v>6.80792140960693</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1313" t="n">
-        <v>6.80792188644409</v>
+        <v>6.80792140960693</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>7</v>
       </c>
       <c r="G1314" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>7</v>
       </c>
       <c r="G1316" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1317" t="n">
-        <v>6.76956748962402</v>
+        <v>6.76956796646118</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>7</v>
       </c>
       <c r="G1320" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1322" t="n">
-        <v>6.69285869598389</v>
+        <v>6.69285917282104</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1325" t="n">
-        <v>6.48190879821777</v>
+        <v>6.48190927505493</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1326" t="n">
-        <v>6.61614990234375</v>
+        <v>6.61615037918091</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>7</v>
       </c>
       <c r="G1327" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>7.22982120513916</v>
+        <v>7.22982168197632</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>6.99010610580444</v>
+        <v>6.99010562896729</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>7.00928258895874</v>
+        <v>7.0092830657959</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1341" t="n">
-        <v>7.04763746261597</v>
+        <v>7.04763793945312</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1343" t="n">
-        <v>7.04763746261597</v>
+        <v>7.04763793945312</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>6.86545372009277</v>
+        <v>6.86545419692993</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.86545372009277</v>
+        <v>6.86545419692993</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1347" t="n">
-        <v>6.99969482421875</v>
+        <v>6.99969434738159</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1349" t="n">
-        <v>7.05722618103027</v>
+        <v>7.05722570419312</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1351" t="n">
-        <v>7.20105600357056</v>
+        <v>7.2010555267334</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1364" t="n">
-        <v>7.11399364471436</v>
+        <v>7.11399412155151</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1370" t="n">
-        <v>7.45137882232666</v>
+        <v>7.4513783454895</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1371" t="n">
-        <v>7.39354085922241</v>
+        <v>7.39354133605957</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>7.63453054428101</v>
+        <v>7.63453006744385</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1374" t="n">
-        <v>7.75984477996826</v>
+        <v>7.7598443031311</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1377" t="n">
-        <v>8.01047325134277</v>
+        <v>8.01047420501709</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1378" t="n">
-        <v>7.93335628509521</v>
+        <v>7.9333553314209</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1382" t="n">
-        <v>8.05867004394531</v>
+        <v>8.058669090271</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1384" t="n">
-        <v>7.93335628509521</v>
+        <v>7.9333553314209</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1385" t="n">
-        <v>7.89479684829712</v>
+        <v>7.89479780197144</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>7.5284948348999</v>
+        <v>7.52849435806274</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1393" t="n">
-        <v>7.5284948348999</v>
+        <v>7.52849435806274</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1403" t="n">
-        <v>7.59597206115723</v>
+        <v>7.59597158432007</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1404" t="n">
-        <v>7.59597206115723</v>
+        <v>7.59597158432007</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>7.63453054428101</v>
+        <v>7.63453006744385</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1410" t="n">
-        <v>7.53813457489014</v>
+        <v>7.53813505172729</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>7.94299554824829</v>
+        <v>7.94299650192261</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>7.86587905883789</v>
+        <v>7.86587953567505</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1431" t="n">
-        <v>8.36713600158691</v>
+        <v>8.36713695526123</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G1432" t="n">
-        <v>8.26110076904297</v>
+        <v>8.26110172271729</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1433" t="n">
-        <v>8.29002094268799</v>
+        <v>8.29001998901367</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G1434" t="n">
-        <v>8.26110076904297</v>
+        <v>8.26110172271729</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1436" t="n">
-        <v>8.36713600158691</v>
+        <v>8.36713695526123</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1439" t="n">
-        <v>8.58884525299072</v>
+        <v>8.58884620666504</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1441" t="n">
-        <v>8.73343944549561</v>
+        <v>8.73344039916992</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1448" t="n">
-        <v>8.72379970550537</v>
+        <v>8.72380065917969</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.29002094268799</v>
+        <v>8.29001998901367</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1454" t="n">
-        <v>8.16470718383789</v>
+        <v>8.16470623016357</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1455" t="n">
-        <v>8.22254276275635</v>
+        <v>8.22254371643066</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.37677574157715</v>
+        <v>8.37677669525146</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1468" t="n">
-        <v>8.06831073760986</v>
+        <v>8.06830978393555</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1475" t="n">
-        <v>8.29002094268799</v>
+        <v>8.29001998901367</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1476" t="n">
-        <v>8.55992794036865</v>
+        <v>8.55992698669434</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1477" t="n">
-        <v>8.50208950042725</v>
+        <v>8.50209045410156</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.53101062774658</v>
+        <v>8.53100967407227</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.34785747528076</v>
+        <v>8.34785652160645</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1480" t="n">
-        <v>8.424973487854</v>
+        <v>8.42497253417969</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1497" t="n">
-        <v>9.67811679840088</v>
+        <v>9.67811584472656</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.32145309448242</v>
+        <v>9.32145214080811</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>8.99370765686035</v>
+        <v>8.99370670318604</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1502" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>9.23469543457031</v>
+        <v>9.23469638824463</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1509" t="n">
-        <v>9.00334644317627</v>
+        <v>9.00334739685059</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1511" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1512" t="n">
-        <v>9.03226661682129</v>
+        <v>9.03226566314697</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.84911441802979</v>
+        <v>8.84911346435547</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1517" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>9.04190635681152</v>
+        <v>9.04190540313721</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1521" t="n">
-        <v>9.27325630187988</v>
+        <v>9.27325534820557</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G1522" t="n">
-        <v>9.53352355957031</v>
+        <v>9.533522605896</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1531" t="n">
-        <v>9.36964988708496</v>
+        <v>9.36965084075928</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1540" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1541" t="n">
-        <v>8.89731311798096</v>
+        <v>8.89731216430664</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1545" t="n">
-        <v>8.41533374786377</v>
+        <v>8.41533279418945</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1547" t="n">
-        <v>8.53101062774658</v>
+        <v>8.53100967407227</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1548" t="n">
-        <v>8.53101062774658</v>
+        <v>8.53100967407227</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1554" t="n">
-        <v>8.2032642364502</v>
+        <v>8.20326328277588</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1564" t="n">
-        <v>8.36713600158691</v>
+        <v>8.36713695526123</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>8.39605617523193</v>
+        <v>8.39605522155762</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1568" t="n">
-        <v>8.29002094268799</v>
+        <v>8.29001998901367</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1569" t="n">
-        <v>8.86839294433594</v>
+        <v>8.86839389801025</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1572" t="n">
-        <v>8.06831073760986</v>
+        <v>8.06830978393555</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1573" t="n">
-        <v>8.08758926391602</v>
+        <v>8.08759021759033</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1576" t="n">
-        <v>8.84911441802979</v>
+        <v>8.84911346435547</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1581" t="n">
-        <v>9.40820980072021</v>
+        <v>9.4082088470459</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.67811679840088</v>
+        <v>9.67811584472656</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1589" t="n">
-        <v>9.67811679840088</v>
+        <v>9.67811584472656</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1593" t="n">
-        <v>9.40820980072021</v>
+        <v>9.4082088470459</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>9.23469543457031</v>
+        <v>9.23469638824463</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1597" t="n">
-        <v>9.17686080932617</v>
+        <v>9.17685985565186</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1599" t="n">
-        <v>9.23469543457031</v>
+        <v>9.23469638824463</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1606" t="n">
-        <v>9.36964988708496</v>
+        <v>9.36965084075928</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1610" t="n">
-        <v>9.23469543457031</v>
+        <v>9.23469638824463</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1612" t="n">
-        <v>9.40820980072021</v>
+        <v>9.4082088470459</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1623" t="n">
-        <v>9.90946578979492</v>
+        <v>9.90946483612061</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1624" t="n">
-        <v>10.0636978149414</v>
+        <v>10.0636987686157</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1625" t="n">
-        <v>9.98658180236816</v>
+        <v>9.98658275604248</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G1629" t="n">
-        <v>9.96730327606201</v>
+        <v>9.9673023223877</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1630" t="n">
-        <v>9.90946578979492</v>
+        <v>9.90946483612061</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1632" t="n">
-        <v>10.0636978149414</v>
+        <v>10.0636987686157</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1633" t="n">
-        <v>10.0444202423096</v>
+        <v>10.0444192886353</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1636" t="n">
-        <v>9.90946578979492</v>
+        <v>9.90946483612061</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1640" t="n">
-        <v>9.13829898834229</v>
+        <v>9.1382999420166</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>9.27325630187988</v>
+        <v>9.27325534820557</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>9.75</v>
       </c>
       <c r="G1648" t="n">
-        <v>9.39857006072998</v>
+        <v>9.39856910705566</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1649" t="n">
-        <v>9.54316329956055</v>
+        <v>9.54316234588623</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1650" t="n">
-        <v>9.67811679840088</v>
+        <v>9.67811584472656</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1658" t="n">
-        <v>11.1626081466675</v>
+        <v>11.1626071929932</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1659" t="n">
-        <v>11.4710731506348</v>
+        <v>11.4710741043091</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1667" t="n">
-        <v>11.2975635528564</v>
+        <v>11.2975625991821</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1668" t="n">
-        <v>11.0276546478271</v>
+        <v>11.0276536941528</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1676" t="n">
-        <v>11.5289115905762</v>
+        <v>11.5289106369019</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>11.9530515670776</v>
+        <v>11.9530506134033</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1685" t="n">
-        <v>12.2422370910645</v>
+        <v>12.2422380447388</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1686" t="n">
-        <v>11.5867500305176</v>
+        <v>11.5867490768433</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1687" t="n">
-        <v>11.9530515670776</v>
+        <v>11.9530506134033</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1690" t="n">
-        <v>11.5289115905762</v>
+        <v>11.5289106369019</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1693" t="n">
-        <v>11.1626081466675</v>
+        <v>11.1626071929932</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1694" t="n">
-        <v>10.7963047027588</v>
+        <v>10.7963037490845</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1702" t="n">
-        <v>10.7963047027588</v>
+        <v>10.7963037490845</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1706" t="n">
-        <v>10.8541421890259</v>
+        <v>10.8541431427002</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1718" t="n">
-        <v>10.7963047027588</v>
+        <v>10.7963037490845</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1730" t="n">
-        <v>11.2975635528564</v>
+        <v>11.2975625991821</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1737" t="n">
-        <v>11.5867500305176</v>
+        <v>11.5867490768433</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1744" t="n">
-        <v>11.9530515670776</v>
+        <v>11.9530506134033</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1745" t="n">
-        <v>12.4157514572144</v>
+        <v>12.41575050354</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.4735870361328</v>
+        <v>12.4735879898071</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1752" t="n">
-        <v>12.4157514572144</v>
+        <v>12.41575050354</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1753" t="n">
-        <v>12.5121469497681</v>
+        <v>12.5121459960938</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1758" t="n">
-        <v>12.4157514572144</v>
+        <v>12.41575050354</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1760" t="n">
-        <v>12.280797958374</v>
+        <v>12.2807970046997</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1761" t="n">
-        <v>12.2422370910645</v>
+        <v>12.2422380447388</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1764" t="n">
-        <v>12.1651229858398</v>
+        <v>12.1651220321655</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1765" t="n">
-        <v>12.1651229858398</v>
+        <v>12.1651220321655</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1772" t="n">
-        <v>11.9723310470581</v>
+        <v>11.9723320007324</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.6663799285889</v>
+        <v>12.6663808822632</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1777" t="n">
-        <v>12.1072845458984</v>
+        <v>12.1072854995728</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1778" t="n">
-        <v>12.2422370910645</v>
+        <v>12.2422380447388</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1780" t="n">
-        <v>11.9530515670776</v>
+        <v>11.9530506134033</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1784" t="n">
-        <v>12.4157514572144</v>
+        <v>12.41575050354</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1786" t="n">
-        <v>12.4735870361328</v>
+        <v>12.4735879898071</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1787" t="n">
-        <v>12.5121469497681</v>
+        <v>12.5121459960938</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1788" t="n">
-        <v>12.4735870361328</v>
+        <v>12.4735879898071</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1792" t="n">
-        <v>12.8398904800415</v>
+        <v>12.8398914337158</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>13.5</v>
       </c>
       <c r="G1797" t="n">
-        <v>13.0134038925171</v>
+        <v>13.0134029388428</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1812" t="n">
-        <v>14.7870817184448</v>
+        <v>14.7870826721191</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1813" t="n">
-        <v>15.712477684021</v>
+        <v>15.7124786376953</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1814" t="n">
-        <v>16.7342720031738</v>
+        <v>16.7342739105225</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1815" t="n">
-        <v>16.8306674957275</v>
+        <v>16.8306655883789</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>17.0620212554932</v>
+        <v>17.0620193481445</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1822" t="n">
-        <v>17.4475994110107</v>
+        <v>17.4476013183594</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1827" t="n">
-        <v>18.0645332336426</v>
+        <v>18.0645313262939</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1828" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1834" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1836" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1839" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1840" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>20.25</v>
       </c>
       <c r="G1842" t="n">
-        <v>19.5201072692871</v>
+        <v>19.5201053619385</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>20.25</v>
       </c>
       <c r="G1845" t="n">
-        <v>19.5201072692871</v>
+        <v>19.5201053619385</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>19.5</v>
       </c>
       <c r="G1856" t="n">
-        <v>18.79714012146</v>
+        <v>18.7971382141113</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1860" t="n">
-        <v>18.4693908691406</v>
+        <v>18.4693927764893</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1870" t="n">
-        <v>19.0670471191406</v>
+        <v>19.067045211792</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1874" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1876" t="n">
-        <v>18.7392997741699</v>
+        <v>18.7393016815186</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1877" t="n">
-        <v>18.8164196014404</v>
+        <v>18.8164176940918</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>19.5</v>
       </c>
       <c r="G1878" t="n">
-        <v>18.79714012146</v>
+        <v>18.7971382141113</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G1879" t="n">
-        <v>18.5465126037598</v>
+        <v>18.5465106964111</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1881" t="n">
-        <v>18.9357299804688</v>
+        <v>18.9357318878174</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1893" t="n">
-        <v>21.7965278625488</v>
+        <v>21.7965259552002</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>22.25</v>
       </c>
       <c r="G1894" t="n">
-        <v>21.6505699157715</v>
+        <v>21.6505680084229</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1897" t="n">
-        <v>21.7965278625488</v>
+        <v>21.7965259552002</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>22.25</v>
       </c>
       <c r="G1910" t="n">
-        <v>21.6505699157715</v>
+        <v>21.6505680084229</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1912" t="n">
-        <v>21.5046119689941</v>
+        <v>21.5046100616455</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>20.5</v>
       </c>
       <c r="G1924" t="n">
-        <v>19.9477138519287</v>
+        <v>19.9477157592773</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1926" t="n">
-        <v>19.8017539978027</v>
+        <v>19.8017559051514</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>17.9042892456055</v>
+        <v>17.9042911529541</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1938" t="n">
-        <v>18.1572856903076</v>
+        <v>18.157283782959</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1939" t="n">
-        <v>18.2351322174072</v>
+        <v>18.2351303100586</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1946" t="n">
-        <v>17.6318340301514</v>
+        <v>17.6318359375</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1949" t="n">
-        <v>17.3399143218994</v>
+        <v>17.339916229248</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1956" t="n">
-        <v>16.8923091888428</v>
+        <v>16.8923110961914</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1957" t="n">
-        <v>16.8923091888428</v>
+        <v>16.8923110961914</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1960" t="n">
-        <v>16.5614700317383</v>
+        <v>16.5614681243896</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1965" t="n">
-        <v>16.1722450256348</v>
+        <v>16.1722469329834</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1968" t="n">
-        <v>16.1138591766357</v>
+        <v>16.1138610839844</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1972" t="n">
-        <v>15.9387083053589</v>
+        <v>15.9387102127075</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1976" t="n">
-        <v>15.9970960617065</v>
+        <v>15.9970941543579</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1978" t="n">
-        <v>15.6662549972534</v>
+        <v>15.6662540435791</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1980" t="n">
-        <v>16.1138591766357</v>
+        <v>16.1138610839844</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1982" t="n">
-        <v>16.2695503234863</v>
+        <v>16.2695484161377</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>15</v>
       </c>
       <c r="G1986" t="n">
-        <v>14.5958881378174</v>
+        <v>14.5958890914917</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1992" t="n">
-        <v>14.4012775421143</v>
+        <v>14.4012765884399</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1993" t="n">
-        <v>14.3623542785645</v>
+        <v>14.3623552322388</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1996" t="n">
-        <v>14.7126560211182</v>
+        <v>14.7126569747925</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G2002" t="n">
-        <v>16.0165557861328</v>
+        <v>16.0165538787842</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G2006" t="n">
-        <v>14.9267292022705</v>
+        <v>14.9267301559448</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G2008" t="n">
-        <v>14.9267292022705</v>
+        <v>14.9267301559448</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G2012" t="n">
-        <v>15.9776334762573</v>
+        <v>15.9776315689087</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2020" t="n">
-        <v>16.6782341003418</v>
+        <v>16.6782360076904</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2024" t="n">
-        <v>16.8923091888428</v>
+        <v>16.8923110961914</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2026" t="n">
-        <v>16.9896144866943</v>
+        <v>16.9896125793457</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2028" t="n">
-        <v>17.6123714447021</v>
+        <v>17.6123733520508</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G2032" t="n">
-        <v>19.2081871032715</v>
+        <v>19.2081890106201</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>20</v>
       </c>
       <c r="G2033" t="n">
-        <v>19.4611873626709</v>
+        <v>19.4611854553223</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2035" t="n">
-        <v>19.2471141815186</v>
+        <v>19.2471122741699</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G2036" t="n">
-        <v>19.2860355377197</v>
+        <v>19.2860336303711</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G2037" t="n">
-        <v>19.2860355377197</v>
+        <v>19.2860336303711</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G2043" t="n">
-        <v>19.6071453094482</v>
+        <v>19.6071434020996</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>20.5</v>
       </c>
       <c r="G2048" t="n">
-        <v>19.9477138519287</v>
+        <v>19.9477157592773</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G2070" t="n">
-        <v>19.7531032562256</v>
+        <v>19.753101348877</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>20.5</v>
       </c>
       <c r="G2071" t="n">
-        <v>19.9477138519287</v>
+        <v>19.9477157592773</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G2072" t="n">
-        <v>19.6071453094482</v>
+        <v>19.6071434020996</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G2073" t="n">
-        <v>19.6071453094482</v>
+        <v>19.6071434020996</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2092" t="n">
-        <v>21.9911403656006</v>
+        <v>21.991138458252</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2093" t="n">
-        <v>21.5046119689941</v>
+        <v>21.5046100616455</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G2094" t="n">
-        <v>21.3586521148682</v>
+        <v>21.3586502075195</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2096" t="n">
-        <v>22.1857490539551</v>
+        <v>22.1857509613037</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2101" t="n">
-        <v>22.1857490539551</v>
+        <v>22.1857509613037</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2102" t="n">
-        <v>22.1857490539551</v>
+        <v>22.1857509613037</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2105" t="n">
-        <v>21.9911403656006</v>
+        <v>21.991138458252</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2106" t="n">
-        <v>21.9911403656006</v>
+        <v>21.991138458252</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G2111" t="n">
-        <v>21.3586521148682</v>
+        <v>21.3586502075195</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55697,7 +55697,7 @@
         <v>22.25</v>
       </c>
       <c r="G2128" t="n">
-        <v>21.6505699157715</v>
+        <v>21.6505680084229</v>
       </c>
       <c r="H2128" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G2132" t="n">
-        <v>22.7209339141846</v>
+        <v>22.7209358215332</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>54.2999992370605</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>23990</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>54.9000015258789</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>53.5999984741211</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>54.2000007629395</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>53.5999984741211</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>53.5999984741211</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>51.7000007629395</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>51.9000015258789</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>22223</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>53.7999992370605</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>51.9000015258789</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>51.9000015258789</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>51.9000015258789</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>52.5999984741211</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>18825</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>50.4000015258789</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>52.7999992370605</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>50.5999984741211</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>17061</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>51.0999984741211</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>49.7000007629395</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>50.5999984741211</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>50.5999984741211</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>49.9000015258789</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>21591</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>52.2999992370605</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>49.9000015258789</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>12228</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>52.7000007629395</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>50.7000007629395</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>52.7000007629395</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>51.2000007629395</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3297905921936</v>
+        <v>6.32979106903076</v>
       </c>
       <c r="H3" t="n">
         <v>13008</v>
@@ -514,7 +514,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G5" t="n">
-        <v>6.17115020751953</v>
+        <v>6.17114973068237</v>
       </c>
       <c r="H5" t="n">
         <v>16648</v>
@@ -717,7 +717,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>5.86973094940186</v>
+        <v>5.86973142623901</v>
       </c>
       <c r="H12" t="n">
         <v>16093</v>
@@ -775,7 +775,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>5.71108961105347</v>
+        <v>5.71109008789062</v>
       </c>
       <c r="H14" t="n">
         <v>19639</v>
@@ -804,7 +804,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.88956069946289</v>
+        <v>5.88956165313721</v>
       </c>
       <c r="H15" t="n">
         <v>21099</v>
@@ -833,7 +833,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G16" t="n">
-        <v>5.71108961105347</v>
+        <v>5.71109008789062</v>
       </c>
       <c r="H16" t="n">
         <v>26982</v>
@@ -891,7 +891,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>5.66746377944946</v>
+        <v>5.66746425628662</v>
       </c>
       <c r="H18" t="n">
         <v>11059</v>
@@ -920,7 +920,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>5.67142963409424</v>
+        <v>5.6714301109314</v>
       </c>
       <c r="H19" t="n">
         <v>7916</v>
@@ -949,7 +949,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>5.68729305267334</v>
+        <v>5.6872935295105</v>
       </c>
       <c r="H20" t="n">
         <v>5637</v>
@@ -978,7 +978,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>5.86973094940186</v>
+        <v>5.86973142623901</v>
       </c>
       <c r="H21" t="n">
         <v>28044</v>
@@ -1007,7 +1007,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G22" t="n">
-        <v>5.94112062454224</v>
+        <v>5.94112014770508</v>
       </c>
       <c r="H22" t="n">
         <v>20130</v>
@@ -1036,7 +1036,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>5.83007144927979</v>
+        <v>5.83007049560547</v>
       </c>
       <c r="H23" t="n">
         <v>5311</v>
@@ -1065,7 +1065,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8617992401123</v>
+        <v>5.86179876327515</v>
       </c>
       <c r="H24" t="n">
         <v>25218</v>
@@ -1094,7 +1094,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G25" t="n">
-        <v>5.86973094940186</v>
+        <v>5.86973142623901</v>
       </c>
       <c r="H25" t="n">
         <v>11676</v>
@@ -1152,7 +1152,7 @@
         <v>7.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.94905233383179</v>
+        <v>5.94905185699463</v>
       </c>
       <c r="H27" t="n">
         <v>30713</v>
@@ -1181,7 +1181,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>5.88956069946289</v>
+        <v>5.88956165313721</v>
       </c>
       <c r="H28" t="n">
         <v>54582</v>
@@ -1210,7 +1210,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>5.86973094940186</v>
+        <v>5.86973142623901</v>
       </c>
       <c r="H29" t="n">
         <v>24172</v>
@@ -1239,7 +1239,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G30" t="n">
-        <v>5.79437637329102</v>
+        <v>5.79437685012817</v>
       </c>
       <c r="H30" t="n">
         <v>12516</v>
@@ -1268,7 +1268,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.72298812866211</v>
+        <v>5.72298765182495</v>
       </c>
       <c r="H31" t="n">
         <v>10712</v>
@@ -1297,7 +1297,7 @@
         <v>7.5</v>
       </c>
       <c r="G32" t="n">
-        <v>5.94905233383179</v>
+        <v>5.94905185699463</v>
       </c>
       <c r="H32" t="n">
         <v>9895</v>
@@ -1326,7 +1326,7 @@
         <v>7.5</v>
       </c>
       <c r="G33" t="n">
-        <v>5.94905233383179</v>
+        <v>5.94905185699463</v>
       </c>
       <c r="H33" t="n">
         <v>5430</v>
@@ -1355,7 +1355,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>6.11562538146973</v>
+        <v>6.11562490463257</v>
       </c>
       <c r="H34" t="n">
         <v>26073</v>
@@ -1384,7 +1384,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>6.09182929992676</v>
+        <v>6.09182977676392</v>
       </c>
       <c r="H35" t="n">
         <v>14233</v>
@@ -1413,7 +1413,7 @@
         <v>7.75</v>
       </c>
       <c r="G36" t="n">
-        <v>6.14735412597656</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H36" t="n">
         <v>5260</v>
@@ -1442,7 +1442,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>6.11562538146973</v>
+        <v>6.11562490463257</v>
       </c>
       <c r="H37" t="n">
         <v>2319</v>
@@ -1471,7 +1471,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>6.23460674285889</v>
+        <v>6.23460578918457</v>
       </c>
       <c r="H38" t="n">
         <v>6760</v>
@@ -1529,7 +1529,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G40" t="n">
-        <v>6.16321706771851</v>
+        <v>6.16321754455566</v>
       </c>
       <c r="H40" t="n">
         <v>3280</v>
@@ -1558,7 +1558,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>6.13942098617554</v>
+        <v>6.1394214630127</v>
       </c>
       <c r="H41" t="n">
         <v>4292</v>
@@ -1587,7 +1587,7 @@
         <v>7.75500011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>6.15131902694702</v>
+        <v>6.15131998062134</v>
       </c>
       <c r="H42" t="n">
         <v>8864</v>
@@ -1616,7 +1616,7 @@
         <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>6.34565496444702</v>
+        <v>6.34565544128418</v>
       </c>
       <c r="H43" t="n">
         <v>28574</v>
@@ -1674,7 +1674,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G45" t="n">
-        <v>6.35358762741089</v>
+        <v>6.35358810424805</v>
       </c>
       <c r="H45" t="n">
         <v>6866</v>
@@ -1761,7 +1761,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G48" t="n">
-        <v>6.43290710449219</v>
+        <v>6.43290758132935</v>
       </c>
       <c r="H48" t="n">
         <v>13973</v>
@@ -1819,7 +1819,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G50" t="n">
-        <v>6.02044010162354</v>
+        <v>6.02044105529785</v>
       </c>
       <c r="H50" t="n">
         <v>18952</v>
@@ -1848,7 +1848,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>6.16321706771851</v>
+        <v>6.16321754455566</v>
       </c>
       <c r="H51" t="n">
         <v>33764</v>
@@ -1877,7 +1877,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>6.1949462890625</v>
+        <v>6.19494581222534</v>
       </c>
       <c r="H52" t="n">
         <v>34336</v>
@@ -1935,7 +1935,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G54" t="n">
-        <v>6.13545560836792</v>
+        <v>6.13545513153076</v>
       </c>
       <c r="H54" t="n">
         <v>35204</v>
@@ -2022,7 +2022,7 @@
         <v>7.75</v>
       </c>
       <c r="G57" t="n">
-        <v>6.14735412597656</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H57" t="n">
         <v>16884</v>
@@ -2051,7 +2051,7 @@
         <v>7.75500011444092</v>
       </c>
       <c r="G58" t="n">
-        <v>6.15131902694702</v>
+        <v>6.15131998062134</v>
       </c>
       <c r="H58" t="n">
         <v>3070</v>
@@ -2109,7 +2109,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>6.08389759063721</v>
+        <v>6.08389663696289</v>
       </c>
       <c r="H60" t="n">
         <v>3636</v>
@@ -2225,7 +2225,7 @@
         <v>7.75</v>
       </c>
       <c r="G64" t="n">
-        <v>6.14735412597656</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H64" t="n">
         <v>7515</v>
@@ -2283,7 +2283,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>5.93318843841553</v>
+        <v>5.93318796157837</v>
       </c>
       <c r="H66" t="n">
         <v>5807</v>
@@ -2341,7 +2341,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G68" t="n">
-        <v>5.89352798461914</v>
+        <v>5.89352655410767</v>
       </c>
       <c r="H68" t="n">
         <v>4226</v>
@@ -2370,7 +2370,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G69" t="n">
-        <v>5.94112062454224</v>
+        <v>5.94112014770508</v>
       </c>
       <c r="H69" t="n">
         <v>4273</v>
@@ -2428,7 +2428,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>5.99664402008057</v>
+        <v>5.99664449691772</v>
       </c>
       <c r="H71" t="n">
         <v>516</v>
@@ -2457,7 +2457,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>6.09976100921631</v>
+        <v>6.09976148605347</v>
       </c>
       <c r="H72" t="n">
         <v>2785</v>
@@ -2486,7 +2486,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>6.04027032852173</v>
+        <v>6.04027080535889</v>
       </c>
       <c r="H73" t="n">
         <v>761</v>
@@ -2515,7 +2515,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>6.04027032852173</v>
+        <v>6.04027080535889</v>
       </c>
       <c r="H74" t="n">
         <v>2714</v>
@@ -2602,7 +2602,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G77" t="n">
-        <v>6.06406736373901</v>
+        <v>6.0640664100647</v>
       </c>
       <c r="H77" t="n">
         <v>2340</v>
@@ -2631,7 +2631,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G78" t="n">
-        <v>6.15528583526611</v>
+        <v>6.15528535842896</v>
       </c>
       <c r="H78" t="n">
         <v>3785</v>
@@ -2660,7 +2660,7 @@
         <v>7.75</v>
       </c>
       <c r="G79" t="n">
-        <v>6.14735412597656</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H79" t="n">
         <v>1611</v>
@@ -2689,7 +2689,7 @@
         <v>7.75</v>
       </c>
       <c r="G80" t="n">
-        <v>6.14735412597656</v>
+        <v>6.14735317230225</v>
       </c>
       <c r="H80" t="n">
         <v>605</v>
@@ -2805,7 +2805,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>5.95698356628418</v>
+        <v>5.95698404312134</v>
       </c>
       <c r="H84" t="n">
         <v>3236</v>
@@ -2834,7 +2834,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G85" t="n">
-        <v>5.95698356628418</v>
+        <v>5.95698404312134</v>
       </c>
       <c r="H85" t="n">
         <v>672</v>
@@ -2921,7 +2921,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>5.8816294670105</v>
+        <v>5.88162851333618</v>
       </c>
       <c r="H88" t="n">
         <v>8816</v>
@@ -2950,7 +2950,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G89" t="n">
-        <v>6.06010103225708</v>
+        <v>6.06010150909424</v>
       </c>
       <c r="H89" t="n">
         <v>10522</v>
@@ -3037,7 +3037,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>6.01647472381592</v>
+        <v>6.01647520065308</v>
       </c>
       <c r="H92" t="n">
         <v>2375</v>
@@ -3066,7 +3066,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>6.01250791549683</v>
+        <v>6.01250839233398</v>
       </c>
       <c r="H93" t="n">
         <v>3115</v>
@@ -3153,7 +3153,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>6.16780424118042</v>
+        <v>6.16780376434326</v>
       </c>
       <c r="H96" t="n">
         <v>9366</v>
@@ -3182,7 +3182,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>6.01606893539429</v>
+        <v>6.0160698890686</v>
       </c>
       <c r="H97" t="n">
         <v>6096</v>
@@ -3211,7 +3211,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G98" t="n">
-        <v>6.10218954086304</v>
+        <v>6.10218906402588</v>
       </c>
       <c r="H98" t="n">
         <v>9952</v>
@@ -3240,7 +3240,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G99" t="n">
-        <v>6.10218954086304</v>
+        <v>6.10218906402588</v>
       </c>
       <c r="H99" t="n">
         <v>5592</v>
@@ -3269,7 +3269,7 @@
         <v>7.5</v>
       </c>
       <c r="G100" t="n">
-        <v>6.15140056610107</v>
+        <v>6.15140008926392</v>
       </c>
       <c r="H100" t="n">
         <v>18183</v>
@@ -3298,7 +3298,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>6.0365743637085</v>
+        <v>6.03657484054565</v>
       </c>
       <c r="H101" t="n">
         <v>2210</v>
@@ -3327,7 +3327,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>6.11039066314697</v>
+        <v>6.11039113998413</v>
       </c>
       <c r="H102" t="n">
         <v>3820</v>
@@ -3385,7 +3385,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>6.14319896697998</v>
+        <v>6.14319849014282</v>
       </c>
       <c r="H104" t="n">
         <v>1034</v>
@@ -3443,7 +3443,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G106" t="n">
-        <v>6.06118011474609</v>
+        <v>6.06117963790894</v>
       </c>
       <c r="H106" t="n">
         <v>2989</v>
@@ -3472,7 +3472,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.14319896697998</v>
+        <v>6.14319849014282</v>
       </c>
       <c r="H107" t="n">
         <v>3212</v>
@@ -3559,7 +3559,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>6.11039066314697</v>
+        <v>6.11039113998413</v>
       </c>
       <c r="H110" t="n">
         <v>4256</v>
@@ -3617,7 +3617,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>6.08168458938599</v>
+        <v>6.08168411254883</v>
       </c>
       <c r="H112" t="n">
         <v>4232</v>
@@ -3704,7 +3704,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>5.83972978591919</v>
+        <v>5.83972930908203</v>
       </c>
       <c r="H115" t="n">
         <v>8035</v>
@@ -3762,7 +3762,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>5.7577109336853</v>
+        <v>5.75771045684814</v>
       </c>
       <c r="H117" t="n">
         <v>4513</v>
@@ -3820,7 +3820,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.02837324142456</v>
+        <v>6.02837181091309</v>
       </c>
       <c r="H119" t="n">
         <v>6355</v>
@@ -3878,7 +3878,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G121" t="n">
-        <v>5.88894033432007</v>
+        <v>5.88894081115723</v>
       </c>
       <c r="H121" t="n">
         <v>4106</v>
@@ -3907,7 +3907,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="n">
-        <v>5.90534400939941</v>
+        <v>5.90534448623657</v>
       </c>
       <c r="H122" t="n">
         <v>2498</v>
@@ -3994,7 +3994,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>5.73310470581055</v>
+        <v>5.73310518264771</v>
       </c>
       <c r="H125" t="n">
         <v>12768</v>
@@ -4110,7 +4110,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G129" t="n">
-        <v>6.06528091430664</v>
+        <v>6.06528043746948</v>
       </c>
       <c r="H129" t="n">
         <v>10485</v>
@@ -4168,7 +4168,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>6.11039066314697</v>
+        <v>6.11039113998413</v>
       </c>
       <c r="H131" t="n">
         <v>8225</v>
@@ -4197,7 +4197,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>6.06118011474609</v>
+        <v>6.06117963790894</v>
       </c>
       <c r="H132" t="n">
         <v>8365</v>
@@ -4226,7 +4226,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G133" t="n">
-        <v>5.95865726470947</v>
+        <v>5.95865678787231</v>
       </c>
       <c r="H133" t="n">
         <v>8061</v>
@@ -4255,7 +4255,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G134" t="n">
-        <v>6.04477596282959</v>
+        <v>6.04477643966675</v>
       </c>
       <c r="H134" t="n">
         <v>7080</v>
@@ -4342,7 +4342,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G137" t="n">
-        <v>6.10218954086304</v>
+        <v>6.10218906402588</v>
       </c>
       <c r="H137" t="n">
         <v>5328</v>
@@ -4371,7 +4371,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="n">
-        <v>6.09808826446533</v>
+        <v>6.09808874130249</v>
       </c>
       <c r="H138" t="n">
         <v>4280</v>
@@ -4400,7 +4400,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="n">
-        <v>5.97505950927734</v>
+        <v>5.97506046295166</v>
       </c>
       <c r="H139" t="n">
         <v>5960</v>
@@ -4429,7 +4429,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>6.04067516326904</v>
+        <v>6.04067468643188</v>
       </c>
       <c r="H140" t="n">
         <v>1790</v>
@@ -4458,7 +4458,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G141" t="n">
-        <v>6.0365743637085</v>
+        <v>6.03657484054565</v>
       </c>
       <c r="H141" t="n">
         <v>8798</v>
@@ -4487,7 +4487,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>6.11859321594238</v>
+        <v>6.11859369277954</v>
       </c>
       <c r="H142" t="n">
         <v>7739</v>
@@ -4516,7 +4516,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.11039066314697</v>
+        <v>6.11039113998413</v>
       </c>
       <c r="H143" t="n">
         <v>4038</v>
@@ -4545,7 +4545,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>6.19240999221802</v>
+        <v>6.19241046905518</v>
       </c>
       <c r="H144" t="n">
         <v>9330</v>
@@ -4574,7 +4574,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>6.06528091430664</v>
+        <v>6.06528043746948</v>
       </c>
       <c r="H145" t="n">
         <v>15326</v>
@@ -4603,7 +4603,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>6.19240999221802</v>
+        <v>6.19241046905518</v>
       </c>
       <c r="H146" t="n">
         <v>11346</v>
@@ -4632,7 +4632,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>6.16780424118042</v>
+        <v>6.16780376434326</v>
       </c>
       <c r="H147" t="n">
         <v>746</v>
@@ -4661,7 +4661,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="n">
-        <v>6.07348299026489</v>
+        <v>6.07348346710205</v>
       </c>
       <c r="H148" t="n">
         <v>2066</v>
@@ -4690,7 +4690,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>6.09398746490479</v>
+        <v>6.09398698806763</v>
       </c>
       <c r="H149" t="n">
         <v>1010</v>
@@ -4719,7 +4719,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>6.09398746490479</v>
+        <v>6.09398698806763</v>
       </c>
       <c r="H150" t="n">
         <v>1823</v>
@@ -4748,7 +4748,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>6.11039066314697</v>
+        <v>6.11039113998413</v>
       </c>
       <c r="H151" t="n">
         <v>5646</v>
@@ -4806,7 +4806,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06118011474609</v>
+        <v>6.06117963790894</v>
       </c>
       <c r="H153" t="n">
         <v>807</v>
@@ -4835,7 +4835,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="n">
-        <v>6.02017116546631</v>
+        <v>6.02017068862915</v>
       </c>
       <c r="H154" t="n">
         <v>7365</v>
@@ -4893,7 +4893,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G156" t="n">
-        <v>6.10218954086304</v>
+        <v>6.10218906402588</v>
       </c>
       <c r="H156" t="n">
         <v>4573</v>
@@ -4922,7 +4922,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>6.08988618850708</v>
+        <v>6.0898871421814</v>
       </c>
       <c r="H157" t="n">
         <v>5151</v>
@@ -5038,7 +5038,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>6.02837324142456</v>
+        <v>6.02837181091309</v>
       </c>
       <c r="H161" t="n">
         <v>1288</v>
@@ -5183,7 +5183,7 @@
         <v>7.375</v>
       </c>
       <c r="G166" t="n">
-        <v>6.04887771606445</v>
+        <v>6.04887676239014</v>
       </c>
       <c r="H166" t="n">
         <v>882</v>
@@ -5212,7 +5212,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G167" t="n">
-        <v>6.0365743637085</v>
+        <v>6.03657484054565</v>
       </c>
       <c r="H167" t="n">
         <v>849</v>
@@ -5241,7 +5241,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>6.02017116546631</v>
+        <v>6.02017068862915</v>
       </c>
       <c r="H168" t="n">
         <v>1068</v>
@@ -5328,7 +5328,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="n">
-        <v>5.86843681335449</v>
+        <v>5.86843633651733</v>
       </c>
       <c r="H171" t="n">
         <v>4962</v>
@@ -5357,7 +5357,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>5.89714241027832</v>
+        <v>5.89714288711548</v>
       </c>
       <c r="H172" t="n">
         <v>4641</v>
@@ -5415,7 +5415,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>5.89714241027832</v>
+        <v>5.89714288711548</v>
       </c>
       <c r="H174" t="n">
         <v>7958</v>
@@ -5531,7 +5531,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G178" t="n">
-        <v>5.95865726470947</v>
+        <v>5.95865678787231</v>
       </c>
       <c r="H178" t="n">
         <v>2952</v>
@@ -5560,7 +5560,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G179" t="n">
-        <v>5.83152770996094</v>
+        <v>5.8315281867981</v>
       </c>
       <c r="H179" t="n">
         <v>3050</v>
@@ -5618,7 +5618,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G181" t="n">
-        <v>5.83972978591919</v>
+        <v>5.83972930908203</v>
       </c>
       <c r="H181" t="n">
         <v>20495</v>
@@ -5647,7 +5647,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>5.7700138092041</v>
+        <v>5.77001285552979</v>
       </c>
       <c r="H182" t="n">
         <v>11989</v>
@@ -5734,7 +5734,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>5.79461908340454</v>
+        <v>5.7946195602417</v>
       </c>
       <c r="H185" t="n">
         <v>3715</v>
@@ -5763,7 +5763,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>5.89714241027832</v>
+        <v>5.89714288711548</v>
       </c>
       <c r="H186" t="n">
         <v>1252</v>
@@ -5792,7 +5792,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>5.80282115936279</v>
+        <v>5.80282163619995</v>
       </c>
       <c r="H187" t="n">
         <v>5168</v>
@@ -5821,7 +5821,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>5.7043981552124</v>
+        <v>5.70439863204956</v>
       </c>
       <c r="H188" t="n">
         <v>5392</v>
@@ -5850,7 +5850,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G189" t="n">
-        <v>5.73310470581055</v>
+        <v>5.73310518264771</v>
       </c>
       <c r="H189" t="n">
         <v>9022</v>
@@ -5908,7 +5908,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G191" t="n">
-        <v>5.88073825836182</v>
+        <v>5.88073921203613</v>
       </c>
       <c r="H191" t="n">
         <v>4275</v>
@@ -5937,7 +5937,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G192" t="n">
-        <v>5.88894033432007</v>
+        <v>5.88894081115723</v>
       </c>
       <c r="H192" t="n">
         <v>3391</v>
@@ -5966,7 +5966,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G193" t="n">
-        <v>5.88073825836182</v>
+        <v>5.88073921203613</v>
       </c>
       <c r="H193" t="n">
         <v>10653</v>
@@ -5995,7 +5995,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>5.82332563400269</v>
+        <v>5.82332611083984</v>
       </c>
       <c r="H194" t="n">
         <v>5604</v>
@@ -6024,7 +6024,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G195" t="n">
-        <v>5.90534400939941</v>
+        <v>5.90534448623657</v>
       </c>
       <c r="H195" t="n">
         <v>7121</v>
@@ -6082,7 +6082,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G197" t="n">
-        <v>5.88894033432007</v>
+        <v>5.88894081115723</v>
       </c>
       <c r="H197" t="n">
         <v>3464</v>
@@ -6111,7 +6111,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>5.86433601379395</v>
+        <v>5.86433553695679</v>
       </c>
       <c r="H198" t="n">
         <v>6106</v>
@@ -6169,7 +6169,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.86843681335449</v>
+        <v>5.86843633651733</v>
       </c>
       <c r="H200" t="n">
         <v>3015</v>
@@ -6198,7 +6198,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>6.00376749038696</v>
+        <v>6.0037670135498</v>
       </c>
       <c r="H201" t="n">
         <v>21056</v>
@@ -6256,7 +6256,7 @@
         <v>7.5</v>
       </c>
       <c r="G203" t="n">
-        <v>6.15140056610107</v>
+        <v>6.15140008926392</v>
       </c>
       <c r="H203" t="n">
         <v>14456</v>
@@ -6314,7 +6314,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>6.38925457000732</v>
+        <v>6.38925409317017</v>
       </c>
       <c r="H205" t="n">
         <v>32065</v>
@@ -6343,7 +6343,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>6.38925457000732</v>
+        <v>6.38925409317017</v>
       </c>
       <c r="H206" t="n">
         <v>11451</v>
@@ -6430,7 +6430,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>6.39335536956787</v>
+        <v>6.39335632324219</v>
       </c>
       <c r="H209" t="n">
         <v>17471</v>
@@ -6459,7 +6459,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.2334189414978</v>
+        <v>6.23341941833496</v>
       </c>
       <c r="H210" t="n">
         <v>9985</v>
@@ -6575,7 +6575,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>6.34004354476929</v>
+        <v>6.34004402160645</v>
       </c>
       <c r="H214" t="n">
         <v>1022</v>
@@ -6662,7 +6662,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G217" t="n">
-        <v>6.27853012084961</v>
+        <v>6.27852964401245</v>
       </c>
       <c r="H217" t="n">
         <v>5404</v>
@@ -6720,7 +6720,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>6.34824466705322</v>
+        <v>6.34824514389038</v>
       </c>
       <c r="H219" t="n">
         <v>6244</v>
@@ -6778,7 +6778,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="n">
-        <v>6.44666814804077</v>
+        <v>6.44666719436646</v>
       </c>
       <c r="H221" t="n">
         <v>18783</v>
@@ -6865,7 +6865,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>6.27442789077759</v>
+        <v>6.2744288444519</v>
       </c>
       <c r="H224" t="n">
         <v>8878</v>
@@ -6894,7 +6894,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>6.3113374710083</v>
+        <v>6.31133651733398</v>
       </c>
       <c r="H225" t="n">
         <v>7717</v>
@@ -6923,7 +6923,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G226" t="n">
-        <v>6.24572134017944</v>
+        <v>6.2457218170166</v>
       </c>
       <c r="H226" t="n">
         <v>9776</v>
@@ -6981,7 +6981,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.24572134017944</v>
+        <v>6.2457218170166</v>
       </c>
       <c r="H228" t="n">
         <v>3286</v>
@@ -7010,7 +7010,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="n">
-        <v>6.12679481506348</v>
+        <v>6.12679433822632</v>
       </c>
       <c r="H229" t="n">
         <v>3730</v>
@@ -7039,7 +7039,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>6.00376749038696</v>
+        <v>6.0037670135498</v>
       </c>
       <c r="H230" t="n">
         <v>7010</v>
@@ -7097,7 +7097,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G232" t="n">
-        <v>5.91764783859253</v>
+        <v>5.91764736175537</v>
       </c>
       <c r="H232" t="n">
         <v>4877</v>
@@ -7126,7 +7126,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>5.95455598831177</v>
+        <v>5.95455551147461</v>
       </c>
       <c r="H233" t="n">
         <v>1206</v>
@@ -7155,7 +7155,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G234" t="n">
-        <v>5.89714241027832</v>
+        <v>5.89714288711548</v>
       </c>
       <c r="H234" t="n">
         <v>7102</v>
@@ -7184,7 +7184,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G235" t="n">
-        <v>5.89714241027832</v>
+        <v>5.89714288711548</v>
       </c>
       <c r="H235" t="n">
         <v>3806</v>
@@ -7271,7 +7271,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G238" t="n">
-        <v>5.91764783859253</v>
+        <v>5.91764736175537</v>
       </c>
       <c r="H238" t="n">
         <v>16751</v>
@@ -7300,7 +7300,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G239" t="n">
-        <v>6.06118011474609</v>
+        <v>6.06117963790894</v>
       </c>
       <c r="H239" t="n">
         <v>8774</v>
@@ -7329,7 +7329,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="n">
-        <v>6.12679481506348</v>
+        <v>6.12679433822632</v>
       </c>
       <c r="H240" t="n">
         <v>12769</v>
@@ -7387,7 +7387,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G242" t="n">
-        <v>6.01606893539429</v>
+        <v>6.0160698890686</v>
       </c>
       <c r="H242" t="n">
         <v>11574</v>
@@ -7416,7 +7416,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.2334189414978</v>
+        <v>6.23341941833496</v>
       </c>
       <c r="H243" t="n">
         <v>11302</v>
@@ -7445,7 +7445,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G244" t="n">
-        <v>6.26622581481934</v>
+        <v>6.26622676849365</v>
       </c>
       <c r="H244" t="n">
         <v>6222</v>
@@ -7561,7 +7561,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>6.35234642028809</v>
+        <v>6.35234594345093</v>
       </c>
       <c r="H248" t="n">
         <v>3898</v>
@@ -7590,7 +7590,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>6.11039066314697</v>
+        <v>6.11039113998413</v>
       </c>
       <c r="H249" t="n">
         <v>15379</v>
@@ -7648,7 +7648,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>6.24572134017944</v>
+        <v>6.2457218170166</v>
       </c>
       <c r="H251" t="n">
         <v>5513</v>
@@ -7677,7 +7677,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>6.2334189414978</v>
+        <v>6.23341941833496</v>
       </c>
       <c r="H252" t="n">
         <v>2645</v>
@@ -7735,7 +7735,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>6.18420791625977</v>
+        <v>6.18420839309692</v>
       </c>
       <c r="H254" t="n">
         <v>5007</v>
@@ -7793,7 +7793,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G256" t="n">
-        <v>6.14319896697998</v>
+        <v>6.14319849014282</v>
       </c>
       <c r="H256" t="n">
         <v>4428</v>
@@ -7822,7 +7822,7 @@
         <v>7.5</v>
       </c>
       <c r="G257" t="n">
-        <v>6.15140056610107</v>
+        <v>6.15140008926392</v>
       </c>
       <c r="H257" t="n">
         <v>2443</v>
@@ -7851,7 +7851,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>6.63531160354614</v>
+        <v>6.63531112670898</v>
       </c>
       <c r="H258" t="n">
         <v>51613</v>
@@ -7938,7 +7938,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>6.65991592407227</v>
+        <v>6.65991640090942</v>
       </c>
       <c r="H261" t="n">
         <v>43661</v>
@@ -8025,7 +8025,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.13562440872192</v>
+        <v>7.13562488555908</v>
       </c>
       <c r="H264" t="n">
         <v>126241</v>
@@ -8054,7 +8054,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>7.11101961135864</v>
+        <v>7.11101913452148</v>
       </c>
       <c r="H265" t="n">
         <v>51830</v>
@@ -8083,7 +8083,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>6.96748638153076</v>
+        <v>6.9674859046936</v>
       </c>
       <c r="H266" t="n">
         <v>47455</v>
@@ -8141,7 +8141,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>7.01259708404541</v>
+        <v>7.01259613037109</v>
       </c>
       <c r="H268" t="n">
         <v>56698</v>
@@ -8170,7 +8170,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G269" t="n">
-        <v>6.95518255233765</v>
+        <v>6.95518350601196</v>
       </c>
       <c r="H269" t="n">
         <v>7078</v>
@@ -8286,7 +8286,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="n">
-        <v>6.92237567901611</v>
+        <v>6.92237663269043</v>
       </c>
       <c r="H273" t="n">
         <v>17128</v>
@@ -8315,7 +8315,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>7.13972473144531</v>
+        <v>7.13972520828247</v>
       </c>
       <c r="H274" t="n">
         <v>77645</v>
@@ -8373,7 +8373,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="n">
-        <v>7.56212186813354</v>
+        <v>7.5621223449707</v>
       </c>
       <c r="H276" t="n">
         <v>139236</v>
@@ -8402,7 +8402,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>7.52521419525146</v>
+        <v>7.52521276473999</v>
       </c>
       <c r="H277" t="n">
         <v>55028</v>
@@ -8431,7 +8431,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>7.02079916000366</v>
+        <v>7.02079963684082</v>
       </c>
       <c r="H278" t="n">
         <v>79509</v>
@@ -8460,7 +8460,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G279" t="n">
-        <v>7.23404741287231</v>
+        <v>7.234046459198</v>
       </c>
       <c r="H279" t="n">
         <v>97867</v>
@@ -8489,7 +8489,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="n">
-        <v>7.37347888946533</v>
+        <v>7.37347841262817</v>
       </c>
       <c r="H280" t="n">
         <v>55388</v>
@@ -8547,7 +8547,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>7.41859006881714</v>
+        <v>7.41858959197998</v>
       </c>
       <c r="H282" t="n">
         <v>10033</v>
@@ -8576,7 +8576,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G283" t="n">
-        <v>7.36527681350708</v>
+        <v>7.36527729034424</v>
       </c>
       <c r="H283" t="n">
         <v>23811</v>
@@ -8605,7 +8605,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>7.20944166183472</v>
+        <v>7.20944118499756</v>
       </c>
       <c r="H284" t="n">
         <v>23541</v>
@@ -8663,7 +8663,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>7.03720235824585</v>
+        <v>7.03720188140869</v>
       </c>
       <c r="H286" t="n">
         <v>24337</v>
@@ -8692,7 +8692,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="n">
-        <v>6.87726593017578</v>
+        <v>6.8772668838501</v>
       </c>
       <c r="H287" t="n">
         <v>21485</v>
@@ -8721,7 +8721,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G288" t="n">
-        <v>7.00439453125</v>
+        <v>7.00439500808716</v>
       </c>
       <c r="H288" t="n">
         <v>13600</v>
@@ -8750,7 +8750,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="n">
-        <v>6.9920916557312</v>
+        <v>6.99209117889404</v>
       </c>
       <c r="H289" t="n">
         <v>10573</v>
@@ -8779,7 +8779,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>6.97568845748901</v>
+        <v>6.97568893432617</v>
       </c>
       <c r="H290" t="n">
         <v>11281</v>
@@ -8895,7 +8895,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>6.88956832885742</v>
+        <v>6.88956785202026</v>
       </c>
       <c r="H294" t="n">
         <v>19796</v>
@@ -8924,7 +8924,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G295" t="n">
-        <v>6.95518255233765</v>
+        <v>6.95518350601196</v>
       </c>
       <c r="H295" t="n">
         <v>18670</v>
@@ -8982,7 +8982,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G297" t="n">
-        <v>6.82395362854004</v>
+        <v>6.82395315170288</v>
       </c>
       <c r="H297" t="n">
         <v>10249</v>
@@ -9069,7 +9069,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="n">
-        <v>7.02079916000366</v>
+        <v>7.02079963684082</v>
       </c>
       <c r="H300" t="n">
         <v>20217</v>
@@ -9098,7 +9098,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>7.13972473144531</v>
+        <v>7.13972520828247</v>
       </c>
       <c r="H301" t="n">
         <v>14332</v>
@@ -9127,7 +9127,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="n">
-        <v>7.16022920608521</v>
+        <v>7.16022968292236</v>
       </c>
       <c r="H302" t="n">
         <v>6618</v>
@@ -9185,7 +9185,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G304" t="n">
-        <v>7.47189998626709</v>
+        <v>7.47190046310425</v>
       </c>
       <c r="H304" t="n">
         <v>95016</v>
@@ -9272,7 +9272,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>7.61953496932983</v>
+        <v>7.61953544616699</v>
       </c>
       <c r="H307" t="n">
         <v>73956</v>
@@ -9301,7 +9301,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="n">
-        <v>7.58672714233398</v>
+        <v>7.58672666549683</v>
       </c>
       <c r="H308" t="n">
         <v>37427</v>
@@ -9330,7 +9330,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="n">
-        <v>7.56212186813354</v>
+        <v>7.5621223449707</v>
       </c>
       <c r="H309" t="n">
         <v>16643</v>
@@ -9359,7 +9359,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>7.82868242263794</v>
+        <v>7.8286828994751</v>
       </c>
       <c r="H310" t="n">
         <v>139701</v>
@@ -9388,7 +9388,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="n">
-        <v>7.93120527267456</v>
+        <v>7.93120622634888</v>
       </c>
       <c r="H311" t="n">
         <v>78649</v>
@@ -9417,7 +9417,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.95580959320068</v>
+        <v>7.955810546875</v>
       </c>
       <c r="H312" t="n">
         <v>35399</v>
@@ -9504,7 +9504,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G315" t="n">
-        <v>7.95580959320068</v>
+        <v>7.955810546875</v>
       </c>
       <c r="H315" t="n">
         <v>45610</v>
@@ -9533,7 +9533,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.18136215209961</v>
+        <v>8.18136310577393</v>
       </c>
       <c r="H316" t="n">
         <v>111521</v>
@@ -9591,7 +9591,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G318" t="n">
-        <v>8.17726230621338</v>
+        <v>8.17726135253906</v>
       </c>
       <c r="H318" t="n">
         <v>42597</v>
@@ -9620,7 +9620,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="n">
-        <v>8.40691471099854</v>
+        <v>8.4069128036499</v>
       </c>
       <c r="H319" t="n">
         <v>93588</v>
@@ -9649,7 +9649,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G320" t="n">
-        <v>8.41511631011963</v>
+        <v>8.41511726379395</v>
       </c>
       <c r="H320" t="n">
         <v>90665</v>
@@ -9678,7 +9678,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>8.28388500213623</v>
+        <v>8.28388595581055</v>
       </c>
       <c r="H321" t="n">
         <v>66369</v>
@@ -9707,7 +9707,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G322" t="n">
-        <v>8.28388500213623</v>
+        <v>8.28388595581055</v>
       </c>
       <c r="H322" t="n">
         <v>34683</v>
@@ -9736,7 +9736,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31669330596924</v>
+        <v>8.31669235229492</v>
       </c>
       <c r="H323" t="n">
         <v>44200</v>
@@ -9765,7 +9765,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="n">
-        <v>8.35770225524902</v>
+        <v>8.35770130157471</v>
       </c>
       <c r="H324" t="n">
         <v>36091</v>
@@ -9794,7 +9794,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G325" t="n">
-        <v>8.54634666442871</v>
+        <v>8.54634571075439</v>
       </c>
       <c r="H325" t="n">
         <v>81233</v>
@@ -9939,7 +9939,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G330" t="n">
-        <v>8.18136215209961</v>
+        <v>8.18136310577393</v>
       </c>
       <c r="H330" t="n">
         <v>36838</v>
@@ -9968,7 +9968,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>7.96401405334473</v>
+        <v>7.96401309967041</v>
       </c>
       <c r="H331" t="n">
         <v>48657</v>
@@ -9997,7 +9997,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>7.69335126876831</v>
+        <v>7.69335174560547</v>
       </c>
       <c r="H332" t="n">
         <v>104870</v>
@@ -10026,7 +10026,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="n">
-        <v>7.88609552383423</v>
+        <v>7.88609504699707</v>
       </c>
       <c r="H333" t="n">
         <v>27574</v>
@@ -10084,7 +10084,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="n">
-        <v>8.09934425354004</v>
+        <v>8.09934520721436</v>
       </c>
       <c r="H335" t="n">
         <v>54990</v>
@@ -10113,7 +10113,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.35770225524902</v>
+        <v>8.35770130157471</v>
       </c>
       <c r="H336" t="n">
         <v>67504</v>
@@ -10142,7 +10142,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="n">
-        <v>8.4315185546875</v>
+        <v>8.43151950836182</v>
       </c>
       <c r="H337" t="n">
         <v>42001</v>
@@ -10171,7 +10171,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="n">
-        <v>8.52174091339111</v>
+        <v>8.5217399597168</v>
       </c>
       <c r="H338" t="n">
         <v>29816</v>
@@ -10229,7 +10229,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G340" t="n">
-        <v>8.77599906921387</v>
+        <v>8.77599716186523</v>
       </c>
       <c r="H340" t="n">
         <v>46403</v>
@@ -10316,7 +10316,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G343" t="n">
-        <v>9.98987483978271</v>
+        <v>9.9898738861084</v>
       </c>
       <c r="H343" t="n">
         <v>281011</v>
@@ -10403,7 +10403,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="n">
-        <v>10.5886096954346</v>
+        <v>10.5886116027832</v>
       </c>
       <c r="H346" t="n">
         <v>290568</v>
@@ -10490,7 +10490,7 @@
         <v>12.5</v>
       </c>
       <c r="G349" t="n">
-        <v>10.2523345947266</v>
+        <v>10.2523355484009</v>
       </c>
       <c r="H349" t="n">
         <v>134551</v>
@@ -10606,7 +10606,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="n">
-        <v>9.96661281585693</v>
+        <v>9.96661376953125</v>
       </c>
       <c r="H353" t="n">
         <v>104210</v>
@@ -10664,7 +10664,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>9.95820999145508</v>
+        <v>9.95821094512939</v>
       </c>
       <c r="H355" t="n">
         <v>32988</v>
@@ -10809,7 +10809,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G360" t="n">
-        <v>9.98341846466064</v>
+        <v>9.98341941833496</v>
       </c>
       <c r="H360" t="n">
         <v>31633</v>
@@ -10838,7 +10838,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G361" t="n">
-        <v>10.2859497070312</v>
+        <v>10.2859487533569</v>
       </c>
       <c r="H361" t="n">
         <v>80781</v>
@@ -10925,7 +10925,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5128440856934</v>
+        <v>10.512843132019</v>
       </c>
       <c r="H364" t="n">
         <v>8757</v>
@@ -10954,7 +10954,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>10.3783884048462</v>
+        <v>10.3783864974976</v>
       </c>
       <c r="H365" t="n">
         <v>51404</v>
@@ -10983,7 +10983,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>10.2523345947266</v>
+        <v>10.2523336410522</v>
       </c>
       <c r="H366" t="n">
         <v>49988</v>
@@ -11012,7 +11012,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G367" t="n">
-        <v>10.622091293335</v>
+        <v>10.6220903396606</v>
       </c>
       <c r="H367" t="n">
         <v>61373</v>
@@ -11041,7 +11041,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>10.5464582443237</v>
+        <v>10.546459197998</v>
       </c>
       <c r="H368" t="n">
         <v>70379</v>
@@ -11070,7 +11070,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G369" t="n">
-        <v>10.5296506881714</v>
+        <v>10.5296516418457</v>
       </c>
       <c r="H369" t="n">
         <v>63299</v>
@@ -11157,7 +11157,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G372" t="n">
-        <v>10.2607364654541</v>
+        <v>10.2607383728027</v>
       </c>
       <c r="H372" t="n">
         <v>24251</v>
@@ -11215,7 +11215,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G374" t="n">
-        <v>10.176700592041</v>
+        <v>10.1767015457153</v>
       </c>
       <c r="H374" t="n">
         <v>47550</v>
@@ -11302,7 +11302,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G377" t="n">
-        <v>9.94980621337891</v>
+        <v>9.94980525970459</v>
       </c>
       <c r="H377" t="n">
         <v>23752</v>
@@ -11360,7 +11360,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G379" t="n">
-        <v>9.73971748352051</v>
+        <v>9.73971843719482</v>
       </c>
       <c r="H379" t="n">
         <v>26775</v>
@@ -11389,7 +11389,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G380" t="n">
-        <v>9.68929576873779</v>
+        <v>9.68929481506348</v>
       </c>
       <c r="H380" t="n">
         <v>13208</v>
@@ -11476,7 +11476,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>9.01701164245605</v>
+        <v>9.01701068878174</v>
       </c>
       <c r="H383" t="n">
         <v>47989</v>
@@ -11505,7 +11505,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>9.07583618164062</v>
+        <v>9.07583522796631</v>
       </c>
       <c r="H384" t="n">
         <v>29565</v>
@@ -11534,7 +11534,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>9.09264373779297</v>
+        <v>9.09264469146729</v>
       </c>
       <c r="H385" t="n">
         <v>45758</v>
@@ -11563,7 +11563,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G386" t="n">
-        <v>9.109450340271</v>
+        <v>9.10945129394531</v>
       </c>
       <c r="H386" t="n">
         <v>22670</v>
@@ -11592,7 +11592,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G387" t="n">
-        <v>9.15146923065186</v>
+        <v>9.15146827697754</v>
       </c>
       <c r="H387" t="n">
         <v>13336</v>
@@ -11621,7 +11621,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>9.07583618164062</v>
+        <v>9.07583522796631</v>
       </c>
       <c r="H388" t="n">
         <v>11440</v>
@@ -11650,7 +11650,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>9.07583618164062</v>
+        <v>9.07583522796631</v>
       </c>
       <c r="H389" t="n">
         <v>13343</v>
@@ -11679,7 +11679,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G390" t="n">
-        <v>9.14306545257568</v>
+        <v>9.14306449890137</v>
       </c>
       <c r="H390" t="n">
         <v>13080</v>
@@ -11708,7 +11708,7 @@
         <v>11</v>
       </c>
       <c r="G391" t="n">
-        <v>9.24390888214111</v>
+        <v>9.2439079284668</v>
       </c>
       <c r="H391" t="n">
         <v>7347</v>
@@ -11737,7 +11737,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G392" t="n">
-        <v>9.12625694274902</v>
+        <v>9.12625885009766</v>
       </c>
       <c r="H392" t="n">
         <v>28124</v>
@@ -11766,7 +11766,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>9.28592586517334</v>
+        <v>9.28592681884766</v>
       </c>
       <c r="H393" t="n">
         <v>25434</v>
@@ -11795,7 +11795,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G394" t="n">
-        <v>9.59685611724854</v>
+        <v>9.59685707092285</v>
       </c>
       <c r="H394" t="n">
         <v>57253</v>
@@ -11824,7 +11824,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>10.000226020813</v>
+        <v>10.0002269744873</v>
       </c>
       <c r="H395" t="n">
         <v>98734</v>
@@ -11853,7 +11853,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G396" t="n">
-        <v>9.94140148162842</v>
+        <v>9.94140243530273</v>
       </c>
       <c r="H396" t="n">
         <v>51764</v>
@@ -11882,7 +11882,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>9.94980621337891</v>
+        <v>9.94980525970459</v>
       </c>
       <c r="H397" t="n">
         <v>27782</v>
@@ -11911,7 +11911,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G398" t="n">
-        <v>9.80694580078125</v>
+        <v>9.80694484710693</v>
       </c>
       <c r="H398" t="n">
         <v>16471</v>
@@ -12056,7 +12056,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G403" t="n">
-        <v>10.1851062774658</v>
+        <v>10.1851072311401</v>
       </c>
       <c r="H403" t="n">
         <v>30833</v>
@@ -12143,7 +12143,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>10.1851062774658</v>
+        <v>10.1851072311401</v>
       </c>
       <c r="H406" t="n">
         <v>8292</v>
@@ -12201,7 +12201,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>10.2523345947266</v>
+        <v>10.2523336410522</v>
       </c>
       <c r="H408" t="n">
         <v>33860</v>
@@ -12230,7 +12230,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G409" t="n">
-        <v>9.98341846466064</v>
+        <v>9.98341941833496</v>
       </c>
       <c r="H409" t="n">
         <v>86615</v>
@@ -12288,7 +12288,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G411" t="n">
-        <v>10.2607364654541</v>
+        <v>10.2607383728027</v>
       </c>
       <c r="H411" t="n">
         <v>33503</v>
@@ -12375,7 +12375,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G414" t="n">
-        <v>9.80694580078125</v>
+        <v>9.80694484710693</v>
       </c>
       <c r="H414" t="n">
         <v>28666</v>
@@ -12404,7 +12404,7 @@
         <v>11.75</v>
       </c>
       <c r="G415" t="n">
-        <v>9.87417507171631</v>
+        <v>9.87417411804199</v>
       </c>
       <c r="H415" t="n">
         <v>9174</v>
@@ -12433,7 +12433,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>10.000226020813</v>
+        <v>10.0002269744873</v>
       </c>
       <c r="H416" t="n">
         <v>51293</v>
@@ -12491,7 +12491,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G418" t="n">
-        <v>9.98341846466064</v>
+        <v>9.98341941833496</v>
       </c>
       <c r="H418" t="n">
         <v>10391</v>
@@ -12549,7 +12549,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>9.76492786407471</v>
+        <v>9.76492691040039</v>
       </c>
       <c r="H420" t="n">
         <v>93670</v>
@@ -12578,7 +12578,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>9.65568161010742</v>
+        <v>9.65568256378174</v>
       </c>
       <c r="H421" t="n">
         <v>13957</v>
@@ -12665,7 +12665,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>9.36995983123779</v>
+        <v>9.36996078491211</v>
       </c>
       <c r="H424" t="n">
         <v>16879</v>
@@ -12723,7 +12723,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G426" t="n">
-        <v>9.47920799255371</v>
+        <v>9.47920703887939</v>
       </c>
       <c r="H426" t="n">
         <v>29868</v>
@@ -12752,7 +12752,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G427" t="n">
-        <v>9.68929576873779</v>
+        <v>9.68929481506348</v>
       </c>
       <c r="H427" t="n">
         <v>56964</v>
@@ -12839,7 +12839,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G430" t="n">
-        <v>9.41197872161865</v>
+        <v>9.41197776794434</v>
       </c>
       <c r="H430" t="n">
         <v>14887</v>
@@ -12868,7 +12868,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G431" t="n">
-        <v>9.30273151397705</v>
+        <v>9.30273246765137</v>
       </c>
       <c r="H431" t="n">
         <v>27038</v>
@@ -12955,7 +12955,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G434" t="n">
-        <v>9.29432964324951</v>
+        <v>9.2943286895752</v>
       </c>
       <c r="H434" t="n">
         <v>17130</v>
@@ -13071,7 +13071,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G438" t="n">
-        <v>9.28592586517334</v>
+        <v>9.28592681884766</v>
       </c>
       <c r="H438" t="n">
         <v>19181</v>
@@ -13100,7 +13100,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G439" t="n">
-        <v>9.29432964324951</v>
+        <v>9.2943286895752</v>
       </c>
       <c r="H439" t="n">
         <v>23798</v>
@@ -13158,7 +13158,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G441" t="n">
-        <v>9.15146923065186</v>
+        <v>9.15146827697754</v>
       </c>
       <c r="H441" t="n">
         <v>23957</v>
@@ -13187,7 +13187,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G442" t="n">
-        <v>9.14306545257568</v>
+        <v>9.14306449890137</v>
       </c>
       <c r="H442" t="n">
         <v>56964</v>
@@ -13216,7 +13216,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>9.11785507202148</v>
+        <v>9.11785221099854</v>
       </c>
       <c r="H443" t="n">
         <v>36814</v>
@@ -13245,7 +13245,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G444" t="n">
-        <v>9.15146923065186</v>
+        <v>9.15146827697754</v>
       </c>
       <c r="H444" t="n">
         <v>43068</v>
@@ -13274,7 +13274,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G445" t="n">
-        <v>9.49601459503174</v>
+        <v>9.49601554870605</v>
       </c>
       <c r="H445" t="n">
         <v>89873</v>
@@ -13303,7 +13303,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G446" t="n">
-        <v>9.80694580078125</v>
+        <v>9.80694484710693</v>
       </c>
       <c r="H446" t="n">
         <v>64936</v>
@@ -13361,7 +13361,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G448" t="n">
-        <v>9.40357398986816</v>
+        <v>9.40357494354248</v>
       </c>
       <c r="H448" t="n">
         <v>50728</v>
@@ -13390,7 +13390,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>9.98341846466064</v>
+        <v>9.98341941833496</v>
       </c>
       <c r="H449" t="n">
         <v>75515</v>
@@ -13448,7 +13448,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G451" t="n">
-        <v>9.58845329284668</v>
+        <v>9.58845233917236</v>
       </c>
       <c r="H451" t="n">
         <v>48735</v>
@@ -13477,7 +13477,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G452" t="n">
-        <v>9.59685611724854</v>
+        <v>9.59685707092285</v>
       </c>
       <c r="H452" t="n">
         <v>23759</v>
@@ -13564,7 +13564,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G455" t="n">
-        <v>9.47920799255371</v>
+        <v>9.47920703887939</v>
       </c>
       <c r="H455" t="n">
         <v>11060</v>
@@ -13622,7 +13622,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G457" t="n">
-        <v>9.54643535614014</v>
+        <v>9.5464334487915</v>
       </c>
       <c r="H457" t="n">
         <v>24620</v>
@@ -13651,7 +13651,7 @@
         <v>11.5</v>
       </c>
       <c r="G458" t="n">
-        <v>9.66408538818359</v>
+        <v>9.66408443450928</v>
       </c>
       <c r="H458" t="n">
         <v>15175</v>
@@ -13680,7 +13680,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G459" t="n">
-        <v>9.73131465911865</v>
+        <v>9.73131275177002</v>
       </c>
       <c r="H459" t="n">
         <v>34529</v>
@@ -13709,7 +13709,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G460" t="n">
-        <v>9.68089294433594</v>
+        <v>9.68089199066162</v>
       </c>
       <c r="H460" t="n">
         <v>23454</v>
@@ -13738,7 +13738,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G461" t="n">
-        <v>9.70610237121582</v>
+        <v>9.70610332489014</v>
       </c>
       <c r="H461" t="n">
         <v>24965</v>
@@ -13767,7 +13767,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G462" t="n">
-        <v>9.60526084899902</v>
+        <v>9.60526180267334</v>
       </c>
       <c r="H462" t="n">
         <v>27373</v>
@@ -13796,7 +13796,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G463" t="n">
-        <v>9.58004856109619</v>
+        <v>9.58004951477051</v>
       </c>
       <c r="H463" t="n">
         <v>16378</v>
@@ -13825,7 +13825,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>9.53803253173828</v>
+        <v>9.5380334854126</v>
       </c>
       <c r="H464" t="n">
         <v>12097</v>
@@ -13854,7 +13854,7 @@
         <v>11.5</v>
       </c>
       <c r="G465" t="n">
-        <v>9.66408538818359</v>
+        <v>9.66408443450928</v>
       </c>
       <c r="H465" t="n">
         <v>9251</v>
@@ -13883,7 +13883,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>9.65568161010742</v>
+        <v>9.65568256378174</v>
       </c>
       <c r="H466" t="n">
         <v>21523</v>
@@ -13999,7 +13999,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G470" t="n">
-        <v>9.68089294433594</v>
+        <v>9.68089199066162</v>
       </c>
       <c r="H470" t="n">
         <v>18751</v>
@@ -14057,7 +14057,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G472" t="n">
-        <v>9.68929576873779</v>
+        <v>9.68929481506348</v>
       </c>
       <c r="H472" t="n">
         <v>19120</v>
@@ -14144,7 +14144,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G475" t="n">
-        <v>9.59685611724854</v>
+        <v>9.59685707092285</v>
       </c>
       <c r="H475" t="n">
         <v>26741</v>
@@ -14173,7 +14173,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.38676738739014</v>
+        <v>9.38676929473877</v>
       </c>
       <c r="H476" t="n">
         <v>165152</v>
@@ -14202,7 +14202,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G477" t="n">
-        <v>9.05062770843506</v>
+        <v>9.05062675476074</v>
       </c>
       <c r="H477" t="n">
         <v>70334</v>
@@ -14231,7 +14231,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G478" t="n">
-        <v>8.91616821289062</v>
+        <v>8.91616916656494</v>
       </c>
       <c r="H478" t="n">
         <v>64290</v>
@@ -14260,7 +14260,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G479" t="n">
-        <v>8.63885116577148</v>
+        <v>8.6388521194458</v>
       </c>
       <c r="H479" t="n">
         <v>69951</v>
@@ -14347,7 +14347,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G482" t="n">
-        <v>8.24808692932129</v>
+        <v>8.24808502197266</v>
       </c>
       <c r="H482" t="n">
         <v>70346</v>
@@ -14376,7 +14376,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G483" t="n">
-        <v>8.02539253234863</v>
+        <v>8.02539157867432</v>
       </c>
       <c r="H483" t="n">
         <v>50200</v>
@@ -14434,7 +14434,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G485" t="n">
-        <v>8.54641151428223</v>
+        <v>8.54641246795654</v>
       </c>
       <c r="H485" t="n">
         <v>123545</v>
@@ -14463,7 +14463,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G486" t="n">
-        <v>8.25228786468506</v>
+        <v>8.25228881835938</v>
       </c>
       <c r="H486" t="n">
         <v>64724</v>
@@ -14550,7 +14550,7 @@
         <v>9.75</v>
       </c>
       <c r="G489" t="n">
-        <v>8.1934642791748</v>
+        <v>8.19346523284912</v>
       </c>
       <c r="H489" t="n">
         <v>20004</v>
@@ -14608,7 +14608,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G491" t="n">
-        <v>8.23548126220703</v>
+        <v>8.23548221588135</v>
       </c>
       <c r="H491" t="n">
         <v>29388</v>
@@ -14637,7 +14637,7 @@
         <v>9.77499961853027</v>
       </c>
       <c r="G492" t="n">
-        <v>8.21447277069092</v>
+        <v>8.21447372436523</v>
       </c>
       <c r="H492" t="n">
         <v>19915</v>
@@ -14724,7 +14724,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>7.77748870849609</v>
+        <v>7.77748727798462</v>
       </c>
       <c r="H495" t="n">
         <v>62230</v>
@@ -14753,7 +14753,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G496" t="n">
-        <v>7.75227737426758</v>
+        <v>7.75227689743042</v>
       </c>
       <c r="H496" t="n">
         <v>52807</v>
@@ -14782,7 +14782,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G497" t="n">
-        <v>7.72706747055054</v>
+        <v>7.72706699371338</v>
       </c>
       <c r="H497" t="n">
         <v>22105</v>
@@ -14811,7 +14811,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>7.83631324768066</v>
+        <v>7.83631229400635</v>
       </c>
       <c r="H498" t="n">
         <v>17635</v>
@@ -14840,7 +14840,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>7.78168964385986</v>
+        <v>7.78169012069702</v>
       </c>
       <c r="H499" t="n">
         <v>29556</v>
@@ -14956,7 +14956,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G503" t="n">
-        <v>7.93715524673462</v>
+        <v>7.93715572357178</v>
       </c>
       <c r="H503" t="n">
         <v>18957</v>
@@ -14985,7 +14985,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G504" t="n">
-        <v>8.17665767669678</v>
+        <v>8.17665576934814</v>
       </c>
       <c r="H504" t="n">
         <v>29105</v>
@@ -15014,7 +15014,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G505" t="n">
-        <v>8.17665767669678</v>
+        <v>8.17665576934814</v>
       </c>
       <c r="H505" t="n">
         <v>20550</v>
@@ -15043,7 +15043,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G506" t="n">
-        <v>8.0842170715332</v>
+        <v>8.08421802520752</v>
       </c>
       <c r="H506" t="n">
         <v>22545</v>
@@ -15072,7 +15072,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G507" t="n">
-        <v>8.07161235809326</v>
+        <v>8.07161140441895</v>
       </c>
       <c r="H507" t="n">
         <v>9767</v>
@@ -15101,7 +15101,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G508" t="n">
-        <v>7.97497034072876</v>
+        <v>7.97497129440308</v>
       </c>
       <c r="H508" t="n">
         <v>26975</v>
@@ -15130,7 +15130,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G509" t="n">
-        <v>8.00438404083252</v>
+        <v>8.0043830871582</v>
       </c>
       <c r="H509" t="n">
         <v>18510</v>
@@ -15217,7 +15217,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G512" t="n">
-        <v>8.14724349975586</v>
+        <v>8.14724445343018</v>
       </c>
       <c r="H512" t="n">
         <v>19344</v>
@@ -15246,7 +15246,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G513" t="n">
-        <v>8.21027088165283</v>
+        <v>8.21027183532715</v>
       </c>
       <c r="H513" t="n">
         <v>15975</v>
@@ -15275,7 +15275,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G514" t="n">
-        <v>8.34472751617432</v>
+        <v>8.34472846984863</v>
       </c>
       <c r="H514" t="n">
         <v>62794</v>
@@ -15391,7 +15391,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G518" t="n">
-        <v>8.47078132629395</v>
+        <v>8.47078037261963</v>
       </c>
       <c r="H518" t="n">
         <v>71165</v>
@@ -15449,7 +15449,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>8.47078132629395</v>
+        <v>8.47078037261963</v>
       </c>
       <c r="H520" t="n">
         <v>22750</v>
@@ -15478,7 +15478,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G521" t="n">
-        <v>8.42036056518555</v>
+        <v>8.42035961151123</v>
       </c>
       <c r="H521" t="n">
         <v>14921</v>
@@ -15536,7 +15536,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G523" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439453125</v>
       </c>
       <c r="H523" t="n">
         <v>29785</v>
@@ -15565,7 +15565,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G524" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439453125</v>
       </c>
       <c r="H524" t="n">
         <v>24349</v>
@@ -15652,7 +15652,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G527" t="n">
-        <v>8.378342628479</v>
+        <v>8.37834167480469</v>
       </c>
       <c r="H527" t="n">
         <v>16588</v>
@@ -15681,7 +15681,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>8.32792091369629</v>
+        <v>8.32791996002197</v>
       </c>
       <c r="H528" t="n">
         <v>19483</v>
@@ -15739,7 +15739,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G530" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439453125</v>
       </c>
       <c r="H530" t="n">
         <v>45441</v>
@@ -15797,7 +15797,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>8.23548126220703</v>
+        <v>8.23548221588135</v>
       </c>
       <c r="H532" t="n">
         <v>34259</v>
@@ -15826,7 +15826,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>8.23548126220703</v>
+        <v>8.23548221588135</v>
       </c>
       <c r="H533" t="n">
         <v>29706</v>
@@ -15855,7 +15855,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G534" t="n">
-        <v>8.12623500823975</v>
+        <v>8.12623596191406</v>
       </c>
       <c r="H534" t="n">
         <v>20972</v>
@@ -15884,7 +15884,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>7.94135761260986</v>
+        <v>7.94135665893555</v>
       </c>
       <c r="H535" t="n">
         <v>30884</v>
@@ -15913,7 +15913,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>7.91614627838135</v>
+        <v>7.91614723205566</v>
       </c>
       <c r="H536" t="n">
         <v>28059</v>
@@ -15942,7 +15942,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>7.84051513671875</v>
+        <v>7.84051418304443</v>
       </c>
       <c r="H537" t="n">
         <v>58718</v>
@@ -16029,7 +16029,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G540" t="n">
-        <v>7.89933967590332</v>
+        <v>7.89933919906616</v>
       </c>
       <c r="H540" t="n">
         <v>43424</v>
@@ -16058,7 +16058,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G541" t="n">
-        <v>8.24388599395752</v>
+        <v>8.24388408660889</v>
       </c>
       <c r="H541" t="n">
         <v>43847</v>
@@ -16087,7 +16087,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G542" t="n">
-        <v>8.47078132629395</v>
+        <v>8.47078037261963</v>
       </c>
       <c r="H542" t="n">
         <v>64708</v>
@@ -16116,7 +16116,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>8.42036056518555</v>
+        <v>8.42035961151123</v>
       </c>
       <c r="H543" t="n">
         <v>36223</v>
@@ -16145,7 +16145,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G544" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439453125</v>
       </c>
       <c r="H544" t="n">
         <v>17457</v>
@@ -16174,7 +16174,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G545" t="n">
-        <v>8.50439548492432</v>
+        <v>8.50439453125</v>
       </c>
       <c r="H545" t="n">
         <v>28115</v>
@@ -16232,7 +16232,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G547" t="n">
-        <v>8.63885116577148</v>
+        <v>8.6388521194458</v>
       </c>
       <c r="H547" t="n">
         <v>24904</v>
@@ -16261,7 +16261,7 @@
         <v>10.5</v>
       </c>
       <c r="G548" t="n">
-        <v>8.82373046875</v>
+        <v>8.82373142242432</v>
       </c>
       <c r="H548" t="n">
         <v>57011</v>
@@ -16290,7 +16290,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G549" t="n">
-        <v>8.67246627807617</v>
+        <v>8.67246532440186</v>
       </c>
       <c r="H549" t="n">
         <v>39043</v>
@@ -16319,7 +16319,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>8.7396936416626</v>
+        <v>8.73969459533691</v>
       </c>
       <c r="H550" t="n">
         <v>29306</v>
@@ -16348,7 +16348,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G551" t="n">
-        <v>8.68927383422852</v>
+        <v>8.68927478790283</v>
       </c>
       <c r="H551" t="n">
         <v>64518</v>
@@ -16493,7 +16493,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G556" t="n">
-        <v>8.75650215148926</v>
+        <v>8.75650119781494</v>
       </c>
       <c r="H556" t="n">
         <v>33392</v>
@@ -16522,7 +16522,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G557" t="n">
-        <v>8.85734462738037</v>
+        <v>8.85734367370605</v>
       </c>
       <c r="H557" t="n">
         <v>32134</v>
@@ -16551,7 +16551,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G558" t="n">
-        <v>9.27752304077148</v>
+        <v>9.27752208709717</v>
       </c>
       <c r="H558" t="n">
         <v>137910</v>
@@ -16580,7 +16580,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G559" t="n">
-        <v>9.41197872161865</v>
+        <v>9.41197776794434</v>
       </c>
       <c r="H559" t="n">
         <v>393902</v>
@@ -16609,7 +16609,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>9.07583618164062</v>
+        <v>9.07583522796631</v>
       </c>
       <c r="H560" t="n">
         <v>338893</v>
@@ -16667,7 +16667,7 @@
         <v>11</v>
       </c>
       <c r="G562" t="n">
-        <v>9.24390888214111</v>
+        <v>9.2439079284668</v>
       </c>
       <c r="H562" t="n">
         <v>104789</v>
@@ -16696,7 +16696,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G563" t="n">
-        <v>9.109450340271</v>
+        <v>9.10945129394531</v>
       </c>
       <c r="H563" t="n">
         <v>46276</v>
@@ -16725,7 +16725,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G564" t="n">
-        <v>9.12625694274902</v>
+        <v>9.12625885009766</v>
       </c>
       <c r="H564" t="n">
         <v>48960</v>
@@ -16783,7 +16783,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>9.07583618164062</v>
+        <v>9.07583522796631</v>
       </c>
       <c r="H566" t="n">
         <v>28705</v>
@@ -16812,7 +16812,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G567" t="n">
-        <v>9.12625694274902</v>
+        <v>9.12625885009766</v>
       </c>
       <c r="H567" t="n">
         <v>23732</v>
@@ -16841,7 +16841,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G568" t="n">
-        <v>9.14306545257568</v>
+        <v>9.14306449890137</v>
       </c>
       <c r="H568" t="n">
         <v>52483</v>
@@ -16870,7 +16870,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G569" t="n">
-        <v>9.04222297668457</v>
+        <v>9.04222393035889</v>
       </c>
       <c r="H569" t="n">
         <v>80924</v>
@@ -16899,7 +16899,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.109450340271</v>
+        <v>9.10945129394531</v>
       </c>
       <c r="H570" t="n">
         <v>40328</v>
@@ -16928,7 +16928,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G571" t="n">
-        <v>9.109450340271</v>
+        <v>9.10945129394531</v>
       </c>
       <c r="H571" t="n">
         <v>28447</v>
@@ -16957,7 +16957,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G572" t="n">
-        <v>9.14306545257568</v>
+        <v>9.14306449890137</v>
       </c>
       <c r="H572" t="n">
         <v>33399</v>
@@ -16986,7 +16986,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G573" t="n">
-        <v>9.02541446685791</v>
+        <v>9.02541637420654</v>
       </c>
       <c r="H573" t="n">
         <v>39104</v>
@@ -17015,7 +17015,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>9.07583618164062</v>
+        <v>9.07583522796631</v>
       </c>
       <c r="H574" t="n">
         <v>27014</v>
@@ -17044,7 +17044,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G575" t="n">
-        <v>9.07583618164062</v>
+        <v>9.07583522796631</v>
       </c>
       <c r="H575" t="n">
         <v>21639</v>
@@ -17073,7 +17073,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G576" t="n">
-        <v>8.95818614959717</v>
+        <v>8.95818710327148</v>
       </c>
       <c r="H576" t="n">
         <v>30924</v>
@@ -17131,7 +17131,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>9.07583618164062</v>
+        <v>9.07583522796631</v>
       </c>
       <c r="H578" t="n">
         <v>27463</v>
@@ -17218,7 +17218,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G581" t="n">
-        <v>9.14306545257568</v>
+        <v>9.14306449890137</v>
       </c>
       <c r="H581" t="n">
         <v>36929</v>
@@ -17247,7 +17247,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G582" t="n">
-        <v>9.12625694274902</v>
+        <v>9.12625885009766</v>
       </c>
       <c r="H582" t="n">
         <v>34722</v>
@@ -17276,7 +17276,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G583" t="n">
-        <v>9.17667865753174</v>
+        <v>9.17667961120605</v>
       </c>
       <c r="H583" t="n">
         <v>16997</v>
@@ -17305,7 +17305,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>9.3279447555542</v>
+        <v>9.32794380187988</v>
       </c>
       <c r="H584" t="n">
         <v>79263</v>
@@ -17334,7 +17334,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>9.41197872161865</v>
+        <v>9.41197776794434</v>
       </c>
       <c r="H585" t="n">
         <v>70836</v>
@@ -17363,7 +17363,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G586" t="n">
-        <v>9.47920799255371</v>
+        <v>9.47920703887939</v>
       </c>
       <c r="H586" t="n">
         <v>52939</v>
@@ -17392,7 +17392,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>9.59685611724854</v>
+        <v>9.59685707092285</v>
       </c>
       <c r="H587" t="n">
         <v>118423</v>
@@ -17450,7 +17450,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G589" t="n">
-        <v>10.4708251953125</v>
+        <v>10.4708261489868</v>
       </c>
       <c r="H589" t="n">
         <v>356336</v>
@@ -17595,7 +17595,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G594" t="n">
-        <v>10.8573904037476</v>
+        <v>10.8573894500732</v>
       </c>
       <c r="H594" t="n">
         <v>178210</v>
@@ -17624,7 +17624,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G595" t="n">
-        <v>11.3279867172241</v>
+        <v>11.3279876708984</v>
       </c>
       <c r="H595" t="n">
         <v>248144</v>
@@ -17740,7 +17740,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G599" t="n">
-        <v>11.7608919143677</v>
+        <v>11.760892868042</v>
       </c>
       <c r="H599" t="n">
         <v>320674</v>
@@ -17769,7 +17769,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G600" t="n">
-        <v>11.7608919143677</v>
+        <v>11.760892868042</v>
       </c>
       <c r="H600" t="n">
         <v>189219</v>
@@ -17798,7 +17798,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G601" t="n">
-        <v>11.7245941162109</v>
+        <v>11.7245931625366</v>
       </c>
       <c r="H601" t="n">
         <v>161033</v>
@@ -17856,7 +17856,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G603" t="n">
-        <v>11.1982574462891</v>
+        <v>11.1982564926147</v>
       </c>
       <c r="H603" t="n">
         <v>237166</v>
@@ -17885,7 +17885,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G604" t="n">
-        <v>11.1801061630249</v>
+        <v>11.1801080703735</v>
       </c>
       <c r="H604" t="n">
         <v>141160</v>
@@ -17943,7 +17943,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G606" t="n">
-        <v>10.7808179855347</v>
+        <v>10.780818939209</v>
       </c>
       <c r="H606" t="n">
         <v>180380</v>
@@ -18001,7 +18001,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G608" t="n">
-        <v>10.5993232727051</v>
+        <v>10.5993223190308</v>
       </c>
       <c r="H608" t="n">
         <v>120612</v>
@@ -18030,7 +18030,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G609" t="n">
-        <v>10.5085754394531</v>
+        <v>10.5085744857788</v>
       </c>
       <c r="H609" t="n">
         <v>171843</v>
@@ -18059,7 +18059,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>10.5085754394531</v>
+        <v>10.5085744857788</v>
       </c>
       <c r="H610" t="n">
         <v>39696</v>
@@ -18146,7 +18146,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>10.0729875564575</v>
+        <v>10.0729866027832</v>
       </c>
       <c r="H613" t="n">
         <v>69002</v>
@@ -18175,7 +18175,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>9.90964031219482</v>
+        <v>9.90964126586914</v>
       </c>
       <c r="H614" t="n">
         <v>65685</v>
@@ -18262,7 +18262,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G617" t="n">
-        <v>10.181884765625</v>
+        <v>10.1818838119507</v>
       </c>
       <c r="H617" t="n">
         <v>59541</v>
@@ -18407,7 +18407,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G622" t="n">
-        <v>10.0366878509521</v>
+        <v>10.0366868972778</v>
       </c>
       <c r="H622" t="n">
         <v>125360</v>
@@ -18465,7 +18465,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G624" t="n">
-        <v>10.2181816101074</v>
+        <v>10.2181835174561</v>
       </c>
       <c r="H624" t="n">
         <v>122169</v>
@@ -18494,7 +18494,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>10.3452281951904</v>
+        <v>10.3452301025391</v>
       </c>
       <c r="H625" t="n">
         <v>15232</v>
@@ -18523,7 +18523,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G626" t="n">
-        <v>10.2363319396973</v>
+        <v>10.2363328933716</v>
       </c>
       <c r="H626" t="n">
         <v>16213</v>
@@ -18552,7 +18552,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G627" t="n">
-        <v>10.1092844009399</v>
+        <v>10.1092853546143</v>
       </c>
       <c r="H627" t="n">
         <v>22029</v>
@@ -18639,7 +18639,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G630" t="n">
-        <v>10.1092844009399</v>
+        <v>10.1092853546143</v>
       </c>
       <c r="H630" t="n">
         <v>61841</v>
@@ -18726,7 +18726,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G633" t="n">
-        <v>9.6918478012085</v>
+        <v>9.69184684753418</v>
       </c>
       <c r="H633" t="n">
         <v>34905</v>
@@ -18842,7 +18842,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G637" t="n">
-        <v>9.5829496383667</v>
+        <v>9.58295059204102</v>
       </c>
       <c r="H637" t="n">
         <v>16681</v>
@@ -18900,7 +18900,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G639" t="n">
-        <v>9.56480121612549</v>
+        <v>9.56479930877686</v>
       </c>
       <c r="H639" t="n">
         <v>13553</v>
@@ -18929,7 +18929,7 @@
         <v>10.5</v>
       </c>
       <c r="G640" t="n">
-        <v>9.52850151062012</v>
+        <v>9.5285005569458</v>
       </c>
       <c r="H640" t="n">
         <v>19624</v>
@@ -18987,7 +18987,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G642" t="n">
-        <v>9.65554714202881</v>
+        <v>9.65554809570312</v>
       </c>
       <c r="H642" t="n">
         <v>11808</v>
@@ -19016,7 +19016,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G643" t="n">
-        <v>9.60109901428223</v>
+        <v>9.60109806060791</v>
       </c>
       <c r="H643" t="n">
         <v>15856</v>
@@ -19074,7 +19074,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>9.2199592590332</v>
+        <v>9.21995830535889</v>
       </c>
       <c r="H645" t="n">
         <v>25750</v>
@@ -19103,7 +19103,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>9.1655101776123</v>
+        <v>9.16550922393799</v>
       </c>
       <c r="H646" t="n">
         <v>30672</v>
@@ -19132,7 +19132,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.1655101776123</v>
+        <v>9.16550922393799</v>
       </c>
       <c r="H647" t="n">
         <v>18337</v>
@@ -19161,7 +19161,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G648" t="n">
-        <v>9.27440643310547</v>
+        <v>9.27440738677979</v>
       </c>
       <c r="H648" t="n">
         <v>14022</v>
@@ -19190,7 +19190,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G649" t="n">
-        <v>9.2199592590332</v>
+        <v>9.21995830535889</v>
       </c>
       <c r="H649" t="n">
         <v>13772</v>
@@ -19219,7 +19219,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G650" t="n">
-        <v>9.23810958862305</v>
+        <v>9.23810768127441</v>
       </c>
       <c r="H650" t="n">
         <v>22208</v>
@@ -19248,7 +19248,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G651" t="n">
-        <v>9.18365955352783</v>
+        <v>9.18366050720215</v>
       </c>
       <c r="H651" t="n">
         <v>12282</v>
@@ -19277,7 +19277,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>8.98401546478271</v>
+        <v>8.98401355743408</v>
       </c>
       <c r="H652" t="n">
         <v>41212</v>
@@ -19306,7 +19306,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>9.00216484069824</v>
+        <v>9.00216388702393</v>
       </c>
       <c r="H653" t="n">
         <v>12349</v>
@@ -19335,7 +19335,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>8.98401546478271</v>
+        <v>8.98401355743408</v>
       </c>
       <c r="H654" t="n">
         <v>26179</v>
@@ -19393,7 +19393,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G656" t="n">
-        <v>8.79344367980957</v>
+        <v>8.79344463348389</v>
       </c>
       <c r="H656" t="n">
         <v>24730</v>
@@ -19422,7 +19422,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G657" t="n">
-        <v>8.94771480560303</v>
+        <v>8.94771671295166</v>
       </c>
       <c r="H657" t="n">
         <v>36135</v>
@@ -19451,7 +19451,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G658" t="n">
-        <v>8.87511730194092</v>
+        <v>8.87511920928955</v>
       </c>
       <c r="H658" t="n">
         <v>16562</v>
@@ -19538,7 +19538,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>8.79344367980957</v>
+        <v>8.79344463348389</v>
       </c>
       <c r="H661" t="n">
         <v>22420</v>
@@ -19683,7 +19683,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G666" t="n">
-        <v>8.79344367980957</v>
+        <v>8.79344463348389</v>
       </c>
       <c r="H666" t="n">
         <v>84147</v>
@@ -19712,7 +19712,7 @@
         <v>9.5</v>
       </c>
       <c r="G667" t="n">
-        <v>8.6210241317749</v>
+        <v>8.62102508544922</v>
       </c>
       <c r="H667" t="n">
         <v>55346</v>
@@ -19741,7 +19741,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G668" t="n">
-        <v>8.55750179290771</v>
+        <v>8.5575008392334</v>
       </c>
       <c r="H668" t="n">
         <v>62585</v>
@@ -19770,7 +19770,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>8.57565021514893</v>
+        <v>8.57565116882324</v>
       </c>
       <c r="H669" t="n">
         <v>41570</v>
@@ -19828,7 +19828,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G671" t="n">
-        <v>8.27618503570557</v>
+        <v>8.27618312835693</v>
       </c>
       <c r="H671" t="n">
         <v>67193</v>
@@ -19915,7 +19915,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G674" t="n">
-        <v>8.94771480560303</v>
+        <v>8.94771671295166</v>
       </c>
       <c r="H674" t="n">
         <v>80694</v>
@@ -19944,7 +19944,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G675" t="n">
-        <v>9.31070709228516</v>
+        <v>9.31070518493652</v>
       </c>
       <c r="H675" t="n">
         <v>86138</v>
@@ -19973,7 +19973,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G676" t="n">
-        <v>9.29255676269531</v>
+        <v>9.292555809021</v>
       </c>
       <c r="H676" t="n">
         <v>47588</v>
@@ -20002,7 +20002,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G677" t="n">
-        <v>9.29255676269531</v>
+        <v>9.292555809021</v>
       </c>
       <c r="H677" t="n">
         <v>49307</v>
@@ -20031,7 +20031,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G678" t="n">
-        <v>9.2199592590332</v>
+        <v>9.21995830535889</v>
       </c>
       <c r="H678" t="n">
         <v>17101</v>
@@ -20060,7 +20060,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>9.23810958862305</v>
+        <v>9.23810768127441</v>
       </c>
       <c r="H679" t="n">
         <v>25575</v>
@@ -20118,7 +20118,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G681" t="n">
-        <v>8.92049121856689</v>
+        <v>8.92049217224121</v>
       </c>
       <c r="H681" t="n">
         <v>19738</v>
@@ -20147,7 +20147,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>9.31070709228516</v>
+        <v>9.31070518493652</v>
       </c>
       <c r="H682" t="n">
         <v>31385</v>
@@ -20176,7 +20176,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G683" t="n">
-        <v>9.27440643310547</v>
+        <v>9.27440738677979</v>
       </c>
       <c r="H683" t="n">
         <v>32438</v>
@@ -20205,7 +20205,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G684" t="n">
-        <v>9.05661296844482</v>
+        <v>9.05661201477051</v>
       </c>
       <c r="H684" t="n">
         <v>23211</v>
@@ -20234,7 +20234,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.0384635925293</v>
+        <v>9.03846454620361</v>
       </c>
       <c r="H685" t="n">
         <v>20707</v>
@@ -20292,7 +20292,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>8.88419151306152</v>
+        <v>8.88419246673584</v>
       </c>
       <c r="H687" t="n">
         <v>176181</v>
@@ -20321,7 +20321,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>8.88419151306152</v>
+        <v>8.88419246673584</v>
       </c>
       <c r="H688" t="n">
         <v>26119</v>
@@ -20350,7 +20350,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>8.88419151306152</v>
+        <v>8.88419246673584</v>
       </c>
       <c r="H689" t="n">
         <v>25899</v>
@@ -20408,7 +20408,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.80251884460449</v>
+        <v>8.80251979827881</v>
       </c>
       <c r="H691" t="n">
         <v>20607</v>
@@ -20437,7 +20437,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>8.88419151306152</v>
+        <v>8.88419246673584</v>
       </c>
       <c r="H692" t="n">
         <v>24251</v>
@@ -20495,7 +20495,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G694" t="n">
-        <v>8.79344367980957</v>
+        <v>8.79344463348389</v>
       </c>
       <c r="H694" t="n">
         <v>14070</v>
@@ -20524,7 +20524,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>8.80251884460449</v>
+        <v>8.80251979827881</v>
       </c>
       <c r="H695" t="n">
         <v>25316</v>
@@ -20553,7 +20553,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G696" t="n">
-        <v>8.80251884460449</v>
+        <v>8.80251979827881</v>
       </c>
       <c r="H696" t="n">
         <v>13873</v>
@@ -20727,7 +20727,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.57565021514893</v>
+        <v>8.57565116882324</v>
       </c>
       <c r="H702" t="n">
         <v>33379</v>
@@ -20843,7 +20843,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G706" t="n">
-        <v>8.33063220977783</v>
+        <v>8.33063316345215</v>
       </c>
       <c r="H706" t="n">
         <v>36589</v>
@@ -20872,7 +20872,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>8.27618503570557</v>
+        <v>8.27618312835693</v>
       </c>
       <c r="H707" t="n">
         <v>40179</v>
@@ -20930,7 +20930,7 @@
         <v>9</v>
       </c>
       <c r="G709" t="n">
-        <v>8.16728687286377</v>
+        <v>8.16728591918945</v>
       </c>
       <c r="H709" t="n">
         <v>28353</v>
@@ -21017,7 +21017,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G712" t="n">
-        <v>7.61372566223145</v>
+        <v>7.6137261390686</v>
       </c>
       <c r="H712" t="n">
         <v>19357</v>
@@ -21075,7 +21075,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>7.52297735214233</v>
+        <v>7.52297878265381</v>
       </c>
       <c r="H714" t="n">
         <v>113497</v>
@@ -21104,7 +21104,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G715" t="n">
-        <v>7.42315673828125</v>
+        <v>7.42315626144409</v>
       </c>
       <c r="H715" t="n">
         <v>32395</v>
@@ -21133,7 +21133,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G716" t="n">
-        <v>7.32333278656006</v>
+        <v>7.32333326339722</v>
       </c>
       <c r="H716" t="n">
         <v>35973</v>
@@ -21191,7 +21191,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>7.0147910118103</v>
+        <v>7.01479148864746</v>
       </c>
       <c r="H718" t="n">
         <v>31399</v>
@@ -21307,7 +21307,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G722" t="n">
-        <v>7.23258590698242</v>
+        <v>7.23258638381958</v>
       </c>
       <c r="H722" t="n">
         <v>24909</v>
@@ -21394,7 +21394,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G725" t="n">
-        <v>7.35055828094482</v>
+        <v>7.35055780410767</v>
       </c>
       <c r="H725" t="n">
         <v>29989</v>
@@ -21423,7 +21423,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G726" t="n">
-        <v>7.61372566223145</v>
+        <v>7.6137261390686</v>
       </c>
       <c r="H726" t="n">
         <v>26120</v>
@@ -21452,7 +21452,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G727" t="n">
-        <v>7.69539833068848</v>
+        <v>7.69539785385132</v>
       </c>
       <c r="H727" t="n">
         <v>32663</v>
@@ -21510,7 +21510,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G729" t="n">
-        <v>7.62279939651489</v>
+        <v>7.62279987335205</v>
       </c>
       <c r="H729" t="n">
         <v>49897</v>
@@ -21539,7 +21539,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G730" t="n">
-        <v>7.38685703277588</v>
+        <v>7.38685750961304</v>
       </c>
       <c r="H730" t="n">
         <v>31609</v>
@@ -21597,7 +21597,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G732" t="n">
-        <v>7.4957537651062</v>
+        <v>7.49575424194336</v>
       </c>
       <c r="H732" t="n">
         <v>12870</v>
@@ -21684,7 +21684,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G735" t="n">
-        <v>7.15998792648315</v>
+        <v>7.15998840332031</v>
       </c>
       <c r="H735" t="n">
         <v>43485</v>
@@ -21713,7 +21713,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>7.07831525802612</v>
+        <v>7.07831573486328</v>
       </c>
       <c r="H736" t="n">
         <v>16363</v>
@@ -21742,7 +21742,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>7.08738946914673</v>
+        <v>7.08738994598389</v>
       </c>
       <c r="H737" t="n">
         <v>7916</v>
@@ -21771,7 +21771,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>6.99664258956909</v>
+        <v>6.99664211273193</v>
       </c>
       <c r="H738" t="n">
         <v>21120</v>
@@ -21829,7 +21829,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>6.99664258956909</v>
+        <v>6.99664211273193</v>
       </c>
       <c r="H740" t="n">
         <v>8422</v>
@@ -21858,7 +21858,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G741" t="n">
-        <v>7.07831525802612</v>
+        <v>7.07831573486328</v>
       </c>
       <c r="H741" t="n">
         <v>30617</v>
@@ -21887,7 +21887,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G742" t="n">
-        <v>7.35055828094482</v>
+        <v>7.35055780410767</v>
       </c>
       <c r="H742" t="n">
         <v>15187</v>
@@ -21945,7 +21945,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G744" t="n">
-        <v>7.35055828094482</v>
+        <v>7.35055780410767</v>
       </c>
       <c r="H744" t="n">
         <v>13555</v>
@@ -21974,7 +21974,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G745" t="n">
-        <v>7.46852874755859</v>
+        <v>7.46852922439575</v>
       </c>
       <c r="H745" t="n">
         <v>18429</v>
@@ -22032,7 +22032,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G747" t="n">
-        <v>7.45945501327515</v>
+        <v>7.4594554901123</v>
       </c>
       <c r="H747" t="n">
         <v>33277</v>
@@ -22090,7 +22090,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G749" t="n">
-        <v>7.45945501327515</v>
+        <v>7.4594554901123</v>
       </c>
       <c r="H749" t="n">
         <v>15116</v>
@@ -22148,7 +22148,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G751" t="n">
-        <v>7.26888465881348</v>
+        <v>7.26888513565063</v>
       </c>
       <c r="H751" t="n">
         <v>9629</v>
@@ -22177,7 +22177,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>7.2235107421875</v>
+        <v>7.22351121902466</v>
       </c>
       <c r="H752" t="n">
         <v>15306</v>
@@ -22409,7 +22409,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G760" t="n">
-        <v>7.17813682556152</v>
+        <v>7.17813730239868</v>
       </c>
       <c r="H760" t="n">
         <v>5002</v>
@@ -22467,7 +22467,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G762" t="n">
-        <v>7.28703355789185</v>
+        <v>7.287034034729</v>
       </c>
       <c r="H762" t="n">
         <v>15400</v>
@@ -22496,7 +22496,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G763" t="n">
-        <v>7.42315673828125</v>
+        <v>7.42315626144409</v>
       </c>
       <c r="H763" t="n">
         <v>12478</v>
@@ -22525,7 +22525,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G764" t="n">
-        <v>7.60465145111084</v>
+        <v>7.60465097427368</v>
       </c>
       <c r="H764" t="n">
         <v>9893</v>
@@ -22554,7 +22554,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G765" t="n">
-        <v>7.6500244140625</v>
+        <v>7.65002489089966</v>
       </c>
       <c r="H765" t="n">
         <v>25050</v>
@@ -22583,7 +22583,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>7.79522180557251</v>
+        <v>7.79522085189819</v>
       </c>
       <c r="H766" t="n">
         <v>12522</v>
@@ -22612,7 +22612,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G767" t="n">
-        <v>7.96764183044434</v>
+        <v>7.96764087677002</v>
       </c>
       <c r="H767" t="n">
         <v>53519</v>
@@ -22641,7 +22641,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G768" t="n">
-        <v>8.27618503570557</v>
+        <v>8.27618312835693</v>
       </c>
       <c r="H768" t="n">
         <v>64182</v>
@@ -22670,7 +22670,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G769" t="n">
-        <v>8.29433441162109</v>
+        <v>8.29433345794678</v>
       </c>
       <c r="H769" t="n">
         <v>42394</v>
@@ -22699,7 +22699,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G770" t="n">
-        <v>8.31248188018799</v>
+        <v>8.3124828338623</v>
       </c>
       <c r="H770" t="n">
         <v>60931</v>
@@ -22728,7 +22728,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G771" t="n">
-        <v>8.41230487823486</v>
+        <v>8.41230392456055</v>
       </c>
       <c r="H771" t="n">
         <v>13815</v>
@@ -22757,7 +22757,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G772" t="n">
-        <v>8.33063220977783</v>
+        <v>8.33063316345215</v>
       </c>
       <c r="H772" t="n">
         <v>12514</v>
@@ -22786,7 +22786,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>8.32155704498291</v>
+        <v>8.32155799865723</v>
       </c>
       <c r="H773" t="n">
         <v>10552</v>
@@ -22815,7 +22815,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G774" t="n">
-        <v>8.26710891723633</v>
+        <v>8.26710796356201</v>
       </c>
       <c r="H774" t="n">
         <v>31249</v>
@@ -22873,7 +22873,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G776" t="n">
-        <v>8.29433441162109</v>
+        <v>8.29433345794678</v>
       </c>
       <c r="H776" t="n">
         <v>17422</v>
@@ -22960,7 +22960,7 @@
         <v>9.5</v>
       </c>
       <c r="G779" t="n">
-        <v>8.6210241317749</v>
+        <v>8.62102508544922</v>
       </c>
       <c r="H779" t="n">
         <v>24121</v>
@@ -23047,7 +23047,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G782" t="n">
-        <v>8.93864059448242</v>
+        <v>8.93864154815674</v>
       </c>
       <c r="H782" t="n">
         <v>43789</v>
@@ -23076,7 +23076,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G783" t="n">
-        <v>9.0475378036499</v>
+        <v>9.04753875732422</v>
       </c>
       <c r="H783" t="n">
         <v>21904</v>
@@ -23221,7 +23221,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G788" t="n">
-        <v>8.96586513519287</v>
+        <v>8.96586608886719</v>
       </c>
       <c r="H788" t="n">
         <v>23953</v>
@@ -23337,7 +23337,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.58472537994385</v>
+        <v>8.58472633361816</v>
       </c>
       <c r="H792" t="n">
         <v>20073</v>
@@ -23482,7 +23482,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>8.92956733703613</v>
+        <v>8.92956638336182</v>
       </c>
       <c r="H797" t="n">
         <v>15673</v>
@@ -23540,7 +23540,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G799" t="n">
-        <v>8.82974338531494</v>
+        <v>8.82974433898926</v>
       </c>
       <c r="H799" t="n">
         <v>2972</v>
@@ -23627,7 +23627,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G802" t="n">
-        <v>8.87511730194092</v>
+        <v>8.87511920928955</v>
       </c>
       <c r="H802" t="n">
         <v>12406</v>
@@ -23714,7 +23714,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G805" t="n">
-        <v>8.72084522247314</v>
+        <v>8.72084617614746</v>
       </c>
       <c r="H805" t="n">
         <v>12218</v>
@@ -23743,7 +23743,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G806" t="n">
-        <v>8.72084522247314</v>
+        <v>8.72084617614746</v>
       </c>
       <c r="H806" t="n">
         <v>12353</v>
@@ -23801,7 +23801,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G808" t="n">
-        <v>8.72992134094238</v>
+        <v>8.7299222946167</v>
       </c>
       <c r="H808" t="n">
         <v>13926</v>
@@ -23830,7 +23830,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G809" t="n">
-        <v>8.87511730194092</v>
+        <v>8.87511920928955</v>
       </c>
       <c r="H809" t="n">
         <v>13318</v>
@@ -23917,7 +23917,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G812" t="n">
-        <v>8.60287475585938</v>
+        <v>8.60287380218506</v>
       </c>
       <c r="H812" t="n">
         <v>14182</v>
@@ -23975,7 +23975,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G814" t="n">
-        <v>8.17636108398438</v>
+        <v>8.17636203765869</v>
       </c>
       <c r="H814" t="n">
         <v>48473</v>
@@ -24033,7 +24033,7 @@
         <v>9</v>
       </c>
       <c r="G816" t="n">
-        <v>8.16728687286377</v>
+        <v>8.16728591918945</v>
       </c>
       <c r="H816" t="n">
         <v>59557</v>
@@ -24062,7 +24062,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G817" t="n">
-        <v>8.19451141357422</v>
+        <v>8.1945104598999</v>
       </c>
       <c r="H817" t="n">
         <v>19654</v>
@@ -24120,7 +24120,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G819" t="n">
-        <v>8.32155704498291</v>
+        <v>8.32155799865723</v>
       </c>
       <c r="H819" t="n">
         <v>7166</v>
@@ -24178,7 +24178,7 @@
         <v>9</v>
       </c>
       <c r="G821" t="n">
-        <v>8.16728687286377</v>
+        <v>8.16728591918945</v>
       </c>
       <c r="H821" t="n">
         <v>12673</v>
@@ -24294,7 +24294,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>8.15821075439453</v>
+        <v>8.15821170806885</v>
       </c>
       <c r="H825" t="n">
         <v>7830</v>
@@ -24323,7 +24323,7 @@
         <v>9</v>
       </c>
       <c r="G826" t="n">
-        <v>8.16728687286377</v>
+        <v>8.16728591918945</v>
       </c>
       <c r="H826" t="n">
         <v>10409</v>
@@ -24410,7 +24410,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>8.35785579681396</v>
+        <v>8.35785675048828</v>
       </c>
       <c r="H829" t="n">
         <v>17785</v>
@@ -24439,7 +24439,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G830" t="n">
-        <v>8.27618503570557</v>
+        <v>8.27618312835693</v>
       </c>
       <c r="H830" t="n">
         <v>18984</v>
@@ -24613,7 +24613,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G836" t="n">
-        <v>8.38508129119873</v>
+        <v>8.38508033752441</v>
       </c>
       <c r="H836" t="n">
         <v>18910</v>
@@ -24671,7 +24671,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G838" t="n">
-        <v>8.45767784118652</v>
+        <v>8.45767879486084</v>
       </c>
       <c r="H838" t="n">
         <v>14251</v>
@@ -24758,7 +24758,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.53027629852295</v>
+        <v>8.53027534484863</v>
       </c>
       <c r="H841" t="n">
         <v>16213</v>
@@ -24787,7 +24787,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G842" t="n">
-        <v>8.53027629852295</v>
+        <v>8.53027534484863</v>
       </c>
       <c r="H842" t="n">
         <v>9977</v>
@@ -24903,7 +24903,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G846" t="n">
-        <v>8.53027629852295</v>
+        <v>8.53027534484863</v>
       </c>
       <c r="H846" t="n">
         <v>18591</v>
@@ -24932,7 +24932,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>8.46675205230713</v>
+        <v>8.46675395965576</v>
       </c>
       <c r="H847" t="n">
         <v>23993</v>
@@ -24990,7 +24990,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G849" t="n">
-        <v>8.62017154693604</v>
+        <v>8.62017250061035</v>
       </c>
       <c r="H849" t="n">
         <v>45436</v>
@@ -25019,7 +25019,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G850" t="n">
-        <v>8.32292461395264</v>
+        <v>8.32292556762695</v>
       </c>
       <c r="H850" t="n">
         <v>28035</v>
@@ -25048,7 +25048,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>8.11197471618652</v>
+        <v>8.11197566986084</v>
       </c>
       <c r="H851" t="n">
         <v>31368</v>
@@ -25135,7 +25135,7 @@
         <v>8.25</v>
       </c>
       <c r="G854" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H854" t="n">
         <v>14109</v>
@@ -25164,7 +25164,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G855" t="n">
-        <v>8.21744823455811</v>
+        <v>8.21744918823242</v>
       </c>
       <c r="H855" t="n">
         <v>17610</v>
@@ -25193,7 +25193,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G856" t="n">
-        <v>8.01608848571777</v>
+        <v>8.01608753204346</v>
       </c>
       <c r="H856" t="n">
         <v>12618</v>
@@ -25309,7 +25309,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>8.02567768096924</v>
+        <v>8.02567672729492</v>
       </c>
       <c r="H860" t="n">
         <v>13382</v>
@@ -25338,7 +25338,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G861" t="n">
-        <v>8.02567768096924</v>
+        <v>8.02567672729492</v>
       </c>
       <c r="H861" t="n">
         <v>3528</v>
@@ -25367,7 +25367,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G862" t="n">
-        <v>8.04485416412354</v>
+        <v>8.04485511779785</v>
       </c>
       <c r="H862" t="n">
         <v>3193</v>
@@ -25396,7 +25396,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G863" t="n">
-        <v>8.07362079620361</v>
+        <v>8.0736198425293</v>
       </c>
       <c r="H863" t="n">
         <v>6671</v>
@@ -25425,7 +25425,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G864" t="n">
-        <v>7.90102481842041</v>
+        <v>7.90102577209473</v>
       </c>
       <c r="H864" t="n">
         <v>16602</v>
@@ -25454,7 +25454,7 @@
         <v>8.25</v>
       </c>
       <c r="G865" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H865" t="n">
         <v>17068</v>
@@ -25483,7 +25483,7 @@
         <v>8.25</v>
       </c>
       <c r="G866" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H866" t="n">
         <v>7115</v>
@@ -25512,7 +25512,7 @@
         <v>8.25</v>
       </c>
       <c r="G867" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H867" t="n">
         <v>2277</v>
@@ -25541,7 +25541,7 @@
         <v>8.25</v>
       </c>
       <c r="G868" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H868" t="n">
         <v>9596</v>
@@ -25599,7 +25599,7 @@
         <v>8.25</v>
       </c>
       <c r="G870" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H870" t="n">
         <v>6729</v>
@@ -25628,7 +25628,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G871" t="n">
-        <v>8.09279727935791</v>
+        <v>8.09279632568359</v>
       </c>
       <c r="H871" t="n">
         <v>3284</v>
@@ -25657,7 +25657,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G872" t="n">
-        <v>8.04485416412354</v>
+        <v>8.04485511779785</v>
       </c>
       <c r="H872" t="n">
         <v>126950</v>
@@ -25715,7 +25715,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G874" t="n">
-        <v>8.16950702667236</v>
+        <v>8.16950607299805</v>
       </c>
       <c r="H874" t="n">
         <v>2190</v>
@@ -25773,7 +25773,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>8.06403064727783</v>
+        <v>8.06403160095215</v>
       </c>
       <c r="H876" t="n">
         <v>56257</v>
@@ -25831,7 +25831,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>8.02567768096924</v>
+        <v>8.02567672729492</v>
       </c>
       <c r="H878" t="n">
         <v>3474</v>
@@ -25889,7 +25889,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G880" t="n">
-        <v>8.02567768096924</v>
+        <v>8.02567672729492</v>
       </c>
       <c r="H880" t="n">
         <v>5768</v>
@@ -25918,7 +25918,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G881" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H881" t="n">
         <v>11083</v>
@@ -25976,7 +25976,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G883" t="n">
-        <v>8.00650119781494</v>
+        <v>8.00650024414062</v>
       </c>
       <c r="H883" t="n">
         <v>1214</v>
@@ -26005,7 +26005,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H884" t="n">
         <v>2839</v>
@@ -26034,7 +26034,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G885" t="n">
-        <v>7.86267042160034</v>
+        <v>7.8626708984375</v>
       </c>
       <c r="H885" t="n">
         <v>3314</v>
@@ -26063,7 +26063,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G886" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H886" t="n">
         <v>3628</v>
@@ -26092,7 +26092,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G887" t="n">
-        <v>7.86267042160034</v>
+        <v>7.8626708984375</v>
       </c>
       <c r="H887" t="n">
         <v>3277</v>
@@ -26121,7 +26121,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H888" t="n">
         <v>5411</v>
@@ -26150,7 +26150,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G889" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H889" t="n">
         <v>24239</v>
@@ -26179,7 +26179,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G890" t="n">
-        <v>8.04485416412354</v>
+        <v>8.04485511779785</v>
       </c>
       <c r="H890" t="n">
         <v>6226</v>
@@ -26208,7 +26208,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G891" t="n">
-        <v>8.10238552093506</v>
+        <v>8.10238456726074</v>
       </c>
       <c r="H891" t="n">
         <v>5780</v>
@@ -26237,7 +26237,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>8.10238552093506</v>
+        <v>8.10238456726074</v>
       </c>
       <c r="H892" t="n">
         <v>5565</v>
@@ -26266,7 +26266,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G893" t="n">
-        <v>8.06403064727783</v>
+        <v>8.06403160095215</v>
       </c>
       <c r="H893" t="n">
         <v>5189</v>
@@ -26295,7 +26295,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G894" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H894" t="n">
         <v>2731</v>
@@ -26324,7 +26324,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H895" t="n">
         <v>2306</v>
@@ -26353,7 +26353,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G896" t="n">
-        <v>8.10238552093506</v>
+        <v>8.10238456726074</v>
       </c>
       <c r="H896" t="n">
         <v>7549</v>
@@ -26382,7 +26382,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G897" t="n">
-        <v>8.05444240570068</v>
+        <v>8.054443359375</v>
       </c>
       <c r="H897" t="n">
         <v>16864</v>
@@ -26411,7 +26411,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96814489364624</v>
+        <v>7.96814680099487</v>
       </c>
       <c r="H898" t="n">
         <v>6261</v>
@@ -26469,7 +26469,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G900" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H900" t="n">
         <v>6338</v>
@@ -26527,7 +26527,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G902" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H902" t="n">
         <v>1761</v>
@@ -26556,7 +26556,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G903" t="n">
-        <v>7.96814489364624</v>
+        <v>7.96814680099487</v>
       </c>
       <c r="H903" t="n">
         <v>3021</v>
@@ -26585,7 +26585,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>7.87225961685181</v>
+        <v>7.87225914001465</v>
       </c>
       <c r="H904" t="n">
         <v>2204</v>
@@ -26643,7 +26643,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G906" t="n">
-        <v>8.00650119781494</v>
+        <v>8.00650024414062</v>
       </c>
       <c r="H906" t="n">
         <v>2340</v>
@@ -26672,7 +26672,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G907" t="n">
-        <v>8.00650119781494</v>
+        <v>8.00650024414062</v>
       </c>
       <c r="H907" t="n">
         <v>1057</v>
@@ -26701,7 +26701,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>8.07362079620361</v>
+        <v>8.0736198425293</v>
       </c>
       <c r="H908" t="n">
         <v>22955</v>
@@ -26759,7 +26759,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H910" t="n">
         <v>22840</v>
@@ -26788,7 +26788,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G911" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H911" t="n">
         <v>9880</v>
@@ -26817,7 +26817,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G912" t="n">
-        <v>8.13115119934082</v>
+        <v>8.13115215301514</v>
       </c>
       <c r="H912" t="n">
         <v>8382</v>
@@ -26846,7 +26846,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>8.06403064727783</v>
+        <v>8.06403160095215</v>
       </c>
       <c r="H913" t="n">
         <v>87973</v>
@@ -26875,7 +26875,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G914" t="n">
-        <v>8.01608848571777</v>
+        <v>8.01608753204346</v>
       </c>
       <c r="H914" t="n">
         <v>32578</v>
@@ -26933,7 +26933,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G916" t="n">
-        <v>8.03526592254639</v>
+        <v>8.03526496887207</v>
       </c>
       <c r="H916" t="n">
         <v>10422</v>
@@ -26991,7 +26991,7 @@
         <v>8.25</v>
       </c>
       <c r="G918" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H918" t="n">
         <v>15260</v>
@@ -27049,7 +27049,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G920" t="n">
-        <v>8.00650119781494</v>
+        <v>8.00650024414062</v>
       </c>
       <c r="H920" t="n">
         <v>4825</v>
@@ -27078,7 +27078,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G921" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H921" t="n">
         <v>9702</v>
@@ -27107,7 +27107,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G922" t="n">
-        <v>7.90102481842041</v>
+        <v>7.90102577209473</v>
       </c>
       <c r="H922" t="n">
         <v>2152</v>
@@ -27136,7 +27136,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G923" t="n">
-        <v>7.92020225524902</v>
+        <v>7.92020273208618</v>
       </c>
       <c r="H923" t="n">
         <v>3214</v>
@@ -27223,7 +27223,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G926" t="n">
-        <v>7.90102481842041</v>
+        <v>7.90102577209473</v>
       </c>
       <c r="H926" t="n">
         <v>15579</v>
@@ -27252,7 +27252,7 @@
         <v>8.25</v>
       </c>
       <c r="G927" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H927" t="n">
         <v>8023</v>
@@ -27339,7 +27339,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>7.87225961685181</v>
+        <v>7.87225914001465</v>
       </c>
       <c r="H930" t="n">
         <v>12627</v>
@@ -27368,7 +27368,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G931" t="n">
-        <v>7.79554986953735</v>
+        <v>7.79555082321167</v>
       </c>
       <c r="H931" t="n">
         <v>16984</v>
@@ -27426,7 +27426,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G933" t="n">
-        <v>7.79554986953735</v>
+        <v>7.79555082321167</v>
       </c>
       <c r="H933" t="n">
         <v>9014</v>
@@ -27513,7 +27513,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G936" t="n">
-        <v>7.87225961685181</v>
+        <v>7.87225914001465</v>
       </c>
       <c r="H936" t="n">
         <v>4063</v>
@@ -27542,7 +27542,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G937" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H937" t="n">
         <v>1199</v>
@@ -27571,7 +27571,7 @@
         <v>8.25</v>
       </c>
       <c r="G938" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H938" t="n">
         <v>2172</v>
@@ -27600,7 +27600,7 @@
         <v>8.25</v>
       </c>
       <c r="G939" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H939" t="n">
         <v>3229</v>
@@ -27629,7 +27629,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>7.88184785842896</v>
+        <v>7.8818473815918</v>
       </c>
       <c r="H940" t="n">
         <v>8098</v>
@@ -27687,7 +27687,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>7.86267042160034</v>
+        <v>7.8626708984375</v>
       </c>
       <c r="H942" t="n">
         <v>15590</v>
@@ -27716,7 +27716,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G943" t="n">
-        <v>7.79554986953735</v>
+        <v>7.79555082321167</v>
       </c>
       <c r="H943" t="n">
         <v>13715</v>
@@ -27745,7 +27745,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G944" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H944" t="n">
         <v>4740</v>
@@ -27861,7 +27861,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G948" t="n">
-        <v>7.86267042160034</v>
+        <v>7.8626708984375</v>
       </c>
       <c r="H948" t="n">
         <v>11927</v>
@@ -27919,7 +27919,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G950" t="n">
-        <v>7.90102481842041</v>
+        <v>7.90102577209473</v>
       </c>
       <c r="H950" t="n">
         <v>12451</v>
@@ -27948,7 +27948,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G951" t="n">
-        <v>7.92020225524902</v>
+        <v>7.92020273208618</v>
       </c>
       <c r="H951" t="n">
         <v>1695</v>
@@ -27977,7 +27977,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G952" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H952" t="n">
         <v>6016</v>
@@ -28064,7 +28064,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G955" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H955" t="n">
         <v>6167</v>
@@ -28093,7 +28093,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H956" t="n">
         <v>3445</v>
@@ -28122,7 +28122,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G957" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H957" t="n">
         <v>3495</v>
@@ -28151,7 +28151,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G958" t="n">
-        <v>7.88184785842896</v>
+        <v>7.8818473815918</v>
       </c>
       <c r="H958" t="n">
         <v>2891</v>
@@ -28180,7 +28180,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G959" t="n">
-        <v>7.88184785842896</v>
+        <v>7.8818473815918</v>
       </c>
       <c r="H959" t="n">
         <v>2299</v>
@@ -28238,7 +28238,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G961" t="n">
-        <v>7.87225961685181</v>
+        <v>7.87225914001465</v>
       </c>
       <c r="H961" t="n">
         <v>3386</v>
@@ -28296,7 +28296,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H963" t="n">
         <v>34842</v>
@@ -28354,7 +28354,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G965" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H965" t="n">
         <v>12268</v>
@@ -28470,7 +28470,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G969" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H969" t="n">
         <v>22596</v>
@@ -28644,7 +28644,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.10238552093506</v>
+        <v>8.10238456726074</v>
       </c>
       <c r="H975" t="n">
         <v>9639</v>
@@ -28673,7 +28673,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>8.11197471618652</v>
+        <v>8.11197566986084</v>
       </c>
       <c r="H976" t="n">
         <v>12430</v>
@@ -28731,7 +28731,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G978" t="n">
-        <v>8.32292461395264</v>
+        <v>8.32292556762695</v>
       </c>
       <c r="H978" t="n">
         <v>35275</v>
@@ -28760,7 +28760,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G979" t="n">
-        <v>8.37086772918701</v>
+        <v>8.3708667755127</v>
       </c>
       <c r="H979" t="n">
         <v>25943</v>
@@ -28818,7 +28818,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>8.70646858215332</v>
+        <v>8.70646953582764</v>
       </c>
       <c r="H981" t="n">
         <v>84618</v>
@@ -28847,7 +28847,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G982" t="n">
-        <v>9.06124687194824</v>
+        <v>9.06124782562256</v>
       </c>
       <c r="H982" t="n">
         <v>377749</v>
@@ -28934,7 +28934,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G985" t="n">
-        <v>9.30096340179443</v>
+        <v>9.30096435546875</v>
       </c>
       <c r="H985" t="n">
         <v>92687</v>
@@ -28963,7 +28963,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>9.39685153961182</v>
+        <v>9.3968505859375</v>
       </c>
       <c r="H986" t="n">
         <v>32732</v>
@@ -28992,7 +28992,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G987" t="n">
-        <v>9.36808586120605</v>
+        <v>9.36808490753174</v>
       </c>
       <c r="H987" t="n">
         <v>46850</v>
@@ -29050,7 +29050,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>9.46396923065186</v>
+        <v>9.46397018432617</v>
       </c>
       <c r="H989" t="n">
         <v>37821</v>
@@ -29079,7 +29079,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G990" t="n">
-        <v>9.44479274749756</v>
+        <v>9.44479465484619</v>
       </c>
       <c r="H990" t="n">
         <v>30039</v>
@@ -29108,7 +29108,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>9.43520450592041</v>
+        <v>9.43520355224609</v>
       </c>
       <c r="H991" t="n">
         <v>20599</v>
@@ -29137,7 +29137,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G992" t="n">
-        <v>9.93381214141846</v>
+        <v>9.93381309509277</v>
       </c>
       <c r="H992" t="n">
         <v>181815</v>
@@ -29195,7 +29195,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G994" t="n">
-        <v>9.95298957824707</v>
+        <v>9.95299053192139</v>
       </c>
       <c r="H994" t="n">
         <v>86253</v>
@@ -29282,7 +29282,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G997" t="n">
-        <v>9.85710430145264</v>
+        <v>9.85710334777832</v>
       </c>
       <c r="H997" t="n">
         <v>48818</v>
@@ -29340,7 +29340,7 @@
         <v>10</v>
       </c>
       <c r="G999" t="n">
-        <v>9.588623046875</v>
+        <v>9.58862113952637</v>
       </c>
       <c r="H999" t="n">
         <v>123572</v>
@@ -29369,7 +29369,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.52150249481201</v>
+        <v>9.52150344848633</v>
       </c>
       <c r="H1000" t="n">
         <v>33125</v>
@@ -29427,7 +29427,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.62697696685791</v>
+        <v>9.62697601318359</v>
       </c>
       <c r="H1002" t="n">
         <v>17662</v>
@@ -29485,7 +29485,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.49273681640625</v>
+        <v>9.49273586273193</v>
       </c>
       <c r="H1004" t="n">
         <v>39216</v>
@@ -29514,7 +29514,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.36808586120605</v>
+        <v>9.36808490753174</v>
       </c>
       <c r="H1005" t="n">
         <v>18745</v>
@@ -29601,7 +29601,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.78039360046387</v>
+        <v>9.78039455413818</v>
       </c>
       <c r="H1008" t="n">
         <v>132458</v>
@@ -29630,7 +29630,7 @@
         <v>10</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.588623046875</v>
+        <v>9.58862113952637</v>
       </c>
       <c r="H1009" t="n">
         <v>108249</v>
@@ -29804,7 +29804,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.26260948181152</v>
+        <v>9.26261043548584</v>
       </c>
       <c r="H1015" t="n">
         <v>14351</v>
@@ -29833,7 +29833,7 @@
         <v>9.75</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.34890747070312</v>
+        <v>9.34890651702881</v>
       </c>
       <c r="H1016" t="n">
         <v>29951</v>
@@ -29862,7 +29862,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.36808586120605</v>
+        <v>9.36808490753174</v>
       </c>
       <c r="H1017" t="n">
         <v>13706</v>
@@ -29891,7 +29891,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.29137420654297</v>
+        <v>9.29137516021729</v>
       </c>
       <c r="H1018" t="n">
         <v>27497</v>
@@ -30036,7 +30036,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>9.55026817321777</v>
+        <v>9.55026912689209</v>
       </c>
       <c r="H1023" t="n">
         <v>22522</v>
@@ -30094,7 +30094,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>9.0324821472168</v>
+        <v>9.03248310089111</v>
       </c>
       <c r="H1025" t="n">
         <v>546034</v>
@@ -30181,7 +30181,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.0324821472168</v>
+        <v>9.03248310089111</v>
       </c>
       <c r="H1028" t="n">
         <v>31478</v>
@@ -30268,7 +30268,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.9941291809082</v>
+        <v>8.99412822723389</v>
       </c>
       <c r="H1031" t="n">
         <v>17377</v>
@@ -30297,7 +30297,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.02289485931396</v>
+        <v>9.02289390563965</v>
       </c>
       <c r="H1032" t="n">
         <v>14861</v>
@@ -30384,7 +30384,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1035" t="n">
-        <v>8.85988807678223</v>
+        <v>8.85988712310791</v>
       </c>
       <c r="H1035" t="n">
         <v>11961</v>
@@ -30500,7 +30500,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.85988807678223</v>
+        <v>8.85988712310791</v>
       </c>
       <c r="H1039" t="n">
         <v>29809</v>
@@ -30616,7 +30616,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1043" t="n">
-        <v>9.06124687194824</v>
+        <v>9.06124782562256</v>
       </c>
       <c r="H1043" t="n">
         <v>32041</v>
@@ -30645,7 +30645,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>9.07083702087402</v>
+        <v>9.07083606719971</v>
       </c>
       <c r="H1044" t="n">
         <v>9950</v>
@@ -30703,7 +30703,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1046" t="n">
-        <v>9.06124687194824</v>
+        <v>9.06124782562256</v>
       </c>
       <c r="H1046" t="n">
         <v>15095</v>
@@ -30732,7 +30732,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1047" t="n">
-        <v>9.06124687194824</v>
+        <v>9.06124782562256</v>
       </c>
       <c r="H1047" t="n">
         <v>17655</v>
@@ -30761,7 +30761,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.96536064147949</v>
+        <v>8.96536254882812</v>
       </c>
       <c r="H1048" t="n">
         <v>17759</v>
@@ -30906,7 +30906,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1053" t="n">
-        <v>8.16950702667236</v>
+        <v>8.16950607299805</v>
       </c>
       <c r="H1053" t="n">
         <v>67960</v>
@@ -30935,7 +30935,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1054" t="n">
-        <v>8.24621677398682</v>
+        <v>8.2462158203125</v>
       </c>
       <c r="H1054" t="n">
         <v>30484</v>
@@ -31022,7 +31022,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.76678514480591</v>
+        <v>7.76678466796875</v>
       </c>
       <c r="H1057" t="n">
         <v>69417</v>
@@ -31109,7 +31109,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.45994806289673</v>
+        <v>7.45994901657104</v>
       </c>
       <c r="H1060" t="n">
         <v>74981</v>
@@ -31167,7 +31167,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.27776479721069</v>
+        <v>7.27776432037354</v>
       </c>
       <c r="H1062" t="n">
         <v>45137</v>
@@ -31254,7 +31254,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.38602209091187</v>
+        <v>6.38602256774902</v>
       </c>
       <c r="H1065" t="n">
         <v>72656</v>
@@ -31341,7 +31341,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.4970645904541</v>
+        <v>4.49706411361694</v>
       </c>
       <c r="H1068" t="n">
         <v>203507</v>
@@ -31370,7 +31370,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.6025390625</v>
+        <v>4.60253858566284</v>
       </c>
       <c r="H1069" t="n">
         <v>61375</v>
@@ -31428,7 +31428,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.47788667678833</v>
+        <v>4.47788715362549</v>
       </c>
       <c r="H1071" t="n">
         <v>30778</v>
@@ -31457,7 +31457,7 @@
         <v>5</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.7943115234375</v>
+        <v>4.79431056976318</v>
       </c>
       <c r="H1072" t="n">
         <v>58945</v>
@@ -31515,7 +31515,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.46551418304443</v>
+        <v>5.46551465988159</v>
       </c>
       <c r="H1074" t="n">
         <v>49730</v>
@@ -31544,7 +31544,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.98330068588257</v>
+        <v>5.98330020904541</v>
       </c>
       <c r="H1075" t="n">
         <v>73699</v>
@@ -31573,7 +31573,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.9449462890625</v>
+        <v>5.94494533538818</v>
       </c>
       <c r="H1076" t="n">
         <v>32019</v>
@@ -31602,7 +31602,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.92576885223389</v>
+        <v>5.92576837539673</v>
       </c>
       <c r="H1077" t="n">
         <v>18590</v>
@@ -31631,7 +31631,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.98330068588257</v>
+        <v>5.98330020904541</v>
       </c>
       <c r="H1078" t="n">
         <v>15736</v>
@@ -31660,7 +31660,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.82988262176514</v>
+        <v>5.82988214492798</v>
       </c>
       <c r="H1079" t="n">
         <v>49747</v>
@@ -31689,7 +31689,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.74358510971069</v>
+        <v>5.74358558654785</v>
       </c>
       <c r="H1080" t="n">
         <v>16778</v>
@@ -31747,7 +31747,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.93535709381104</v>
+        <v>5.93535757064819</v>
       </c>
       <c r="H1082" t="n">
         <v>11998</v>
@@ -31834,7 +31834,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.38602209091187</v>
+        <v>6.38602256774902</v>
       </c>
       <c r="H1085" t="n">
         <v>14540</v>
@@ -31950,7 +31950,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.36684560775757</v>
+        <v>6.36684513092041</v>
       </c>
       <c r="H1089" t="n">
         <v>11544</v>
@@ -31979,7 +31979,7 @@
         <v>6.75</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.47232007980347</v>
+        <v>6.47232055664062</v>
       </c>
       <c r="H1090" t="n">
         <v>14073</v>
@@ -32008,7 +32008,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.48190927505493</v>
+        <v>6.48190879821777</v>
       </c>
       <c r="H1091" t="n">
         <v>19667</v>
@@ -32037,7 +32037,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.48190927505493</v>
+        <v>6.48190879821777</v>
       </c>
       <c r="H1092" t="n">
         <v>11084</v>
@@ -32095,7 +32095,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.92020225524902</v>
+        <v>7.92020273208618</v>
       </c>
       <c r="H1094" t="n">
         <v>133533</v>
@@ -32124,7 +32124,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.76678514480591</v>
+        <v>7.76678466796875</v>
       </c>
       <c r="H1095" t="n">
         <v>41464</v>
@@ -32182,7 +32182,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.4791259765625</v>
+        <v>7.47912549972534</v>
       </c>
       <c r="H1097" t="n">
         <v>43748</v>
@@ -32211,7 +32211,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1098" t="n">
-        <v>7.4791259765625</v>
+        <v>7.47912549972534</v>
       </c>
       <c r="H1098" t="n">
         <v>16310</v>
@@ -32269,7 +32269,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.4791259765625</v>
+        <v>7.47912549972534</v>
       </c>
       <c r="H1100" t="n">
         <v>11453</v>
@@ -32414,7 +32414,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.1243462562561</v>
+        <v>7.12434577941895</v>
       </c>
       <c r="H1105" t="n">
         <v>28348</v>
@@ -32443,7 +32443,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.33529663085938</v>
+        <v>7.33529615402222</v>
       </c>
       <c r="H1106" t="n">
         <v>19098</v>
@@ -32472,7 +32472,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.21064424514771</v>
+        <v>7.21064376831055</v>
       </c>
       <c r="H1107" t="n">
         <v>25477</v>
@@ -32501,7 +32501,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1108" t="n">
         <v>17297</v>
@@ -32530,7 +32530,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1109" t="n">
-        <v>7.21064424514771</v>
+        <v>7.21064376831055</v>
       </c>
       <c r="H1109" t="n">
         <v>9899</v>
@@ -32559,7 +32559,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.42159366607666</v>
+        <v>7.42159414291382</v>
       </c>
       <c r="H1110" t="n">
         <v>15343</v>
@@ -32588,7 +32588,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.39282894134521</v>
+        <v>7.39282846450806</v>
       </c>
       <c r="H1111" t="n">
         <v>7992</v>
@@ -32762,7 +32762,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H1117" t="n">
         <v>14731</v>
@@ -32791,7 +32791,7 @@
         <v>8.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H1118" t="n">
         <v>16629</v>
@@ -32849,7 +32849,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1120" t="n">
-        <v>7.85308074951172</v>
+        <v>7.85308122634888</v>
       </c>
       <c r="H1120" t="n">
         <v>7527</v>
@@ -32878,7 +32878,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.96814489364624</v>
+        <v>7.96814680099487</v>
       </c>
       <c r="H1121" t="n">
         <v>15248</v>
@@ -32907,7 +32907,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.88184785842896</v>
+        <v>7.8818473815918</v>
       </c>
       <c r="H1122" t="n">
         <v>14416</v>
@@ -32965,7 +32965,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.90102481842041</v>
+        <v>7.90102577209473</v>
       </c>
       <c r="H1124" t="n">
         <v>17606</v>
@@ -33023,7 +33023,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>7.83390474319458</v>
+        <v>7.83390426635742</v>
       </c>
       <c r="H1126" t="n">
         <v>17349</v>
@@ -33052,7 +33052,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1127" t="n">
-        <v>7.7763729095459</v>
+        <v>7.77637243270874</v>
       </c>
       <c r="H1127" t="n">
         <v>6292</v>
@@ -33081,7 +33081,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1128" t="n">
-        <v>7.25858688354492</v>
+        <v>7.25858736038208</v>
       </c>
       <c r="H1128" t="n">
         <v>57871</v>
@@ -33110,7 +33110,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1129" t="n">
         <v>27324</v>
@@ -33255,7 +33255,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1134" t="n">
-        <v>7.4791259765625</v>
+        <v>7.47912549972534</v>
       </c>
       <c r="H1134" t="n">
         <v>16708</v>
@@ -33284,7 +33284,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1135" t="n">
-        <v>7.4791259765625</v>
+        <v>7.47912549972534</v>
       </c>
       <c r="H1135" t="n">
         <v>11552</v>
@@ -33313,7 +33313,7 @@
         <v>7.75</v>
       </c>
       <c r="G1136" t="n">
-        <v>7.43118238449097</v>
+        <v>7.43118190765381</v>
       </c>
       <c r="H1136" t="n">
         <v>14241</v>
@@ -33342,7 +33342,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>7.24899816513062</v>
+        <v>7.24899911880493</v>
       </c>
       <c r="H1137" t="n">
         <v>6370</v>
@@ -33371,7 +33371,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.23941040039062</v>
+        <v>7.23940992355347</v>
       </c>
       <c r="H1138" t="n">
         <v>6166</v>
@@ -33400,7 +33400,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1139" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1139" t="n">
         <v>5368</v>
@@ -33429,7 +33429,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1140" t="n">
-        <v>7.16270112991333</v>
+        <v>7.16270065307617</v>
       </c>
       <c r="H1140" t="n">
         <v>13726</v>
@@ -33458,7 +33458,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1141" t="n">
-        <v>7.24899816513062</v>
+        <v>7.24899911880493</v>
       </c>
       <c r="H1141" t="n">
         <v>6738</v>
@@ -33487,7 +33487,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1142" t="n">
-        <v>7.45035982131958</v>
+        <v>7.45035934448242</v>
       </c>
       <c r="H1142" t="n">
         <v>23941</v>
@@ -33574,7 +33574,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>7.31611919403076</v>
+        <v>7.3161187171936</v>
       </c>
       <c r="H1145" t="n">
         <v>8629</v>
@@ -33603,7 +33603,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>7.21064424514771</v>
+        <v>7.21064376831055</v>
       </c>
       <c r="H1146" t="n">
         <v>14786</v>
@@ -33632,7 +33632,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>7.21064424514771</v>
+        <v>7.21064376831055</v>
       </c>
       <c r="H1147" t="n">
         <v>8192</v>
@@ -33661,7 +33661,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1148" t="n">
-        <v>7.26817607879639</v>
+        <v>7.26817560195923</v>
       </c>
       <c r="H1148" t="n">
         <v>5586</v>
@@ -33719,7 +33719,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1150" t="n">
         <v>9807</v>
@@ -33748,7 +33748,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.287353515625</v>
+        <v>7.28735303878784</v>
       </c>
       <c r="H1151" t="n">
         <v>18719</v>
@@ -33951,7 +33951,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.4791259765625</v>
+        <v>7.47912549972534</v>
       </c>
       <c r="H1158" t="n">
         <v>7319</v>
@@ -34125,7 +34125,7 @@
         <v>7.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1164" t="n">
         <v>4750</v>
@@ -34154,7 +34154,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>7.287353515625</v>
+        <v>7.28735303878784</v>
       </c>
       <c r="H1165" t="n">
         <v>7319</v>
@@ -34299,7 +34299,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1170" t="n">
-        <v>7.81472682952881</v>
+        <v>7.81472730636597</v>
       </c>
       <c r="H1170" t="n">
         <v>20528</v>
@@ -34328,7 +34328,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1171" t="n">
-        <v>7.92020225524902</v>
+        <v>7.92020273208618</v>
       </c>
       <c r="H1171" t="n">
         <v>32382</v>
@@ -34357,7 +34357,7 @@
         <v>8.25</v>
       </c>
       <c r="G1172" t="n">
-        <v>7.91061401367188</v>
+        <v>7.91061353683472</v>
       </c>
       <c r="H1172" t="n">
         <v>25185</v>
@@ -34386,7 +34386,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1173" t="n">
-        <v>7.79554986953735</v>
+        <v>7.79555082321167</v>
       </c>
       <c r="H1173" t="n">
         <v>18265</v>
@@ -34415,7 +34415,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1174" t="n">
-        <v>7.75719547271729</v>
+        <v>7.75719594955444</v>
       </c>
       <c r="H1174" t="n">
         <v>2998</v>
@@ -34444,7 +34444,7 @@
         <v>8</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.67089796066284</v>
+        <v>7.6708984375</v>
       </c>
       <c r="H1175" t="n">
         <v>7301</v>
@@ -34473,7 +34473,7 @@
         <v>8</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.67089796066284</v>
+        <v>7.6708984375</v>
       </c>
       <c r="H1176" t="n">
         <v>5528</v>
@@ -34560,7 +34560,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1179" t="n">
-        <v>7.66130971908569</v>
+        <v>7.66130924224854</v>
       </c>
       <c r="H1179" t="n">
         <v>2679</v>
@@ -34647,7 +34647,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1182" t="n">
-        <v>7.66130971908569</v>
+        <v>7.66130924224854</v>
       </c>
       <c r="H1182" t="n">
         <v>7015</v>
@@ -34734,7 +34734,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1185" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1185" t="n">
         <v>10048</v>
@@ -34792,7 +34792,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1187" t="n">
-        <v>7.45994806289673</v>
+        <v>7.45994901657104</v>
       </c>
       <c r="H1187" t="n">
         <v>4524</v>
@@ -34821,7 +34821,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1188" t="n">
-        <v>7.45994806289673</v>
+        <v>7.45994901657104</v>
       </c>
       <c r="H1188" t="n">
         <v>10413</v>
@@ -34850,7 +34850,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>7.26817607879639</v>
+        <v>7.26817560195923</v>
       </c>
       <c r="H1189" t="n">
         <v>8883</v>
@@ -34908,7 +34908,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.39282894134521</v>
+        <v>7.39282846450806</v>
       </c>
       <c r="H1191" t="n">
         <v>7483</v>
@@ -34937,7 +34937,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1192" t="n">
-        <v>7.42159366607666</v>
+        <v>7.42159414291382</v>
       </c>
       <c r="H1192" t="n">
         <v>7775</v>
@@ -34966,7 +34966,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1193" t="n">
-        <v>7.45035982131958</v>
+        <v>7.45035934448242</v>
       </c>
       <c r="H1193" t="n">
         <v>9071</v>
@@ -35053,7 +35053,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1196" t="n">
-        <v>7.29694175720215</v>
+        <v>7.29694223403931</v>
       </c>
       <c r="H1196" t="n">
         <v>5328</v>
@@ -35082,7 +35082,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>7.24899816513062</v>
+        <v>7.24899911880493</v>
       </c>
       <c r="H1197" t="n">
         <v>4694</v>
@@ -35140,7 +35140,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1199" t="n">
-        <v>7.29694175720215</v>
+        <v>7.29694223403931</v>
       </c>
       <c r="H1199" t="n">
         <v>4893</v>
@@ -35198,7 +35198,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1201" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1201" t="n">
         <v>11586</v>
@@ -35256,7 +35256,7 @@
         <v>7.5</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1203" t="n">
         <v>3700</v>
@@ -35285,7 +35285,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1204" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1204" t="n">
         <v>3411</v>
@@ -35314,7 +35314,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1205" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1205" t="n">
         <v>7145</v>
@@ -35343,7 +35343,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1206" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1206" t="n">
         <v>10032</v>
@@ -35372,7 +35372,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.05722665786743</v>
+        <v>7.05722570419312</v>
       </c>
       <c r="H1207" t="n">
         <v>10822</v>
@@ -35488,7 +35488,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.287353515625</v>
+        <v>7.28735303878784</v>
       </c>
       <c r="H1211" t="n">
         <v>3493</v>
@@ -35517,7 +35517,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1212" t="n">
-        <v>7.27776479721069</v>
+        <v>7.27776432037354</v>
       </c>
       <c r="H1212" t="n">
         <v>4524</v>
@@ -35546,7 +35546,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.63254308700562</v>
+        <v>7.63254356384277</v>
       </c>
       <c r="H1213" t="n">
         <v>12003</v>
@@ -35778,7 +35778,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1221" t="n">
-        <v>7.63254308700562</v>
+        <v>7.63254356384277</v>
       </c>
       <c r="H1221" t="n">
         <v>9632</v>
@@ -35836,7 +35836,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.59418916702271</v>
+        <v>7.59418869018555</v>
       </c>
       <c r="H1223" t="n">
         <v>10123</v>
@@ -35894,7 +35894,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.287353515625</v>
+        <v>7.28735303878784</v>
       </c>
       <c r="H1225" t="n">
         <v>10976</v>
@@ -35952,7 +35952,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1227" t="n">
-        <v>7.07640314102173</v>
+        <v>7.07640361785889</v>
       </c>
       <c r="H1227" t="n">
         <v>11619</v>
@@ -36010,7 +36010,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1229" t="n">
-        <v>7.03804922103882</v>
+        <v>7.03804969787598</v>
       </c>
       <c r="H1229" t="n">
         <v>8972</v>
@@ -36068,7 +36068,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>7.03804922103882</v>
+        <v>7.03804969787598</v>
       </c>
       <c r="H1231" t="n">
         <v>10854</v>
@@ -36155,7 +36155,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1234" t="n">
         <v>48477</v>
@@ -36184,7 +36184,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>7.287353515625</v>
+        <v>7.28735303878784</v>
       </c>
       <c r="H1235" t="n">
         <v>15274</v>
@@ -36213,7 +36213,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1236" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1236" t="n">
         <v>14812</v>
@@ -36300,7 +36300,7 @@
         <v>7.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1239" t="n">
         <v>4019</v>
@@ -36387,7 +36387,7 @@
         <v>7.75</v>
       </c>
       <c r="G1242" t="n">
-        <v>7.43118238449097</v>
+        <v>7.43118190765381</v>
       </c>
       <c r="H1242" t="n">
         <v>25704</v>
@@ -36416,7 +36416,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.45994806289673</v>
+        <v>7.45994901657104</v>
       </c>
       <c r="H1243" t="n">
         <v>7069</v>
@@ -36503,7 +36503,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1246" t="n">
-        <v>7.33529663085938</v>
+        <v>7.33529615402222</v>
       </c>
       <c r="H1246" t="n">
         <v>24527</v>
@@ -36532,7 +36532,7 @@
         <v>7.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1247" t="n">
         <v>70831</v>
@@ -36590,7 +36590,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.17228984832764</v>
+        <v>7.17228937149048</v>
       </c>
       <c r="H1249" t="n">
         <v>16744</v>
@@ -36677,7 +36677,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1252" t="n">
-        <v>7.1243462562561</v>
+        <v>7.12434577941895</v>
       </c>
       <c r="H1252" t="n">
         <v>27846</v>
@@ -36706,7 +36706,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.13393449783325</v>
+        <v>7.13393497467041</v>
       </c>
       <c r="H1253" t="n">
         <v>18347</v>
@@ -36764,7 +36764,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.1243462562561</v>
+        <v>7.12434577941895</v>
       </c>
       <c r="H1255" t="n">
         <v>6276</v>
@@ -36822,7 +36822,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1257" t="n">
         <v>14991</v>
@@ -36851,7 +36851,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1258" t="n">
         <v>14313</v>
@@ -36909,7 +36909,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1260" t="n">
         <v>6601</v>
@@ -36938,7 +36938,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1261" t="n">
         <v>12140</v>
@@ -36996,7 +36996,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1263" t="n">
-        <v>7.0955810546875</v>
+        <v>7.09558057785034</v>
       </c>
       <c r="H1263" t="n">
         <v>7829</v>
@@ -37025,7 +37025,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1264" t="n">
-        <v>7.1243462562561</v>
+        <v>7.12434577941895</v>
       </c>
       <c r="H1264" t="n">
         <v>14543</v>
@@ -37199,7 +37199,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.55583477020264</v>
+        <v>7.55583429336548</v>
       </c>
       <c r="H1270" t="n">
         <v>20552</v>
@@ -37257,7 +37257,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1272" t="n">
-        <v>7.29694175720215</v>
+        <v>7.29694223403931</v>
       </c>
       <c r="H1272" t="n">
         <v>18970</v>
@@ -37286,7 +37286,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1273" t="n">
-        <v>7.33529663085938</v>
+        <v>7.33529615402222</v>
       </c>
       <c r="H1273" t="n">
         <v>7536</v>
@@ -37315,7 +37315,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.287353515625</v>
+        <v>7.28735303878784</v>
       </c>
       <c r="H1274" t="n">
         <v>11863</v>
@@ -37344,7 +37344,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.26817607879639</v>
+        <v>7.26817560195923</v>
       </c>
       <c r="H1275" t="n">
         <v>6153</v>
@@ -37373,7 +37373,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1276" t="n">
         <v>13327</v>
@@ -37402,7 +37402,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1277" t="n">
-        <v>7.37365055084229</v>
+        <v>7.37365102767944</v>
       </c>
       <c r="H1277" t="n">
         <v>18713</v>
@@ -37431,7 +37431,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>7.33529663085938</v>
+        <v>7.33529615402222</v>
       </c>
       <c r="H1278" t="n">
         <v>15364</v>
@@ -37460,7 +37460,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1279" t="n">
-        <v>7.23941040039062</v>
+        <v>7.23940992355347</v>
       </c>
       <c r="H1279" t="n">
         <v>7842</v>
@@ -37489,7 +37489,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.287353515625</v>
+        <v>7.28735303878784</v>
       </c>
       <c r="H1280" t="n">
         <v>7941</v>
@@ -37518,7 +37518,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.21064424514771</v>
+        <v>7.21064376831055</v>
       </c>
       <c r="H1281" t="n">
         <v>8529</v>
@@ -37605,7 +37605,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1284" t="n">
-        <v>7.17228984832764</v>
+        <v>7.17228937149048</v>
       </c>
       <c r="H1284" t="n">
         <v>3373</v>
@@ -37866,7 +37866,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.91339731216431</v>
+        <v>6.91339683532715</v>
       </c>
       <c r="H1293" t="n">
         <v>8592</v>
@@ -37895,7 +37895,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.99969482421875</v>
+        <v>6.99969434738159</v>
       </c>
       <c r="H1294" t="n">
         <v>7750</v>
@@ -37924,7 +37924,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.03804922103882</v>
+        <v>7.03804969787598</v>
       </c>
       <c r="H1295" t="n">
         <v>41692</v>
@@ -37953,7 +37953,7 @@
         <v>7.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1296" t="n">
         <v>66724</v>
@@ -37982,7 +37982,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1297" t="n">
-        <v>7.05722665786743</v>
+        <v>7.05722570419312</v>
       </c>
       <c r="H1297" t="n">
         <v>80201</v>
@@ -38098,7 +38098,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1301" t="n">
-        <v>6.99969482421875</v>
+        <v>6.99969434738159</v>
       </c>
       <c r="H1301" t="n">
         <v>11968</v>
@@ -38185,7 +38185,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.80792140960693</v>
+        <v>6.80792188644409</v>
       </c>
       <c r="H1304" t="n">
         <v>25146</v>
@@ -38272,7 +38272,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1307" t="n">
-        <v>6.75997877120972</v>
+        <v>6.75997924804688</v>
       </c>
       <c r="H1307" t="n">
         <v>31707</v>
@@ -38301,7 +38301,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1308" t="n">
-        <v>6.74080181121826</v>
+        <v>6.74080228805542</v>
       </c>
       <c r="H1308" t="n">
         <v>10265</v>
@@ -38359,7 +38359,7 @@
         <v>7</v>
       </c>
       <c r="G1310" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1310" t="n">
         <v>10747</v>
@@ -38388,7 +38388,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.80792140960693</v>
+        <v>6.80792188644409</v>
       </c>
       <c r="H1311" t="n">
         <v>9606</v>
@@ -38417,7 +38417,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1312" t="n">
-        <v>6.80792140960693</v>
+        <v>6.80792188644409</v>
       </c>
       <c r="H1312" t="n">
         <v>37179</v>
@@ -38446,7 +38446,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1313" t="n">
-        <v>6.80792140960693</v>
+        <v>6.80792188644409</v>
       </c>
       <c r="H1313" t="n">
         <v>13271</v>
@@ -38475,7 +38475,7 @@
         <v>7</v>
       </c>
       <c r="G1314" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1314" t="n">
         <v>14334</v>
@@ -38533,7 +38533,7 @@
         <v>7</v>
       </c>
       <c r="G1316" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1316" t="n">
         <v>25428</v>
@@ -38620,7 +38620,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>6.75039005279541</v>
+        <v>6.75038957595825</v>
       </c>
       <c r="H1319" t="n">
         <v>33588</v>
@@ -38649,7 +38649,7 @@
         <v>7</v>
       </c>
       <c r="G1320" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1320" t="n">
         <v>27563</v>
@@ -38707,7 +38707,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1322" t="n">
-        <v>6.69285869598389</v>
+        <v>6.69285917282104</v>
       </c>
       <c r="H1322" t="n">
         <v>29473</v>
@@ -38736,7 +38736,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>6.67368173599243</v>
+        <v>6.67368125915527</v>
       </c>
       <c r="H1323" t="n">
         <v>39564</v>
@@ -38765,7 +38765,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1324" t="n">
-        <v>6.56820631027222</v>
+        <v>6.56820678710938</v>
       </c>
       <c r="H1324" t="n">
         <v>79422</v>
@@ -38794,7 +38794,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1325" t="n">
-        <v>6.48190927505493</v>
+        <v>6.48190879821777</v>
       </c>
       <c r="H1325" t="n">
         <v>35932</v>
@@ -38852,7 +38852,7 @@
         <v>7</v>
       </c>
       <c r="G1327" t="n">
-        <v>6.71203517913818</v>
+        <v>6.71203565597534</v>
       </c>
       <c r="H1327" t="n">
         <v>39534</v>
@@ -38910,7 +38910,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1329" t="n">
-        <v>7.25858688354492</v>
+        <v>7.25858736038208</v>
       </c>
       <c r="H1329" t="n">
         <v>74996</v>
@@ -38997,7 +38997,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>7.26817607879639</v>
+        <v>7.26817560195923</v>
       </c>
       <c r="H1332" t="n">
         <v>92492</v>
@@ -39055,7 +39055,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1334" t="n">
-        <v>7.27776479721069</v>
+        <v>7.27776432037354</v>
       </c>
       <c r="H1334" t="n">
         <v>31376</v>
@@ -39113,7 +39113,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1336" t="n">
-        <v>7.25858688354492</v>
+        <v>7.25858736038208</v>
       </c>
       <c r="H1336" t="n">
         <v>13765</v>
@@ -39142,7 +39142,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1337" t="n">
-        <v>7.13393449783325</v>
+        <v>7.13393497467041</v>
       </c>
       <c r="H1337" t="n">
         <v>19451</v>
@@ -39171,7 +39171,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1338" t="n">
-        <v>7.13393449783325</v>
+        <v>7.13393497467041</v>
       </c>
       <c r="H1338" t="n">
         <v>17704</v>
@@ -39345,7 +39345,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1344" t="n">
-        <v>7.07640314102173</v>
+        <v>7.07640361785889</v>
       </c>
       <c r="H1344" t="n">
         <v>23487</v>
@@ -39432,7 +39432,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1347" t="n">
-        <v>6.99969482421875</v>
+        <v>6.99969434738159</v>
       </c>
       <c r="H1347" t="n">
         <v>23477</v>
@@ -39461,7 +39461,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1348" t="n">
-        <v>7.07640314102173</v>
+        <v>7.07640361785889</v>
       </c>
       <c r="H1348" t="n">
         <v>12530</v>
@@ -39490,7 +39490,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1349" t="n">
-        <v>7.05722665786743</v>
+        <v>7.05722570419312</v>
       </c>
       <c r="H1349" t="n">
         <v>27980</v>
@@ -39519,7 +39519,7 @@
         <v>7.5</v>
       </c>
       <c r="G1350" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1350" t="n">
         <v>27211</v>
@@ -39606,7 +39606,7 @@
         <v>7.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1353" t="n">
         <v>13043</v>
@@ -39635,7 +39635,7 @@
         <v>7.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1354" t="n">
         <v>10273</v>
@@ -39664,7 +39664,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1355" t="n">
-        <v>7.21064424514771</v>
+        <v>7.21064376831055</v>
       </c>
       <c r="H1355" t="n">
         <v>17746</v>
@@ -39722,7 +39722,7 @@
         <v>7.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>7.19146680831909</v>
+        <v>7.19146728515625</v>
       </c>
       <c r="H1357" t="n">
         <v>24316</v>
@@ -39751,7 +39751,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1358" t="n">
-        <v>7.25858688354492</v>
+        <v>7.25858736038208</v>
       </c>
       <c r="H1358" t="n">
         <v>30902</v>
@@ -39867,7 +39867,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1362" t="n">
-        <v>7.22002840042114</v>
+        <v>7.2200288772583</v>
       </c>
       <c r="H1362" t="n">
         <v>35733</v>
@@ -39925,7 +39925,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1364" t="n">
-        <v>7.11399364471436</v>
+        <v>7.11399412155151</v>
       </c>
       <c r="H1364" t="n">
         <v>25455</v>
@@ -39954,7 +39954,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1365" t="n">
-        <v>7.36462163925171</v>
+        <v>7.36462211608887</v>
       </c>
       <c r="H1365" t="n">
         <v>76455</v>
@@ -40128,7 +40128,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1371" t="n">
-        <v>7.39354085922241</v>
+        <v>7.39354133605957</v>
       </c>
       <c r="H1371" t="n">
         <v>8578</v>
@@ -40186,7 +40186,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>7.63453054428101</v>
+        <v>7.63453006744385</v>
       </c>
       <c r="H1373" t="n">
         <v>51355</v>
@@ -40215,7 +40215,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1374" t="n">
-        <v>7.75984477996826</v>
+        <v>7.7598443031311</v>
       </c>
       <c r="H1374" t="n">
         <v>93432</v>
@@ -40244,7 +40244,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1375" t="n">
-        <v>7.9911937713623</v>
+        <v>7.99119281768799</v>
       </c>
       <c r="H1375" t="n">
         <v>91240</v>
@@ -40273,7 +40273,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1376" t="n">
-        <v>7.9622745513916</v>
+        <v>7.96227550506592</v>
       </c>
       <c r="H1376" t="n">
         <v>29775</v>
@@ -40302,7 +40302,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1377" t="n">
-        <v>8.01047229766846</v>
+        <v>8.01047420501709</v>
       </c>
       <c r="H1377" t="n">
         <v>81575</v>
@@ -40331,7 +40331,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1378" t="n">
-        <v>7.93335628509521</v>
+        <v>7.9333553314209</v>
       </c>
       <c r="H1378" t="n">
         <v>30136</v>
@@ -40360,7 +40360,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1379" t="n">
-        <v>8.02011108398438</v>
+        <v>8.02011203765869</v>
       </c>
       <c r="H1379" t="n">
         <v>29104</v>
@@ -40447,7 +40447,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1382" t="n">
-        <v>8.05867099761963</v>
+        <v>8.058669090271</v>
       </c>
       <c r="H1382" t="n">
         <v>14418</v>
@@ -40505,7 +40505,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1384" t="n">
-        <v>7.93335628509521</v>
+        <v>7.9333553314209</v>
       </c>
       <c r="H1384" t="n">
         <v>19918</v>
@@ -40563,7 +40563,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1386" t="n">
-        <v>7.81768178939819</v>
+        <v>7.81768131256104</v>
       </c>
       <c r="H1386" t="n">
         <v>34542</v>
@@ -40621,7 +40621,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>7.5284948348999</v>
+        <v>7.52849435806274</v>
       </c>
       <c r="H1388" t="n">
         <v>27983</v>
@@ -40766,7 +40766,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1393" t="n">
-        <v>7.5284948348999</v>
+        <v>7.52849435806274</v>
       </c>
       <c r="H1393" t="n">
         <v>11245</v>
@@ -40795,7 +40795,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1394" t="n">
-        <v>7.48029708862305</v>
+        <v>7.48029756546021</v>
       </c>
       <c r="H1394" t="n">
         <v>10328</v>
@@ -40969,7 +40969,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1400" t="n">
-        <v>7.66344833374023</v>
+        <v>7.66344881057739</v>
       </c>
       <c r="H1400" t="n">
         <v>15557</v>
@@ -41143,7 +41143,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>7.63453054428101</v>
+        <v>7.63453006744385</v>
       </c>
       <c r="H1406" t="n">
         <v>11367</v>
@@ -41201,7 +41201,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.57669305801392</v>
+        <v>7.57669258117676</v>
       </c>
       <c r="H1408" t="n">
         <v>23551</v>
@@ -41259,7 +41259,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1410" t="n">
-        <v>7.53813457489014</v>
+        <v>7.53813505172729</v>
       </c>
       <c r="H1410" t="n">
         <v>4860</v>
@@ -41346,7 +41346,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1413" t="n">
-        <v>7.57669305801392</v>
+        <v>7.57669258117676</v>
       </c>
       <c r="H1413" t="n">
         <v>5439</v>
@@ -41375,7 +41375,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1414" t="n">
-        <v>7.57669305801392</v>
+        <v>7.57669258117676</v>
       </c>
       <c r="H1414" t="n">
         <v>18094</v>
@@ -41607,7 +41607,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>7.94299602508545</v>
+        <v>7.94299650192261</v>
       </c>
       <c r="H1422" t="n">
         <v>87984</v>
@@ -41665,7 +41665,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>7.86587905883789</v>
+        <v>7.86587953567505</v>
       </c>
       <c r="H1424" t="n">
         <v>22209</v>
@@ -41723,7 +41723,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1426" t="n">
-        <v>8.21290397644043</v>
+        <v>8.21290302276611</v>
       </c>
       <c r="H1426" t="n">
         <v>76699</v>
@@ -41752,7 +41752,7 @@
         <v>8.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>8.19362449645996</v>
+        <v>8.19362545013428</v>
       </c>
       <c r="H1427" t="n">
         <v>38648</v>
@@ -41810,7 +41810,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1429" t="n">
-        <v>8.00083351135254</v>
+        <v>8.00083255767822</v>
       </c>
       <c r="H1429" t="n">
         <v>21400</v>
@@ -41868,7 +41868,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1431" t="n">
-        <v>8.36713600158691</v>
+        <v>8.36713695526123</v>
       </c>
       <c r="H1431" t="n">
         <v>46746</v>
@@ -41897,7 +41897,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G1432" t="n">
-        <v>8.26110076904297</v>
+        <v>8.26110172271729</v>
       </c>
       <c r="H1432" t="n">
         <v>28919</v>
@@ -41926,7 +41926,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1433" t="n">
-        <v>8.29002094268799</v>
+        <v>8.29001998901367</v>
       </c>
       <c r="H1433" t="n">
         <v>11492</v>
@@ -41955,7 +41955,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G1434" t="n">
-        <v>8.26110076904297</v>
+        <v>8.26110172271729</v>
       </c>
       <c r="H1434" t="n">
         <v>27138</v>
@@ -41984,7 +41984,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>8.2707405090332</v>
+        <v>8.27073955535889</v>
       </c>
       <c r="H1435" t="n">
         <v>9431</v>
@@ -42013,7 +42013,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1436" t="n">
-        <v>8.36713600158691</v>
+        <v>8.36713695526123</v>
       </c>
       <c r="H1436" t="n">
         <v>23217</v>
@@ -42100,7 +42100,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1439" t="n">
-        <v>8.58884525299072</v>
+        <v>8.58884620666504</v>
       </c>
       <c r="H1439" t="n">
         <v>51639</v>
@@ -42158,7 +42158,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1441" t="n">
-        <v>8.73343944549561</v>
+        <v>8.73344039916992</v>
       </c>
       <c r="H1441" t="n">
         <v>48827</v>
@@ -42390,7 +42390,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1449" t="n">
-        <v>8.49245071411133</v>
+        <v>8.49244976043701</v>
       </c>
       <c r="H1449" t="n">
         <v>23199</v>
@@ -42419,7 +42419,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>8.47317123413086</v>
+        <v>8.47317218780518</v>
       </c>
       <c r="H1450" t="n">
         <v>41057</v>
@@ -42477,7 +42477,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.29002094268799</v>
+        <v>8.29001998901367</v>
       </c>
       <c r="H1452" t="n">
         <v>10486</v>
@@ -42535,7 +42535,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1454" t="n">
-        <v>8.16470718383789</v>
+        <v>8.16470623016357</v>
       </c>
       <c r="H1454" t="n">
         <v>29037</v>
@@ -42593,7 +42593,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1456" t="n">
-        <v>8.2418212890625</v>
+        <v>8.24182224273682</v>
       </c>
       <c r="H1456" t="n">
         <v>10344</v>
@@ -42680,7 +42680,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1459" t="n">
-        <v>8.47317123413086</v>
+        <v>8.47317218780518</v>
       </c>
       <c r="H1459" t="n">
         <v>43643</v>
@@ -42738,7 +42738,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.37677574157715</v>
+        <v>8.37677669525146</v>
       </c>
       <c r="H1461" t="n">
         <v>14312</v>
@@ -42912,7 +42912,7 @@
         <v>8.5</v>
       </c>
       <c r="G1467" t="n">
-        <v>8.19362449645996</v>
+        <v>8.19362545013428</v>
       </c>
       <c r="H1467" t="n">
         <v>5823</v>
@@ -42999,7 +42999,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.17434597015381</v>
+        <v>8.17434501647949</v>
       </c>
       <c r="H1470" t="n">
         <v>8266</v>
@@ -43028,7 +43028,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1471" t="n">
-        <v>8.2418212890625</v>
+        <v>8.24182224273682</v>
       </c>
       <c r="H1471" t="n">
         <v>8847</v>
@@ -43057,7 +43057,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1472" t="n">
-        <v>8.2418212890625</v>
+        <v>8.24182224273682</v>
       </c>
       <c r="H1472" t="n">
         <v>18495</v>
@@ -43115,7 +43115,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1474" t="n">
-        <v>8.25146102905273</v>
+        <v>8.25146198272705</v>
       </c>
       <c r="H1474" t="n">
         <v>13596</v>
@@ -43144,7 +43144,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1475" t="n">
-        <v>8.29002094268799</v>
+        <v>8.29001998901367</v>
       </c>
       <c r="H1475" t="n">
         <v>9087</v>
@@ -43173,7 +43173,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1476" t="n">
-        <v>8.55992889404297</v>
+        <v>8.55992698669434</v>
       </c>
       <c r="H1476" t="n">
         <v>24266</v>
@@ -43260,7 +43260,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.34785747528076</v>
+        <v>8.34785652160645</v>
       </c>
       <c r="H1479" t="n">
         <v>9600</v>
@@ -43289,7 +43289,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1480" t="n">
-        <v>8.424973487854</v>
+        <v>8.42497253417969</v>
       </c>
       <c r="H1480" t="n">
         <v>16185</v>
@@ -43318,7 +43318,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.47317123413086</v>
+        <v>8.47317218780518</v>
       </c>
       <c r="H1481" t="n">
         <v>32038</v>
@@ -43347,7 +43347,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.47317123413086</v>
+        <v>8.47317218780518</v>
       </c>
       <c r="H1482" t="n">
         <v>18487</v>
@@ -43405,7 +43405,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>8.75271797180176</v>
+        <v>8.75271892547607</v>
       </c>
       <c r="H1484" t="n">
         <v>22829</v>
@@ -43434,7 +43434,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.62740421295166</v>
+        <v>8.62740516662598</v>
       </c>
       <c r="H1485" t="n">
         <v>22493</v>
@@ -43463,7 +43463,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.76235771179199</v>
+        <v>8.76235866546631</v>
       </c>
       <c r="H1486" t="n">
         <v>64156</v>
@@ -43550,7 +43550,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.83234977722168</v>
+        <v>9.83234882354736</v>
       </c>
       <c r="H1489" t="n">
         <v>202866</v>
@@ -43579,7 +43579,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.65883827209473</v>
+        <v>9.65883731842041</v>
       </c>
       <c r="H1490" t="n">
         <v>227750</v>
@@ -43637,7 +43637,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1492" t="n">
-        <v>10.2179317474365</v>
+        <v>10.2179307937622</v>
       </c>
       <c r="H1492" t="n">
         <v>155817</v>
@@ -43724,7 +43724,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>10.2179317474365</v>
+        <v>10.2179307937622</v>
       </c>
       <c r="H1495" t="n">
         <v>47218</v>
@@ -43753,7 +43753,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1496" t="n">
-        <v>9.83234977722168</v>
+        <v>9.83234882354736</v>
       </c>
       <c r="H1496" t="n">
         <v>79737</v>
@@ -43840,7 +43840,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.32145309448242</v>
+        <v>9.32145214080811</v>
       </c>
       <c r="H1499" t="n">
         <v>52402</v>
@@ -43898,7 +43898,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>8.99370765686035</v>
+        <v>8.99370670318604</v>
       </c>
       <c r="H1501" t="n">
         <v>25088</v>
@@ -43927,7 +43927,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1502" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1502" t="n">
         <v>39812</v>
@@ -44043,7 +44043,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>9.23469543457031</v>
+        <v>9.23469638824463</v>
       </c>
       <c r="H1506" t="n">
         <v>39472</v>
@@ -44188,7 +44188,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1511" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1511" t="n">
         <v>14106</v>
@@ -44217,7 +44217,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1512" t="n">
-        <v>9.03226661682129</v>
+        <v>9.03226566314697</v>
       </c>
       <c r="H1512" t="n">
         <v>6322</v>
@@ -44333,7 +44333,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.84911441802979</v>
+        <v>8.84911346435547</v>
       </c>
       <c r="H1516" t="n">
         <v>6090</v>
@@ -44362,7 +44362,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1517" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1517" t="n">
         <v>6785</v>
@@ -44507,7 +44507,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G1522" t="n">
-        <v>9.53352355957031</v>
+        <v>9.533522605896</v>
       </c>
       <c r="H1522" t="n">
         <v>40110</v>
@@ -44594,7 +44594,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1525" t="n">
-        <v>9.73595333099365</v>
+        <v>9.73595428466797</v>
       </c>
       <c r="H1525" t="n">
         <v>40747</v>
@@ -44652,7 +44652,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1527" t="n">
-        <v>9.62027740478516</v>
+        <v>9.62027835845947</v>
       </c>
       <c r="H1527" t="n">
         <v>11338</v>
@@ -44884,7 +44884,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1535" t="n">
-        <v>9.12866115570068</v>
+        <v>9.128662109375</v>
       </c>
       <c r="H1535" t="n">
         <v>5802</v>
@@ -44913,7 +44913,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1536" t="n">
-        <v>9.14794158935547</v>
+        <v>9.14794063568115</v>
       </c>
       <c r="H1536" t="n">
         <v>6290</v>
@@ -44942,7 +44942,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1537" t="n">
-        <v>9.11902141571045</v>
+        <v>9.11902236938477</v>
       </c>
       <c r="H1537" t="n">
         <v>12343</v>
@@ -45029,7 +45029,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1540" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1540" t="n">
         <v>11975</v>
@@ -45087,7 +45087,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1542" t="n">
-        <v>8.49245071411133</v>
+        <v>8.49244976043701</v>
       </c>
       <c r="H1542" t="n">
         <v>30397</v>
@@ -45145,7 +45145,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1544" t="n">
-        <v>8.48281097412109</v>
+        <v>8.48281192779541</v>
       </c>
       <c r="H1544" t="n">
         <v>27721</v>
@@ -45174,7 +45174,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1545" t="n">
-        <v>8.41533374786377</v>
+        <v>8.41533279418945</v>
       </c>
       <c r="H1545" t="n">
         <v>39507</v>
@@ -45319,7 +45319,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1550" t="n">
-        <v>8.49245071411133</v>
+        <v>8.49244976043701</v>
       </c>
       <c r="H1550" t="n">
         <v>8206</v>
@@ -45377,7 +45377,7 @@
         <v>8.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>8.19362449645996</v>
+        <v>8.19362545013428</v>
       </c>
       <c r="H1552" t="n">
         <v>6027</v>
@@ -45435,7 +45435,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1554" t="n">
-        <v>8.2032642364502</v>
+        <v>8.20326328277588</v>
       </c>
       <c r="H1554" t="n">
         <v>19516</v>
@@ -45464,7 +45464,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1555" t="n">
-        <v>8.29965877532959</v>
+        <v>8.29965972900391</v>
       </c>
       <c r="H1555" t="n">
         <v>12973</v>
@@ -45522,7 +45522,7 @@
         <v>8.5</v>
       </c>
       <c r="G1557" t="n">
-        <v>8.19362449645996</v>
+        <v>8.19362545013428</v>
       </c>
       <c r="H1557" t="n">
         <v>36955</v>
@@ -45580,7 +45580,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>8.63704395294189</v>
+        <v>8.63704299926758</v>
       </c>
       <c r="H1559" t="n">
         <v>30021</v>
@@ -45638,7 +45638,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1561" t="n">
-        <v>8.2418212890625</v>
+        <v>8.24182224273682</v>
       </c>
       <c r="H1561" t="n">
         <v>19272</v>
@@ -45725,7 +45725,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1564" t="n">
-        <v>8.36713600158691</v>
+        <v>8.36713695526123</v>
       </c>
       <c r="H1564" t="n">
         <v>10713</v>
@@ -45754,7 +45754,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1565" t="n">
-        <v>7.9622745513916</v>
+        <v>7.96227550506592</v>
       </c>
       <c r="H1565" t="n">
         <v>65993</v>
@@ -45783,7 +45783,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>8.39605617523193</v>
+        <v>8.39605522155762</v>
       </c>
       <c r="H1566" t="n">
         <v>16663</v>
@@ -45841,7 +45841,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1568" t="n">
-        <v>8.29002094268799</v>
+        <v>8.29001998901367</v>
       </c>
       <c r="H1568" t="n">
         <v>25803</v>
@@ -45870,7 +45870,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1569" t="n">
-        <v>8.86839294433594</v>
+        <v>8.86839389801025</v>
       </c>
       <c r="H1569" t="n">
         <v>53572</v>
@@ -45899,7 +45899,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1570" t="n">
-        <v>8.48281097412109</v>
+        <v>8.48281192779541</v>
       </c>
       <c r="H1570" t="n">
         <v>29360</v>
@@ -45928,7 +45928,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.97191476821899</v>
+        <v>7.97191572189331</v>
       </c>
       <c r="H1571" t="n">
         <v>36480</v>
@@ -45986,7 +45986,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1573" t="n">
-        <v>8.08758926391602</v>
+        <v>8.08759021759033</v>
       </c>
       <c r="H1573" t="n">
         <v>26765</v>
@@ -46073,7 +46073,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1576" t="n">
-        <v>8.84911441802979</v>
+        <v>8.84911346435547</v>
       </c>
       <c r="H1576" t="n">
         <v>90671</v>
@@ -46189,7 +46189,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G1580" t="n">
-        <v>9.34073066711426</v>
+        <v>9.34073162078857</v>
       </c>
       <c r="H1580" t="n">
         <v>77589</v>
@@ -46247,7 +46247,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1582" t="n">
-        <v>9.7166748046875</v>
+        <v>9.71667385101318</v>
       </c>
       <c r="H1582" t="n">
         <v>61231</v>
@@ -46305,7 +46305,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1584" t="n">
-        <v>9.62027740478516</v>
+        <v>9.62027835845947</v>
       </c>
       <c r="H1584" t="n">
         <v>54310</v>
@@ -46363,7 +46363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1586" t="n">
-        <v>9.83234977722168</v>
+        <v>9.83234882354736</v>
       </c>
       <c r="H1586" t="n">
         <v>38157</v>
@@ -46392,7 +46392,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.89018821716309</v>
+        <v>9.89018726348877</v>
       </c>
       <c r="H1587" t="n">
         <v>28277</v>
@@ -46421,7 +46421,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1588" t="n">
-        <v>9.89018821716309</v>
+        <v>9.89018726348877</v>
       </c>
       <c r="H1588" t="n">
         <v>37635</v>
@@ -46479,7 +46479,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1590" t="n">
-        <v>9.42748832702637</v>
+        <v>9.42748737335205</v>
       </c>
       <c r="H1590" t="n">
         <v>47874</v>
@@ -46537,7 +46537,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1592" t="n">
-        <v>9.62027740478516</v>
+        <v>9.62027835845947</v>
       </c>
       <c r="H1592" t="n">
         <v>23592</v>
@@ -46624,7 +46624,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G1595" t="n">
-        <v>9.34073066711426</v>
+        <v>9.34073162078857</v>
       </c>
       <c r="H1595" t="n">
         <v>26279</v>
@@ -46653,7 +46653,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>9.23469543457031</v>
+        <v>9.23469638824463</v>
       </c>
       <c r="H1596" t="n">
         <v>7511</v>
@@ -46740,7 +46740,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1599" t="n">
-        <v>9.23469543457031</v>
+        <v>9.23469638824463</v>
       </c>
       <c r="H1599" t="n">
         <v>17410</v>
@@ -46798,7 +46798,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>9.2828950881958</v>
+        <v>9.28289413452148</v>
       </c>
       <c r="H1601" t="n">
         <v>6195</v>
@@ -47030,7 +47030,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1609" t="n">
-        <v>9.42748832702637</v>
+        <v>9.42748737335205</v>
       </c>
       <c r="H1609" t="n">
         <v>7673</v>
@@ -47059,7 +47059,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1610" t="n">
-        <v>9.23469543457031</v>
+        <v>9.23469638824463</v>
       </c>
       <c r="H1610" t="n">
         <v>15762</v>
@@ -47204,7 +47204,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1615" t="n">
-        <v>8.75271797180176</v>
+        <v>8.75271892547607</v>
       </c>
       <c r="H1615" t="n">
         <v>18017</v>
@@ -47291,7 +47291,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1618" t="n">
-        <v>9.73595333099365</v>
+        <v>9.73595428466797</v>
       </c>
       <c r="H1618" t="n">
         <v>66060</v>
@@ -47465,7 +47465,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1624" t="n">
-        <v>10.0636978149414</v>
+        <v>10.0636987686157</v>
       </c>
       <c r="H1624" t="n">
         <v>31476</v>
@@ -47494,7 +47494,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1625" t="n">
-        <v>9.98658180236816</v>
+        <v>9.98658275604248</v>
       </c>
       <c r="H1625" t="n">
         <v>7822</v>
@@ -47552,7 +47552,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1627" t="n">
-        <v>9.92874526977539</v>
+        <v>9.92874431610107</v>
       </c>
       <c r="H1627" t="n">
         <v>18262</v>
@@ -47581,7 +47581,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1628" t="n">
-        <v>9.94802474975586</v>
+        <v>9.94802379608154</v>
       </c>
       <c r="H1628" t="n">
         <v>11643</v>
@@ -47697,7 +47697,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1632" t="n">
-        <v>10.0636978149414</v>
+        <v>10.0636987686157</v>
       </c>
       <c r="H1632" t="n">
         <v>37505</v>
@@ -47726,7 +47726,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1633" t="n">
-        <v>10.0444202423096</v>
+        <v>10.0444192886353</v>
       </c>
       <c r="H1633" t="n">
         <v>6264</v>
@@ -47784,7 +47784,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1635" t="n">
-        <v>9.89018821716309</v>
+        <v>9.89018726348877</v>
       </c>
       <c r="H1635" t="n">
         <v>13661</v>
@@ -47842,7 +47842,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>9.92874526977539</v>
+        <v>9.92874431610107</v>
       </c>
       <c r="H1637" t="n">
         <v>7709</v>
@@ -47900,7 +47900,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1639" t="n">
-        <v>9.7166748046875</v>
+        <v>9.71667385101318</v>
       </c>
       <c r="H1639" t="n">
         <v>17704</v>
@@ -47987,7 +47987,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1642" t="n">
-        <v>9.2828950881958</v>
+        <v>9.28289413452148</v>
       </c>
       <c r="H1642" t="n">
         <v>16545</v>
@@ -48045,7 +48045,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.0129861831665</v>
+        <v>9.01298713684082</v>
       </c>
       <c r="H1644" t="n">
         <v>19098</v>
@@ -48190,7 +48190,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1649" t="n">
-        <v>9.54316329956055</v>
+        <v>9.54316234588623</v>
       </c>
       <c r="H1649" t="n">
         <v>17099</v>
@@ -48248,7 +48248,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1651" t="n">
-        <v>9.83234977722168</v>
+        <v>9.83234882354736</v>
       </c>
       <c r="H1651" t="n">
         <v>13022</v>
@@ -48306,7 +48306,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1653" t="n">
-        <v>10.2179317474365</v>
+        <v>10.2179307937622</v>
       </c>
       <c r="H1653" t="n">
         <v>102077</v>
@@ -48422,7 +48422,7 @@
         <v>11.5</v>
       </c>
       <c r="G1657" t="n">
-        <v>11.0854921340942</v>
+        <v>11.0854911804199</v>
       </c>
       <c r="H1657" t="n">
         <v>109178</v>
@@ -48451,7 +48451,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1658" t="n">
-        <v>11.1626081466675</v>
+        <v>11.1626071929932</v>
       </c>
       <c r="H1658" t="n">
         <v>60500</v>
@@ -48480,7 +48480,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1659" t="n">
-        <v>11.4710731506348</v>
+        <v>11.4710741043091</v>
       </c>
       <c r="H1659" t="n">
         <v>126220</v>
@@ -48567,7 +48567,7 @@
         <v>12</v>
       </c>
       <c r="G1662" t="n">
-        <v>11.5674686431885</v>
+        <v>11.5674695968628</v>
       </c>
       <c r="H1662" t="n">
         <v>35295</v>
@@ -48625,7 +48625,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1664" t="n">
-        <v>11.3168411254883</v>
+        <v>11.316840171814</v>
       </c>
       <c r="H1664" t="n">
         <v>32226</v>
@@ -48683,7 +48683,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1666" t="n">
-        <v>11.3361196517944</v>
+        <v>11.3361206054688</v>
       </c>
       <c r="H1666" t="n">
         <v>29632</v>
@@ -48741,7 +48741,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1668" t="n">
-        <v>11.0276546478271</v>
+        <v>11.0276536941528</v>
       </c>
       <c r="H1668" t="n">
         <v>19492</v>
@@ -48770,7 +48770,7 @@
         <v>11.5</v>
       </c>
       <c r="G1669" t="n">
-        <v>11.0854921340942</v>
+        <v>11.0854911804199</v>
       </c>
       <c r="H1669" t="n">
         <v>16263</v>
@@ -48886,7 +48886,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1673" t="n">
-        <v>11.5096321105957</v>
+        <v>11.50963306427</v>
       </c>
       <c r="H1673" t="n">
         <v>12840</v>
@@ -48915,7 +48915,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1674" t="n">
-        <v>11.3746786117554</v>
+        <v>11.3746776580811</v>
       </c>
       <c r="H1674" t="n">
         <v>20281</v>
@@ -48973,7 +48973,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1676" t="n">
-        <v>11.5289115905762</v>
+        <v>11.5289106369019</v>
       </c>
       <c r="H1676" t="n">
         <v>23396</v>
@@ -49002,7 +49002,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>11.3746786117554</v>
+        <v>11.3746776580811</v>
       </c>
       <c r="H1677" t="n">
         <v>36916</v>
@@ -49031,7 +49031,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>11.9530515670776</v>
+        <v>11.9530506134033</v>
       </c>
       <c r="H1678" t="n">
         <v>74667</v>
@@ -49089,7 +49089,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1680" t="n">
-        <v>12.4543085098267</v>
+        <v>12.454309463501</v>
       </c>
       <c r="H1680" t="n">
         <v>48736</v>
@@ -49292,7 +49292,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1687" t="n">
-        <v>11.9530515670776</v>
+        <v>11.9530506134033</v>
       </c>
       <c r="H1687" t="n">
         <v>17875</v>
@@ -49321,7 +49321,7 @@
         <v>12</v>
       </c>
       <c r="G1688" t="n">
-        <v>11.5674686431885</v>
+        <v>11.5674695968628</v>
       </c>
       <c r="H1688" t="n">
         <v>21082</v>
@@ -49379,7 +49379,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1690" t="n">
-        <v>11.5289115905762</v>
+        <v>11.5289106369019</v>
       </c>
       <c r="H1690" t="n">
         <v>10025</v>
@@ -49408,7 +49408,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1691" t="n">
-        <v>11.1240491867065</v>
+        <v>11.1240501403809</v>
       </c>
       <c r="H1691" t="n">
         <v>15429</v>
@@ -49437,7 +49437,7 @@
         <v>11.5</v>
       </c>
       <c r="G1692" t="n">
-        <v>11.0854921340942</v>
+        <v>11.0854911804199</v>
       </c>
       <c r="H1692" t="n">
         <v>14980</v>
@@ -49466,7 +49466,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1693" t="n">
-        <v>11.1626081466675</v>
+        <v>11.1626071929932</v>
       </c>
       <c r="H1693" t="n">
         <v>11888</v>
@@ -49495,7 +49495,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1694" t="n">
-        <v>10.7963047027588</v>
+        <v>10.7963037490845</v>
       </c>
       <c r="H1694" t="n">
         <v>36843</v>
@@ -49553,7 +49553,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1696" t="n">
-        <v>10.8734216690063</v>
+        <v>10.873420715332</v>
       </c>
       <c r="H1696" t="n">
         <v>20758</v>
@@ -49727,7 +49727,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1702" t="n">
-        <v>10.7963047027588</v>
+        <v>10.7963037490845</v>
       </c>
       <c r="H1702" t="n">
         <v>11936</v>
@@ -49843,7 +49843,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1706" t="n">
-        <v>10.8541421890259</v>
+        <v>10.8541431427002</v>
       </c>
       <c r="H1706" t="n">
         <v>15303</v>
@@ -50191,7 +50191,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1718" t="n">
-        <v>10.7963047027588</v>
+        <v>10.7963037490845</v>
       </c>
       <c r="H1718" t="n">
         <v>6812</v>
@@ -50249,7 +50249,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1720" t="n">
-        <v>10.8734216690063</v>
+        <v>10.873420715332</v>
       </c>
       <c r="H1720" t="n">
         <v>10167</v>
@@ -50278,7 +50278,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1721" t="n">
-        <v>11.0083751678467</v>
+        <v>11.008376121521</v>
       </c>
       <c r="H1721" t="n">
         <v>12988</v>
@@ -50336,7 +50336,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1723" t="n">
-        <v>11.0083751678467</v>
+        <v>11.008376121521</v>
       </c>
       <c r="H1723" t="n">
         <v>9206</v>
@@ -50365,7 +50365,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1724" t="n">
-        <v>10.7577466964722</v>
+        <v>10.7577457427979</v>
       </c>
       <c r="H1724" t="n">
         <v>8447</v>
@@ -50394,7 +50394,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1725" t="n">
-        <v>10.5263986587524</v>
+        <v>10.5263977050781</v>
       </c>
       <c r="H1725" t="n">
         <v>5247</v>
@@ -50423,7 +50423,7 @@
         <v>11.5</v>
       </c>
       <c r="G1726" t="n">
-        <v>11.0854921340942</v>
+        <v>11.0854911804199</v>
       </c>
       <c r="H1726" t="n">
         <v>6357</v>
@@ -50452,7 +50452,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1727" t="n">
-        <v>10.8155851364136</v>
+        <v>10.8155841827393</v>
       </c>
       <c r="H1727" t="n">
         <v>19045</v>
@@ -50481,7 +50481,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1728" t="n">
-        <v>10.8734216690063</v>
+        <v>10.873420715332</v>
       </c>
       <c r="H1728" t="n">
         <v>14440</v>
@@ -50510,7 +50510,7 @@
         <v>11.5</v>
       </c>
       <c r="G1729" t="n">
-        <v>11.0854921340942</v>
+        <v>11.0854911804199</v>
       </c>
       <c r="H1729" t="n">
         <v>8065</v>
@@ -50568,7 +50568,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1731" t="n">
-        <v>11.1047716140747</v>
+        <v>11.1047706604004</v>
       </c>
       <c r="H1731" t="n">
         <v>5653</v>
@@ -50597,7 +50597,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1732" t="n">
-        <v>11.3168411254883</v>
+        <v>11.316840171814</v>
       </c>
       <c r="H1732" t="n">
         <v>8890</v>
@@ -50655,7 +50655,7 @@
         <v>12</v>
       </c>
       <c r="G1734" t="n">
-        <v>11.5674686431885</v>
+        <v>11.5674695968628</v>
       </c>
       <c r="H1734" t="n">
         <v>21938</v>
@@ -50713,7 +50713,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1736" t="n">
-        <v>11.6253061294556</v>
+        <v>11.6253070831299</v>
       </c>
       <c r="H1736" t="n">
         <v>24723</v>
@@ -50771,7 +50771,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1738" t="n">
-        <v>11.8566560745239</v>
+        <v>11.8566570281982</v>
       </c>
       <c r="H1738" t="n">
         <v>12381</v>
@@ -50945,7 +50945,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1744" t="n">
-        <v>11.9530515670776</v>
+        <v>11.9530506134033</v>
       </c>
       <c r="H1744" t="n">
         <v>11941</v>
@@ -50974,7 +50974,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1745" t="n">
-        <v>12.4157514572144</v>
+        <v>12.41575050354</v>
       </c>
       <c r="H1745" t="n">
         <v>28880</v>
@@ -51032,7 +51032,7 @@
         <v>13</v>
       </c>
       <c r="G1747" t="n">
-        <v>12.5314264297485</v>
+        <v>12.5314254760742</v>
       </c>
       <c r="H1747" t="n">
         <v>84018</v>
@@ -51061,7 +51061,7 @@
         <v>13</v>
       </c>
       <c r="G1748" t="n">
-        <v>12.5314264297485</v>
+        <v>12.5314254760742</v>
       </c>
       <c r="H1748" t="n">
         <v>28783</v>
@@ -51090,7 +51090,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1749" t="n">
-        <v>12.7049379348755</v>
+        <v>12.7049369812012</v>
       </c>
       <c r="H1749" t="n">
         <v>24520</v>
@@ -51119,7 +51119,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1750" t="n">
-        <v>12.7627754211426</v>
+        <v>12.7627744674683</v>
       </c>
       <c r="H1750" t="n">
         <v>29641</v>
@@ -51177,7 +51177,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1752" t="n">
-        <v>12.4157514572144</v>
+        <v>12.41575050354</v>
       </c>
       <c r="H1752" t="n">
         <v>21174</v>
@@ -51264,7 +51264,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.7434959411621</v>
+        <v>12.7434968948364</v>
       </c>
       <c r="H1755" t="n">
         <v>46418</v>
@@ -51322,7 +51322,7 @@
         <v>13</v>
       </c>
       <c r="G1757" t="n">
-        <v>12.5314264297485</v>
+        <v>12.5314254760742</v>
       </c>
       <c r="H1757" t="n">
         <v>26520</v>
@@ -51351,7 +51351,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1758" t="n">
-        <v>12.4157514572144</v>
+        <v>12.41575050354</v>
       </c>
       <c r="H1758" t="n">
         <v>16481</v>
@@ -51525,7 +51525,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1764" t="n">
-        <v>12.1651229858398</v>
+        <v>12.1651220321655</v>
       </c>
       <c r="H1764" t="n">
         <v>27270</v>
@@ -51554,7 +51554,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1765" t="n">
-        <v>12.1651229858398</v>
+        <v>12.1651220321655</v>
       </c>
       <c r="H1765" t="n">
         <v>20505</v>
@@ -51670,7 +51670,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1769" t="n">
-        <v>12.2229595184326</v>
+        <v>12.2229604721069</v>
       </c>
       <c r="H1769" t="n">
         <v>15999</v>
@@ -51757,7 +51757,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1772" t="n">
-        <v>11.9723310470581</v>
+        <v>11.9723320007324</v>
       </c>
       <c r="H1772" t="n">
         <v>18821</v>
@@ -51786,7 +51786,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.6663789749146</v>
+        <v>12.6663808822632</v>
       </c>
       <c r="H1773" t="n">
         <v>57625</v>
@@ -51989,7 +51989,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1780" t="n">
-        <v>11.9530515670776</v>
+        <v>11.9530506134033</v>
       </c>
       <c r="H1780" t="n">
         <v>12476</v>
@@ -52105,7 +52105,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1784" t="n">
-        <v>12.4157514572144</v>
+        <v>12.41575050354</v>
       </c>
       <c r="H1784" t="n">
         <v>4453</v>
@@ -52279,7 +52279,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1790" t="n">
-        <v>12.7434959411621</v>
+        <v>12.7434968948364</v>
       </c>
       <c r="H1790" t="n">
         <v>33138</v>
@@ -52308,7 +52308,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1791" t="n">
-        <v>13.051962852478</v>
+        <v>13.0519618988037</v>
       </c>
       <c r="H1791" t="n">
         <v>20683</v>
@@ -52337,7 +52337,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1792" t="n">
-        <v>12.8398904800415</v>
+        <v>12.8398914337158</v>
       </c>
       <c r="H1792" t="n">
         <v>28949</v>
@@ -52366,7 +52366,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1793" t="n">
-        <v>12.7434959411621</v>
+        <v>12.7434968948364</v>
       </c>
       <c r="H1793" t="n">
         <v>9353</v>
@@ -52395,7 +52395,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1794" t="n">
-        <v>12.7242155075073</v>
+        <v>12.7242164611816</v>
       </c>
       <c r="H1794" t="n">
         <v>6179</v>
@@ -52424,7 +52424,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1795" t="n">
-        <v>12.9362878799438</v>
+        <v>12.9362869262695</v>
       </c>
       <c r="H1795" t="n">
         <v>23830</v>
@@ -52453,7 +52453,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1796" t="n">
-        <v>12.8206129074097</v>
+        <v>12.8206119537354</v>
       </c>
       <c r="H1796" t="n">
         <v>9156</v>
@@ -52511,7 +52511,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1798" t="n">
-        <v>12.9555654525757</v>
+        <v>12.95556640625</v>
       </c>
       <c r="H1798" t="n">
         <v>5736</v>
@@ -52685,7 +52685,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1804" t="n">
-        <v>13.8038463592529</v>
+        <v>13.8038473129272</v>
       </c>
       <c r="H1804" t="n">
         <v>19612</v>
@@ -52743,7 +52743,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.1701498031616</v>
+        <v>14.1701507568359</v>
       </c>
       <c r="H1806" t="n">
         <v>40141</v>
@@ -52772,7 +52772,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>14.4786167144775</v>
+        <v>14.4786157608032</v>
       </c>
       <c r="H1807" t="n">
         <v>84944</v>
@@ -52801,7 +52801,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1808" t="n">
-        <v>14.6135692596436</v>
+        <v>14.6135702133179</v>
       </c>
       <c r="H1808" t="n">
         <v>48361</v>
@@ -52917,7 +52917,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1812" t="n">
-        <v>14.7870817184448</v>
+        <v>14.7870826721191</v>
       </c>
       <c r="H1812" t="n">
         <v>16732</v>
@@ -52975,7 +52975,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1814" t="n">
-        <v>16.7342720031738</v>
+        <v>16.7342739105225</v>
       </c>
       <c r="H1814" t="n">
         <v>98512</v>
@@ -53004,7 +53004,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1815" t="n">
-        <v>16.8306674957275</v>
+        <v>16.8306655883789</v>
       </c>
       <c r="H1815" t="n">
         <v>36888</v>
@@ -53149,7 +53149,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1820" t="n">
-        <v>17.2548084259033</v>
+        <v>17.254810333252</v>
       </c>
       <c r="H1820" t="n">
         <v>19919</v>
@@ -53178,7 +53178,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1821" t="n">
-        <v>17.6211128234863</v>
+        <v>17.621114730835</v>
       </c>
       <c r="H1821" t="n">
         <v>37899</v>
@@ -53352,7 +53352,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1827" t="n">
-        <v>18.0645332336426</v>
+        <v>18.0645313262939</v>
       </c>
       <c r="H1827" t="n">
         <v>43241</v>
@@ -53381,7 +53381,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1828" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1828" t="n">
         <v>111098</v>
@@ -53468,7 +53468,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1831" t="n">
-        <v>18.8549766540527</v>
+        <v>18.8549747467041</v>
       </c>
       <c r="H1831" t="n">
         <v>69633</v>
@@ -53555,7 +53555,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1834" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1834" t="n">
         <v>43557</v>
@@ -53613,7 +53613,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1836" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1836" t="n">
         <v>22029</v>
@@ -53700,7 +53700,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1839" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1839" t="n">
         <v>11544</v>
@@ -53729,7 +53729,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1840" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1840" t="n">
         <v>29923</v>
@@ -53816,7 +53816,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1843" t="n">
-        <v>19.6646995544434</v>
+        <v>19.6646976470947</v>
       </c>
       <c r="H1843" t="n">
         <v>31300</v>
@@ -53932,7 +53932,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1847" t="n">
-        <v>19.2405548095703</v>
+        <v>19.2405567169189</v>
       </c>
       <c r="H1847" t="n">
         <v>6726</v>
@@ -54135,7 +54135,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1854" t="n">
-        <v>18.700740814209</v>
+        <v>18.7007427215576</v>
       </c>
       <c r="H1854" t="n">
         <v>21673</v>
@@ -54222,7 +54222,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1857" t="n">
-        <v>18.8549766540527</v>
+        <v>18.8549747467041</v>
       </c>
       <c r="H1857" t="n">
         <v>8335</v>
@@ -54251,7 +54251,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1858" t="n">
-        <v>18.6814613342285</v>
+        <v>18.6814632415771</v>
       </c>
       <c r="H1858" t="n">
         <v>39655</v>
@@ -54309,7 +54309,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1860" t="n">
-        <v>18.4693908691406</v>
+        <v>18.4693927764893</v>
       </c>
       <c r="H1860" t="n">
         <v>11766</v>
@@ -54367,7 +54367,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1862" t="n">
-        <v>18.2958831787109</v>
+        <v>18.2958812713623</v>
       </c>
       <c r="H1862" t="n">
         <v>13979</v>
@@ -54570,7 +54570,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1869" t="n">
-        <v>18.2958831787109</v>
+        <v>18.2958812713623</v>
       </c>
       <c r="H1869" t="n">
         <v>7315</v>
@@ -54599,7 +54599,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1870" t="n">
-        <v>19.0670471191406</v>
+        <v>19.067045211792</v>
       </c>
       <c r="H1870" t="n">
         <v>42686</v>
@@ -54628,7 +54628,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1871" t="n">
-        <v>18.8742561340332</v>
+        <v>18.8742542266846</v>
       </c>
       <c r="H1871" t="n">
         <v>25993</v>
@@ -54657,7 +54657,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1872" t="n">
-        <v>18.6814613342285</v>
+        <v>18.6814632415771</v>
       </c>
       <c r="H1872" t="n">
         <v>11200</v>
@@ -54715,7 +54715,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1874" t="n">
-        <v>18.6429061889648</v>
+        <v>18.6429042816162</v>
       </c>
       <c r="H1874" t="n">
         <v>42616</v>
@@ -54744,7 +54744,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1875" t="n">
-        <v>18.6814613342285</v>
+        <v>18.6814632415771</v>
       </c>
       <c r="H1875" t="n">
         <v>16932</v>
@@ -54918,7 +54918,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1881" t="n">
-        <v>18.9357299804688</v>
+        <v>18.9357318878174</v>
       </c>
       <c r="H1881" t="n">
         <v>9055</v>
@@ -55266,7 +55266,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1893" t="n">
-        <v>21.7965278625488</v>
+        <v>21.7965259552002</v>
       </c>
       <c r="H1893" t="n">
         <v>19964</v>
@@ -55295,7 +55295,7 @@
         <v>22.25</v>
       </c>
       <c r="G1894" t="n">
-        <v>21.6505699157715</v>
+        <v>21.6505680084229</v>
       </c>
       <c r="H1894" t="n">
         <v>30813</v>
@@ -55382,7 +55382,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1897" t="n">
-        <v>21.7965278625488</v>
+        <v>21.7965259552002</v>
       </c>
       <c r="H1897" t="n">
         <v>36058</v>
@@ -55759,7 +55759,7 @@
         <v>22.25</v>
       </c>
       <c r="G1910" t="n">
-        <v>21.6505699157715</v>
+        <v>21.6505680084229</v>
       </c>
       <c r="H1910" t="n">
         <v>7586</v>
@@ -55817,7 +55817,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1912" t="n">
-        <v>21.5046119689941</v>
+        <v>21.5046100616455</v>
       </c>
       <c r="H1912" t="n">
         <v>5818</v>
@@ -56165,7 +56165,7 @@
         <v>20.5</v>
       </c>
       <c r="G1924" t="n">
-        <v>19.9477138519287</v>
+        <v>19.9477157592773</v>
       </c>
       <c r="H1924" t="n">
         <v>36932</v>
@@ -56223,7 +56223,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1926" t="n">
-        <v>19.8017539978027</v>
+        <v>19.8017559051514</v>
       </c>
       <c r="H1926" t="n">
         <v>31074</v>
@@ -56542,7 +56542,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>17.9042892456055</v>
+        <v>17.9042911529541</v>
       </c>
       <c r="H1937" t="n">
         <v>48411</v>
@@ -56571,7 +56571,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1938" t="n">
-        <v>18.1572856903076</v>
+        <v>18.157283782959</v>
       </c>
       <c r="H1938" t="n">
         <v>35476</v>
@@ -56600,7 +56600,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1939" t="n">
-        <v>18.2351322174072</v>
+        <v>18.2351303100586</v>
       </c>
       <c r="H1939" t="n">
         <v>14734</v>
@@ -56803,7 +56803,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1946" t="n">
-        <v>17.6318340301514</v>
+        <v>17.6318359375</v>
       </c>
       <c r="H1946" t="n">
         <v>17633</v>
@@ -56890,7 +56890,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1949" t="n">
-        <v>17.3399143218994</v>
+        <v>17.339916229248</v>
       </c>
       <c r="H1949" t="n">
         <v>17649</v>
@@ -57093,7 +57093,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1956" t="n">
-        <v>16.8923091888428</v>
+        <v>16.8923110961914</v>
       </c>
       <c r="H1956" t="n">
         <v>44488</v>
@@ -57122,7 +57122,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1957" t="n">
-        <v>16.8923091888428</v>
+        <v>16.8923110961914</v>
       </c>
       <c r="H1957" t="n">
         <v>36199</v>
@@ -57209,7 +57209,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1960" t="n">
-        <v>16.5614700317383</v>
+        <v>16.5614681243896</v>
       </c>
       <c r="H1960" t="n">
         <v>9665</v>
@@ -57354,7 +57354,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1965" t="n">
-        <v>16.1722450256348</v>
+        <v>16.1722469329834</v>
       </c>
       <c r="H1965" t="n">
         <v>5855</v>
@@ -57441,7 +57441,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1968" t="n">
-        <v>16.1138591766357</v>
+        <v>16.1138610839844</v>
       </c>
       <c r="H1968" t="n">
         <v>14432</v>
@@ -57557,7 +57557,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1972" t="n">
-        <v>15.9387083053589</v>
+        <v>15.9387102127075</v>
       </c>
       <c r="H1972" t="n">
         <v>7692</v>
@@ -57673,7 +57673,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1976" t="n">
-        <v>15.9970960617065</v>
+        <v>15.9970941543579</v>
       </c>
       <c r="H1976" t="n">
         <v>11037</v>
@@ -57731,7 +57731,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1978" t="n">
-        <v>15.6662549972534</v>
+        <v>15.6662540435791</v>
       </c>
       <c r="H1978" t="n">
         <v>15513</v>
@@ -57789,7 +57789,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1980" t="n">
-        <v>16.1138591766357</v>
+        <v>16.1138610839844</v>
       </c>
       <c r="H1980" t="n">
         <v>20140</v>
@@ -57847,7 +57847,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1982" t="n">
-        <v>16.2695503234863</v>
+        <v>16.2695484161377</v>
       </c>
       <c r="H1982" t="n">
         <v>14569</v>
@@ -57963,7 +57963,7 @@
         <v>15</v>
       </c>
       <c r="G1986" t="n">
-        <v>14.5958881378174</v>
+        <v>14.5958890914917</v>
       </c>
       <c r="H1986" t="n">
         <v>29170</v>
@@ -58137,7 +58137,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1992" t="n">
-        <v>14.4012775421143</v>
+        <v>14.4012765884399</v>
       </c>
       <c r="H1992" t="n">
         <v>8892</v>
@@ -58166,7 +58166,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1993" t="n">
-        <v>14.3623542785645</v>
+        <v>14.3623552322388</v>
       </c>
       <c r="H1993" t="n">
         <v>12670</v>
@@ -58253,7 +58253,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1996" t="n">
-        <v>14.7126560211182</v>
+        <v>14.7126569747925</v>
       </c>
       <c r="H1996" t="n">
         <v>4797</v>
@@ -58427,7 +58427,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G2002" t="n">
-        <v>16.0165557861328</v>
+        <v>16.0165538787842</v>
       </c>
       <c r="H2002" t="n">
         <v>42952</v>
@@ -58543,7 +58543,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G2006" t="n">
-        <v>14.9267292022705</v>
+        <v>14.9267301559448</v>
       </c>
       <c r="H2006" t="n">
         <v>34045</v>
@@ -58601,7 +58601,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G2008" t="n">
-        <v>14.9267292022705</v>
+        <v>14.9267301559448</v>
       </c>
       <c r="H2008" t="n">
         <v>23253</v>
@@ -58717,7 +58717,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G2012" t="n">
-        <v>15.9776334762573</v>
+        <v>15.9776315689087</v>
       </c>
       <c r="H2012" t="n">
         <v>21724</v>
@@ -58949,7 +58949,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2020" t="n">
-        <v>16.6782341003418</v>
+        <v>16.6782360076904</v>
       </c>
       <c r="H2020" t="n">
         <v>32473</v>
@@ -59065,7 +59065,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2024" t="n">
-        <v>16.8923091888428</v>
+        <v>16.8923110961914</v>
       </c>
       <c r="H2024" t="n">
         <v>17919</v>
@@ -59123,7 +59123,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2026" t="n">
-        <v>16.9896144866943</v>
+        <v>16.9896125793457</v>
       </c>
       <c r="H2026" t="n">
         <v>18451</v>
@@ -59181,7 +59181,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2028" t="n">
-        <v>17.6123714447021</v>
+        <v>17.6123733520508</v>
       </c>
       <c r="H2028" t="n">
         <v>11109</v>
@@ -59297,7 +59297,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G2032" t="n">
-        <v>19.2081871032715</v>
+        <v>19.2081890106201</v>
       </c>
       <c r="H2032" t="n">
         <v>53090</v>
@@ -59326,7 +59326,7 @@
         <v>20</v>
       </c>
       <c r="G2033" t="n">
-        <v>19.4611873626709</v>
+        <v>19.4611854553223</v>
       </c>
       <c r="H2033" t="n">
         <v>37940</v>
@@ -59384,7 +59384,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G2035" t="n">
-        <v>19.2471141815186</v>
+        <v>19.2471122741699</v>
       </c>
       <c r="H2035" t="n">
         <v>13551</v>
@@ -59413,7 +59413,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G2036" t="n">
-        <v>19.2860355377197</v>
+        <v>19.2860336303711</v>
       </c>
       <c r="H2036" t="n">
         <v>25843</v>
@@ -59442,7 +59442,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G2037" t="n">
-        <v>19.2860355377197</v>
+        <v>19.2860336303711</v>
       </c>
       <c r="H2037" t="n">
         <v>19171</v>
@@ -59616,7 +59616,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G2043" t="n">
-        <v>19.6071453094482</v>
+        <v>19.6071434020996</v>
       </c>
       <c r="H2043" t="n">
         <v>29061</v>
@@ -59761,7 +59761,7 @@
         <v>20.5</v>
       </c>
       <c r="G2048" t="n">
-        <v>19.9477138519287</v>
+        <v>19.9477157592773</v>
       </c>
       <c r="H2048" t="n">
         <v>11532</v>
@@ -60399,7 +60399,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G2070" t="n">
-        <v>19.7531032562256</v>
+        <v>19.753101348877</v>
       </c>
       <c r="H2070" t="n">
         <v>25887</v>
@@ -60428,7 +60428,7 @@
         <v>20.5</v>
       </c>
       <c r="G2071" t="n">
-        <v>19.9477138519287</v>
+        <v>19.9477157592773</v>
       </c>
       <c r="H2071" t="n">
         <v>9246</v>
@@ -60457,7 +60457,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G2072" t="n">
-        <v>19.6071453094482</v>
+        <v>19.6071434020996</v>
       </c>
       <c r="H2072" t="n">
         <v>7129</v>
@@ -60486,7 +60486,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G2073" t="n">
-        <v>19.6071453094482</v>
+        <v>19.6071434020996</v>
       </c>
       <c r="H2073" t="n">
         <v>4806</v>
@@ -61037,7 +61037,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2092" t="n">
-        <v>21.9911403656006</v>
+        <v>21.991138458252</v>
       </c>
       <c r="H2092" t="n">
         <v>36056</v>
@@ -61066,7 +61066,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2093" t="n">
-        <v>21.5046119689941</v>
+        <v>21.5046100616455</v>
       </c>
       <c r="H2093" t="n">
         <v>13522</v>
@@ -61095,7 +61095,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G2094" t="n">
-        <v>21.3586521148682</v>
+        <v>21.3586502075195</v>
       </c>
       <c r="H2094" t="n">
         <v>14665</v>
@@ -61153,7 +61153,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2096" t="n">
-        <v>22.1857490539551</v>
+        <v>22.1857509613037</v>
       </c>
       <c r="H2096" t="n">
         <v>36017</v>
@@ -61298,7 +61298,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2101" t="n">
-        <v>22.1857490539551</v>
+        <v>22.1857509613037</v>
       </c>
       <c r="H2101" t="n">
         <v>14582</v>
@@ -61327,7 +61327,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2102" t="n">
-        <v>22.1857490539551</v>
+        <v>22.1857509613037</v>
       </c>
       <c r="H2102" t="n">
         <v>21182</v>
@@ -61414,7 +61414,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2105" t="n">
-        <v>21.9911403656006</v>
+        <v>21.991138458252</v>
       </c>
       <c r="H2105" t="n">
         <v>18162</v>
@@ -61443,7 +61443,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2106" t="n">
-        <v>21.9911403656006</v>
+        <v>21.991138458252</v>
       </c>
       <c r="H2106" t="n">
         <v>5744</v>
@@ -61588,7 +61588,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G2111" t="n">
-        <v>21.3586521148682</v>
+        <v>21.3586502075195</v>
       </c>
       <c r="H2111" t="n">
         <v>7994</v>
@@ -62081,7 +62081,7 @@
         <v>22.25</v>
       </c>
       <c r="G2128" t="n">
-        <v>21.6505699157715</v>
+        <v>21.6505680084229</v>
       </c>
       <c r="H2128" t="n">
         <v>11102</v>
@@ -62197,7 +62197,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G2132" t="n">
-        <v>22.7209339141846</v>
+        <v>22.7209358215332</v>
       </c>
       <c r="H2132" t="n">
         <v>22616</v>
@@ -80038,6 +80038,35 @@
         <v>9329</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>46.0999984741211</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>47.7000007629395</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>46.0999984741211</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>46.6500015258789</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>46.6500015258789</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>10731</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TXT.MI.xlsx
+++ b/data/TXT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G2" t="n">
-        <v>6.34962129592896</v>
+        <v>6.34962177276611</v>
       </c>
       <c r="H2" t="n">
         <v>6271</v>
@@ -514,7 +514,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G5" t="n">
-        <v>6.17114973068237</v>
+        <v>6.17115068435669</v>
       </c>
       <c r="H5" t="n">
         <v>16648</v>
@@ -543,7 +543,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>6.21081018447876</v>
+        <v>6.21080923080444</v>
       </c>
       <c r="H6" t="n">
         <v>12595</v>
@@ -572,7 +572,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03630495071411</v>
+        <v>6.03630447387695</v>
       </c>
       <c r="H7" t="n">
         <v>17372</v>
@@ -601,7 +601,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>6.06803274154663</v>
+        <v>6.06803369522095</v>
       </c>
       <c r="H8" t="n">
         <v>4370</v>
@@ -630,7 +630,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>6.06803274154663</v>
+        <v>6.06803369522095</v>
       </c>
       <c r="H9" t="n">
         <v>7669</v>
@@ -659,7 +659,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>6.03630495071411</v>
+        <v>6.03630447387695</v>
       </c>
       <c r="H10" t="n">
         <v>22298</v>
@@ -688,7 +688,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>6.02837228775024</v>
+        <v>6.0283727645874</v>
       </c>
       <c r="H11" t="n">
         <v>12483</v>
@@ -717,7 +717,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>5.86973142623901</v>
+        <v>5.86973094940186</v>
       </c>
       <c r="H12" t="n">
         <v>16093</v>
@@ -775,7 +775,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>5.71109008789062</v>
+        <v>5.71108961105347</v>
       </c>
       <c r="H14" t="n">
         <v>19639</v>
@@ -833,7 +833,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G16" t="n">
-        <v>5.71109008789062</v>
+        <v>5.71108961105347</v>
       </c>
       <c r="H16" t="n">
         <v>26982</v>
@@ -891,7 +891,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>5.66746425628662</v>
+        <v>5.6674633026123</v>
       </c>
       <c r="H18" t="n">
         <v>11059</v>
@@ -920,7 +920,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>5.6714301109314</v>
+        <v>5.67142963409424</v>
       </c>
       <c r="H19" t="n">
         <v>7916</v>
@@ -949,7 +949,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>5.6872935295105</v>
+        <v>5.68729400634766</v>
       </c>
       <c r="H20" t="n">
         <v>5637</v>
@@ -978,7 +978,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>5.86973142623901</v>
+        <v>5.86973094940186</v>
       </c>
       <c r="H21" t="n">
         <v>28044</v>
@@ -1007,7 +1007,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G22" t="n">
-        <v>5.94112014770508</v>
+        <v>5.94111919403076</v>
       </c>
       <c r="H22" t="n">
         <v>20130</v>
@@ -1094,7 +1094,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G25" t="n">
-        <v>5.86973142623901</v>
+        <v>5.86973094940186</v>
       </c>
       <c r="H25" t="n">
         <v>11676</v>
@@ -1123,7 +1123,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>5.88559532165527</v>
+        <v>5.88559484481812</v>
       </c>
       <c r="H26" t="n">
         <v>12006</v>
@@ -1152,7 +1152,7 @@
         <v>7.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.94905185699463</v>
+        <v>5.94905138015747</v>
       </c>
       <c r="H27" t="n">
         <v>30713</v>
@@ -1210,7 +1210,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>5.86973142623901</v>
+        <v>5.86973094940186</v>
       </c>
       <c r="H29" t="n">
         <v>24172</v>
@@ -1239,7 +1239,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G30" t="n">
-        <v>5.79437685012817</v>
+        <v>5.79437637329102</v>
       </c>
       <c r="H30" t="n">
         <v>12516</v>
@@ -1268,7 +1268,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.72298765182495</v>
+        <v>5.72298812866211</v>
       </c>
       <c r="H31" t="n">
         <v>10712</v>
@@ -1297,7 +1297,7 @@
         <v>7.5</v>
       </c>
       <c r="G32" t="n">
-        <v>5.94905185699463</v>
+        <v>5.94905138015747</v>
       </c>
       <c r="H32" t="n">
         <v>9895</v>
@@ -1326,7 +1326,7 @@
         <v>7.5</v>
       </c>
       <c r="G33" t="n">
-        <v>5.94905185699463</v>
+        <v>5.94905138015747</v>
       </c>
       <c r="H33" t="n">
         <v>5430</v>
@@ -1355,7 +1355,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>6.11562490463257</v>
+        <v>6.11562538146973</v>
       </c>
       <c r="H34" t="n">
         <v>26073</v>
@@ -1384,7 +1384,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>6.09182977676392</v>
+        <v>6.09182929992676</v>
       </c>
       <c r="H35" t="n">
         <v>14233</v>
@@ -1442,7 +1442,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>6.11562490463257</v>
+        <v>6.11562538146973</v>
       </c>
       <c r="H37" t="n">
         <v>2319</v>
@@ -1471,7 +1471,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>6.23460578918457</v>
+        <v>6.23460674285889</v>
       </c>
       <c r="H38" t="n">
         <v>6760</v>
@@ -1500,7 +1500,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>5.88559532165527</v>
+        <v>5.88559484481812</v>
       </c>
       <c r="H39" t="n">
         <v>11690</v>
@@ -1529,7 +1529,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G40" t="n">
-        <v>6.16321754455566</v>
+        <v>6.16321802139282</v>
       </c>
       <c r="H40" t="n">
         <v>3280</v>
@@ -1558,7 +1558,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>6.1394214630127</v>
+        <v>6.13942193984985</v>
       </c>
       <c r="H41" t="n">
         <v>4292</v>
@@ -1674,7 +1674,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G45" t="n">
-        <v>6.35358810424805</v>
+        <v>6.35358667373657</v>
       </c>
       <c r="H45" t="n">
         <v>6866</v>
@@ -1703,7 +1703,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>6.42497634887695</v>
+        <v>6.42497587203979</v>
       </c>
       <c r="H46" t="n">
         <v>2467</v>
@@ -1732,7 +1732,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>6.44083976745605</v>
+        <v>6.44084024429321</v>
       </c>
       <c r="H47" t="n">
         <v>9059</v>
@@ -1819,7 +1819,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G50" t="n">
-        <v>6.02044105529785</v>
+        <v>6.02044057846069</v>
       </c>
       <c r="H50" t="n">
         <v>18952</v>
@@ -1848,7 +1848,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>6.16321754455566</v>
+        <v>6.16321802139282</v>
       </c>
       <c r="H51" t="n">
         <v>33764</v>
@@ -1906,7 +1906,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>6.21081018447876</v>
+        <v>6.21080923080444</v>
       </c>
       <c r="H53" t="n">
         <v>19678</v>
@@ -1935,7 +1935,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G54" t="n">
-        <v>6.13545513153076</v>
+        <v>6.13545560836792</v>
       </c>
       <c r="H54" t="n">
         <v>35204</v>
@@ -1964,7 +1964,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>6.06803274154663</v>
+        <v>6.06803369522095</v>
       </c>
       <c r="H55" t="n">
         <v>6802</v>
@@ -1993,7 +1993,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G56" t="n">
-        <v>6.03630495071411</v>
+        <v>6.03630447387695</v>
       </c>
       <c r="H56" t="n">
         <v>3814</v>
@@ -2080,7 +2080,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>6.02837228775024</v>
+        <v>6.0283727645874</v>
       </c>
       <c r="H59" t="n">
         <v>10610</v>
@@ -2109,7 +2109,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>6.08389663696289</v>
+        <v>6.08389759063721</v>
       </c>
       <c r="H60" t="n">
         <v>3636</v>
@@ -2138,7 +2138,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>6.09579515457153</v>
+        <v>6.09579563140869</v>
       </c>
       <c r="H61" t="n">
         <v>1054</v>
@@ -2167,7 +2167,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>6.05216884613037</v>
+        <v>6.05216932296753</v>
       </c>
       <c r="H62" t="n">
         <v>4497</v>
@@ -2254,7 +2254,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G65" t="n">
-        <v>6.06803274154663</v>
+        <v>6.06803369522095</v>
       </c>
       <c r="H65" t="n">
         <v>2655</v>
@@ -2312,7 +2312,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G67" t="n">
-        <v>5.96094989776611</v>
+        <v>5.96094942092896</v>
       </c>
       <c r="H67" t="n">
         <v>4806</v>
@@ -2341,7 +2341,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G68" t="n">
-        <v>5.89352655410767</v>
+        <v>5.89352703094482</v>
       </c>
       <c r="H68" t="n">
         <v>4226</v>
@@ -2370,7 +2370,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G69" t="n">
-        <v>5.94112014770508</v>
+        <v>5.94111919403076</v>
       </c>
       <c r="H69" t="n">
         <v>4273</v>
@@ -2399,7 +2399,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G70" t="n">
-        <v>6.07596445083618</v>
+        <v>6.07596492767334</v>
       </c>
       <c r="H70" t="n">
         <v>2125</v>
@@ -2457,7 +2457,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>6.09976148605347</v>
+        <v>6.09976196289062</v>
       </c>
       <c r="H72" t="n">
         <v>2785</v>
@@ -2544,7 +2544,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G75" t="n">
-        <v>6.02837228775024</v>
+        <v>6.0283727645874</v>
       </c>
       <c r="H75" t="n">
         <v>3723</v>
@@ -2573,7 +2573,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G76" t="n">
-        <v>6.12355756759644</v>
+        <v>6.12355661392212</v>
       </c>
       <c r="H76" t="n">
         <v>2070</v>
@@ -2602,7 +2602,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G77" t="n">
-        <v>6.0640664100647</v>
+        <v>6.06406688690186</v>
       </c>
       <c r="H77" t="n">
         <v>2340</v>
@@ -2631,7 +2631,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G78" t="n">
-        <v>6.15528535842896</v>
+        <v>6.15528583526611</v>
       </c>
       <c r="H78" t="n">
         <v>3785</v>
@@ -2718,7 +2718,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>5.97681379318237</v>
+        <v>5.97681427001953</v>
       </c>
       <c r="H81" t="n">
         <v>12733</v>
@@ -2747,7 +2747,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>6.04423666000366</v>
+        <v>6.0442361831665</v>
       </c>
       <c r="H82" t="n">
         <v>8632</v>
@@ -2776,7 +2776,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>6.05216884613037</v>
+        <v>6.05216932296753</v>
       </c>
       <c r="H83" t="n">
         <v>4974</v>
@@ -2805,7 +2805,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>5.95698404312134</v>
+        <v>5.95698356628418</v>
       </c>
       <c r="H84" t="n">
         <v>3236</v>
@@ -2834,7 +2834,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G85" t="n">
-        <v>5.95698404312134</v>
+        <v>5.95698356628418</v>
       </c>
       <c r="H85" t="n">
         <v>672</v>
@@ -2892,7 +2892,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>5.90145921707153</v>
+        <v>5.90145969390869</v>
       </c>
       <c r="H87" t="n">
         <v>13071</v>
@@ -2921,7 +2921,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>5.88162851333618</v>
+        <v>5.88162899017334</v>
       </c>
       <c r="H88" t="n">
         <v>8816</v>
@@ -2950,7 +2950,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G89" t="n">
-        <v>6.06010150909424</v>
+        <v>6.06010103225708</v>
       </c>
       <c r="H89" t="n">
         <v>10522</v>
@@ -2979,7 +2979,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G90" t="n">
-        <v>6.02837228775024</v>
+        <v>6.0283727645874</v>
       </c>
       <c r="H90" t="n">
         <v>3658</v>
@@ -3008,7 +3008,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>6.04423666000366</v>
+        <v>6.0442361831665</v>
       </c>
       <c r="H91" t="n">
         <v>4419</v>
@@ -3037,7 +3037,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>6.01647520065308</v>
+        <v>6.01647472381592</v>
       </c>
       <c r="H92" t="n">
         <v>2375</v>
@@ -3095,7 +3095,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>6.02837228775024</v>
+        <v>6.0283727645874</v>
       </c>
       <c r="H94" t="n">
         <v>9374</v>
@@ -3153,7 +3153,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>6.16780376434326</v>
+        <v>6.16780424118042</v>
       </c>
       <c r="H96" t="n">
         <v>9366</v>
@@ -3211,7 +3211,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G98" t="n">
-        <v>6.10218906402588</v>
+        <v>6.10218954086304</v>
       </c>
       <c r="H98" t="n">
         <v>9952</v>
@@ -3240,7 +3240,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G99" t="n">
-        <v>6.10218906402588</v>
+        <v>6.10218954086304</v>
       </c>
       <c r="H99" t="n">
         <v>5592</v>
@@ -3298,7 +3298,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>6.03657484054565</v>
+        <v>6.0365743637085</v>
       </c>
       <c r="H101" t="n">
         <v>2210</v>
@@ -3385,7 +3385,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>6.14319849014282</v>
+        <v>6.14319801330566</v>
       </c>
       <c r="H104" t="n">
         <v>1034</v>
@@ -3472,7 +3472,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>6.14319849014282</v>
+        <v>6.14319801330566</v>
       </c>
       <c r="H107" t="n">
         <v>3212</v>
@@ -3530,7 +3530,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G109" t="n">
-        <v>6.13909769058228</v>
+        <v>6.13909816741943</v>
       </c>
       <c r="H109" t="n">
         <v>1776</v>
@@ -3646,7 +3646,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>6.052978515625</v>
+        <v>6.05297803878784</v>
       </c>
       <c r="H113" t="n">
         <v>11462</v>
@@ -3733,7 +3733,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G116" t="n">
-        <v>5.85203266143799</v>
+        <v>5.85203313827515</v>
       </c>
       <c r="H116" t="n">
         <v>8581</v>
@@ -3791,7 +3791,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G118" t="n">
-        <v>5.93815183639526</v>
+        <v>5.93815231323242</v>
       </c>
       <c r="H118" t="n">
         <v>13817</v>
@@ -3820,7 +3820,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>6.02837181091309</v>
+        <v>6.02837228775024</v>
       </c>
       <c r="H119" t="n">
         <v>6355</v>
@@ -3965,7 +3965,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G124" t="n">
-        <v>5.79872035980225</v>
+        <v>5.79872131347656</v>
       </c>
       <c r="H124" t="n">
         <v>27949</v>
@@ -4023,7 +4023,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>5.80692195892334</v>
+        <v>5.80692291259766</v>
       </c>
       <c r="H126" t="n">
         <v>2074</v>
@@ -4081,7 +4081,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G128" t="n">
-        <v>5.81102323532104</v>
+        <v>5.81102275848389</v>
       </c>
       <c r="H128" t="n">
         <v>2338</v>
@@ -4255,7 +4255,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G134" t="n">
-        <v>6.04477643966675</v>
+        <v>6.04477691650391</v>
       </c>
       <c r="H134" t="n">
         <v>7080</v>
@@ -4284,7 +4284,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>6.13909769058228</v>
+        <v>6.13909816741943</v>
       </c>
       <c r="H135" t="n">
         <v>4619</v>
@@ -4313,7 +4313,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G136" t="n">
-        <v>6.20881319046021</v>
+        <v>6.20881366729736</v>
       </c>
       <c r="H136" t="n">
         <v>9112</v>
@@ -4342,7 +4342,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G137" t="n">
-        <v>6.10218906402588</v>
+        <v>6.10218954086304</v>
       </c>
       <c r="H137" t="n">
         <v>5328</v>
@@ -4371,7 +4371,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G138" t="n">
-        <v>6.09808874130249</v>
+        <v>6.09808778762817</v>
       </c>
       <c r="H138" t="n">
         <v>4280</v>
@@ -4400,7 +4400,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G139" t="n">
-        <v>5.97506046295166</v>
+        <v>5.9750599861145</v>
       </c>
       <c r="H139" t="n">
         <v>5960</v>
@@ -4429,7 +4429,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>6.04067468643188</v>
+        <v>6.04067516326904</v>
       </c>
       <c r="H140" t="n">
         <v>1790</v>
@@ -4458,7 +4458,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G141" t="n">
-        <v>6.03657484054565</v>
+        <v>6.0365743637085</v>
       </c>
       <c r="H141" t="n">
         <v>8798</v>
@@ -4487,7 +4487,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>6.11859369277954</v>
+        <v>6.11859273910522</v>
       </c>
       <c r="H142" t="n">
         <v>7739</v>
@@ -4545,7 +4545,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>6.19241046905518</v>
+        <v>6.19240999221802</v>
       </c>
       <c r="H144" t="n">
         <v>9330</v>
@@ -4603,7 +4603,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>6.19241046905518</v>
+        <v>6.19240999221802</v>
       </c>
       <c r="H146" t="n">
         <v>11346</v>
@@ -4632,7 +4632,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>6.16780376434326</v>
+        <v>6.16780424118042</v>
       </c>
       <c r="H147" t="n">
         <v>746</v>
@@ -4661,7 +4661,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G148" t="n">
-        <v>6.07348346710205</v>
+        <v>6.07348299026489</v>
       </c>
       <c r="H148" t="n">
         <v>2066</v>
@@ -4777,7 +4777,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G152" t="n">
-        <v>6.08578586578369</v>
+        <v>6.08578491210938</v>
       </c>
       <c r="H152" t="n">
         <v>2752</v>
@@ -4835,7 +4835,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G154" t="n">
-        <v>6.02017068862915</v>
+        <v>6.02017116546631</v>
       </c>
       <c r="H154" t="n">
         <v>7365</v>
@@ -4864,7 +4864,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>6.052978515625</v>
+        <v>6.05297803878784</v>
       </c>
       <c r="H155" t="n">
         <v>5660</v>
@@ -4893,7 +4893,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G156" t="n">
-        <v>6.10218906402588</v>
+        <v>6.10218954086304</v>
       </c>
       <c r="H156" t="n">
         <v>4573</v>
@@ -4922,7 +4922,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>6.0898871421814</v>
+        <v>6.08988666534424</v>
       </c>
       <c r="H157" t="n">
         <v>5151</v>
@@ -4951,7 +4951,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>6.01196908950806</v>
+        <v>6.0119686126709</v>
       </c>
       <c r="H158" t="n">
         <v>5384</v>
@@ -4980,7 +4980,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>5.99556493759155</v>
+        <v>5.99556446075439</v>
       </c>
       <c r="H159" t="n">
         <v>5498</v>
@@ -5009,7 +5009,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.01196908950806</v>
+        <v>6.0119686126709</v>
       </c>
       <c r="H160" t="n">
         <v>1989</v>
@@ -5038,7 +5038,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>6.02837181091309</v>
+        <v>6.02837228775024</v>
       </c>
       <c r="H161" t="n">
         <v>1288</v>
@@ -5096,7 +5096,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>5.91354656219482</v>
+        <v>5.91354608535767</v>
       </c>
       <c r="H163" t="n">
         <v>4317</v>
@@ -5125,7 +5125,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>5.80692195892334</v>
+        <v>5.80692291259766</v>
       </c>
       <c r="H164" t="n">
         <v>3042</v>
@@ -5154,7 +5154,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>5.99556493759155</v>
+        <v>5.99556446075439</v>
       </c>
       <c r="H165" t="n">
         <v>12209</v>
@@ -5212,7 +5212,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G167" t="n">
-        <v>6.03657484054565</v>
+        <v>6.0365743637085</v>
       </c>
       <c r="H167" t="n">
         <v>849</v>
@@ -5241,7 +5241,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>6.02017068862915</v>
+        <v>6.02017116546631</v>
       </c>
       <c r="H168" t="n">
         <v>1068</v>
@@ -5299,7 +5299,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G170" t="n">
-        <v>5.92995023727417</v>
+        <v>5.92994976043701</v>
       </c>
       <c r="H170" t="n">
         <v>8802</v>
@@ -5328,7 +5328,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G171" t="n">
-        <v>5.86843633651733</v>
+        <v>5.86843585968018</v>
       </c>
       <c r="H171" t="n">
         <v>4962</v>
@@ -5357,7 +5357,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>5.89714288711548</v>
+        <v>5.89714241027832</v>
       </c>
       <c r="H172" t="n">
         <v>4641</v>
@@ -5386,7 +5386,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>5.97916126251221</v>
+        <v>5.97916078567505</v>
       </c>
       <c r="H173" t="n">
         <v>2984</v>
@@ -5415,7 +5415,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>5.89714288711548</v>
+        <v>5.89714241027832</v>
       </c>
       <c r="H174" t="n">
         <v>7958</v>
@@ -5444,7 +5444,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90124368667603</v>
+        <v>5.90124320983887</v>
       </c>
       <c r="H175" t="n">
         <v>5459</v>
@@ -5502,7 +5502,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G177" t="n">
-        <v>5.90124368667603</v>
+        <v>5.90124320983887</v>
       </c>
       <c r="H177" t="n">
         <v>15403</v>
@@ -5647,7 +5647,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>5.77001285552979</v>
+        <v>5.7700138092041</v>
       </c>
       <c r="H182" t="n">
         <v>11989</v>
@@ -5676,7 +5676,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>5.76181173324585</v>
+        <v>5.76181125640869</v>
       </c>
       <c r="H183" t="n">
         <v>4173</v>
@@ -5734,7 +5734,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>5.7946195602417</v>
+        <v>5.79461908340454</v>
       </c>
       <c r="H185" t="n">
         <v>3715</v>
@@ -5763,7 +5763,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>5.89714288711548</v>
+        <v>5.89714241027832</v>
       </c>
       <c r="H186" t="n">
         <v>1252</v>
@@ -5792,7 +5792,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>5.80282163619995</v>
+        <v>5.80282068252563</v>
       </c>
       <c r="H187" t="n">
         <v>5168</v>
@@ -5879,7 +5879,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.84793186187744</v>
+        <v>5.84793138504028</v>
       </c>
       <c r="H190" t="n">
         <v>3770</v>
@@ -5995,7 +5995,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>5.82332611083984</v>
+        <v>5.82332563400269</v>
       </c>
       <c r="H194" t="n">
         <v>5604</v>
@@ -6053,7 +6053,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G196" t="n">
-        <v>5.90124368667603</v>
+        <v>5.90124320983887</v>
       </c>
       <c r="H196" t="n">
         <v>5101</v>
@@ -6140,7 +6140,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G199" t="n">
-        <v>5.93815183639526</v>
+        <v>5.93815231323242</v>
       </c>
       <c r="H199" t="n">
         <v>1034</v>
@@ -6169,7 +6169,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G200" t="n">
-        <v>5.86843633651733</v>
+        <v>5.86843585968018</v>
       </c>
       <c r="H200" t="n">
         <v>3015</v>
@@ -6198,7 +6198,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>6.0037670135498</v>
+        <v>6.00376653671265</v>
       </c>
       <c r="H201" t="n">
         <v>21056</v>
@@ -6285,7 +6285,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G204" t="n">
-        <v>6.36464881896973</v>
+        <v>6.36464929580688</v>
       </c>
       <c r="H204" t="n">
         <v>29595</v>
@@ -6488,7 +6488,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.39745664596558</v>
+        <v>6.39745616912842</v>
       </c>
       <c r="H211" t="n">
         <v>21711</v>
@@ -6517,7 +6517,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>6.32363939285278</v>
+        <v>6.32363986968994</v>
       </c>
       <c r="H212" t="n">
         <v>8017</v>
@@ -6546,7 +6546,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>6.32363939285278</v>
+        <v>6.32363986968994</v>
       </c>
       <c r="H213" t="n">
         <v>3852</v>
@@ -6575,7 +6575,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>6.34004402160645</v>
+        <v>6.34004354476929</v>
       </c>
       <c r="H214" t="n">
         <v>1022</v>
@@ -6604,7 +6604,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>6.32363939285278</v>
+        <v>6.32363986968994</v>
       </c>
       <c r="H215" t="n">
         <v>3373</v>
@@ -6633,7 +6633,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G216" t="n">
-        <v>6.17600631713867</v>
+        <v>6.17600584030151</v>
       </c>
       <c r="H216" t="n">
         <v>7136</v>
@@ -6720,7 +6720,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>6.34824514389038</v>
+        <v>6.34824562072754</v>
       </c>
       <c r="H219" t="n">
         <v>6244</v>
@@ -6749,7 +6749,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G220" t="n">
-        <v>6.31543731689453</v>
+        <v>6.31543779373169</v>
       </c>
       <c r="H220" t="n">
         <v>2743</v>
@@ -6778,7 +6778,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G221" t="n">
-        <v>6.44666719436646</v>
+        <v>6.44666814804077</v>
       </c>
       <c r="H221" t="n">
         <v>18783</v>
@@ -6807,7 +6807,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28262996673584</v>
+        <v>6.282630443573</v>
       </c>
       <c r="H222" t="n">
         <v>13550</v>
@@ -6836,7 +6836,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>6.43026399612427</v>
+        <v>6.43026447296143</v>
       </c>
       <c r="H223" t="n">
         <v>11325</v>
@@ -6865,7 +6865,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>6.2744288444519</v>
+        <v>6.27442932128906</v>
       </c>
       <c r="H224" t="n">
         <v>8878</v>
@@ -6923,7 +6923,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G226" t="n">
-        <v>6.2457218170166</v>
+        <v>6.24572229385376</v>
       </c>
       <c r="H226" t="n">
         <v>9776</v>
@@ -6952,7 +6952,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G227" t="n">
-        <v>6.33184146881104</v>
+        <v>6.33184099197388</v>
       </c>
       <c r="H227" t="n">
         <v>3258</v>
@@ -6981,7 +6981,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.2457218170166</v>
+        <v>6.24572229385376</v>
       </c>
       <c r="H228" t="n">
         <v>3286</v>
@@ -7010,7 +7010,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G229" t="n">
-        <v>6.12679433822632</v>
+        <v>6.12679481506348</v>
       </c>
       <c r="H229" t="n">
         <v>3730</v>
@@ -7039,7 +7039,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>6.0037670135498</v>
+        <v>6.00376653671265</v>
       </c>
       <c r="H230" t="n">
         <v>7010</v>
@@ -7068,7 +7068,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>5.91354656219482</v>
+        <v>5.91354608535767</v>
       </c>
       <c r="H231" t="n">
         <v>13268</v>
@@ -7126,7 +7126,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>5.95455551147461</v>
+        <v>5.95455598831177</v>
       </c>
       <c r="H233" t="n">
         <v>1206</v>
@@ -7155,7 +7155,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G234" t="n">
-        <v>5.89714288711548</v>
+        <v>5.89714241027832</v>
       </c>
       <c r="H234" t="n">
         <v>7102</v>
@@ -7184,7 +7184,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G235" t="n">
-        <v>5.89714288711548</v>
+        <v>5.89714241027832</v>
       </c>
       <c r="H235" t="n">
         <v>3806</v>
@@ -7213,7 +7213,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>5.96275806427002</v>
+        <v>5.96275758743286</v>
       </c>
       <c r="H236" t="n">
         <v>3334</v>
@@ -7242,7 +7242,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G237" t="n">
-        <v>5.97095966339111</v>
+        <v>5.97096014022827</v>
       </c>
       <c r="H237" t="n">
         <v>3105</v>
@@ -7329,7 +7329,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G240" t="n">
-        <v>6.12679433822632</v>
+        <v>6.12679481506348</v>
       </c>
       <c r="H240" t="n">
         <v>12769</v>
@@ -7358,7 +7358,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>6.052978515625</v>
+        <v>6.05297803878784</v>
       </c>
       <c r="H241" t="n">
         <v>9958</v>
@@ -7474,7 +7474,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>6.3072361946106</v>
+        <v>6.30723667144775</v>
       </c>
       <c r="H245" t="n">
         <v>5251</v>
@@ -7532,7 +7532,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>6.31543731689453</v>
+        <v>6.31543779373169</v>
       </c>
       <c r="H247" t="n">
         <v>7972</v>
@@ -7561,7 +7561,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>6.35234594345093</v>
+        <v>6.35234642028809</v>
       </c>
       <c r="H248" t="n">
         <v>3898</v>
@@ -7648,7 +7648,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>6.2457218170166</v>
+        <v>6.24572229385376</v>
       </c>
       <c r="H251" t="n">
         <v>5513</v>
@@ -7735,7 +7735,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>6.18420839309692</v>
+        <v>6.18420791625977</v>
       </c>
       <c r="H254" t="n">
         <v>5007</v>
@@ -7764,7 +7764,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>6.11449241638184</v>
+        <v>6.11449193954468</v>
       </c>
       <c r="H255" t="n">
         <v>10999</v>
@@ -7793,7 +7793,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G256" t="n">
-        <v>6.14319849014282</v>
+        <v>6.14319801330566</v>
       </c>
       <c r="H256" t="n">
         <v>4428</v>
@@ -7851,7 +7851,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>6.63531112670898</v>
+        <v>6.63531064987183</v>
       </c>
       <c r="H258" t="n">
         <v>51613</v>
@@ -7909,7 +7909,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G260" t="n">
-        <v>6.58609962463379</v>
+        <v>6.58609914779663</v>
       </c>
       <c r="H260" t="n">
         <v>7732</v>
@@ -7996,7 +7996,7 @@
         <v>8.5</v>
       </c>
       <c r="G263" t="n">
-        <v>6.97158670425415</v>
+        <v>6.97158765792847</v>
       </c>
       <c r="H263" t="n">
         <v>136363</v>
@@ -8025,7 +8025,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.13562488555908</v>
+        <v>7.13562393188477</v>
       </c>
       <c r="H264" t="n">
         <v>126241</v>
@@ -8054,7 +8054,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>7.11101913452148</v>
+        <v>7.11101865768433</v>
       </c>
       <c r="H265" t="n">
         <v>51830</v>
@@ -8083,7 +8083,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>6.9674859046936</v>
+        <v>6.96748638153076</v>
       </c>
       <c r="H266" t="n">
         <v>47455</v>
@@ -8170,7 +8170,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G269" t="n">
-        <v>6.95518350601196</v>
+        <v>6.95518255233765</v>
       </c>
       <c r="H269" t="n">
         <v>7078</v>
@@ -8257,7 +8257,7 @@
         <v>8.5</v>
       </c>
       <c r="G272" t="n">
-        <v>6.97158670425415</v>
+        <v>6.97158765792847</v>
       </c>
       <c r="H272" t="n">
         <v>6862</v>
@@ -8286,7 +8286,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G273" t="n">
-        <v>6.92237663269043</v>
+        <v>6.92237567901611</v>
       </c>
       <c r="H273" t="n">
         <v>17128</v>
@@ -8344,7 +8344,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G275" t="n">
-        <v>7.52931451797485</v>
+        <v>7.52931499481201</v>
       </c>
       <c r="H275" t="n">
         <v>232741</v>
@@ -8373,7 +8373,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G276" t="n">
-        <v>7.5621223449707</v>
+        <v>7.56212091445923</v>
       </c>
       <c r="H276" t="n">
         <v>139236</v>
@@ -8402,7 +8402,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>7.52521276473999</v>
+        <v>7.52521324157715</v>
       </c>
       <c r="H277" t="n">
         <v>55028</v>
@@ -8431,7 +8431,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>7.02079963684082</v>
+        <v>7.0207986831665</v>
       </c>
       <c r="H278" t="n">
         <v>79509</v>
@@ -8489,7 +8489,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G280" t="n">
-        <v>7.37347841262817</v>
+        <v>7.37347984313965</v>
       </c>
       <c r="H280" t="n">
         <v>55388</v>
@@ -8518,7 +8518,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G281" t="n">
-        <v>7.40628623962402</v>
+        <v>7.40628576278687</v>
       </c>
       <c r="H281" t="n">
         <v>24588</v>
@@ -8547,7 +8547,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>7.41858959197998</v>
+        <v>7.41858911514282</v>
       </c>
       <c r="H282" t="n">
         <v>10033</v>
@@ -8576,7 +8576,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G283" t="n">
-        <v>7.36527729034424</v>
+        <v>7.36527633666992</v>
       </c>
       <c r="H283" t="n">
         <v>23811</v>
@@ -8605,7 +8605,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>7.20944118499756</v>
+        <v>7.2094407081604</v>
       </c>
       <c r="H284" t="n">
         <v>23541</v>
@@ -8634,7 +8634,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G285" t="n">
-        <v>7.10281705856323</v>
+        <v>7.10281610488892</v>
       </c>
       <c r="H285" t="n">
         <v>18283</v>
@@ -8692,7 +8692,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G287" t="n">
-        <v>6.8772668838501</v>
+        <v>6.87726593017578</v>
       </c>
       <c r="H287" t="n">
         <v>21485</v>
@@ -8750,7 +8750,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G289" t="n">
-        <v>6.99209117889404</v>
+        <v>6.99209213256836</v>
       </c>
       <c r="H289" t="n">
         <v>10573</v>
@@ -8779,7 +8779,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>6.97568893432617</v>
+        <v>6.97568798065186</v>
       </c>
       <c r="H290" t="n">
         <v>11281</v>
@@ -8808,7 +8808,7 @@
         <v>8.5</v>
       </c>
       <c r="G291" t="n">
-        <v>6.97158670425415</v>
+        <v>6.97158765792847</v>
       </c>
       <c r="H291" t="n">
         <v>13964</v>
@@ -8924,7 +8924,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G295" t="n">
-        <v>6.95518350601196</v>
+        <v>6.95518255233765</v>
       </c>
       <c r="H295" t="n">
         <v>18670</v>
@@ -8953,7 +8953,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>6.95108270645142</v>
+        <v>6.95108318328857</v>
       </c>
       <c r="H296" t="n">
         <v>8382</v>
@@ -9069,7 +9069,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G300" t="n">
-        <v>7.02079963684082</v>
+        <v>7.0207986831665</v>
       </c>
       <c r="H300" t="n">
         <v>20217</v>
@@ -9127,7 +9127,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G302" t="n">
-        <v>7.16022968292236</v>
+        <v>7.16022920608521</v>
       </c>
       <c r="H302" t="n">
         <v>6618</v>
@@ -9156,7 +9156,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G303" t="n">
-        <v>7.20123863220215</v>
+        <v>7.20123958587646</v>
       </c>
       <c r="H303" t="n">
         <v>23677</v>
@@ -9214,7 +9214,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G305" t="n">
-        <v>7.43909406661987</v>
+        <v>7.43909311294556</v>
       </c>
       <c r="H305" t="n">
         <v>38477</v>
@@ -9243,7 +9243,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G306" t="n">
-        <v>7.57032299041748</v>
+        <v>7.5703239440918</v>
       </c>
       <c r="H306" t="n">
         <v>140423</v>
@@ -9272,7 +9272,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>7.61953544616699</v>
+        <v>7.61953353881836</v>
       </c>
       <c r="H307" t="n">
         <v>73956</v>
@@ -9301,7 +9301,7 @@
         <v>9.25</v>
       </c>
       <c r="G308" t="n">
-        <v>7.58672666549683</v>
+        <v>7.5867280960083</v>
       </c>
       <c r="H308" t="n">
         <v>37427</v>
@@ -9330,7 +9330,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G309" t="n">
-        <v>7.5621223449707</v>
+        <v>7.56212091445923</v>
       </c>
       <c r="H309" t="n">
         <v>16643</v>
@@ -9359,7 +9359,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>7.8286828994751</v>
+        <v>7.82868242263794</v>
       </c>
       <c r="H310" t="n">
         <v>139701</v>
@@ -9388,7 +9388,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G311" t="n">
-        <v>7.93120622634888</v>
+        <v>7.93120527267456</v>
       </c>
       <c r="H311" t="n">
         <v>78649</v>
@@ -9417,7 +9417,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.955810546875</v>
+        <v>7.95581293106079</v>
       </c>
       <c r="H312" t="n">
         <v>35399</v>
@@ -9446,7 +9446,7 @@
         <v>9.75</v>
       </c>
       <c r="G313" t="n">
-        <v>7.99682140350342</v>
+        <v>7.99681997299194</v>
       </c>
       <c r="H313" t="n">
         <v>48883</v>
@@ -9504,7 +9504,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G315" t="n">
-        <v>7.955810546875</v>
+        <v>7.95581293106079</v>
       </c>
       <c r="H315" t="n">
         <v>45610</v>
@@ -9562,7 +9562,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G317" t="n">
-        <v>8.11574840545654</v>
+        <v>8.11574745178223</v>
       </c>
       <c r="H317" t="n">
         <v>62279</v>
@@ -9591,7 +9591,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G318" t="n">
-        <v>8.17726135253906</v>
+        <v>8.17726230621338</v>
       </c>
       <c r="H318" t="n">
         <v>42597</v>
@@ -9620,7 +9620,7 @@
         <v>10.25</v>
       </c>
       <c r="G319" t="n">
-        <v>8.4069128036499</v>
+        <v>8.40691471099854</v>
       </c>
       <c r="H319" t="n">
         <v>93588</v>
@@ -9678,7 +9678,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>8.28388595581055</v>
+        <v>8.28388690948486</v>
       </c>
       <c r="H321" t="n">
         <v>66369</v>
@@ -9707,7 +9707,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G322" t="n">
-        <v>8.28388595581055</v>
+        <v>8.28388690948486</v>
       </c>
       <c r="H322" t="n">
         <v>34683</v>
@@ -9736,7 +9736,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31669235229492</v>
+        <v>8.31669425964355</v>
       </c>
       <c r="H323" t="n">
         <v>44200</v>
@@ -9765,7 +9765,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G324" t="n">
-        <v>8.35770130157471</v>
+        <v>8.35770225524902</v>
       </c>
       <c r="H324" t="n">
         <v>36091</v>
@@ -9823,7 +9823,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>8.55454921722412</v>
+        <v>8.55454730987549</v>
       </c>
       <c r="H326" t="n">
         <v>46049</v>
@@ -9852,7 +9852,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>8.5135383605957</v>
+        <v>8.51353740692139</v>
       </c>
       <c r="H327" t="n">
         <v>13734</v>
@@ -9910,7 +9910,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G329" t="n">
-        <v>8.25107860565186</v>
+        <v>8.25108051300049</v>
       </c>
       <c r="H329" t="n">
         <v>45655</v>
@@ -9968,7 +9968,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>7.96401309967041</v>
+        <v>7.96401262283325</v>
       </c>
       <c r="H331" t="n">
         <v>48657</v>
@@ -9997,7 +9997,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>7.69335174560547</v>
+        <v>7.69335079193115</v>
       </c>
       <c r="H332" t="n">
         <v>104870</v>
@@ -10026,7 +10026,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G333" t="n">
-        <v>7.88609504699707</v>
+        <v>7.88609600067139</v>
       </c>
       <c r="H333" t="n">
         <v>27574</v>
@@ -10055,7 +10055,7 @@
         <v>9.75</v>
       </c>
       <c r="G334" t="n">
-        <v>7.99682140350342</v>
+        <v>7.99681997299194</v>
       </c>
       <c r="H334" t="n">
         <v>43511</v>
@@ -10084,7 +10084,7 @@
         <v>9.875</v>
       </c>
       <c r="G335" t="n">
-        <v>8.09934520721436</v>
+        <v>8.09934425354004</v>
       </c>
       <c r="H335" t="n">
         <v>54990</v>
@@ -10113,7 +10113,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.35770130157471</v>
+        <v>8.35770225524902</v>
       </c>
       <c r="H336" t="n">
         <v>67504</v>
@@ -10142,7 +10142,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G337" t="n">
-        <v>8.43151950836182</v>
+        <v>8.43152046203613</v>
       </c>
       <c r="H337" t="n">
         <v>42001</v>
@@ -10171,7 +10171,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G338" t="n">
-        <v>8.5217399597168</v>
+        <v>8.52174091339111</v>
       </c>
       <c r="H338" t="n">
         <v>29816</v>
@@ -10200,7 +10200,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>8.69398021697998</v>
+        <v>8.69397926330566</v>
       </c>
       <c r="H339" t="n">
         <v>114917</v>
@@ -10316,7 +10316,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G343" t="n">
-        <v>9.9898738861084</v>
+        <v>9.98987483978271</v>
       </c>
       <c r="H343" t="n">
         <v>281011</v>
@@ -10403,7 +10403,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G346" t="n">
-        <v>10.5886116027832</v>
+        <v>10.5886106491089</v>
       </c>
       <c r="H346" t="n">
         <v>290568</v>
@@ -10432,7 +10432,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G347" t="n">
-        <v>10.6542253494263</v>
+        <v>10.6542263031006</v>
       </c>
       <c r="H347" t="n">
         <v>102170</v>
@@ -10461,7 +10461,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G348" t="n">
-        <v>10.1949214935303</v>
+        <v>10.1949195861816</v>
       </c>
       <c r="H348" t="n">
         <v>198646</v>
@@ -10490,7 +10490,7 @@
         <v>12.5</v>
       </c>
       <c r="G349" t="n">
-        <v>10.2523355484009</v>
+        <v>10.2523345947266</v>
       </c>
       <c r="H349" t="n">
         <v>134551</v>
@@ -10519,7 +10519,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G350" t="n">
-        <v>10.4792308807373</v>
+        <v>10.4792289733887</v>
       </c>
       <c r="H350" t="n">
         <v>100598</v>
@@ -10548,7 +10548,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G351" t="n">
-        <v>10.3615808486938</v>
+        <v>10.3615798950195</v>
       </c>
       <c r="H351" t="n">
         <v>35533</v>
@@ -10577,7 +10577,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G352" t="n">
-        <v>9.78173542022705</v>
+        <v>9.78173637390137</v>
       </c>
       <c r="H352" t="n">
         <v>115913</v>
@@ -10606,7 +10606,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G353" t="n">
-        <v>9.96661376953125</v>
+        <v>9.96661281585693</v>
       </c>
       <c r="H353" t="n">
         <v>104210</v>
@@ -10635,7 +10635,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G354" t="n">
-        <v>10.0254373550415</v>
+        <v>10.0254383087158</v>
       </c>
       <c r="H354" t="n">
         <v>45429</v>
@@ -10664,7 +10664,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>9.95821094512939</v>
+        <v>9.95820999145508</v>
       </c>
       <c r="H355" t="n">
         <v>32988</v>
@@ -10693,7 +10693,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G356" t="n">
-        <v>10.0758590698242</v>
+        <v>10.0758600234985</v>
       </c>
       <c r="H356" t="n">
         <v>32939</v>
@@ -10751,7 +10751,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G358" t="n">
-        <v>10.0758590698242</v>
+        <v>10.0758600234985</v>
       </c>
       <c r="H358" t="n">
         <v>21925</v>
@@ -10780,7 +10780,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G359" t="n">
-        <v>10.0758590698242</v>
+        <v>10.0758600234985</v>
       </c>
       <c r="H359" t="n">
         <v>16023</v>
@@ -10809,7 +10809,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G360" t="n">
-        <v>9.98341941833496</v>
+        <v>9.98342037200928</v>
       </c>
       <c r="H360" t="n">
         <v>31633</v>
@@ -10896,7 +10896,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G363" t="n">
-        <v>10.5632648468018</v>
+        <v>10.5632658004761</v>
       </c>
       <c r="H363" t="n">
         <v>65188</v>
@@ -10925,7 +10925,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G364" t="n">
-        <v>10.512843132019</v>
+        <v>10.5128440856934</v>
       </c>
       <c r="H364" t="n">
         <v>8757</v>
@@ -11012,7 +11012,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G367" t="n">
-        <v>10.6220903396606</v>
+        <v>10.622091293335</v>
       </c>
       <c r="H367" t="n">
         <v>61373</v>
@@ -11041,7 +11041,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>10.546459197998</v>
+        <v>10.5464582443237</v>
       </c>
       <c r="H368" t="n">
         <v>70379</v>
@@ -11099,7 +11099,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G370" t="n">
-        <v>10.5380554199219</v>
+        <v>10.5380544662476</v>
       </c>
       <c r="H370" t="n">
         <v>77917</v>
@@ -11128,7 +11128,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G371" t="n">
-        <v>10.319561958313</v>
+        <v>10.3195629119873</v>
       </c>
       <c r="H371" t="n">
         <v>24680</v>
@@ -11157,7 +11157,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G372" t="n">
-        <v>10.2607383728027</v>
+        <v>10.2607374191284</v>
       </c>
       <c r="H372" t="n">
         <v>24251</v>
@@ -11186,7 +11186,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G373" t="n">
-        <v>10.0254373550415</v>
+        <v>10.0254383087158</v>
       </c>
       <c r="H373" t="n">
         <v>42041</v>
@@ -11215,7 +11215,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G374" t="n">
-        <v>10.1767015457153</v>
+        <v>10.1767024993896</v>
       </c>
       <c r="H374" t="n">
         <v>47550</v>
@@ -11273,7 +11273,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G376" t="n">
-        <v>10.0254373550415</v>
+        <v>10.0254383087158</v>
       </c>
       <c r="H376" t="n">
         <v>8687</v>
@@ -11302,7 +11302,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G377" t="n">
-        <v>9.94980525970459</v>
+        <v>9.94980621337891</v>
       </c>
       <c r="H377" t="n">
         <v>23752</v>
@@ -11331,7 +11331,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G378" t="n">
-        <v>9.81534957885742</v>
+        <v>9.81535053253174</v>
       </c>
       <c r="H378" t="n">
         <v>17064</v>
@@ -11360,7 +11360,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G379" t="n">
-        <v>9.73971843719482</v>
+        <v>9.73971748352051</v>
       </c>
       <c r="H379" t="n">
         <v>26775</v>
@@ -11389,7 +11389,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G380" t="n">
-        <v>9.68929481506348</v>
+        <v>9.68929576873779</v>
       </c>
       <c r="H380" t="n">
         <v>13208</v>
@@ -11418,7 +11418,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G381" t="n">
-        <v>9.52122592926025</v>
+        <v>9.52122402191162</v>
       </c>
       <c r="H381" t="n">
         <v>71419</v>
@@ -11476,7 +11476,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>9.01701068878174</v>
+        <v>9.01701164245605</v>
       </c>
       <c r="H383" t="n">
         <v>47989</v>
@@ -11505,7 +11505,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>9.07583522796631</v>
+        <v>9.07583618164062</v>
       </c>
       <c r="H384" t="n">
         <v>29565</v>
@@ -11534,7 +11534,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>9.09264469146729</v>
+        <v>9.09264278411865</v>
       </c>
       <c r="H385" t="n">
         <v>45758</v>
@@ -11563,7 +11563,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G386" t="n">
-        <v>9.10945129394531</v>
+        <v>9.10945224761963</v>
       </c>
       <c r="H386" t="n">
         <v>22670</v>
@@ -11592,7 +11592,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G387" t="n">
-        <v>9.15146827697754</v>
+        <v>9.15147018432617</v>
       </c>
       <c r="H387" t="n">
         <v>13336</v>
@@ -11621,7 +11621,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>9.07583522796631</v>
+        <v>9.07583618164062</v>
       </c>
       <c r="H388" t="n">
         <v>11440</v>
@@ -11650,7 +11650,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>9.07583522796631</v>
+        <v>9.07583618164062</v>
       </c>
       <c r="H389" t="n">
         <v>13343</v>
@@ -11679,7 +11679,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G390" t="n">
-        <v>9.14306449890137</v>
+        <v>9.14306640625</v>
       </c>
       <c r="H390" t="n">
         <v>13080</v>
@@ -11737,7 +11737,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G392" t="n">
-        <v>9.12625885009766</v>
+        <v>9.12625789642334</v>
       </c>
       <c r="H392" t="n">
         <v>28124</v>
@@ -11766,7 +11766,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>9.28592681884766</v>
+        <v>9.28592586517334</v>
       </c>
       <c r="H393" t="n">
         <v>25434</v>
@@ -11795,7 +11795,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G394" t="n">
-        <v>9.59685707092285</v>
+        <v>9.59685802459717</v>
       </c>
       <c r="H394" t="n">
         <v>57253</v>
@@ -11824,7 +11824,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>10.0002269744873</v>
+        <v>10.0002279281616</v>
       </c>
       <c r="H395" t="n">
         <v>98734</v>
@@ -11853,7 +11853,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G396" t="n">
-        <v>9.94140243530273</v>
+        <v>9.94140338897705</v>
       </c>
       <c r="H396" t="n">
         <v>51764</v>
@@ -11882,7 +11882,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>9.94980525970459</v>
+        <v>9.94980621337891</v>
       </c>
       <c r="H397" t="n">
         <v>27782</v>
@@ -11911,7 +11911,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G398" t="n">
-        <v>9.80694484710693</v>
+        <v>9.80694675445557</v>
       </c>
       <c r="H398" t="n">
         <v>16471</v>
@@ -11940,7 +11940,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G399" t="n">
-        <v>9.75652503967285</v>
+        <v>9.75652408599854</v>
       </c>
       <c r="H399" t="n">
         <v>17960</v>
@@ -11969,7 +11969,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G400" t="n">
-        <v>10.1262807846069</v>
+        <v>10.1262817382812</v>
       </c>
       <c r="H400" t="n">
         <v>172165</v>
@@ -12027,7 +12027,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G402" t="n">
-        <v>10.0758590698242</v>
+        <v>10.0758600234985</v>
       </c>
       <c r="H402" t="n">
         <v>27302</v>
@@ -12056,7 +12056,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G403" t="n">
-        <v>10.1851072311401</v>
+        <v>10.1851062774658</v>
       </c>
       <c r="H403" t="n">
         <v>30833</v>
@@ -12085,7 +12085,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G404" t="n">
-        <v>10.1598949432373</v>
+        <v>10.1598958969116</v>
       </c>
       <c r="H404" t="n">
         <v>24085</v>
@@ -12114,7 +12114,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>10.1262807846069</v>
+        <v>10.1262817382812</v>
       </c>
       <c r="H405" t="n">
         <v>20792</v>
@@ -12143,7 +12143,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>10.1851072311401</v>
+        <v>10.1851062774658</v>
       </c>
       <c r="H406" t="n">
         <v>8292</v>
@@ -12230,7 +12230,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G409" t="n">
-        <v>9.98341941833496</v>
+        <v>9.98342037200928</v>
       </c>
       <c r="H409" t="n">
         <v>86615</v>
@@ -12259,7 +12259,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G410" t="n">
-        <v>10.2691421508789</v>
+        <v>10.2691411972046</v>
       </c>
       <c r="H410" t="n">
         <v>34343</v>
@@ -12288,7 +12288,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G411" t="n">
-        <v>10.2607383728027</v>
+        <v>10.2607374191284</v>
       </c>
       <c r="H411" t="n">
         <v>33503</v>
@@ -12346,7 +12346,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G413" t="n">
-        <v>9.92459678649902</v>
+        <v>9.92459583282471</v>
       </c>
       <c r="H413" t="n">
         <v>24847</v>
@@ -12375,7 +12375,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G414" t="n">
-        <v>9.80694484710693</v>
+        <v>9.80694675445557</v>
       </c>
       <c r="H414" t="n">
         <v>28666</v>
@@ -12433,7 +12433,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>10.0002269744873</v>
+        <v>10.0002279281616</v>
       </c>
       <c r="H416" t="n">
         <v>51293</v>
@@ -12462,7 +12462,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>10.1262807846069</v>
+        <v>10.1262817382812</v>
       </c>
       <c r="H417" t="n">
         <v>16444</v>
@@ -12491,7 +12491,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G418" t="n">
-        <v>9.98341941833496</v>
+        <v>9.98342037200928</v>
       </c>
       <c r="H418" t="n">
         <v>10391</v>
@@ -12549,7 +12549,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>9.76492691040039</v>
+        <v>9.76492881774902</v>
       </c>
       <c r="H420" t="n">
         <v>93670</v>
@@ -12752,7 +12752,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G427" t="n">
-        <v>9.68929481506348</v>
+        <v>9.68929576873779</v>
       </c>
       <c r="H427" t="n">
         <v>56964</v>
@@ -12781,7 +12781,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G428" t="n">
-        <v>9.57164669036865</v>
+        <v>9.57164573669434</v>
       </c>
       <c r="H428" t="n">
         <v>49315</v>
@@ -12955,7 +12955,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G434" t="n">
-        <v>9.2943286895752</v>
+        <v>9.29432964324951</v>
       </c>
       <c r="H434" t="n">
         <v>17130</v>
@@ -13071,7 +13071,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G438" t="n">
-        <v>9.28592681884766</v>
+        <v>9.28592586517334</v>
       </c>
       <c r="H438" t="n">
         <v>19181</v>
@@ -13100,7 +13100,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G439" t="n">
-        <v>9.2943286895752</v>
+        <v>9.29432964324951</v>
       </c>
       <c r="H439" t="n">
         <v>23798</v>
@@ -13129,7 +13129,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G440" t="n">
-        <v>9.18508243560791</v>
+        <v>9.18508338928223</v>
       </c>
       <c r="H440" t="n">
         <v>25740</v>
@@ -13158,7 +13158,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G441" t="n">
-        <v>9.15146827697754</v>
+        <v>9.15147018432617</v>
       </c>
       <c r="H441" t="n">
         <v>23957</v>
@@ -13187,7 +13187,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G442" t="n">
-        <v>9.14306449890137</v>
+        <v>9.14306640625</v>
       </c>
       <c r="H442" t="n">
         <v>56964</v>
@@ -13216,7 +13216,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>9.11785221099854</v>
+        <v>9.1178560256958</v>
       </c>
       <c r="H443" t="n">
         <v>36814</v>
@@ -13245,7 +13245,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G444" t="n">
-        <v>9.15146827697754</v>
+        <v>9.15147018432617</v>
       </c>
       <c r="H444" t="n">
         <v>43068</v>
@@ -13303,7 +13303,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G446" t="n">
-        <v>9.80694484710693</v>
+        <v>9.80694675445557</v>
       </c>
       <c r="H446" t="n">
         <v>64936</v>
@@ -13361,7 +13361,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G448" t="n">
-        <v>9.40357494354248</v>
+        <v>9.40357398986816</v>
       </c>
       <c r="H448" t="n">
         <v>50728</v>
@@ -13390,7 +13390,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>9.98341941833496</v>
+        <v>9.98342037200928</v>
       </c>
       <c r="H449" t="n">
         <v>75515</v>
@@ -13419,7 +13419,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>9.74812030792236</v>
+        <v>9.74812126159668</v>
       </c>
       <c r="H450" t="n">
         <v>108579</v>
@@ -13448,7 +13448,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G451" t="n">
-        <v>9.58845233917236</v>
+        <v>9.588454246521</v>
       </c>
       <c r="H451" t="n">
         <v>48735</v>
@@ -13477,7 +13477,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G452" t="n">
-        <v>9.59685707092285</v>
+        <v>9.59685802459717</v>
       </c>
       <c r="H452" t="n">
         <v>23759</v>
@@ -13535,7 +13535,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G454" t="n">
-        <v>9.57164669036865</v>
+        <v>9.57164573669434</v>
       </c>
       <c r="H454" t="n">
         <v>25930</v>
@@ -13622,7 +13622,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G457" t="n">
-        <v>9.5464334487915</v>
+        <v>9.54643535614014</v>
       </c>
       <c r="H457" t="n">
         <v>24620</v>
@@ -13651,7 +13651,7 @@
         <v>11.5</v>
       </c>
       <c r="G458" t="n">
-        <v>9.66408443450928</v>
+        <v>9.66408538818359</v>
       </c>
       <c r="H458" t="n">
         <v>15175</v>
@@ -13709,7 +13709,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G460" t="n">
-        <v>9.68089199066162</v>
+        <v>9.68089294433594</v>
       </c>
       <c r="H460" t="n">
         <v>23454</v>
@@ -13738,7 +13738,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G461" t="n">
-        <v>9.70610332489014</v>
+        <v>9.70610237121582</v>
       </c>
       <c r="H461" t="n">
         <v>24965</v>
@@ -13767,7 +13767,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G462" t="n">
-        <v>9.60526180267334</v>
+        <v>9.60526084899902</v>
       </c>
       <c r="H462" t="n">
         <v>27373</v>
@@ -13825,7 +13825,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>9.5380334854126</v>
+        <v>9.53803253173828</v>
       </c>
       <c r="H464" t="n">
         <v>12097</v>
@@ -13854,7 +13854,7 @@
         <v>11.5</v>
       </c>
       <c r="G465" t="n">
-        <v>9.66408443450928</v>
+        <v>9.66408538818359</v>
       </c>
       <c r="H465" t="n">
         <v>9251</v>
@@ -13912,7 +13912,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G467" t="n">
-        <v>9.74812030792236</v>
+        <v>9.74812126159668</v>
       </c>
       <c r="H467" t="n">
         <v>16260</v>
@@ -13941,7 +13941,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G468" t="n">
-        <v>9.69769954681396</v>
+        <v>9.69769859313965</v>
       </c>
       <c r="H468" t="n">
         <v>15945</v>
@@ -13999,7 +13999,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G470" t="n">
-        <v>9.68089199066162</v>
+        <v>9.68089294433594</v>
       </c>
       <c r="H470" t="n">
         <v>18751</v>
@@ -14057,7 +14057,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G472" t="n">
-        <v>9.68929481506348</v>
+        <v>9.68929576873779</v>
       </c>
       <c r="H472" t="n">
         <v>19120</v>
@@ -14086,7 +14086,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>9.69769954681396</v>
+        <v>9.69769859313965</v>
       </c>
       <c r="H473" t="n">
         <v>19980</v>
@@ -14115,7 +14115,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>9.74812030792236</v>
+        <v>9.74812126159668</v>
       </c>
       <c r="H474" t="n">
         <v>27589</v>
@@ -14144,7 +14144,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G475" t="n">
-        <v>9.59685707092285</v>
+        <v>9.59685802459717</v>
       </c>
       <c r="H475" t="n">
         <v>26741</v>
@@ -14173,7 +14173,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G476" t="n">
-        <v>9.38676929473877</v>
+        <v>9.38676738739014</v>
       </c>
       <c r="H476" t="n">
         <v>165152</v>
@@ -14202,7 +14202,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G477" t="n">
-        <v>9.05062675476074</v>
+        <v>9.05062580108643</v>
       </c>
       <c r="H477" t="n">
         <v>70334</v>
@@ -14231,7 +14231,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G478" t="n">
-        <v>8.91616916656494</v>
+        <v>8.91616821289062</v>
       </c>
       <c r="H478" t="n">
         <v>64290</v>
@@ -14318,7 +14318,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G481" t="n">
-        <v>8.00018310546875</v>
+        <v>8.00018215179443</v>
       </c>
       <c r="H481" t="n">
         <v>108495</v>
@@ -14376,7 +14376,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G483" t="n">
-        <v>8.02539157867432</v>
+        <v>8.02539253234863</v>
       </c>
       <c r="H483" t="n">
         <v>50200</v>
@@ -14405,7 +14405,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>8.04640007019043</v>
+        <v>8.04640102386475</v>
       </c>
       <c r="H484" t="n">
         <v>32229</v>
@@ -14463,7 +14463,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G486" t="n">
-        <v>8.25228881835938</v>
+        <v>8.25228786468506</v>
       </c>
       <c r="H486" t="n">
         <v>64724</v>
@@ -14492,7 +14492,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>8.26489448547363</v>
+        <v>8.26489353179932</v>
       </c>
       <c r="H487" t="n">
         <v>27311</v>
@@ -14550,7 +14550,7 @@
         <v>9.75</v>
       </c>
       <c r="G489" t="n">
-        <v>8.19346523284912</v>
+        <v>8.1934642791748</v>
       </c>
       <c r="H489" t="n">
         <v>20004</v>
@@ -14608,7 +14608,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G491" t="n">
-        <v>8.23548221588135</v>
+        <v>8.23548126220703</v>
       </c>
       <c r="H491" t="n">
         <v>29388</v>
@@ -14666,7 +14666,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>8.01698970794678</v>
+        <v>8.01698875427246</v>
       </c>
       <c r="H493" t="n">
         <v>36289</v>
@@ -14695,7 +14695,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G494" t="n">
-        <v>7.96236658096313</v>
+        <v>7.96236610412598</v>
       </c>
       <c r="H494" t="n">
         <v>29812</v>
@@ -14724,7 +14724,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>7.77748727798462</v>
+        <v>7.77748823165894</v>
       </c>
       <c r="H495" t="n">
         <v>62230</v>
@@ -14782,7 +14782,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G497" t="n">
-        <v>7.72706699371338</v>
+        <v>7.7270655632019</v>
       </c>
       <c r="H497" t="n">
         <v>22105</v>
@@ -14811,7 +14811,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>7.83631229400635</v>
+        <v>7.83631277084351</v>
       </c>
       <c r="H498" t="n">
         <v>17635</v>
@@ -14840,7 +14840,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>7.78169012069702</v>
+        <v>7.78168964385986</v>
       </c>
       <c r="H499" t="n">
         <v>29556</v>
@@ -14869,7 +14869,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G500" t="n">
-        <v>7.88253211975098</v>
+        <v>7.88253259658813</v>
       </c>
       <c r="H500" t="n">
         <v>34640</v>
@@ -14898,7 +14898,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G501" t="n">
-        <v>7.90354108810425</v>
+        <v>7.90354156494141</v>
       </c>
       <c r="H501" t="n">
         <v>26616</v>
@@ -14927,7 +14927,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>7.94555807113647</v>
+        <v>7.94555854797363</v>
       </c>
       <c r="H502" t="n">
         <v>9016</v>
@@ -14956,7 +14956,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G503" t="n">
-        <v>7.93715572357178</v>
+        <v>7.93715476989746</v>
       </c>
       <c r="H503" t="n">
         <v>18957</v>
@@ -14985,7 +14985,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G504" t="n">
-        <v>8.17665576934814</v>
+        <v>8.17665672302246</v>
       </c>
       <c r="H504" t="n">
         <v>29105</v>
@@ -15014,7 +15014,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G505" t="n">
-        <v>8.17665576934814</v>
+        <v>8.17665672302246</v>
       </c>
       <c r="H505" t="n">
         <v>20550</v>
@@ -15101,7 +15101,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G508" t="n">
-        <v>7.97497129440308</v>
+        <v>7.97497081756592</v>
       </c>
       <c r="H508" t="n">
         <v>26975</v>
@@ -15188,7 +15188,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G511" t="n">
-        <v>8.09682273864746</v>
+        <v>8.09682369232178</v>
       </c>
       <c r="H511" t="n">
         <v>22662</v>
@@ -15275,7 +15275,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G514" t="n">
-        <v>8.34472846984863</v>
+        <v>8.34472751617432</v>
       </c>
       <c r="H514" t="n">
         <v>62794</v>
@@ -15304,7 +15304,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>8.48758792877197</v>
+        <v>8.48758888244629</v>
       </c>
       <c r="H515" t="n">
         <v>38481</v>
@@ -15362,7 +15362,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>8.65565967559814</v>
+        <v>8.65565872192383</v>
       </c>
       <c r="H517" t="n">
         <v>77397</v>
@@ -15391,7 +15391,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G518" t="n">
-        <v>8.47078037261963</v>
+        <v>8.47078132629395</v>
       </c>
       <c r="H518" t="n">
         <v>71165</v>
@@ -15449,7 +15449,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>8.47078037261963</v>
+        <v>8.47078132629395</v>
       </c>
       <c r="H520" t="n">
         <v>22750</v>
@@ -15710,7 +15710,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G529" t="n">
-        <v>8.30270957946777</v>
+        <v>8.30271148681641</v>
       </c>
       <c r="H529" t="n">
         <v>40326</v>
@@ -15768,7 +15768,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>8.48758792877197</v>
+        <v>8.48758888244629</v>
       </c>
       <c r="H531" t="n">
         <v>28382</v>
@@ -15797,7 +15797,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>8.23548221588135</v>
+        <v>8.23548126220703</v>
       </c>
       <c r="H532" t="n">
         <v>34259</v>
@@ -15826,7 +15826,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>8.23548221588135</v>
+        <v>8.23548126220703</v>
       </c>
       <c r="H533" t="n">
         <v>29706</v>
@@ -15855,7 +15855,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G534" t="n">
-        <v>8.12623596191406</v>
+        <v>8.12623500823975</v>
       </c>
       <c r="H534" t="n">
         <v>20972</v>
@@ -15884,7 +15884,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>7.94135665893555</v>
+        <v>7.94135713577271</v>
       </c>
       <c r="H535" t="n">
         <v>30884</v>
@@ -15913,7 +15913,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>7.91614723205566</v>
+        <v>7.91614675521851</v>
       </c>
       <c r="H536" t="n">
         <v>28059</v>
@@ -15971,7 +15971,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>8.05060291290283</v>
+        <v>8.05060386657715</v>
       </c>
       <c r="H538" t="n">
         <v>28487</v>
@@ -16000,7 +16000,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G539" t="n">
-        <v>8.00018310546875</v>
+        <v>8.00018215179443</v>
       </c>
       <c r="H539" t="n">
         <v>14502</v>
@@ -16058,7 +16058,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G541" t="n">
-        <v>8.24388408660889</v>
+        <v>8.2438850402832</v>
       </c>
       <c r="H541" t="n">
         <v>43847</v>
@@ -16087,7 +16087,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G542" t="n">
-        <v>8.47078037261963</v>
+        <v>8.47078132629395</v>
       </c>
       <c r="H542" t="n">
         <v>64708</v>
@@ -16261,7 +16261,7 @@
         <v>10.5</v>
       </c>
       <c r="G548" t="n">
-        <v>8.82373142242432</v>
+        <v>8.82372951507568</v>
       </c>
       <c r="H548" t="n">
         <v>57011</v>
@@ -16319,7 +16319,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>8.73969459533691</v>
+        <v>8.7396936416626</v>
       </c>
       <c r="H550" t="n">
         <v>29306</v>
@@ -16348,7 +16348,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G551" t="n">
-        <v>8.68927478790283</v>
+        <v>8.6892728805542</v>
       </c>
       <c r="H551" t="n">
         <v>64518</v>
@@ -16406,7 +16406,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G553" t="n">
-        <v>8.53800964355469</v>
+        <v>8.53800868988037</v>
       </c>
       <c r="H553" t="n">
         <v>62149</v>
@@ -16435,7 +16435,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G554" t="n">
-        <v>8.48758792877197</v>
+        <v>8.48758888244629</v>
       </c>
       <c r="H554" t="n">
         <v>29672</v>
@@ -16551,7 +16551,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G558" t="n">
-        <v>9.27752208709717</v>
+        <v>9.27752304077148</v>
       </c>
       <c r="H558" t="n">
         <v>137910</v>
@@ -16609,7 +16609,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>9.07583522796631</v>
+        <v>9.07583618164062</v>
       </c>
       <c r="H560" t="n">
         <v>338893</v>
@@ -16696,7 +16696,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G563" t="n">
-        <v>9.10945129394531</v>
+        <v>9.10945224761963</v>
       </c>
       <c r="H563" t="n">
         <v>46276</v>
@@ -16725,7 +16725,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G564" t="n">
-        <v>9.12625885009766</v>
+        <v>9.12625789642334</v>
       </c>
       <c r="H564" t="n">
         <v>48960</v>
@@ -16783,7 +16783,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>9.07583522796631</v>
+        <v>9.07583618164062</v>
       </c>
       <c r="H566" t="n">
         <v>28705</v>
@@ -16812,7 +16812,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G567" t="n">
-        <v>9.12625885009766</v>
+        <v>9.12625789642334</v>
       </c>
       <c r="H567" t="n">
         <v>23732</v>
@@ -16841,7 +16841,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G568" t="n">
-        <v>9.14306449890137</v>
+        <v>9.14306640625</v>
       </c>
       <c r="H568" t="n">
         <v>52483</v>
@@ -16870,7 +16870,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G569" t="n">
-        <v>9.04222393035889</v>
+        <v>9.04222202301025</v>
       </c>
       <c r="H569" t="n">
         <v>80924</v>
@@ -16899,7 +16899,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.10945129394531</v>
+        <v>9.10945224761963</v>
       </c>
       <c r="H570" t="n">
         <v>40328</v>
@@ -16928,7 +16928,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G571" t="n">
-        <v>9.10945129394531</v>
+        <v>9.10945224761963</v>
       </c>
       <c r="H571" t="n">
         <v>28447</v>
@@ -16957,7 +16957,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G572" t="n">
-        <v>9.14306449890137</v>
+        <v>9.14306640625</v>
       </c>
       <c r="H572" t="n">
         <v>33399</v>
@@ -16986,7 +16986,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G573" t="n">
-        <v>9.02541637420654</v>
+        <v>9.02541542053223</v>
       </c>
       <c r="H573" t="n">
         <v>39104</v>
@@ -17015,7 +17015,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>9.07583522796631</v>
+        <v>9.07583618164062</v>
       </c>
       <c r="H574" t="n">
         <v>27014</v>
@@ -17044,7 +17044,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G575" t="n">
-        <v>9.07583522796631</v>
+        <v>9.07583618164062</v>
       </c>
       <c r="H575" t="n">
         <v>21639</v>
@@ -17131,7 +17131,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>9.07583522796631</v>
+        <v>9.07583618164062</v>
       </c>
       <c r="H578" t="n">
         <v>27463</v>
@@ -17218,7 +17218,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G581" t="n">
-        <v>9.14306449890137</v>
+        <v>9.14306640625</v>
       </c>
       <c r="H581" t="n">
         <v>36929</v>
@@ -17247,7 +17247,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G582" t="n">
-        <v>9.12625885009766</v>
+        <v>9.12625789642334</v>
       </c>
       <c r="H582" t="n">
         <v>34722</v>
@@ -17276,7 +17276,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G583" t="n">
-        <v>9.17667961120605</v>
+        <v>9.17667865753174</v>
       </c>
       <c r="H583" t="n">
         <v>16997</v>
@@ -17305,7 +17305,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>9.32794380187988</v>
+        <v>9.3279447555542</v>
       </c>
       <c r="H584" t="n">
         <v>79263</v>
@@ -17392,7 +17392,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>9.59685707092285</v>
+        <v>9.59685802459717</v>
       </c>
       <c r="H587" t="n">
         <v>118423</v>
@@ -17479,7 +17479,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G590" t="n">
-        <v>10.5716695785522</v>
+        <v>10.5716686248779</v>
       </c>
       <c r="H590" t="n">
         <v>269431</v>
@@ -17508,7 +17508,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G591" t="n">
-        <v>10.5212488174438</v>
+        <v>10.5212478637695</v>
       </c>
       <c r="H591" t="n">
         <v>60159</v>
@@ -17537,7 +17537,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G592" t="n">
-        <v>10.5212488174438</v>
+        <v>10.5212478637695</v>
       </c>
       <c r="H592" t="n">
         <v>61864</v>
@@ -17566,7 +17566,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G593" t="n">
-        <v>10.5716695785522</v>
+        <v>10.5716686248779</v>
       </c>
       <c r="H593" t="n">
         <v>147469</v>
@@ -17682,7 +17682,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G597" t="n">
-        <v>11.3616027832031</v>
+        <v>11.3616046905518</v>
       </c>
       <c r="H597" t="n">
         <v>396275</v>
@@ -17711,7 +17711,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>11.4342012405396</v>
+        <v>11.4342002868652</v>
       </c>
       <c r="H598" t="n">
         <v>294416</v>
@@ -17740,7 +17740,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G599" t="n">
-        <v>11.760892868042</v>
+        <v>11.7608919143677</v>
       </c>
       <c r="H599" t="n">
         <v>320674</v>
@@ -17769,7 +17769,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G600" t="n">
-        <v>11.760892868042</v>
+        <v>11.7608919143677</v>
       </c>
       <c r="H600" t="n">
         <v>189219</v>
@@ -17827,7 +17827,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G602" t="n">
-        <v>11.3071537017822</v>
+        <v>11.3071546554565</v>
       </c>
       <c r="H602" t="n">
         <v>303676</v>
@@ -17885,7 +17885,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G604" t="n">
-        <v>11.1801080703735</v>
+        <v>11.1801061630249</v>
       </c>
       <c r="H604" t="n">
         <v>141160</v>
@@ -17914,7 +17914,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G605" t="n">
-        <v>10.8534164428711</v>
+        <v>10.8534154891968</v>
       </c>
       <c r="H605" t="n">
         <v>142896</v>
@@ -17943,7 +17943,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G606" t="n">
-        <v>10.780818939209</v>
+        <v>10.7808179855347</v>
       </c>
       <c r="H606" t="n">
         <v>180380</v>
@@ -18001,7 +18001,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G608" t="n">
-        <v>10.5993223190308</v>
+        <v>10.5993242263794</v>
       </c>
       <c r="H608" t="n">
         <v>120612</v>
@@ -18088,7 +18088,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G611" t="n">
-        <v>10.5448741912842</v>
+        <v>10.5448751449585</v>
       </c>
       <c r="H611" t="n">
         <v>86171</v>
@@ -18117,7 +18117,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G612" t="n">
-        <v>10.3815288543701</v>
+        <v>10.3815279006958</v>
       </c>
       <c r="H612" t="n">
         <v>69168</v>
@@ -18146,7 +18146,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>10.0729866027832</v>
+        <v>10.0729875564575</v>
       </c>
       <c r="H613" t="n">
         <v>69002</v>
@@ -18175,7 +18175,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G614" t="n">
-        <v>9.90964126586914</v>
+        <v>9.90964031219482</v>
       </c>
       <c r="H614" t="n">
         <v>65685</v>
@@ -18204,7 +18204,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>9.89148998260498</v>
+        <v>9.8914909362793</v>
       </c>
       <c r="H615" t="n">
         <v>66703</v>
@@ -18233,7 +18233,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G616" t="n">
-        <v>9.96408843994141</v>
+        <v>9.96408748626709</v>
       </c>
       <c r="H616" t="n">
         <v>86629</v>
@@ -18262,7 +18262,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G617" t="n">
-        <v>10.1818838119507</v>
+        <v>10.181884765625</v>
       </c>
       <c r="H617" t="n">
         <v>59541</v>
@@ -18291,7 +18291,7 @@
         <v>11</v>
       </c>
       <c r="G618" t="n">
-        <v>9.98223876953125</v>
+        <v>9.98223972320557</v>
       </c>
       <c r="H618" t="n">
         <v>90447</v>
@@ -18320,7 +18320,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G619" t="n">
-        <v>10.1274337768555</v>
+        <v>10.1274347305298</v>
       </c>
       <c r="H619" t="n">
         <v>112197</v>
@@ -18349,7 +18349,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>10.1637344360352</v>
+        <v>10.1637334823608</v>
       </c>
       <c r="H620" t="n">
         <v>58047</v>
@@ -18378,7 +18378,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G621" t="n">
-        <v>10.1637344360352</v>
+        <v>10.1637334823608</v>
       </c>
       <c r="H621" t="n">
         <v>60479</v>
@@ -18407,7 +18407,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G622" t="n">
-        <v>10.0366868972778</v>
+        <v>10.0366888046265</v>
       </c>
       <c r="H622" t="n">
         <v>125360</v>
@@ -18436,7 +18436,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>10.3089303970337</v>
+        <v>10.3089294433594</v>
       </c>
       <c r="H623" t="n">
         <v>44230</v>
@@ -18494,7 +18494,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>10.3452301025391</v>
+        <v>10.3452291488647</v>
       </c>
       <c r="H625" t="n">
         <v>15232</v>
@@ -18523,7 +18523,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G626" t="n">
-        <v>10.2363328933716</v>
+        <v>10.2363319396973</v>
       </c>
       <c r="H626" t="n">
         <v>16213</v>
@@ -18581,7 +18581,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G628" t="n">
-        <v>9.96408843994141</v>
+        <v>9.96408748626709</v>
       </c>
       <c r="H628" t="n">
         <v>55640</v>
@@ -18610,7 +18610,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G629" t="n">
-        <v>10.1274337768555</v>
+        <v>10.1274347305298</v>
       </c>
       <c r="H629" t="n">
         <v>32992</v>
@@ -18668,7 +18668,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G631" t="n">
-        <v>10.0003881454468</v>
+        <v>10.0003890991211</v>
       </c>
       <c r="H631" t="n">
         <v>24110</v>
@@ -18697,7 +18697,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>9.89148998260498</v>
+        <v>9.8914909362793</v>
       </c>
       <c r="H632" t="n">
         <v>34032</v>
@@ -18726,7 +18726,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G633" t="n">
-        <v>9.69184684753418</v>
+        <v>9.6918478012085</v>
       </c>
       <c r="H633" t="n">
         <v>34905</v>
@@ -18755,7 +18755,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>9.70999526977539</v>
+        <v>9.70999622344971</v>
       </c>
       <c r="H634" t="n">
         <v>13684</v>
@@ -18784,7 +18784,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>9.61924934387207</v>
+        <v>9.61924743652344</v>
       </c>
       <c r="H635" t="n">
         <v>16744</v>
@@ -18813,7 +18813,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G636" t="n">
-        <v>9.38330364227295</v>
+        <v>9.38330459594727</v>
       </c>
       <c r="H636" t="n">
         <v>31244</v>
@@ -18842,7 +18842,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G637" t="n">
-        <v>9.58295059204102</v>
+        <v>9.5829496383667</v>
       </c>
       <c r="H637" t="n">
         <v>16681</v>
@@ -19016,7 +19016,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G643" t="n">
-        <v>9.60109806060791</v>
+        <v>9.60109901428223</v>
       </c>
       <c r="H643" t="n">
         <v>15856</v>
@@ -19045,7 +19045,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G644" t="n">
-        <v>9.4740514755249</v>
+        <v>9.47405242919922</v>
       </c>
       <c r="H644" t="n">
         <v>26140</v>
@@ -19074,7 +19074,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>9.21995830535889</v>
+        <v>9.2199592590332</v>
       </c>
       <c r="H645" t="n">
         <v>25750</v>
@@ -19103,7 +19103,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>9.16550922393799</v>
+        <v>9.16551113128662</v>
       </c>
       <c r="H646" t="n">
         <v>30672</v>
@@ -19132,7 +19132,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.16550922393799</v>
+        <v>9.16551113128662</v>
       </c>
       <c r="H647" t="n">
         <v>18337</v>
@@ -19161,7 +19161,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G648" t="n">
-        <v>9.27440738677979</v>
+        <v>9.2744083404541</v>
       </c>
       <c r="H648" t="n">
         <v>14022</v>
@@ -19190,7 +19190,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G649" t="n">
-        <v>9.21995830535889</v>
+        <v>9.2199592590332</v>
       </c>
       <c r="H649" t="n">
         <v>13772</v>
@@ -19219,7 +19219,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G650" t="n">
-        <v>9.23810768127441</v>
+        <v>9.23810863494873</v>
       </c>
       <c r="H650" t="n">
         <v>22208</v>
@@ -19248,7 +19248,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G651" t="n">
-        <v>9.18366050720215</v>
+        <v>9.18365955352783</v>
       </c>
       <c r="H651" t="n">
         <v>12282</v>
@@ -19277,7 +19277,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G652" t="n">
-        <v>8.98401355743408</v>
+        <v>8.9840145111084</v>
       </c>
       <c r="H652" t="n">
         <v>41212</v>
@@ -19306,7 +19306,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>9.00216388702393</v>
+        <v>9.00216484069824</v>
       </c>
       <c r="H653" t="n">
         <v>12349</v>
@@ -19335,7 +19335,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G654" t="n">
-        <v>8.98401355743408</v>
+        <v>8.9840145111084</v>
       </c>
       <c r="H654" t="n">
         <v>26179</v>
@@ -19364,7 +19364,7 @@
         <v>9.75</v>
       </c>
       <c r="G655" t="n">
-        <v>8.84789371490479</v>
+        <v>8.84789276123047</v>
       </c>
       <c r="H655" t="n">
         <v>16074</v>
@@ -19422,7 +19422,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G657" t="n">
-        <v>8.94771671295166</v>
+        <v>8.94771480560303</v>
       </c>
       <c r="H657" t="n">
         <v>36135</v>
@@ -19451,7 +19451,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G658" t="n">
-        <v>8.87511920928955</v>
+        <v>8.87511730194092</v>
       </c>
       <c r="H658" t="n">
         <v>16562</v>
@@ -19480,7 +19480,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>8.89326858520508</v>
+        <v>8.89326763153076</v>
       </c>
       <c r="H659" t="n">
         <v>19700</v>
@@ -19509,7 +19509,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>8.89326858520508</v>
+        <v>8.89326763153076</v>
       </c>
       <c r="H660" t="n">
         <v>38983</v>
@@ -19567,7 +19567,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G662" t="n">
-        <v>8.85696887969971</v>
+        <v>8.85696792602539</v>
       </c>
       <c r="H662" t="n">
         <v>26026</v>
@@ -19654,7 +19654,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G665" t="n">
-        <v>8.83881855010986</v>
+        <v>8.83881759643555</v>
       </c>
       <c r="H665" t="n">
         <v>144957</v>
@@ -19741,7 +19741,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G668" t="n">
-        <v>8.5575008392334</v>
+        <v>8.55750179290771</v>
       </c>
       <c r="H668" t="n">
         <v>62585</v>
@@ -19770,7 +19770,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>8.57565116882324</v>
+        <v>8.57565021514893</v>
       </c>
       <c r="H669" t="n">
         <v>41570</v>
@@ -19799,7 +19799,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>8.54842662811279</v>
+        <v>8.54842567443848</v>
       </c>
       <c r="H670" t="n">
         <v>31402</v>
@@ -19828,7 +19828,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G671" t="n">
-        <v>8.27618312835693</v>
+        <v>8.27618408203125</v>
       </c>
       <c r="H671" t="n">
         <v>67193</v>
@@ -19886,7 +19886,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G673" t="n">
-        <v>8.54842662811279</v>
+        <v>8.54842567443848</v>
       </c>
       <c r="H673" t="n">
         <v>34455</v>
@@ -19915,7 +19915,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G674" t="n">
-        <v>8.94771671295166</v>
+        <v>8.94771480560303</v>
       </c>
       <c r="H674" t="n">
         <v>80694</v>
@@ -19944,7 +19944,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G675" t="n">
-        <v>9.31070518493652</v>
+        <v>9.31070709228516</v>
       </c>
       <c r="H675" t="n">
         <v>86138</v>
@@ -19973,7 +19973,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G676" t="n">
-        <v>9.292555809021</v>
+        <v>9.29255676269531</v>
       </c>
       <c r="H676" t="n">
         <v>47588</v>
@@ -20002,7 +20002,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G677" t="n">
-        <v>9.292555809021</v>
+        <v>9.29255676269531</v>
       </c>
       <c r="H677" t="n">
         <v>49307</v>
@@ -20031,7 +20031,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G678" t="n">
-        <v>9.21995830535889</v>
+        <v>9.2199592590332</v>
       </c>
       <c r="H678" t="n">
         <v>17101</v>
@@ -20060,7 +20060,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>9.23810768127441</v>
+        <v>9.23810863494873</v>
       </c>
       <c r="H679" t="n">
         <v>25575</v>
@@ -20089,7 +20089,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G680" t="n">
-        <v>9.11106204986572</v>
+        <v>9.11106109619141</v>
       </c>
       <c r="H680" t="n">
         <v>30403</v>
@@ -20147,7 +20147,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>9.31070518493652</v>
+        <v>9.31070709228516</v>
       </c>
       <c r="H682" t="n">
         <v>31385</v>
@@ -20176,7 +20176,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G683" t="n">
-        <v>9.27440738677979</v>
+        <v>9.2744083404541</v>
       </c>
       <c r="H683" t="n">
         <v>32438</v>
@@ -20263,7 +20263,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G686" t="n">
-        <v>8.95678997039795</v>
+        <v>8.95679092407227</v>
       </c>
       <c r="H686" t="n">
         <v>18944</v>
@@ -20466,7 +20466,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G693" t="n">
-        <v>8.78437042236328</v>
+        <v>8.7843713760376</v>
       </c>
       <c r="H693" t="n">
         <v>22136</v>
@@ -20582,7 +20582,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G697" t="n">
-        <v>8.70269775390625</v>
+        <v>8.70269680023193</v>
       </c>
       <c r="H697" t="n">
         <v>27151</v>
@@ -20611,7 +20611,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G698" t="n">
-        <v>8.74807071685791</v>
+        <v>8.74807167053223</v>
       </c>
       <c r="H698" t="n">
         <v>44177</v>
@@ -20640,7 +20640,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G699" t="n">
-        <v>8.75714683532715</v>
+        <v>8.75714588165283</v>
       </c>
       <c r="H699" t="n">
         <v>10398</v>
@@ -20669,7 +20669,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G700" t="n">
-        <v>8.69362163543701</v>
+        <v>8.69362258911133</v>
       </c>
       <c r="H700" t="n">
         <v>14070</v>
@@ -20727,7 +20727,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.57565116882324</v>
+        <v>8.57565021514893</v>
       </c>
       <c r="H702" t="n">
         <v>33379</v>
@@ -20843,7 +20843,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G706" t="n">
-        <v>8.33063316345215</v>
+        <v>8.33063220977783</v>
       </c>
       <c r="H706" t="n">
         <v>36589</v>
@@ -20872,7 +20872,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>8.27618312835693</v>
+        <v>8.27618408203125</v>
       </c>
       <c r="H707" t="n">
         <v>40179</v>
@@ -20959,7 +20959,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G710" t="n">
-        <v>7.66817378997803</v>
+        <v>7.66817474365234</v>
       </c>
       <c r="H710" t="n">
         <v>86131</v>
@@ -20988,7 +20988,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G711" t="n">
-        <v>7.63187456130981</v>
+        <v>7.63187551498413</v>
       </c>
       <c r="H711" t="n">
         <v>25341</v>
@@ -21017,7 +21017,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G712" t="n">
-        <v>7.6137261390686</v>
+        <v>7.61372661590576</v>
       </c>
       <c r="H712" t="n">
         <v>19357</v>
@@ -21075,7 +21075,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>7.52297878265381</v>
+        <v>7.52297687530518</v>
       </c>
       <c r="H714" t="n">
         <v>113497</v>
@@ -21104,7 +21104,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G715" t="n">
-        <v>7.42315626144409</v>
+        <v>7.42315578460693</v>
       </c>
       <c r="H715" t="n">
         <v>32395</v>
@@ -21162,7 +21162,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>7.33240795135498</v>
+        <v>7.33240842819214</v>
       </c>
       <c r="H717" t="n">
         <v>23394</v>
@@ -21220,7 +21220,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G719" t="n">
-        <v>7.04201650619507</v>
+        <v>7.04201602935791</v>
       </c>
       <c r="H719" t="n">
         <v>18183</v>
@@ -21307,7 +21307,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G722" t="n">
-        <v>7.23258638381958</v>
+        <v>7.23258590698242</v>
       </c>
       <c r="H722" t="n">
         <v>24909</v>
@@ -21336,7 +21336,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G723" t="n">
-        <v>7.25073528289795</v>
+        <v>7.25073575973511</v>
       </c>
       <c r="H723" t="n">
         <v>8099</v>
@@ -21365,7 +21365,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>7.41408157348633</v>
+        <v>7.41408014297485</v>
       </c>
       <c r="H724" t="n">
         <v>21730</v>
@@ -21394,7 +21394,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G725" t="n">
-        <v>7.35055780410767</v>
+        <v>7.35055828094482</v>
       </c>
       <c r="H725" t="n">
         <v>29989</v>
@@ -21423,7 +21423,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G726" t="n">
-        <v>7.6137261390686</v>
+        <v>7.61372661590576</v>
       </c>
       <c r="H726" t="n">
         <v>26120</v>
@@ -21452,7 +21452,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G727" t="n">
-        <v>7.69539785385132</v>
+        <v>7.695396900177</v>
       </c>
       <c r="H727" t="n">
         <v>32663</v>
@@ -21481,7 +21481,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G728" t="n">
-        <v>7.73169851303101</v>
+        <v>7.73169755935669</v>
       </c>
       <c r="H728" t="n">
         <v>50273</v>
@@ -21510,7 +21510,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G729" t="n">
-        <v>7.62279987335205</v>
+        <v>7.62280082702637</v>
       </c>
       <c r="H729" t="n">
         <v>49897</v>
@@ -21539,7 +21539,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G730" t="n">
-        <v>7.38685750961304</v>
+        <v>7.38685655593872</v>
       </c>
       <c r="H730" t="n">
         <v>31609</v>
@@ -21597,7 +21597,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G732" t="n">
-        <v>7.49575424194336</v>
+        <v>7.49575328826904</v>
       </c>
       <c r="H732" t="n">
         <v>12870</v>
@@ -21626,7 +21626,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G733" t="n">
-        <v>7.2779598236084</v>
+        <v>7.27796030044556</v>
       </c>
       <c r="H733" t="n">
         <v>32961</v>
@@ -21655,7 +21655,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>7.44130516052246</v>
+        <v>7.44130611419678</v>
       </c>
       <c r="H734" t="n">
         <v>23801</v>
@@ -21684,7 +21684,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G735" t="n">
-        <v>7.15998840332031</v>
+        <v>7.15998792648315</v>
       </c>
       <c r="H735" t="n">
         <v>43485</v>
@@ -21713,7 +21713,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>7.07831573486328</v>
+        <v>7.07831478118896</v>
       </c>
       <c r="H736" t="n">
         <v>16363</v>
@@ -21742,7 +21742,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>7.08738994598389</v>
+        <v>7.08738946914673</v>
       </c>
       <c r="H737" t="n">
         <v>7916</v>
@@ -21858,7 +21858,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G741" t="n">
-        <v>7.07831573486328</v>
+        <v>7.07831478118896</v>
       </c>
       <c r="H741" t="n">
         <v>30617</v>
@@ -21887,7 +21887,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G742" t="n">
-        <v>7.35055780410767</v>
+        <v>7.35055828094482</v>
       </c>
       <c r="H742" t="n">
         <v>15187</v>
@@ -21945,7 +21945,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G744" t="n">
-        <v>7.35055780410767</v>
+        <v>7.35055828094482</v>
       </c>
       <c r="H744" t="n">
         <v>13555</v>
@@ -21974,7 +21974,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G745" t="n">
-        <v>7.46852922439575</v>
+        <v>7.46852970123291</v>
       </c>
       <c r="H745" t="n">
         <v>18429</v>
@@ -22003,7 +22003,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G746" t="n">
-        <v>7.2779598236084</v>
+        <v>7.27796030044556</v>
       </c>
       <c r="H746" t="n">
         <v>31349</v>
@@ -22148,7 +22148,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G751" t="n">
-        <v>7.26888513565063</v>
+        <v>7.26888465881348</v>
       </c>
       <c r="H751" t="n">
         <v>9629</v>
@@ -22206,7 +22206,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G753" t="n">
-        <v>7.25073528289795</v>
+        <v>7.25073575973511</v>
       </c>
       <c r="H753" t="n">
         <v>11117</v>
@@ -22264,7 +22264,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>7.41408157348633</v>
+        <v>7.41408014297485</v>
       </c>
       <c r="H755" t="n">
         <v>8865</v>
@@ -22293,7 +22293,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>7.41408157348633</v>
+        <v>7.41408014297485</v>
       </c>
       <c r="H756" t="n">
         <v>18824</v>
@@ -22322,7 +22322,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>7.33240795135498</v>
+        <v>7.33240842819214</v>
       </c>
       <c r="H757" t="n">
         <v>8342</v>
@@ -22380,7 +22380,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G759" t="n">
-        <v>7.24166059494019</v>
+        <v>7.24166011810303</v>
       </c>
       <c r="H759" t="n">
         <v>9299</v>
@@ -22409,7 +22409,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G760" t="n">
-        <v>7.17813730239868</v>
+        <v>7.17813682556152</v>
       </c>
       <c r="H760" t="n">
         <v>5002</v>
@@ -22438,7 +22438,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20536136627197</v>
+        <v>7.20536184310913</v>
       </c>
       <c r="H761" t="n">
         <v>6447</v>
@@ -22496,7 +22496,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G763" t="n">
-        <v>7.42315626144409</v>
+        <v>7.42315578460693</v>
       </c>
       <c r="H763" t="n">
         <v>12478</v>
@@ -22525,7 +22525,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G764" t="n">
-        <v>7.60465097427368</v>
+        <v>7.60465145111084</v>
       </c>
       <c r="H764" t="n">
         <v>9893</v>
@@ -22583,7 +22583,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>7.79522085189819</v>
+        <v>7.79522180557251</v>
       </c>
       <c r="H766" t="n">
         <v>12522</v>
@@ -22612,7 +22612,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G767" t="n">
-        <v>7.96764087677002</v>
+        <v>7.96764183044434</v>
       </c>
       <c r="H767" t="n">
         <v>53519</v>
@@ -22641,7 +22641,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G768" t="n">
-        <v>8.27618312835693</v>
+        <v>8.27618408203125</v>
       </c>
       <c r="H768" t="n">
         <v>64182</v>
@@ -22728,7 +22728,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G771" t="n">
-        <v>8.41230392456055</v>
+        <v>8.41230583190918</v>
       </c>
       <c r="H771" t="n">
         <v>13815</v>
@@ -22757,7 +22757,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G772" t="n">
-        <v>8.33063316345215</v>
+        <v>8.33063220977783</v>
       </c>
       <c r="H772" t="n">
         <v>12514</v>
@@ -22815,7 +22815,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G774" t="n">
-        <v>8.26710796356201</v>
+        <v>8.26710891723633</v>
       </c>
       <c r="H774" t="n">
         <v>31249</v>
@@ -22844,7 +22844,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G775" t="n">
-        <v>8.25803470611572</v>
+        <v>8.25803375244141</v>
       </c>
       <c r="H775" t="n">
         <v>8892</v>
@@ -22989,7 +22989,7 @@
         <v>9.75</v>
       </c>
       <c r="G780" t="n">
-        <v>8.84789371490479</v>
+        <v>8.84789276123047</v>
       </c>
       <c r="H780" t="n">
         <v>41703</v>
@@ -23018,7 +23018,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G781" t="n">
-        <v>8.89326858520508</v>
+        <v>8.89326763153076</v>
       </c>
       <c r="H781" t="n">
         <v>21119</v>
@@ -23076,7 +23076,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G783" t="n">
-        <v>9.04753875732422</v>
+        <v>9.0475378036499</v>
       </c>
       <c r="H783" t="n">
         <v>21904</v>
@@ -23105,7 +23105,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>8.89326858520508</v>
+        <v>8.89326763153076</v>
       </c>
       <c r="H784" t="n">
         <v>9135</v>
@@ -23163,7 +23163,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G786" t="n">
-        <v>8.75714683532715</v>
+        <v>8.75714588165283</v>
       </c>
       <c r="H786" t="n">
         <v>9285</v>
@@ -23192,7 +23192,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>9.02031421661377</v>
+        <v>9.02031326293945</v>
       </c>
       <c r="H787" t="n">
         <v>12115</v>
@@ -23221,7 +23221,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G788" t="n">
-        <v>8.96586608886719</v>
+        <v>8.9658670425415</v>
       </c>
       <c r="H788" t="n">
         <v>23953</v>
@@ -23250,7 +23250,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>8.89326858520508</v>
+        <v>8.89326763153076</v>
       </c>
       <c r="H789" t="n">
         <v>23921</v>
@@ -23279,7 +23279,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G790" t="n">
-        <v>8.71177196502686</v>
+        <v>8.71177291870117</v>
       </c>
       <c r="H790" t="n">
         <v>16196</v>
@@ -23337,7 +23337,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>8.58472633361816</v>
+        <v>8.58472537994385</v>
       </c>
       <c r="H792" t="n">
         <v>20073</v>
@@ -23366,7 +23366,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>8.89326858520508</v>
+        <v>8.89326763153076</v>
       </c>
       <c r="H793" t="n">
         <v>18906</v>
@@ -23395,7 +23395,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>8.77529621124268</v>
+        <v>8.77529525756836</v>
       </c>
       <c r="H794" t="n">
         <v>13182</v>
@@ -23424,7 +23424,7 @@
         <v>9.75</v>
       </c>
       <c r="G795" t="n">
-        <v>8.84789371490479</v>
+        <v>8.84789276123047</v>
       </c>
       <c r="H795" t="n">
         <v>5267</v>
@@ -23511,7 +23511,7 @@
         <v>9.75</v>
       </c>
       <c r="G798" t="n">
-        <v>8.84789371490479</v>
+        <v>8.84789276123047</v>
       </c>
       <c r="H798" t="n">
         <v>11060</v>
@@ -23569,7 +23569,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G800" t="n">
-        <v>8.74807071685791</v>
+        <v>8.74807167053223</v>
       </c>
       <c r="H800" t="n">
         <v>5404</v>
@@ -23598,7 +23598,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G801" t="n">
-        <v>8.83881855010986</v>
+        <v>8.83881759643555</v>
       </c>
       <c r="H801" t="n">
         <v>6688</v>
@@ -23627,7 +23627,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G802" t="n">
-        <v>8.87511920928955</v>
+        <v>8.87511730194092</v>
       </c>
       <c r="H802" t="n">
         <v>12406</v>
@@ -23656,7 +23656,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G803" t="n">
-        <v>8.82066917419434</v>
+        <v>8.82067012786865</v>
       </c>
       <c r="H803" t="n">
         <v>4124</v>
@@ -23685,7 +23685,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G804" t="n">
-        <v>8.76622009277344</v>
+        <v>8.76622104644775</v>
       </c>
       <c r="H804" t="n">
         <v>8670</v>
@@ -23772,7 +23772,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G807" t="n">
-        <v>8.75714683532715</v>
+        <v>8.75714588165283</v>
       </c>
       <c r="H807" t="n">
         <v>12608</v>
@@ -23801,7 +23801,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G808" t="n">
-        <v>8.7299222946167</v>
+        <v>8.72992134094238</v>
       </c>
       <c r="H808" t="n">
         <v>13926</v>
@@ -23830,7 +23830,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G809" t="n">
-        <v>8.87511920928955</v>
+        <v>8.87511730194092</v>
       </c>
       <c r="H809" t="n">
         <v>13318</v>
@@ -23859,7 +23859,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G810" t="n">
-        <v>8.74807071685791</v>
+        <v>8.74807167053223</v>
       </c>
       <c r="H810" t="n">
         <v>16973</v>
@@ -23888,7 +23888,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G811" t="n">
-        <v>8.50305271148682</v>
+        <v>8.5030517578125</v>
       </c>
       <c r="H811" t="n">
         <v>38512</v>
@@ -23946,7 +23946,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>8.50305271148682</v>
+        <v>8.5030517578125</v>
       </c>
       <c r="H813" t="n">
         <v>6494</v>
@@ -23975,7 +23975,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G814" t="n">
-        <v>8.17636203765869</v>
+        <v>8.17636108398438</v>
       </c>
       <c r="H814" t="n">
         <v>48473</v>
@@ -24062,7 +24062,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G817" t="n">
-        <v>8.1945104598999</v>
+        <v>8.19450950622559</v>
       </c>
       <c r="H817" t="n">
         <v>19654</v>
@@ -24236,7 +24236,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G823" t="n">
-        <v>8.1854362487793</v>
+        <v>8.18543720245361</v>
       </c>
       <c r="H823" t="n">
         <v>7696</v>
@@ -24294,7 +24294,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>8.15821170806885</v>
+        <v>8.15821266174316</v>
       </c>
       <c r="H825" t="n">
         <v>7830</v>
@@ -24410,7 +24410,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>8.35785675048828</v>
+        <v>8.3578577041626</v>
       </c>
       <c r="H829" t="n">
         <v>17785</v>
@@ -24439,7 +24439,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G830" t="n">
-        <v>8.27618312835693</v>
+        <v>8.27618408203125</v>
       </c>
       <c r="H830" t="n">
         <v>18984</v>
@@ -24497,7 +24497,7 @@
         <v>9.25</v>
       </c>
       <c r="G832" t="n">
-        <v>8.39415550231934</v>
+        <v>8.39415645599365</v>
       </c>
       <c r="H832" t="n">
         <v>9650</v>
@@ -24584,7 +24584,7 @@
         <v>9.25</v>
       </c>
       <c r="G835" t="n">
-        <v>8.39415550231934</v>
+        <v>8.39415645599365</v>
       </c>
       <c r="H835" t="n">
         <v>4985</v>
@@ -24642,7 +24642,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G837" t="n">
-        <v>8.43045425415039</v>
+        <v>8.43045234680176</v>
       </c>
       <c r="H837" t="n">
         <v>6707</v>
@@ -24700,7 +24700,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G839" t="n">
-        <v>8.53935241699219</v>
+        <v>8.53935146331787</v>
       </c>
       <c r="H839" t="n">
         <v>13665</v>
@@ -24729,7 +24729,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>8.53935241699219</v>
+        <v>8.53935146331787</v>
       </c>
       <c r="H840" t="n">
         <v>7521</v>
@@ -24758,7 +24758,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.53027534484863</v>
+        <v>8.53027725219727</v>
       </c>
       <c r="H841" t="n">
         <v>16213</v>
@@ -24787,7 +24787,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G842" t="n">
-        <v>8.53027534484863</v>
+        <v>8.53027725219727</v>
       </c>
       <c r="H842" t="n">
         <v>9977</v>
@@ -24845,7 +24845,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>8.43045425415039</v>
+        <v>8.43045234680176</v>
       </c>
       <c r="H844" t="n">
         <v>21451</v>
@@ -24903,7 +24903,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G846" t="n">
-        <v>8.53027534484863</v>
+        <v>8.53027725219727</v>
       </c>
       <c r="H846" t="n">
         <v>18591</v>
@@ -24932,7 +24932,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>8.46675395965576</v>
+        <v>8.46675300598145</v>
       </c>
       <c r="H847" t="n">
         <v>23993</v>
@@ -25019,7 +25019,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G850" t="n">
-        <v>8.32292556762695</v>
+        <v>8.32292461395264</v>
       </c>
       <c r="H850" t="n">
         <v>28035</v>
@@ -25048,7 +25048,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>8.11197566986084</v>
+        <v>8.11197471618652</v>
       </c>
       <c r="H851" t="n">
         <v>31368</v>
@@ -25106,7 +25106,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>7.98732280731201</v>
+        <v>7.9873218536377</v>
       </c>
       <c r="H853" t="n">
         <v>8039</v>
@@ -25135,7 +25135,7 @@
         <v>8.25</v>
       </c>
       <c r="G854" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H854" t="n">
         <v>14109</v>
@@ -25193,7 +25193,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G856" t="n">
-        <v>8.01608753204346</v>
+        <v>8.01608848571777</v>
       </c>
       <c r="H856" t="n">
         <v>12618</v>
@@ -25222,7 +25222,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G857" t="n">
-        <v>7.95855665206909</v>
+        <v>7.95855569839478</v>
       </c>
       <c r="H857" t="n">
         <v>14002</v>
@@ -25251,7 +25251,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G858" t="n">
-        <v>7.97773361206055</v>
+        <v>7.97773265838623</v>
       </c>
       <c r="H858" t="n">
         <v>14639</v>
@@ -25309,7 +25309,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>8.02567672729492</v>
+        <v>8.02567768096924</v>
       </c>
       <c r="H860" t="n">
         <v>13382</v>
@@ -25338,7 +25338,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G861" t="n">
-        <v>8.02567672729492</v>
+        <v>8.02567768096924</v>
       </c>
       <c r="H861" t="n">
         <v>3528</v>
@@ -25396,7 +25396,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G863" t="n">
-        <v>8.0736198425293</v>
+        <v>8.07362079620361</v>
       </c>
       <c r="H863" t="n">
         <v>6671</v>
@@ -25425,7 +25425,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G864" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H864" t="n">
         <v>16602</v>
@@ -25454,7 +25454,7 @@
         <v>8.25</v>
       </c>
       <c r="G865" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H865" t="n">
         <v>17068</v>
@@ -25483,7 +25483,7 @@
         <v>8.25</v>
       </c>
       <c r="G866" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H866" t="n">
         <v>7115</v>
@@ -25512,7 +25512,7 @@
         <v>8.25</v>
       </c>
       <c r="G867" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H867" t="n">
         <v>2277</v>
@@ -25541,7 +25541,7 @@
         <v>8.25</v>
       </c>
       <c r="G868" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H868" t="n">
         <v>9596</v>
@@ -25570,7 +25570,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G869" t="n">
-        <v>7.89143562316895</v>
+        <v>7.89143657684326</v>
       </c>
       <c r="H869" t="n">
         <v>20139</v>
@@ -25599,7 +25599,7 @@
         <v>8.25</v>
       </c>
       <c r="G870" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H870" t="n">
         <v>6729</v>
@@ -25686,7 +25686,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>7.98732280731201</v>
+        <v>7.9873218536377</v>
       </c>
       <c r="H873" t="n">
         <v>6260</v>
@@ -25831,7 +25831,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>8.02567672729492</v>
+        <v>8.02567768096924</v>
       </c>
       <c r="H878" t="n">
         <v>3474</v>
@@ -25860,7 +25860,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>7.98732280731201</v>
+        <v>7.9873218536377</v>
       </c>
       <c r="H879" t="n">
         <v>9202</v>
@@ -25889,7 +25889,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G880" t="n">
-        <v>8.02567672729492</v>
+        <v>8.02567768096924</v>
       </c>
       <c r="H880" t="n">
         <v>5768</v>
@@ -25976,7 +25976,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G883" t="n">
-        <v>8.00650024414062</v>
+        <v>8.00650119781494</v>
       </c>
       <c r="H883" t="n">
         <v>1214</v>
@@ -26005,7 +26005,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>7.83390426635742</v>
+        <v>7.83390378952026</v>
       </c>
       <c r="H884" t="n">
         <v>2839</v>
@@ -26034,7 +26034,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G885" t="n">
-        <v>7.8626708984375</v>
+        <v>7.86267137527466</v>
       </c>
       <c r="H885" t="n">
         <v>3314</v>
@@ -26092,7 +26092,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G887" t="n">
-        <v>7.8626708984375</v>
+        <v>7.86267137527466</v>
       </c>
       <c r="H887" t="n">
         <v>3277</v>
@@ -26208,7 +26208,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G891" t="n">
-        <v>8.10238456726074</v>
+        <v>8.10238647460938</v>
       </c>
       <c r="H891" t="n">
         <v>5780</v>
@@ -26237,7 +26237,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G892" t="n">
-        <v>8.10238456726074</v>
+        <v>8.10238647460938</v>
       </c>
       <c r="H892" t="n">
         <v>5565</v>
@@ -26295,7 +26295,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G894" t="n">
-        <v>8.03526496887207</v>
+        <v>8.03526592254639</v>
       </c>
       <c r="H894" t="n">
         <v>2731</v>
@@ -26324,7 +26324,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>8.03526496887207</v>
+        <v>8.03526592254639</v>
       </c>
       <c r="H895" t="n">
         <v>2306</v>
@@ -26353,7 +26353,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G896" t="n">
-        <v>8.10238456726074</v>
+        <v>8.10238647460938</v>
       </c>
       <c r="H896" t="n">
         <v>7549</v>
@@ -26411,7 +26411,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G898" t="n">
-        <v>7.96814680099487</v>
+        <v>7.96814584732056</v>
       </c>
       <c r="H898" t="n">
         <v>6261</v>
@@ -26469,7 +26469,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G900" t="n">
-        <v>8.03526496887207</v>
+        <v>8.03526592254639</v>
       </c>
       <c r="H900" t="n">
         <v>6338</v>
@@ -26527,7 +26527,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G902" t="n">
-        <v>8.03526496887207</v>
+        <v>8.03526592254639</v>
       </c>
       <c r="H902" t="n">
         <v>1761</v>
@@ -26556,7 +26556,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G903" t="n">
-        <v>7.96814680099487</v>
+        <v>7.96814584732056</v>
       </c>
       <c r="H903" t="n">
         <v>3021</v>
@@ -26614,7 +26614,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>7.98732280731201</v>
+        <v>7.9873218536377</v>
       </c>
       <c r="H905" t="n">
         <v>16319</v>
@@ -26643,7 +26643,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G906" t="n">
-        <v>8.00650024414062</v>
+        <v>8.00650119781494</v>
       </c>
       <c r="H906" t="n">
         <v>2340</v>
@@ -26672,7 +26672,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G907" t="n">
-        <v>8.00650024414062</v>
+        <v>8.00650119781494</v>
       </c>
       <c r="H907" t="n">
         <v>1057</v>
@@ -26701,7 +26701,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>8.0736198425293</v>
+        <v>8.07362079620361</v>
       </c>
       <c r="H908" t="n">
         <v>22955</v>
@@ -26759,7 +26759,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>8.03526496887207</v>
+        <v>8.03526592254639</v>
       </c>
       <c r="H910" t="n">
         <v>22840</v>
@@ -26788,7 +26788,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G911" t="n">
-        <v>8.03526496887207</v>
+        <v>8.03526592254639</v>
       </c>
       <c r="H911" t="n">
         <v>9880</v>
@@ -26817,7 +26817,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G912" t="n">
-        <v>8.13115215301514</v>
+        <v>8.1311502456665</v>
       </c>
       <c r="H912" t="n">
         <v>8382</v>
@@ -26875,7 +26875,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G914" t="n">
-        <v>8.01608753204346</v>
+        <v>8.01608848571777</v>
       </c>
       <c r="H914" t="n">
         <v>32578</v>
@@ -26933,7 +26933,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G916" t="n">
-        <v>8.03526496887207</v>
+        <v>8.03526592254639</v>
       </c>
       <c r="H916" t="n">
         <v>10422</v>
@@ -26991,7 +26991,7 @@
         <v>8.25</v>
       </c>
       <c r="G918" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H918" t="n">
         <v>15260</v>
@@ -27020,7 +27020,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G919" t="n">
-        <v>7.98732280731201</v>
+        <v>7.9873218536377</v>
       </c>
       <c r="H919" t="n">
         <v>6514</v>
@@ -27049,7 +27049,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G920" t="n">
-        <v>8.00650024414062</v>
+        <v>8.00650119781494</v>
       </c>
       <c r="H920" t="n">
         <v>4825</v>
@@ -27107,7 +27107,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G922" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H922" t="n">
         <v>2152</v>
@@ -27136,7 +27136,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G923" t="n">
-        <v>7.92020273208618</v>
+        <v>7.92020177841187</v>
       </c>
       <c r="H923" t="n">
         <v>3214</v>
@@ -27165,7 +27165,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G924" t="n">
-        <v>7.92979145050049</v>
+        <v>7.92979097366333</v>
       </c>
       <c r="H924" t="n">
         <v>1119</v>
@@ -27223,7 +27223,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G926" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H926" t="n">
         <v>15579</v>
@@ -27252,7 +27252,7 @@
         <v>8.25</v>
       </c>
       <c r="G927" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H927" t="n">
         <v>8023</v>
@@ -27281,7 +27281,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G928" t="n">
-        <v>7.89143562316895</v>
+        <v>7.89143657684326</v>
       </c>
       <c r="H928" t="n">
         <v>6514</v>
@@ -27310,7 +27310,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G929" t="n">
-        <v>7.89143562316895</v>
+        <v>7.89143657684326</v>
       </c>
       <c r="H929" t="n">
         <v>6272</v>
@@ -27484,7 +27484,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G935" t="n">
-        <v>7.84349393844604</v>
+        <v>7.84349346160889</v>
       </c>
       <c r="H935" t="n">
         <v>9048</v>
@@ -27571,7 +27571,7 @@
         <v>8.25</v>
       </c>
       <c r="G938" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H938" t="n">
         <v>2172</v>
@@ -27600,7 +27600,7 @@
         <v>8.25</v>
       </c>
       <c r="G939" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H939" t="n">
         <v>3229</v>
@@ -27629,7 +27629,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G940" t="n">
-        <v>7.8818473815918</v>
+        <v>7.88184833526611</v>
       </c>
       <c r="H940" t="n">
         <v>8098</v>
@@ -27658,7 +27658,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G941" t="n">
-        <v>7.84349393844604</v>
+        <v>7.84349346160889</v>
       </c>
       <c r="H941" t="n">
         <v>17479</v>
@@ -27687,7 +27687,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>7.8626708984375</v>
+        <v>7.86267137527466</v>
       </c>
       <c r="H942" t="n">
         <v>15590</v>
@@ -27745,7 +27745,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G944" t="n">
-        <v>7.83390426635742</v>
+        <v>7.83390378952026</v>
       </c>
       <c r="H944" t="n">
         <v>4740</v>
@@ -27774,7 +27774,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G945" t="n">
-        <v>7.89143562316895</v>
+        <v>7.89143657684326</v>
       </c>
       <c r="H945" t="n">
         <v>6784</v>
@@ -27861,7 +27861,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G948" t="n">
-        <v>7.8626708984375</v>
+        <v>7.86267137527466</v>
       </c>
       <c r="H948" t="n">
         <v>11927</v>
@@ -27919,7 +27919,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G950" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H950" t="n">
         <v>12451</v>
@@ -27948,7 +27948,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G951" t="n">
-        <v>7.92020273208618</v>
+        <v>7.92020177841187</v>
       </c>
       <c r="H951" t="n">
         <v>1695</v>
@@ -28006,7 +28006,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G953" t="n">
-        <v>7.84349393844604</v>
+        <v>7.84349346160889</v>
       </c>
       <c r="H953" t="n">
         <v>8720</v>
@@ -28035,7 +28035,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G954" t="n">
-        <v>7.89143562316895</v>
+        <v>7.89143657684326</v>
       </c>
       <c r="H954" t="n">
         <v>10444</v>
@@ -28093,7 +28093,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>7.83390426635742</v>
+        <v>7.83390378952026</v>
       </c>
       <c r="H956" t="n">
         <v>3445</v>
@@ -28151,7 +28151,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G958" t="n">
-        <v>7.8818473815918</v>
+        <v>7.88184833526611</v>
       </c>
       <c r="H958" t="n">
         <v>2891</v>
@@ -28180,7 +28180,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G959" t="n">
-        <v>7.8818473815918</v>
+        <v>7.88184833526611</v>
       </c>
       <c r="H959" t="n">
         <v>2299</v>
@@ -28209,7 +28209,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G960" t="n">
-        <v>7.89143562316895</v>
+        <v>7.89143657684326</v>
       </c>
       <c r="H960" t="n">
         <v>5563</v>
@@ -28267,7 +28267,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G962" t="n">
-        <v>7.89143562316895</v>
+        <v>7.89143657684326</v>
       </c>
       <c r="H962" t="n">
         <v>14806</v>
@@ -28296,7 +28296,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>7.83390426635742</v>
+        <v>7.83390378952026</v>
       </c>
       <c r="H963" t="n">
         <v>34842</v>
@@ -28325,7 +28325,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G964" t="n">
-        <v>7.84349393844604</v>
+        <v>7.84349346160889</v>
       </c>
       <c r="H964" t="n">
         <v>6707</v>
@@ -28441,7 +28441,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G968" t="n">
-        <v>7.84349393844604</v>
+        <v>7.84349346160889</v>
       </c>
       <c r="H968" t="n">
         <v>8604</v>
@@ -28499,7 +28499,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G970" t="n">
-        <v>7.97773361206055</v>
+        <v>7.97773265838623</v>
       </c>
       <c r="H970" t="n">
         <v>80776</v>
@@ -28644,7 +28644,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.10238456726074</v>
+        <v>8.10238647460938</v>
       </c>
       <c r="H975" t="n">
         <v>9639</v>
@@ -28673,7 +28673,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>8.11197566986084</v>
+        <v>8.11197471618652</v>
       </c>
       <c r="H976" t="n">
         <v>12430</v>
@@ -28731,7 +28731,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G978" t="n">
-        <v>8.32292556762695</v>
+        <v>8.32292461395264</v>
       </c>
       <c r="H978" t="n">
         <v>35275</v>
@@ -28760,7 +28760,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G979" t="n">
-        <v>8.3708667755127</v>
+        <v>8.37086772918701</v>
       </c>
       <c r="H979" t="n">
         <v>25943</v>
@@ -28818,7 +28818,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>8.70646953582764</v>
+        <v>8.70646858215332</v>
       </c>
       <c r="H981" t="n">
         <v>84618</v>
@@ -28992,7 +28992,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G987" t="n">
-        <v>9.36808490753174</v>
+        <v>9.36808586120605</v>
       </c>
       <c r="H987" t="n">
         <v>46850</v>
@@ -29050,7 +29050,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>9.46397018432617</v>
+        <v>9.46397113800049</v>
       </c>
       <c r="H989" t="n">
         <v>37821</v>
@@ -29079,7 +29079,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G990" t="n">
-        <v>9.44479465484619</v>
+        <v>9.44479370117188</v>
       </c>
       <c r="H990" t="n">
         <v>30039</v>
@@ -29108,7 +29108,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>9.43520355224609</v>
+        <v>9.43520450592041</v>
       </c>
       <c r="H991" t="n">
         <v>20599</v>
@@ -29137,7 +29137,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G992" t="n">
-        <v>9.93381309509277</v>
+        <v>9.93381214141846</v>
       </c>
       <c r="H992" t="n">
         <v>181815</v>
@@ -29195,7 +29195,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G994" t="n">
-        <v>9.95299053192139</v>
+        <v>9.95298957824707</v>
       </c>
       <c r="H994" t="n">
         <v>86253</v>
@@ -29282,7 +29282,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G997" t="n">
-        <v>9.85710334777832</v>
+        <v>9.85710430145264</v>
       </c>
       <c r="H997" t="n">
         <v>48818</v>
@@ -29369,7 +29369,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.52150344848633</v>
+        <v>9.52150249481201</v>
       </c>
       <c r="H1000" t="n">
         <v>33125</v>
@@ -29514,7 +29514,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.36808490753174</v>
+        <v>9.36808586120605</v>
       </c>
       <c r="H1005" t="n">
         <v>18745</v>
@@ -29804,7 +29804,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.26261043548584</v>
+        <v>9.26260948181152</v>
       </c>
       <c r="H1015" t="n">
         <v>14351</v>
@@ -29862,7 +29862,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.36808490753174</v>
+        <v>9.36808586120605</v>
       </c>
       <c r="H1017" t="n">
         <v>13706</v>
@@ -30007,7 +30007,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.68450832366943</v>
+        <v>9.68450927734375</v>
       </c>
       <c r="H1022" t="n">
         <v>70585</v>
@@ -30094,7 +30094,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>9.03248310089111</v>
+        <v>9.0324821472168</v>
       </c>
       <c r="H1025" t="n">
         <v>546034</v>
@@ -30123,7 +30123,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1026" t="n">
-        <v>9.01330471038818</v>
+        <v>9.0133056640625</v>
       </c>
       <c r="H1026" t="n">
         <v>49137</v>
@@ -30181,7 +30181,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.03248310089111</v>
+        <v>9.0324821472168</v>
       </c>
       <c r="H1028" t="n">
         <v>31478</v>
@@ -30413,7 +30413,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.77359008789062</v>
+        <v>8.77358913421631</v>
       </c>
       <c r="H1036" t="n">
         <v>25236</v>
@@ -30471,7 +30471,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.68729209899902</v>
+        <v>8.68729305267334</v>
       </c>
       <c r="H1038" t="n">
         <v>19558</v>
@@ -30558,7 +30558,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.90783023834229</v>
+        <v>8.90782833099365</v>
       </c>
       <c r="H1041" t="n">
         <v>15127</v>
@@ -30645,7 +30645,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>9.07083606719971</v>
+        <v>9.07083702087402</v>
       </c>
       <c r="H1044" t="n">
         <v>9950</v>
@@ -30819,7 +30819,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.90783023834229</v>
+        <v>8.90782833099365</v>
       </c>
       <c r="H1050" t="n">
         <v>25055</v>
@@ -30848,7 +30848,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.77359008789062</v>
+        <v>8.77358913421631</v>
       </c>
       <c r="H1051" t="n">
         <v>34371</v>
@@ -30935,7 +30935,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1054" t="n">
-        <v>8.2462158203125</v>
+        <v>8.24621677398682</v>
       </c>
       <c r="H1054" t="n">
         <v>30484</v>
@@ -31022,7 +31022,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.76678466796875</v>
+        <v>7.76678514480591</v>
       </c>
       <c r="H1057" t="n">
         <v>69417</v>
@@ -31051,7 +31051,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.71884155273438</v>
+        <v>7.71884107589722</v>
       </c>
       <c r="H1058" t="n">
         <v>51900</v>
@@ -31080,7 +31080,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.53665781021118</v>
+        <v>7.53665733337402</v>
       </c>
       <c r="H1059" t="n">
         <v>37114</v>
@@ -31109,7 +31109,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.45994901657104</v>
+        <v>7.45994853973389</v>
       </c>
       <c r="H1060" t="n">
         <v>74981</v>
@@ -31138,7 +31138,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.54624557495117</v>
+        <v>7.54624605178833</v>
       </c>
       <c r="H1061" t="n">
         <v>28225</v>
@@ -31167,7 +31167,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.27776432037354</v>
+        <v>7.27776479721069</v>
       </c>
       <c r="H1062" t="n">
         <v>45137</v>
@@ -31254,7 +31254,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.38602256774902</v>
+        <v>6.38602304458618</v>
       </c>
       <c r="H1065" t="n">
         <v>72656</v>
@@ -31312,7 +31312,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1067" t="n">
-        <v>5.42716026306152</v>
+        <v>5.42715978622437</v>
       </c>
       <c r="H1067" t="n">
         <v>134749</v>
@@ -31370,7 +31370,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.60253858566284</v>
+        <v>4.6025390625</v>
       </c>
       <c r="H1069" t="n">
         <v>61375</v>
@@ -31428,7 +31428,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.47788715362549</v>
+        <v>4.47788667678833</v>
       </c>
       <c r="H1071" t="n">
         <v>30778</v>
@@ -31486,7 +31486,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.08197021484375</v>
+        <v>5.08196973800659</v>
       </c>
       <c r="H1073" t="n">
         <v>47095</v>
@@ -31573,7 +31573,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.94494533538818</v>
+        <v>5.94494581222534</v>
       </c>
       <c r="H1076" t="n">
         <v>32019</v>
@@ -31689,7 +31689,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.74358558654785</v>
+        <v>5.74358510971069</v>
       </c>
       <c r="H1080" t="n">
         <v>16778</v>
@@ -31834,7 +31834,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.38602256774902</v>
+        <v>6.38602304458618</v>
       </c>
       <c r="H1085" t="n">
         <v>14540</v>
@@ -31863,7 +31863,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1086" t="n">
-        <v>6.40520000457764</v>
+        <v>6.40519952774048</v>
       </c>
       <c r="H1086" t="n">
         <v>21927</v>
@@ -31892,7 +31892,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.37643432617188</v>
+        <v>6.37643384933472</v>
       </c>
       <c r="H1087" t="n">
         <v>23169</v>
@@ -31921,7 +31921,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.16548442840576</v>
+        <v>6.1654839515686</v>
       </c>
       <c r="H1088" t="n">
         <v>23094</v>
@@ -31950,7 +31950,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.36684513092041</v>
+        <v>6.36684560775757</v>
       </c>
       <c r="H1089" t="n">
         <v>11544</v>
@@ -31979,7 +31979,7 @@
         <v>6.75</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.47232055664062</v>
+        <v>6.47232007980347</v>
       </c>
       <c r="H1090" t="n">
         <v>14073</v>
@@ -32008,7 +32008,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.48190879821777</v>
+        <v>6.48190927505493</v>
       </c>
       <c r="H1091" t="n">
         <v>19667</v>
@@ -32037,7 +32037,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.48190879821777</v>
+        <v>6.48190927505493</v>
       </c>
       <c r="H1092" t="n">
         <v>11084</v>
@@ -32095,7 +32095,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.92020273208618</v>
+        <v>7.92020177841187</v>
       </c>
       <c r="H1094" t="n">
         <v>133533</v>
@@ -32124,7 +32124,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.76678466796875</v>
+        <v>7.76678514480591</v>
       </c>
       <c r="H1095" t="n">
         <v>41464</v>
@@ -32153,7 +32153,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.60377788543701</v>
+        <v>7.60377740859985</v>
       </c>
       <c r="H1096" t="n">
         <v>44255</v>
@@ -32240,7 +32240,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.51748037338257</v>
+        <v>7.51748085021973</v>
       </c>
       <c r="H1099" t="n">
         <v>9544</v>
@@ -32414,7 +32414,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.12434577941895</v>
+        <v>7.1243462562561</v>
       </c>
       <c r="H1105" t="n">
         <v>28348</v>
@@ -32559,7 +32559,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.42159414291382</v>
+        <v>7.42159366607666</v>
       </c>
       <c r="H1110" t="n">
         <v>15343</v>
@@ -32588,7 +32588,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.39282846450806</v>
+        <v>7.3928279876709</v>
       </c>
       <c r="H1111" t="n">
         <v>7992</v>
@@ -32646,7 +32646,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.53665781021118</v>
+        <v>7.53665733337402</v>
       </c>
       <c r="H1113" t="n">
         <v>21555</v>
@@ -32733,7 +32733,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>7.84349393844604</v>
+        <v>7.84349346160889</v>
       </c>
       <c r="H1116" t="n">
         <v>14549</v>
@@ -32762,7 +32762,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.83390426635742</v>
+        <v>7.83390378952026</v>
       </c>
       <c r="H1117" t="n">
         <v>14731</v>
@@ -32791,7 +32791,7 @@
         <v>8.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H1118" t="n">
         <v>16629</v>
@@ -32878,7 +32878,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.96814680099487</v>
+        <v>7.96814584732056</v>
       </c>
       <c r="H1121" t="n">
         <v>15248</v>
@@ -32907,7 +32907,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.8818473815918</v>
+        <v>7.88184833526611</v>
       </c>
       <c r="H1122" t="n">
         <v>14416</v>
@@ -32965,7 +32965,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1124" t="n">
-        <v>7.90102577209473</v>
+        <v>7.90102529525757</v>
       </c>
       <c r="H1124" t="n">
         <v>17606</v>
@@ -33023,7 +33023,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>7.83390426635742</v>
+        <v>7.83390378952026</v>
       </c>
       <c r="H1126" t="n">
         <v>17349</v>
@@ -33313,7 +33313,7 @@
         <v>7.75</v>
       </c>
       <c r="G1136" t="n">
-        <v>7.43118190765381</v>
+        <v>7.43118238449097</v>
       </c>
       <c r="H1136" t="n">
         <v>14241</v>
@@ -33371,7 +33371,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.23940992355347</v>
+        <v>7.23941040039062</v>
       </c>
       <c r="H1138" t="n">
         <v>6166</v>
@@ -33429,7 +33429,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1140" t="n">
-        <v>7.16270065307617</v>
+        <v>7.16270112991333</v>
       </c>
       <c r="H1140" t="n">
         <v>13726</v>
@@ -33487,7 +33487,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1142" t="n">
-        <v>7.45035934448242</v>
+        <v>7.45035982131958</v>
       </c>
       <c r="H1142" t="n">
         <v>23941</v>
@@ -33574,7 +33574,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>7.3161187171936</v>
+        <v>7.31611967086792</v>
       </c>
       <c r="H1145" t="n">
         <v>8629</v>
@@ -33661,7 +33661,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1148" t="n">
-        <v>7.26817560195923</v>
+        <v>7.26817607879639</v>
       </c>
       <c r="H1148" t="n">
         <v>5586</v>
@@ -33748,7 +33748,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.28735303878784</v>
+        <v>7.28735256195068</v>
       </c>
       <c r="H1151" t="n">
         <v>18719</v>
@@ -33806,7 +33806,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1153" t="n">
-        <v>7.57501173019409</v>
+        <v>7.57501125335693</v>
       </c>
       <c r="H1153" t="n">
         <v>16769</v>
@@ -33835,7 +33835,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1154" t="n">
-        <v>7.60377788543701</v>
+        <v>7.60377740859985</v>
       </c>
       <c r="H1154" t="n">
         <v>6233</v>
@@ -33864,7 +33864,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1155" t="n">
-        <v>7.51748037338257</v>
+        <v>7.51748085021973</v>
       </c>
       <c r="H1155" t="n">
         <v>45026</v>
@@ -34125,7 +34125,7 @@
         <v>7.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1164" t="n">
         <v>4750</v>
@@ -34154,7 +34154,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>7.28735303878784</v>
+        <v>7.28735256195068</v>
       </c>
       <c r="H1165" t="n">
         <v>7319</v>
@@ -34212,7 +34212,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.51748037338257</v>
+        <v>7.51748085021973</v>
       </c>
       <c r="H1167" t="n">
         <v>16168</v>
@@ -34328,7 +34328,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1171" t="n">
-        <v>7.92020273208618</v>
+        <v>7.92020177841187</v>
       </c>
       <c r="H1171" t="n">
         <v>32382</v>
@@ -34357,7 +34357,7 @@
         <v>8.25</v>
       </c>
       <c r="G1172" t="n">
-        <v>7.91061353683472</v>
+        <v>7.91061401367188</v>
       </c>
       <c r="H1172" t="n">
         <v>25185</v>
@@ -34444,7 +34444,7 @@
         <v>8</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.6708984375</v>
+        <v>7.67089796066284</v>
       </c>
       <c r="H1175" t="n">
         <v>7301</v>
@@ -34473,7 +34473,7 @@
         <v>8</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.6708984375</v>
+        <v>7.67089796066284</v>
       </c>
       <c r="H1176" t="n">
         <v>5528</v>
@@ -34560,7 +34560,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1179" t="n">
-        <v>7.66130924224854</v>
+        <v>7.66130971908569</v>
       </c>
       <c r="H1179" t="n">
         <v>2679</v>
@@ -34589,7 +34589,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1180" t="n">
-        <v>7.54624557495117</v>
+        <v>7.54624605178833</v>
       </c>
       <c r="H1180" t="n">
         <v>13650</v>
@@ -34647,7 +34647,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1182" t="n">
-        <v>7.66130924224854</v>
+        <v>7.66130971908569</v>
       </c>
       <c r="H1182" t="n">
         <v>7015</v>
@@ -34676,7 +34676,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1183" t="n">
-        <v>7.57501173019409</v>
+        <v>7.57501125335693</v>
       </c>
       <c r="H1183" t="n">
         <v>8189</v>
@@ -34792,7 +34792,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1187" t="n">
-        <v>7.45994901657104</v>
+        <v>7.45994853973389</v>
       </c>
       <c r="H1187" t="n">
         <v>4524</v>
@@ -34821,7 +34821,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1188" t="n">
-        <v>7.45994901657104</v>
+        <v>7.45994853973389</v>
       </c>
       <c r="H1188" t="n">
         <v>10413</v>
@@ -34850,7 +34850,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>7.26817560195923</v>
+        <v>7.26817607879639</v>
       </c>
       <c r="H1189" t="n">
         <v>8883</v>
@@ -34908,7 +34908,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.39282846450806</v>
+        <v>7.3928279876709</v>
       </c>
       <c r="H1191" t="n">
         <v>7483</v>
@@ -34937,7 +34937,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1192" t="n">
-        <v>7.42159414291382</v>
+        <v>7.42159366607666</v>
       </c>
       <c r="H1192" t="n">
         <v>7775</v>
@@ -34966,7 +34966,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1193" t="n">
-        <v>7.45035934448242</v>
+        <v>7.45035982131958</v>
       </c>
       <c r="H1193" t="n">
         <v>9071</v>
@@ -35053,7 +35053,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1196" t="n">
-        <v>7.29694223403931</v>
+        <v>7.29694175720215</v>
       </c>
       <c r="H1196" t="n">
         <v>5328</v>
@@ -35140,7 +35140,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1199" t="n">
-        <v>7.29694223403931</v>
+        <v>7.29694175720215</v>
       </c>
       <c r="H1199" t="n">
         <v>4893</v>
@@ -35256,7 +35256,7 @@
         <v>7.5</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1203" t="n">
         <v>3700</v>
@@ -35372,7 +35372,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.05722570419312</v>
+        <v>7.05722618103027</v>
       </c>
       <c r="H1207" t="n">
         <v>10822</v>
@@ -35430,7 +35430,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.15311288833618</v>
+        <v>7.15311241149902</v>
       </c>
       <c r="H1209" t="n">
         <v>5754</v>
@@ -35459,7 +35459,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.15311288833618</v>
+        <v>7.15311241149902</v>
       </c>
       <c r="H1210" t="n">
         <v>5884</v>
@@ -35488,7 +35488,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.28735303878784</v>
+        <v>7.28735256195068</v>
       </c>
       <c r="H1211" t="n">
         <v>3493</v>
@@ -35517,7 +35517,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1212" t="n">
-        <v>7.27776432037354</v>
+        <v>7.27776479721069</v>
       </c>
       <c r="H1212" t="n">
         <v>4524</v>
@@ -35633,7 +35633,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1216" t="n">
-        <v>7.65172100067139</v>
+        <v>7.65172052383423</v>
       </c>
       <c r="H1216" t="n">
         <v>10117</v>
@@ -35807,7 +35807,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1222" t="n">
-        <v>7.57501173019409</v>
+        <v>7.57501125335693</v>
       </c>
       <c r="H1222" t="n">
         <v>5904</v>
@@ -35836,7 +35836,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.59418869018555</v>
+        <v>7.59418916702271</v>
       </c>
       <c r="H1223" t="n">
         <v>10123</v>
@@ -35894,7 +35894,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.28735303878784</v>
+        <v>7.28735256195068</v>
       </c>
       <c r="H1225" t="n">
         <v>10976</v>
@@ -35981,7 +35981,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1228" t="n">
-        <v>6.98051738739014</v>
+        <v>6.98051786422729</v>
       </c>
       <c r="H1228" t="n">
         <v>9715</v>
@@ -36010,7 +36010,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1229" t="n">
-        <v>7.03804969787598</v>
+        <v>7.03804922103882</v>
       </c>
       <c r="H1229" t="n">
         <v>8972</v>
@@ -36039,7 +36039,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.98051738739014</v>
+        <v>6.98051786422729</v>
       </c>
       <c r="H1230" t="n">
         <v>15225</v>
@@ -36068,7 +36068,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>7.03804969787598</v>
+        <v>7.03804922103882</v>
       </c>
       <c r="H1231" t="n">
         <v>10854</v>
@@ -36097,7 +36097,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.04763746261597</v>
+        <v>7.04763793945312</v>
       </c>
       <c r="H1232" t="n">
         <v>19900</v>
@@ -36126,7 +36126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>7.04763746261597</v>
+        <v>7.04763793945312</v>
       </c>
       <c r="H1233" t="n">
         <v>18331</v>
@@ -36184,7 +36184,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>7.28735303878784</v>
+        <v>7.28735256195068</v>
       </c>
       <c r="H1235" t="n">
         <v>15274</v>
@@ -36242,7 +36242,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.10516929626465</v>
+        <v>7.10516881942749</v>
       </c>
       <c r="H1237" t="n">
         <v>21889</v>
@@ -36300,7 +36300,7 @@
         <v>7.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1239" t="n">
         <v>4019</v>
@@ -36387,7 +36387,7 @@
         <v>7.75</v>
       </c>
       <c r="G1242" t="n">
-        <v>7.43118190765381</v>
+        <v>7.43118238449097</v>
       </c>
       <c r="H1242" t="n">
         <v>25704</v>
@@ -36416,7 +36416,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.45994901657104</v>
+        <v>7.45994853973389</v>
       </c>
       <c r="H1243" t="n">
         <v>7069</v>
@@ -36532,7 +36532,7 @@
         <v>7.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1247" t="n">
         <v>70831</v>
@@ -36590,7 +36590,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.17228937149048</v>
+        <v>7.17228984832764</v>
       </c>
       <c r="H1249" t="n">
         <v>16744</v>
@@ -36619,7 +36619,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>7.15311288833618</v>
+        <v>7.15311241149902</v>
       </c>
       <c r="H1250" t="n">
         <v>11964</v>
@@ -36677,7 +36677,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1252" t="n">
-        <v>7.12434577941895</v>
+        <v>7.1243462562561</v>
       </c>
       <c r="H1252" t="n">
         <v>27846</v>
@@ -36706,7 +36706,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.13393497467041</v>
+        <v>7.13393545150757</v>
       </c>
       <c r="H1253" t="n">
         <v>18347</v>
@@ -36735,7 +36735,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.11475849151611</v>
+        <v>7.11475801467896</v>
       </c>
       <c r="H1254" t="n">
         <v>103812</v>
@@ -36764,7 +36764,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.12434577941895</v>
+        <v>7.1243462562561</v>
       </c>
       <c r="H1255" t="n">
         <v>6276</v>
@@ -36793,7 +36793,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.11475849151611</v>
+        <v>7.11475801467896</v>
       </c>
       <c r="H1256" t="n">
         <v>9096</v>
@@ -36880,7 +36880,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.06681489944458</v>
+        <v>7.06681537628174</v>
       </c>
       <c r="H1259" t="n">
         <v>6550</v>
@@ -36967,7 +36967,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1262" t="n">
-        <v>7.06681489944458</v>
+        <v>7.06681537628174</v>
       </c>
       <c r="H1262" t="n">
         <v>7643</v>
@@ -37025,7 +37025,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1264" t="n">
-        <v>7.12434577941895</v>
+        <v>7.1243462562561</v>
       </c>
       <c r="H1264" t="n">
         <v>14543</v>
@@ -37054,7 +37054,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1265" t="n">
-        <v>7.08599185943604</v>
+        <v>7.08599138259888</v>
       </c>
       <c r="H1265" t="n">
         <v>9563</v>
@@ -37083,7 +37083,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1266" t="n">
-        <v>7.11475849151611</v>
+        <v>7.11475801467896</v>
       </c>
       <c r="H1266" t="n">
         <v>12859</v>
@@ -37112,7 +37112,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.06681489944458</v>
+        <v>7.06681537628174</v>
       </c>
       <c r="H1267" t="n">
         <v>10750</v>
@@ -37170,7 +37170,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>7.65172100067139</v>
+        <v>7.65172052383423</v>
       </c>
       <c r="H1269" t="n">
         <v>129988</v>
@@ -37257,7 +37257,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1272" t="n">
-        <v>7.29694223403931</v>
+        <v>7.29694175720215</v>
       </c>
       <c r="H1272" t="n">
         <v>18970</v>
@@ -37315,7 +37315,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.28735303878784</v>
+        <v>7.28735256195068</v>
       </c>
       <c r="H1274" t="n">
         <v>11863</v>
@@ -37344,7 +37344,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.26817560195923</v>
+        <v>7.26817607879639</v>
       </c>
       <c r="H1275" t="n">
         <v>6153</v>
@@ -37460,7 +37460,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1279" t="n">
-        <v>7.23940992355347</v>
+        <v>7.23941040039062</v>
       </c>
       <c r="H1279" t="n">
         <v>7842</v>
@@ -37489,7 +37489,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.28735303878784</v>
+        <v>7.28735256195068</v>
       </c>
       <c r="H1280" t="n">
         <v>7941</v>
@@ -37547,7 +37547,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.10516929626465</v>
+        <v>7.10516881942749</v>
       </c>
       <c r="H1282" t="n">
         <v>12773</v>
@@ -37605,7 +37605,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1284" t="n">
-        <v>7.17228937149048</v>
+        <v>7.17228984832764</v>
       </c>
       <c r="H1284" t="n">
         <v>3373</v>
@@ -37634,7 +37634,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.08599185943604</v>
+        <v>7.08599138259888</v>
       </c>
       <c r="H1285" t="n">
         <v>6624</v>
@@ -37663,7 +37663,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1286" t="n">
-        <v>6.96133995056152</v>
+        <v>6.96134042739868</v>
       </c>
       <c r="H1286" t="n">
         <v>12243</v>
@@ -37721,7 +37721,7 @@
         <v>7.25</v>
       </c>
       <c r="G1288" t="n">
-        <v>6.95175123214722</v>
+        <v>6.95175170898438</v>
       </c>
       <c r="H1288" t="n">
         <v>7118</v>
@@ -37750,7 +37750,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.90380811691284</v>
+        <v>6.90380764007568</v>
       </c>
       <c r="H1289" t="n">
         <v>18881</v>
@@ -37779,7 +37779,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1290" t="n">
-        <v>6.82709932327271</v>
+        <v>6.82709884643555</v>
       </c>
       <c r="H1290" t="n">
         <v>16595</v>
@@ -37808,7 +37808,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1291" t="n">
-        <v>6.82709932327271</v>
+        <v>6.82709884643555</v>
       </c>
       <c r="H1291" t="n">
         <v>4443</v>
@@ -37837,7 +37837,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1292" t="n">
-        <v>6.82709932327271</v>
+        <v>6.82709884643555</v>
       </c>
       <c r="H1292" t="n">
         <v>7171</v>
@@ -37924,7 +37924,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.03804969787598</v>
+        <v>7.03804922103882</v>
       </c>
       <c r="H1295" t="n">
         <v>41692</v>
@@ -37953,7 +37953,7 @@
         <v>7.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1296" t="n">
         <v>66724</v>
@@ -37982,7 +37982,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1297" t="n">
-        <v>7.05722570419312</v>
+        <v>7.05722618103027</v>
       </c>
       <c r="H1297" t="n">
         <v>80201</v>
@@ -38011,7 +38011,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1298" t="n">
-        <v>7.08599185943604</v>
+        <v>7.08599138259888</v>
       </c>
       <c r="H1298" t="n">
         <v>43738</v>
@@ -38040,7 +38040,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1299" t="n">
-        <v>6.96133995056152</v>
+        <v>6.96134042739868</v>
       </c>
       <c r="H1299" t="n">
         <v>51819</v>
@@ -38069,7 +38069,7 @@
         <v>7.25</v>
       </c>
       <c r="G1300" t="n">
-        <v>6.95175123214722</v>
+        <v>6.95175170898438</v>
       </c>
       <c r="H1300" t="n">
         <v>14258</v>
@@ -38127,7 +38127,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>6.99010610580444</v>
+        <v>6.99010562896729</v>
       </c>
       <c r="H1302" t="n">
         <v>12880</v>
@@ -38156,7 +38156,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.90380811691284</v>
+        <v>6.90380764007568</v>
       </c>
       <c r="H1303" t="n">
         <v>12470</v>
@@ -38185,7 +38185,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.80792188644409</v>
+        <v>6.80792140960693</v>
       </c>
       <c r="H1304" t="n">
         <v>25146</v>
@@ -38243,7 +38243,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1306" t="n">
-        <v>6.83668804168701</v>
+        <v>6.83668756484985</v>
       </c>
       <c r="H1306" t="n">
         <v>5349</v>
@@ -38301,7 +38301,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1308" t="n">
-        <v>6.74080228805542</v>
+        <v>6.74080181121826</v>
       </c>
       <c r="H1308" t="n">
         <v>10265</v>
@@ -38330,7 +38330,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1309" t="n">
-        <v>6.83668804168701</v>
+        <v>6.83668756484985</v>
       </c>
       <c r="H1309" t="n">
         <v>17387</v>
@@ -38388,7 +38388,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.80792188644409</v>
+        <v>6.80792140960693</v>
       </c>
       <c r="H1311" t="n">
         <v>9606</v>
@@ -38417,7 +38417,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1312" t="n">
-        <v>6.80792188644409</v>
+        <v>6.80792140960693</v>
       </c>
       <c r="H1312" t="n">
         <v>37179</v>
@@ -38446,7 +38446,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1313" t="n">
-        <v>6.80792188644409</v>
+        <v>6.80792140960693</v>
       </c>
       <c r="H1313" t="n">
         <v>13271</v>
@@ -38562,7 +38562,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1317" t="n">
-        <v>6.76956748962402</v>
+        <v>6.76956796646118</v>
       </c>
       <c r="H1317" t="n">
         <v>28920</v>
@@ -38591,7 +38591,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1318" t="n">
-        <v>6.72162485122681</v>
+        <v>6.72162437438965</v>
       </c>
       <c r="H1318" t="n">
         <v>139450</v>
@@ -38620,7 +38620,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>6.75038957595825</v>
+        <v>6.75039005279541</v>
       </c>
       <c r="H1319" t="n">
         <v>33588</v>
@@ -38678,7 +38678,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.73121309280396</v>
+        <v>6.7312126159668</v>
       </c>
       <c r="H1321" t="n">
         <v>204873</v>
@@ -38736,7 +38736,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>6.67368125915527</v>
+        <v>6.67368173599243</v>
       </c>
       <c r="H1323" t="n">
         <v>39564</v>
@@ -38794,7 +38794,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1325" t="n">
-        <v>6.48190879821777</v>
+        <v>6.48190927505493</v>
       </c>
       <c r="H1325" t="n">
         <v>35932</v>
@@ -38823,7 +38823,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1326" t="n">
-        <v>6.61615037918091</v>
+        <v>6.61614990234375</v>
       </c>
       <c r="H1326" t="n">
         <v>60991</v>
@@ -38881,7 +38881,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1328" t="n">
-        <v>7.08599185943604</v>
+        <v>7.08599138259888</v>
       </c>
       <c r="H1328" t="n">
         <v>331922</v>
@@ -38997,7 +38997,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>7.26817560195923</v>
+        <v>7.26817607879639</v>
       </c>
       <c r="H1332" t="n">
         <v>92492</v>
@@ -39026,7 +39026,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>7.11475849151611</v>
+        <v>7.11475801467896</v>
       </c>
       <c r="H1333" t="n">
         <v>54970</v>
@@ -39055,7 +39055,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1334" t="n">
-        <v>7.27776432037354</v>
+        <v>7.27776479721069</v>
       </c>
       <c r="H1334" t="n">
         <v>31376</v>
@@ -39142,7 +39142,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1337" t="n">
-        <v>7.13393497467041</v>
+        <v>7.13393545150757</v>
       </c>
       <c r="H1337" t="n">
         <v>19451</v>
@@ -39171,7 +39171,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1338" t="n">
-        <v>7.13393497467041</v>
+        <v>7.13393545150757</v>
       </c>
       <c r="H1338" t="n">
         <v>17704</v>
@@ -39200,7 +39200,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>6.99010610580444</v>
+        <v>6.99010562896729</v>
       </c>
       <c r="H1339" t="n">
         <v>22032</v>
@@ -39258,7 +39258,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1341" t="n">
-        <v>7.04763746261597</v>
+        <v>7.04763793945312</v>
       </c>
       <c r="H1341" t="n">
         <v>18935</v>
@@ -39316,7 +39316,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1343" t="n">
-        <v>7.04763746261597</v>
+        <v>7.04763793945312</v>
       </c>
       <c r="H1343" t="n">
         <v>15902</v>
@@ -39374,7 +39374,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>6.86545372009277</v>
+        <v>6.86545419692993</v>
       </c>
       <c r="H1345" t="n">
         <v>35603</v>
@@ -39403,7 +39403,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.86545372009277</v>
+        <v>6.86545419692993</v>
       </c>
       <c r="H1346" t="n">
         <v>24013</v>
@@ -39490,7 +39490,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1349" t="n">
-        <v>7.05722570419312</v>
+        <v>7.05722618103027</v>
       </c>
       <c r="H1349" t="n">
         <v>27980</v>
@@ -39519,7 +39519,7 @@
         <v>7.5</v>
       </c>
       <c r="G1350" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1350" t="n">
         <v>27211</v>
@@ -39606,7 +39606,7 @@
         <v>7.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1353" t="n">
         <v>13043</v>
@@ -39635,7 +39635,7 @@
         <v>7.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1354" t="n">
         <v>10273</v>
@@ -39722,7 +39722,7 @@
         <v>7.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>7.19146728515625</v>
+        <v>7.19146680831909</v>
       </c>
       <c r="H1357" t="n">
         <v>24316</v>
@@ -39780,7 +39780,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1359" t="n">
-        <v>7.27786636352539</v>
+        <v>7.27786684036255</v>
       </c>
       <c r="H1359" t="n">
         <v>10636</v>
@@ -39838,7 +39838,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1361" t="n">
-        <v>7.15255212783813</v>
+        <v>7.15255165100098</v>
       </c>
       <c r="H1361" t="n">
         <v>10435</v>
@@ -39896,7 +39896,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1363" t="n">
-        <v>7.10435390472412</v>
+        <v>7.10435438156128</v>
       </c>
       <c r="H1363" t="n">
         <v>40072</v>
@@ -40012,7 +40012,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1367" t="n">
-        <v>7.43209981918335</v>
+        <v>7.43209934234619</v>
       </c>
       <c r="H1367" t="n">
         <v>31969</v>
@@ -40070,7 +40070,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1369" t="n">
-        <v>7.51885557174683</v>
+        <v>7.51885509490967</v>
       </c>
       <c r="H1369" t="n">
         <v>18641</v>
@@ -40157,7 +40157,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>7.51885557174683</v>
+        <v>7.51885509490967</v>
       </c>
       <c r="H1372" t="n">
         <v>18289</v>
@@ -40273,7 +40273,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1376" t="n">
-        <v>7.96227550506592</v>
+        <v>7.9622745513916</v>
       </c>
       <c r="H1376" t="n">
         <v>29775</v>
@@ -40302,7 +40302,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1377" t="n">
-        <v>8.01047420501709</v>
+        <v>8.01047325134277</v>
       </c>
       <c r="H1377" t="n">
         <v>81575</v>
@@ -40331,7 +40331,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1378" t="n">
-        <v>7.9333553314209</v>
+        <v>7.93335628509521</v>
       </c>
       <c r="H1378" t="n">
         <v>30136</v>
@@ -40360,7 +40360,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1379" t="n">
-        <v>8.02011203765869</v>
+        <v>8.02011108398438</v>
       </c>
       <c r="H1379" t="n">
         <v>29104</v>
@@ -40447,7 +40447,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1382" t="n">
-        <v>8.058669090271</v>
+        <v>8.05867004394531</v>
       </c>
       <c r="H1382" t="n">
         <v>14418</v>
@@ -40505,7 +40505,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1384" t="n">
-        <v>7.9333553314209</v>
+        <v>7.93335628509521</v>
       </c>
       <c r="H1384" t="n">
         <v>19918</v>
@@ -40621,7 +40621,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>7.52849435806274</v>
+        <v>7.5284948348999</v>
       </c>
       <c r="H1388" t="n">
         <v>27983</v>
@@ -40650,7 +40650,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1389" t="n">
-        <v>7.51885557174683</v>
+        <v>7.51885509490967</v>
       </c>
       <c r="H1389" t="n">
         <v>31337</v>
@@ -40708,7 +40708,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1391" t="n">
-        <v>7.51885557174683</v>
+        <v>7.51885509490967</v>
       </c>
       <c r="H1391" t="n">
         <v>15382</v>
@@ -40766,7 +40766,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1393" t="n">
-        <v>7.52849435806274</v>
+        <v>7.5284948348999</v>
       </c>
       <c r="H1393" t="n">
         <v>11245</v>
@@ -40882,7 +40882,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>7.51885557174683</v>
+        <v>7.51885509490967</v>
       </c>
       <c r="H1397" t="n">
         <v>8404</v>
@@ -41752,7 +41752,7 @@
         <v>8.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>8.19362545013428</v>
+        <v>8.19362449645996</v>
       </c>
       <c r="H1427" t="n">
         <v>38648</v>
@@ -41868,7 +41868,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1431" t="n">
-        <v>8.36713695526123</v>
+        <v>8.36713600158691</v>
       </c>
       <c r="H1431" t="n">
         <v>46746</v>
@@ -41926,7 +41926,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1433" t="n">
-        <v>8.29001998901367</v>
+        <v>8.29002094268799</v>
       </c>
       <c r="H1433" t="n">
         <v>11492</v>
@@ -41984,7 +41984,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>8.27073955535889</v>
+        <v>8.2707405090332</v>
       </c>
       <c r="H1435" t="n">
         <v>9431</v>
@@ -42013,7 +42013,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1436" t="n">
-        <v>8.36713695526123</v>
+        <v>8.36713600158691</v>
       </c>
       <c r="H1436" t="n">
         <v>23217</v>
@@ -42274,7 +42274,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1445" t="n">
-        <v>8.95514869689941</v>
+        <v>8.9551477432251</v>
       </c>
       <c r="H1445" t="n">
         <v>23167</v>
@@ -42390,7 +42390,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1449" t="n">
-        <v>8.49244976043701</v>
+        <v>8.49245071411133</v>
       </c>
       <c r="H1449" t="n">
         <v>23199</v>
@@ -42477,7 +42477,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.29001998901367</v>
+        <v>8.29002094268799</v>
       </c>
       <c r="H1452" t="n">
         <v>10486</v>
@@ -42535,7 +42535,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1454" t="n">
-        <v>8.16470623016357</v>
+        <v>8.16470527648926</v>
       </c>
       <c r="H1454" t="n">
         <v>29037</v>
@@ -42651,7 +42651,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>8.38641548156738</v>
+        <v>8.38641452789307</v>
       </c>
       <c r="H1458" t="n">
         <v>14045</v>
@@ -42738,7 +42738,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.37677669525146</v>
+        <v>8.37677574157715</v>
       </c>
       <c r="H1461" t="n">
         <v>14312</v>
@@ -42825,7 +42825,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.07794952392578</v>
+        <v>8.0779504776001</v>
       </c>
       <c r="H1464" t="n">
         <v>41953</v>
@@ -42854,7 +42854,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.15506649017334</v>
+        <v>8.15506553649902</v>
       </c>
       <c r="H1465" t="n">
         <v>8279</v>
@@ -42912,7 +42912,7 @@
         <v>8.5</v>
       </c>
       <c r="G1467" t="n">
-        <v>8.19362545013428</v>
+        <v>8.19362449645996</v>
       </c>
       <c r="H1467" t="n">
         <v>5823</v>
@@ -42941,7 +42941,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1468" t="n">
-        <v>8.06830978393555</v>
+        <v>8.06831073760986</v>
       </c>
       <c r="H1468" t="n">
         <v>14720</v>
@@ -42970,7 +42970,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1469" t="n">
-        <v>8.12614631652832</v>
+        <v>8.12614727020264</v>
       </c>
       <c r="H1469" t="n">
         <v>6446</v>
@@ -42999,7 +42999,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.17434501647949</v>
+        <v>8.17434406280518</v>
       </c>
       <c r="H1470" t="n">
         <v>8266</v>
@@ -43086,7 +43086,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.14542579650879</v>
+        <v>8.14542675018311</v>
       </c>
       <c r="H1473" t="n">
         <v>8033</v>
@@ -43144,7 +43144,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1475" t="n">
-        <v>8.29001998901367</v>
+        <v>8.29002094268799</v>
       </c>
       <c r="H1475" t="n">
         <v>9087</v>
@@ -43260,7 +43260,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.34785652160645</v>
+        <v>8.34785747528076</v>
       </c>
       <c r="H1479" t="n">
         <v>9600</v>
@@ -43289,7 +43289,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1480" t="n">
-        <v>8.42497253417969</v>
+        <v>8.424973487854</v>
       </c>
       <c r="H1480" t="n">
         <v>16185</v>
@@ -43405,7 +43405,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>8.75271892547607</v>
+        <v>8.75271797180176</v>
       </c>
       <c r="H1484" t="n">
         <v>22829</v>
@@ -43463,7 +43463,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.76235866546631</v>
+        <v>8.76235771179199</v>
       </c>
       <c r="H1486" t="n">
         <v>64156</v>
@@ -43666,7 +43666,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1493" t="n">
-        <v>10.2564897537231</v>
+        <v>10.2564907073975</v>
       </c>
       <c r="H1493" t="n">
         <v>79668</v>
@@ -43898,7 +43898,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>8.99370670318604</v>
+        <v>8.99370765686035</v>
       </c>
       <c r="H1501" t="n">
         <v>25088</v>
@@ -43956,7 +43956,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1503" t="n">
-        <v>8.77199840545654</v>
+        <v>8.77199745178223</v>
       </c>
       <c r="H1503" t="n">
         <v>44127</v>
@@ -44333,7 +44333,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.84911346435547</v>
+        <v>8.84911441802979</v>
       </c>
       <c r="H1516" t="n">
         <v>6090</v>
@@ -44623,7 +44623,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1526" t="n">
-        <v>9.77451324462891</v>
+        <v>9.77451229095459</v>
       </c>
       <c r="H1526" t="n">
         <v>40122</v>
@@ -44710,7 +44710,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1529" t="n">
-        <v>9.52388381958008</v>
+        <v>9.52388477325439</v>
       </c>
       <c r="H1529" t="n">
         <v>13832</v>
@@ -45087,7 +45087,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1542" t="n">
-        <v>8.49244976043701</v>
+        <v>8.49245071411133</v>
       </c>
       <c r="H1542" t="n">
         <v>30397</v>
@@ -45174,7 +45174,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1545" t="n">
-        <v>8.41533279418945</v>
+        <v>8.41533374786377</v>
       </c>
       <c r="H1545" t="n">
         <v>39507</v>
@@ -45319,7 +45319,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1550" t="n">
-        <v>8.49244976043701</v>
+        <v>8.49245071411133</v>
       </c>
       <c r="H1550" t="n">
         <v>8206</v>
@@ -45377,7 +45377,7 @@
         <v>8.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>8.19362545013428</v>
+        <v>8.19362449645996</v>
       </c>
       <c r="H1552" t="n">
         <v>6027</v>
@@ -45406,7 +45406,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1553" t="n">
-        <v>8.15506649017334</v>
+        <v>8.15506553649902</v>
       </c>
       <c r="H1553" t="n">
         <v>30801</v>
@@ -45522,7 +45522,7 @@
         <v>8.5</v>
       </c>
       <c r="G1557" t="n">
-        <v>8.19362545013428</v>
+        <v>8.19362449645996</v>
       </c>
       <c r="H1557" t="n">
         <v>36955</v>
@@ -45580,7 +45580,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>8.63704299926758</v>
+        <v>8.63704395294189</v>
       </c>
       <c r="H1559" t="n">
         <v>30021</v>
@@ -45696,7 +45696,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1563" t="n">
-        <v>8.38641548156738</v>
+        <v>8.38641452789307</v>
       </c>
       <c r="H1563" t="n">
         <v>29594</v>
@@ -45725,7 +45725,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1564" t="n">
-        <v>8.36713695526123</v>
+        <v>8.36713600158691</v>
       </c>
       <c r="H1564" t="n">
         <v>10713</v>
@@ -45754,7 +45754,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1565" t="n">
-        <v>7.96227550506592</v>
+        <v>7.9622745513916</v>
       </c>
       <c r="H1565" t="n">
         <v>65993</v>
@@ -45783,7 +45783,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1566" t="n">
-        <v>8.39605522155762</v>
+        <v>8.3960542678833</v>
       </c>
       <c r="H1566" t="n">
         <v>16663</v>
@@ -45841,7 +45841,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1568" t="n">
-        <v>8.29001998901367</v>
+        <v>8.29002094268799</v>
       </c>
       <c r="H1568" t="n">
         <v>25803</v>
@@ -45928,7 +45928,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.97191572189331</v>
+        <v>7.97191476821899</v>
       </c>
       <c r="H1571" t="n">
         <v>36480</v>
@@ -45957,7 +45957,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1572" t="n">
-        <v>8.06830978393555</v>
+        <v>8.06831073760986</v>
       </c>
       <c r="H1572" t="n">
         <v>33251</v>
@@ -46073,7 +46073,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1576" t="n">
-        <v>8.84911346435547</v>
+        <v>8.84911441802979</v>
       </c>
       <c r="H1576" t="n">
         <v>90671</v>
@@ -46102,7 +46102,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1577" t="n">
-        <v>8.9455099105835</v>
+        <v>8.94550895690918</v>
       </c>
       <c r="H1577" t="n">
         <v>46902</v>
@@ -46247,7 +46247,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1582" t="n">
-        <v>9.71667385101318</v>
+        <v>9.7166748046875</v>
       </c>
       <c r="H1582" t="n">
         <v>61231</v>
@@ -46392,7 +46392,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.89018726348877</v>
+        <v>9.89018821716309</v>
       </c>
       <c r="H1587" t="n">
         <v>28277</v>
@@ -46421,7 +46421,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1588" t="n">
-        <v>9.89018726348877</v>
+        <v>9.89018821716309</v>
       </c>
       <c r="H1588" t="n">
         <v>37635</v>
@@ -47204,7 +47204,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1615" t="n">
-        <v>8.75271892547607</v>
+        <v>8.75271797180176</v>
       </c>
       <c r="H1615" t="n">
         <v>18017</v>
@@ -47233,7 +47233,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1616" t="n">
-        <v>8.77199840545654</v>
+        <v>8.77199745178223</v>
       </c>
       <c r="H1616" t="n">
         <v>12143</v>
@@ -47349,7 +47349,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1620" t="n">
-        <v>9.77451324462891</v>
+        <v>9.77451229095459</v>
       </c>
       <c r="H1620" t="n">
         <v>23628</v>
@@ -47378,7 +47378,7 @@
         <v>10</v>
       </c>
       <c r="G1621" t="n">
-        <v>9.63955879211426</v>
+        <v>9.63955783843994</v>
       </c>
       <c r="H1621" t="n">
         <v>8142</v>
@@ -47436,7 +47436,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1623" t="n">
-        <v>9.90946483612061</v>
+        <v>9.90946578979492</v>
       </c>
       <c r="H1623" t="n">
         <v>31962</v>
@@ -47465,7 +47465,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1624" t="n">
-        <v>10.0636987686157</v>
+        <v>10.0636978149414</v>
       </c>
       <c r="H1624" t="n">
         <v>31476</v>
@@ -47494,7 +47494,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1625" t="n">
-        <v>9.98658275604248</v>
+        <v>9.98658180236816</v>
       </c>
       <c r="H1625" t="n">
         <v>7822</v>
@@ -47523,7 +47523,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1626" t="n">
-        <v>10.0829772949219</v>
+        <v>10.0829782485962</v>
       </c>
       <c r="H1626" t="n">
         <v>32868</v>
@@ -47639,7 +47639,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1630" t="n">
-        <v>9.90946483612061</v>
+        <v>9.90946578979492</v>
       </c>
       <c r="H1630" t="n">
         <v>8929</v>
@@ -47697,7 +47697,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1632" t="n">
-        <v>10.0636987686157</v>
+        <v>10.0636978149414</v>
       </c>
       <c r="H1632" t="n">
         <v>37505</v>
@@ -47784,7 +47784,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1635" t="n">
-        <v>9.89018726348877</v>
+        <v>9.89018821716309</v>
       </c>
       <c r="H1635" t="n">
         <v>13661</v>
@@ -47813,7 +47813,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1636" t="n">
-        <v>9.90946483612061</v>
+        <v>9.90946578979492</v>
       </c>
       <c r="H1636" t="n">
         <v>12798</v>
@@ -47900,7 +47900,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1639" t="n">
-        <v>9.71667385101318</v>
+        <v>9.7166748046875</v>
       </c>
       <c r="H1639" t="n">
         <v>17704</v>
@@ -48335,7 +48335,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1654" t="n">
-        <v>10.0829772949219</v>
+        <v>10.0829782485962</v>
       </c>
       <c r="H1654" t="n">
         <v>33325</v>
@@ -48422,7 +48422,7 @@
         <v>11.5</v>
       </c>
       <c r="G1657" t="n">
-        <v>11.0854911804199</v>
+        <v>11.0854921340942</v>
       </c>
       <c r="H1657" t="n">
         <v>109178</v>
@@ -48683,7 +48683,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1666" t="n">
-        <v>11.3361206054688</v>
+        <v>11.3361196517944</v>
       </c>
       <c r="H1666" t="n">
         <v>29632</v>
@@ -48741,7 +48741,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1668" t="n">
-        <v>11.0276536941528</v>
+        <v>11.0276546478271</v>
       </c>
       <c r="H1668" t="n">
         <v>19492</v>
@@ -48770,7 +48770,7 @@
         <v>11.5</v>
       </c>
       <c r="G1669" t="n">
-        <v>11.0854911804199</v>
+        <v>11.0854921340942</v>
       </c>
       <c r="H1669" t="n">
         <v>16263</v>
@@ -48799,7 +48799,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1670" t="n">
-        <v>11.1818876266479</v>
+        <v>11.1818885803223</v>
       </c>
       <c r="H1670" t="n">
         <v>14430</v>
@@ -48828,7 +48828,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1671" t="n">
-        <v>11.1818876266479</v>
+        <v>11.1818885803223</v>
       </c>
       <c r="H1671" t="n">
         <v>35070</v>
@@ -48857,7 +48857,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1672" t="n">
-        <v>11.1818876266479</v>
+        <v>11.1818885803223</v>
       </c>
       <c r="H1672" t="n">
         <v>11816</v>
@@ -48886,7 +48886,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1673" t="n">
-        <v>11.50963306427</v>
+        <v>11.5096321105957</v>
       </c>
       <c r="H1673" t="n">
         <v>12840</v>
@@ -48915,7 +48915,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1674" t="n">
-        <v>11.3746776580811</v>
+        <v>11.3746786117554</v>
       </c>
       <c r="H1674" t="n">
         <v>20281</v>
@@ -49002,7 +49002,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>11.3746776580811</v>
+        <v>11.3746786117554</v>
       </c>
       <c r="H1677" t="n">
         <v>36916</v>
@@ -49031,7 +49031,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>11.9530506134033</v>
+        <v>11.9530515670776</v>
       </c>
       <c r="H1678" t="n">
         <v>74667</v>
@@ -49089,7 +49089,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1680" t="n">
-        <v>12.454309463501</v>
+        <v>12.4543085098267</v>
       </c>
       <c r="H1680" t="n">
         <v>48736</v>
@@ -49292,7 +49292,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1687" t="n">
-        <v>11.9530506134033</v>
+        <v>11.9530515670776</v>
       </c>
       <c r="H1687" t="n">
         <v>17875</v>
@@ -49408,7 +49408,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1691" t="n">
-        <v>11.1240501403809</v>
+        <v>11.1240491867065</v>
       </c>
       <c r="H1691" t="n">
         <v>15429</v>
@@ -49437,7 +49437,7 @@
         <v>11.5</v>
       </c>
       <c r="G1692" t="n">
-        <v>11.0854911804199</v>
+        <v>11.0854921340942</v>
       </c>
       <c r="H1692" t="n">
         <v>14980</v>
@@ -49553,7 +49553,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1696" t="n">
-        <v>10.873420715332</v>
+        <v>10.8734216690063</v>
       </c>
       <c r="H1696" t="n">
         <v>20758</v>
@@ -49611,7 +49611,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1698" t="n">
-        <v>10.911979675293</v>
+        <v>10.9119787216187</v>
       </c>
       <c r="H1698" t="n">
         <v>8554</v>
@@ -49698,7 +49698,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1701" t="n">
-        <v>10.777027130127</v>
+        <v>10.7770261764526</v>
       </c>
       <c r="H1701" t="n">
         <v>13887</v>
@@ -50075,7 +50075,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.1022567749023</v>
+        <v>10.1022577285767</v>
       </c>
       <c r="H1714" t="n">
         <v>17549</v>
@@ -50133,7 +50133,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1716" t="n">
-        <v>10.5071172714233</v>
+        <v>10.5071182250977</v>
       </c>
       <c r="H1716" t="n">
         <v>12897</v>
@@ -50220,7 +50220,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1719" t="n">
-        <v>10.777027130127</v>
+        <v>10.7770261764526</v>
       </c>
       <c r="H1719" t="n">
         <v>15595</v>
@@ -50249,7 +50249,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1720" t="n">
-        <v>10.873420715332</v>
+        <v>10.8734216690063</v>
       </c>
       <c r="H1720" t="n">
         <v>10167</v>
@@ -50423,7 +50423,7 @@
         <v>11.5</v>
       </c>
       <c r="G1726" t="n">
-        <v>11.0854911804199</v>
+        <v>11.0854921340942</v>
       </c>
       <c r="H1726" t="n">
         <v>6357</v>
@@ -50452,7 +50452,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1727" t="n">
-        <v>10.8155841827393</v>
+        <v>10.8155851364136</v>
       </c>
       <c r="H1727" t="n">
         <v>19045</v>
@@ -50481,7 +50481,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1728" t="n">
-        <v>10.873420715332</v>
+        <v>10.8734216690063</v>
       </c>
       <c r="H1728" t="n">
         <v>14440</v>
@@ -50510,7 +50510,7 @@
         <v>11.5</v>
       </c>
       <c r="G1729" t="n">
-        <v>11.0854911804199</v>
+        <v>11.0854921340942</v>
       </c>
       <c r="H1729" t="n">
         <v>8065</v>
@@ -50829,7 +50829,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1740" t="n">
-        <v>11.7409811019897</v>
+        <v>11.7409820556641</v>
       </c>
       <c r="H1740" t="n">
         <v>4187</v>
@@ -50945,7 +50945,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1744" t="n">
-        <v>11.9530506134033</v>
+        <v>11.9530515670776</v>
       </c>
       <c r="H1744" t="n">
         <v>11941</v>
@@ -51148,7 +51148,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.4735879898071</v>
+        <v>12.4735889434814</v>
       </c>
       <c r="H1751" t="n">
         <v>27824</v>
@@ -51264,7 +51264,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.7434968948364</v>
+        <v>12.7434959411621</v>
       </c>
       <c r="H1755" t="n">
         <v>46418</v>
@@ -51989,7 +51989,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1780" t="n">
-        <v>11.9530506134033</v>
+        <v>11.9530515670776</v>
       </c>
       <c r="H1780" t="n">
         <v>12476</v>
@@ -52163,7 +52163,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1786" t="n">
-        <v>12.4735879898071</v>
+        <v>12.4735889434814</v>
       </c>
       <c r="H1786" t="n">
         <v>9157</v>
@@ -52221,7 +52221,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1788" t="n">
-        <v>12.4735879898071</v>
+        <v>12.4735889434814</v>
       </c>
       <c r="H1788" t="n">
         <v>11933</v>
@@ -52279,7 +52279,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1790" t="n">
-        <v>12.7434968948364</v>
+        <v>12.7434959411621</v>
       </c>
       <c r="H1790" t="n">
         <v>33138</v>
@@ -52308,7 +52308,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1791" t="n">
-        <v>13.0519618988037</v>
+        <v>13.051962852478</v>
       </c>
       <c r="H1791" t="n">
         <v>20683</v>
@@ -52337,7 +52337,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1792" t="n">
-        <v>12.8398914337158</v>
+        <v>12.8398923873901</v>
       </c>
       <c r="H1792" t="n">
         <v>28949</v>
@@ -52366,7 +52366,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1793" t="n">
-        <v>12.7434968948364</v>
+        <v>12.7434959411621</v>
       </c>
       <c r="H1793" t="n">
         <v>9353</v>
@@ -52511,7 +52511,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1798" t="n">
-        <v>12.95556640625</v>
+        <v>12.9555654525757</v>
       </c>
       <c r="H1798" t="n">
         <v>5736</v>
@@ -52540,7 +52540,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1799" t="n">
-        <v>13.3218688964844</v>
+        <v>13.3218679428101</v>
       </c>
       <c r="H1799" t="n">
         <v>49541</v>
@@ -52656,7 +52656,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1803" t="n">
-        <v>13.5339393615723</v>
+        <v>13.5339384078979</v>
       </c>
       <c r="H1803" t="n">
         <v>13149</v>
@@ -52714,7 +52714,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1805" t="n">
-        <v>13.8424043655396</v>
+        <v>13.8424053192139</v>
       </c>
       <c r="H1805" t="n">
         <v>24994</v>
@@ -52830,7 +52830,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1809" t="n">
-        <v>15.0377111434937</v>
+        <v>15.0377101898193</v>
       </c>
       <c r="H1809" t="n">
         <v>47453</v>
@@ -52888,7 +52888,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1811" t="n">
-        <v>15.0377111434937</v>
+        <v>15.0377101898193</v>
       </c>
       <c r="H1811" t="n">
         <v>29003</v>
@@ -52975,7 +52975,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1814" t="n">
-        <v>16.7342739105225</v>
+        <v>16.7342720031738</v>
       </c>
       <c r="H1814" t="n">
         <v>98512</v>
@@ -53004,7 +53004,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1815" t="n">
-        <v>16.8306655883789</v>
+        <v>16.8306674957275</v>
       </c>
       <c r="H1815" t="n">
         <v>36888</v>
@@ -53845,7 +53845,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1844" t="n">
-        <v>19.568302154541</v>
+        <v>19.5683002471924</v>
       </c>
       <c r="H1844" t="n">
         <v>19272</v>
@@ -80067,6 +80067,35 @@
         <v>10731</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>46.0499992370605</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>47.0499992370605</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>47.0499992370605</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>18449</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>
